--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -39,19 +39,361 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0DEBA"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF259C40"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,13 +405,853 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,25 +1263,397 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEFF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,7 +1665,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,7 +1827,763 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,49 +2595,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,7 +2643,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,6 +2661,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -213,175 +2691,325 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDB3444"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -393,7 +3021,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -405,1207 +3069,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
+        <fgColor rgb="FFD83342"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1617,1471 +3081,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEEF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8537,40 +8537,40 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>4.95</v>
       </c>
       <c r="J2" s="8">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="9">
         <v>1.74</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="7">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="2">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="3">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="4">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="10">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="12">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="1">
         <v>-4.59</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="5">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="9">
+      <c r="T2" s="6">
         <v>-15.96</v>
       </c>
     </row>
@@ -8599,40 +8599,40 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="17">
         <v>-1.24</v>
       </c>
       <c r="J3" s="24">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="14">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="13">
         <v>0.1</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="15">
         <v>3.32</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="16">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="18">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="19">
         <v>2.59</v>
       </c>
       <c r="Q3" s="20">
         <v>2.8</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="21">
         <v>1.66</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="22">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="23">
         <v>20.62</v>
       </c>
     </row>
@@ -8661,40 +8661,40 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="34">
         <v>4.19</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="31">
         <v>5.08</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="26">
         <v>15.59</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="30">
         <v>27.15</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="27">
         <v>36.04</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="28">
         <v>41.33</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="32">
         <v>37.54</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="35">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="36">
         <v>32.33</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="33">
         <v>45.56</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="25">
         <v>56.03</v>
       </c>
-      <c r="T4" s="25">
+      <c r="T4" s="29">
         <v>27.06</v>
       </c>
     </row>
@@ -8723,40 +8723,40 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="37">
         <v>11.97</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="46">
         <v>17.45</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="39">
         <v>14.27</v>
       </c>
-      <c r="L5" s="37">
+      <c r="L5" s="40">
         <v>17.32</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="41">
         <v>25.33</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="42">
         <v>21.54</v>
       </c>
       <c r="O5" s="47">
         <v>22.72</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="43">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="39">
+      <c r="Q5" s="48">
         <v>17.54</v>
       </c>
-      <c r="R5" s="38">
+      <c r="R5" s="44">
         <v>16.88</v>
       </c>
       <c r="S5" s="45">
         <v>11.79</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="38">
         <v>16.67</v>
       </c>
     </row>
@@ -8785,40 +8785,40 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="54">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="51">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="55">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="60">
         <v>-0.66</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="56">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="49">
+      <c r="N6" s="57">
         <v>-0.79</v>
       </c>
       <c r="O6" s="52">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="50">
+      <c r="P6" s="58">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="49">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="51">
+      <c r="R6" s="53">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="59">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="59">
+      <c r="T6" s="50">
         <v>-18.59</v>
       </c>
     </row>
@@ -8847,40 +8847,40 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="66">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="62">
         <v>1.8</v>
       </c>
-      <c r="K7" s="65">
+      <c r="K7" s="68">
         <v>0.07</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="63">
         <v>0.63</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="71">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="64">
         <v>1.55</v>
       </c>
-      <c r="O7" s="61">
+      <c r="O7" s="72">
         <v>0.85</v>
       </c>
-      <c r="P7" s="62">
+      <c r="P7" s="65">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="69">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="63">
+      <c r="R7" s="61">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="70">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="66">
+      <c r="T7" s="67">
         <v>4.01</v>
       </c>
     </row>
@@ -8909,40 +8909,40 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="78">
+      <c r="I8" s="79">
         <v>3.13</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="83">
         <v>5.21</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="75">
         <v>0.43</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="76">
         <v>3.68</v>
       </c>
-      <c r="M8" s="73">
+      <c r="M8" s="84">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="74">
+      <c r="N8" s="80">
         <v>1.66</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="73">
         <v>1.72</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="77">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="75">
+      <c r="Q8" s="78">
         <v>15.33</v>
       </c>
-      <c r="R8" s="76">
+      <c r="R8" s="81">
         <v>12.57</v>
       </c>
-      <c r="S8" s="77">
+      <c r="S8" s="82">
         <v>23.85</v>
       </c>
-      <c r="T8" s="83">
+      <c r="T8" s="74">
         <v>-13.37</v>
       </c>
     </row>
@@ -8971,40 +8971,40 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="93">
         <v>1.35</v>
       </c>
-      <c r="J9" s="90">
+      <c r="J9" s="85">
         <v>2.48</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="86">
         <v>1.58</v>
       </c>
-      <c r="L9" s="91">
+      <c r="L9" s="94">
         <v>1.35</v>
       </c>
-      <c r="M9" s="86">
+      <c r="M9" s="95">
         <v>2.93</v>
       </c>
-      <c r="N9" s="87">
+      <c r="N9" s="90">
         <v>0.23</v>
       </c>
-      <c r="O9" s="88">
+      <c r="O9" s="87">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="96">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="88">
         <v>3.83</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="91">
         <v>7.43</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="89">
         <v>17.12</v>
       </c>
-      <c r="T9" s="85">
+      <c r="T9" s="92">
         <v>3.15</v>
       </c>
     </row>
@@ -9033,16 +9033,16 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="99">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="97">
+      <c r="J10" s="108">
         <v>-6.79</v>
       </c>
       <c r="K10" s="102">
         <v>-7.86</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="100">
         <v>-9.72</v>
       </c>
       <c r="M10" s="106">
@@ -9051,22 +9051,22 @@
       <c r="N10" s="103">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="98">
+      <c r="O10" s="104">
         <v>-9.15</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="101">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="99">
+      <c r="Q10" s="107">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="100">
+      <c r="R10" s="105">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="101">
+      <c r="S10" s="97">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="104">
+      <c r="T10" s="98">
         <v>-10.94</v>
       </c>
     </row>
@@ -9095,40 +9095,40 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="109">
+      <c r="I11" s="118">
         <v>7.32</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="109">
         <v>7.76</v>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="110">
         <v>15.37</v>
       </c>
-      <c r="L11" s="110">
+      <c r="L11" s="114">
         <v>8.64</v>
       </c>
-      <c r="M11" s="116">
+      <c r="M11" s="115">
         <v>0.59</v>
       </c>
-      <c r="N11" s="113">
+      <c r="N11" s="111">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="114">
+      <c r="O11" s="119">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="115">
+      <c r="P11" s="120">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="111">
+      <c r="Q11" s="112">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="112">
+      <c r="R11" s="113">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="117">
+      <c r="S11" s="116">
         <v>0.15</v>
       </c>
-      <c r="T11" s="118">
+      <c r="T11" s="117">
         <v>-21.08</v>
       </c>
     </row>
@@ -9157,40 +9157,40 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="121">
+      <c r="I12" s="122">
         <v>10.48</v>
       </c>
-      <c r="J12" s="125">
+      <c r="J12" s="126">
         <v>13.87</v>
       </c>
-      <c r="K12" s="126">
+      <c r="K12" s="127">
         <v>4.11</v>
       </c>
-      <c r="L12" s="129">
+      <c r="L12" s="123">
         <v>6.13</v>
       </c>
       <c r="M12" s="130">
         <v>9.68</v>
       </c>
-      <c r="N12" s="122">
+      <c r="N12" s="124">
         <v>2.66</v>
       </c>
-      <c r="O12" s="127">
+      <c r="O12" s="131">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="123">
+      <c r="P12" s="132">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="128">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="124">
+      <c r="R12" s="125">
         <v>0.97</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="121">
         <v>3.06</v>
       </c>
-      <c r="T12" s="128">
+      <c r="T12" s="129">
         <v>-21.53</v>
       </c>
     </row>
@@ -9219,40 +9219,40 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="133">
+      <c r="I13" s="143">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="138">
+      <c r="J13" s="144">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="141">
+      <c r="K13" s="137">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="139">
+      <c r="L13" s="133">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="142">
+      <c r="M13" s="139">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="135">
+      <c r="N13" s="134">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="134">
+      <c r="O13" s="135">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="136">
+      <c r="P13" s="138">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="143">
+      <c r="Q13" s="140">
         <v>-4.93</v>
       </c>
-      <c r="R13" s="137">
+      <c r="R13" s="141">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="142">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="140">
+      <c r="T13" s="136">
         <v>-20.66</v>
       </c>
     </row>
@@ -9281,40 +9281,40 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="155">
+      <c r="I14" s="146">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="146">
+      <c r="J14" s="149">
         <v>-5</v>
       </c>
-      <c r="K14" s="150">
+      <c r="K14" s="155">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="147">
+      <c r="L14" s="156">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="156">
+      <c r="M14" s="150">
         <v>-7.37</v>
       </c>
-      <c r="N14" s="151">
+      <c r="N14" s="145">
         <v>-9.88</v>
       </c>
       <c r="O14" s="152">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="145">
+      <c r="P14" s="147">
         <v>-5.63</v>
       </c>
-      <c r="Q14" s="154">
+      <c r="Q14" s="151">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="148">
+      <c r="R14" s="153">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="153">
+      <c r="S14" s="154">
         <v>0</v>
       </c>
-      <c r="T14" s="149">
+      <c r="T14" s="148">
         <v>-8.25</v>
       </c>
     </row>
@@ -9343,40 +9343,40 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="163">
+      <c r="I15" s="164">
         <v>9.9</v>
       </c>
-      <c r="J15" s="167">
+      <c r="J15" s="165">
         <v>9.43</v>
       </c>
-      <c r="K15" s="164">
+      <c r="K15" s="166">
         <v>8.82</v>
       </c>
-      <c r="L15" s="168">
+      <c r="L15" s="167">
         <v>4.15</v>
       </c>
-      <c r="M15" s="159">
+      <c r="M15" s="160">
         <v>7.79</v>
       </c>
-      <c r="N15" s="157">
+      <c r="N15" s="168">
         <v>1.3</v>
       </c>
-      <c r="O15" s="158">
+      <c r="O15" s="162">
         <v>8.69</v>
       </c>
-      <c r="P15" s="161">
+      <c r="P15" s="163">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="165">
+      <c r="Q15" s="157">
         <v>5.84</v>
       </c>
-      <c r="R15" s="162">
+      <c r="R15" s="158">
         <v>6.88</v>
       </c>
-      <c r="S15" s="160">
+      <c r="S15" s="161">
         <v>2.34</v>
       </c>
-      <c r="T15" s="166">
+      <c r="T15" s="159">
         <v>-7.35</v>
       </c>
     </row>
@@ -9405,22 +9405,22 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="174">
+      <c r="I16" s="179">
         <v>2.67</v>
       </c>
-      <c r="J16" s="175">
+      <c r="J16" s="171">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="179">
+      <c r="K16" s="180">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="180">
+      <c r="L16" s="172">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="170">
+      <c r="M16" s="173">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="169">
+      <c r="N16" s="175">
         <v>-5.82</v>
       </c>
       <c r="O16" s="176">
@@ -9429,16 +9429,16 @@
       <c r="P16" s="177">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="178">
+      <c r="Q16" s="169">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="171">
+      <c r="R16" s="178">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="172">
+      <c r="S16" s="174">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="173">
+      <c r="T16" s="170">
         <v>-21.15</v>
       </c>
     </row>
@@ -9467,37 +9467,37 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="192">
+      <c r="I17" s="181">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="190">
+      <c r="J17" s="186">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="186">
+      <c r="K17" s="187">
         <v>0.2</v>
       </c>
-      <c r="L17" s="187">
+      <c r="L17" s="182">
         <v>-0.8</v>
       </c>
       <c r="M17" s="188">
         <v>0.53</v>
       </c>
-      <c r="N17" s="181">
+      <c r="N17" s="183">
         <v>3.31</v>
       </c>
       <c r="O17" s="191">
         <v>6.89</v>
       </c>
-      <c r="P17" s="183">
+      <c r="P17" s="184">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="189">
+      <c r="Q17" s="192">
         <v>4.09</v>
       </c>
-      <c r="R17" s="184">
+      <c r="R17" s="189">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="182">
+      <c r="S17" s="190">
         <v>-1.45</v>
       </c>
       <c r="T17" s="185">
@@ -9529,40 +9529,40 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="195">
+      <c r="I18" s="200">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="196">
+      <c r="J18" s="204">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="197">
+      <c r="K18" s="195">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="200">
+      <c r="L18" s="201">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="198">
+      <c r="M18" s="197">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="201">
+      <c r="N18" s="198">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="203">
+      <c r="O18" s="196">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="202">
+      <c r="P18" s="193">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="193">
+      <c r="Q18" s="194">
         <v>-20.52</v>
       </c>
-      <c r="R18" s="204">
+      <c r="R18" s="202">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="199">
+      <c r="S18" s="203">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="194">
+      <c r="T18" s="199">
         <v>-24.97</v>
       </c>
     </row>
@@ -9591,40 +9591,40 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="212">
+      <c r="I19" s="209">
         <v>1.39</v>
       </c>
-      <c r="J19" s="213">
+      <c r="J19" s="214">
         <v>0.39</v>
       </c>
-      <c r="K19" s="205">
+      <c r="K19" s="210">
         <v>1.93</v>
       </c>
-      <c r="L19" s="206">
+      <c r="L19" s="215">
         <v>3.7</v>
       </c>
-      <c r="M19" s="207">
+      <c r="M19" s="212">
         <v>9.45</v>
       </c>
-      <c r="N19" s="209">
+      <c r="N19" s="216">
         <v>5.75</v>
       </c>
-      <c r="O19" s="214">
+      <c r="O19" s="207">
         <v>12.85</v>
       </c>
-      <c r="P19" s="210">
+      <c r="P19" s="213">
         <v>8.68</v>
       </c>
-      <c r="Q19" s="208">
+      <c r="Q19" s="205">
         <v>14.74</v>
       </c>
-      <c r="R19" s="215">
+      <c r="R19" s="206">
         <v>14.89</v>
       </c>
       <c r="S19" s="211">
         <v>9.1</v>
       </c>
-      <c r="T19" s="216">
+      <c r="T19" s="208">
         <v>3.43</v>
       </c>
     </row>
@@ -9653,40 +9653,40 @@
       <c r="H20">
         <v>-1.89</v>
       </c>
-      <c r="I20" s="221">
+      <c r="I20" s="226">
         <v>1.85</v>
       </c>
-      <c r="J20" s="224">
+      <c r="J20" s="218">
         <v>8.14</v>
       </c>
-      <c r="K20" s="228">
+      <c r="K20" s="219">
         <v>2.43</v>
       </c>
-      <c r="L20" s="217">
+      <c r="L20" s="227">
         <v>1.09</v>
       </c>
-      <c r="M20" s="222">
+      <c r="M20" s="220">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="226">
+      <c r="N20" s="221">
         <v>-0.76</v>
       </c>
-      <c r="O20" s="218">
+      <c r="O20" s="222">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="225">
+      <c r="P20" s="223">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="219">
+      <c r="Q20" s="225">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="223">
+      <c r="R20" s="224">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="227">
+      <c r="S20" s="228">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="220">
+      <c r="T20" s="217">
         <v>-8.14</v>
       </c>
     </row>
@@ -9715,40 +9715,40 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="237">
+      <c r="I21" s="240">
         <v>8.65</v>
       </c>
-      <c r="J21" s="238">
+      <c r="J21" s="237">
         <v>9.13</v>
       </c>
-      <c r="K21" s="229">
+      <c r="K21" s="231">
         <v>12.02</v>
       </c>
-      <c r="L21" s="230">
+      <c r="L21" s="229">
         <v>9.13</v>
       </c>
-      <c r="M21" s="234">
+      <c r="M21" s="232">
         <v>12.86</v>
       </c>
-      <c r="N21" s="231">
+      <c r="N21" s="230">
         <v>8.29</v>
       </c>
-      <c r="O21" s="232">
+      <c r="O21" s="233">
         <v>0.36</v>
       </c>
-      <c r="P21" s="239">
+      <c r="P21" s="238">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="233">
+      <c r="Q21" s="234">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="235">
+      <c r="R21" s="239">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="236">
+      <c r="S21" s="235">
         <v>2.04</v>
       </c>
-      <c r="T21" s="240">
+      <c r="T21" s="236">
         <v>-9.86</v>
       </c>
     </row>
@@ -9777,19 +9777,19 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="250">
+      <c r="I22" s="243">
         <v>9.66</v>
       </c>
       <c r="J22" s="244">
         <v>14</v>
       </c>
-      <c r="K22" s="251">
+      <c r="K22" s="245">
         <v>19.72</v>
       </c>
-      <c r="L22" s="242">
+      <c r="L22" s="246">
         <v>17.55</v>
       </c>
-      <c r="M22" s="243">
+      <c r="M22" s="247">
         <v>15.78</v>
       </c>
       <c r="N22" s="248">
@@ -9798,19 +9798,19 @@
       <c r="O22" s="252">
         <v>0.99</v>
       </c>
-      <c r="P22" s="245">
+      <c r="P22" s="249">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="246">
+      <c r="Q22" s="241">
         <v>8.88</v>
       </c>
-      <c r="R22" s="241">
+      <c r="R22" s="242">
         <v>4.73</v>
       </c>
-      <c r="S22" s="247">
+      <c r="S22" s="250">
         <v>5.92</v>
       </c>
-      <c r="T22" s="249">
+      <c r="T22" s="251">
         <v>-12.23</v>
       </c>
     </row>
@@ -9839,40 +9839,40 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="261">
+      <c r="I23" s="259">
         <v>5.78</v>
       </c>
-      <c r="J23" s="262">
+      <c r="J23" s="260">
         <v>3.91</v>
       </c>
-      <c r="K23" s="259">
+      <c r="K23" s="256">
         <v>6.83</v>
       </c>
-      <c r="L23" s="260">
+      <c r="L23" s="264">
         <v>4.79</v>
       </c>
-      <c r="M23" s="254">
+      <c r="M23" s="257">
         <v>5.08</v>
       </c>
-      <c r="N23" s="263">
+      <c r="N23" s="261">
         <v>4.5</v>
       </c>
-      <c r="O23" s="255">
+      <c r="O23" s="254">
         <v>1.4</v>
       </c>
-      <c r="P23" s="264">
+      <c r="P23" s="262">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="256">
+      <c r="Q23" s="258">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="257">
+      <c r="R23" s="253">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="253">
+      <c r="S23" s="255">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="258">
+      <c r="T23" s="263">
         <v>5.95</v>
       </c>
     </row>
@@ -9901,7 +9901,7 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="265">
+      <c r="I24" s="271">
         <v>-0.93</v>
       </c>
       <c r="J24" s="266">
@@ -9910,31 +9910,31 @@
       <c r="K24" s="267">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="271">
+      <c r="L24" s="274">
         <v>-12.46</v>
       </c>
-      <c r="M24" s="269">
+      <c r="M24" s="272">
         <v>-11.46</v>
       </c>
-      <c r="N24" s="272">
+      <c r="N24" s="268">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="273">
+      <c r="O24" s="269">
         <v>-7.66</v>
       </c>
-      <c r="P24" s="274">
+      <c r="P24" s="270">
         <v>-9.54</v>
       </c>
-      <c r="Q24" s="275">
+      <c r="Q24" s="276">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="268">
+      <c r="R24" s="275">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="276">
+      <c r="S24" s="265">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="270">
+      <c r="T24" s="273">
         <v>-10.65</v>
       </c>
     </row>
@@ -9963,37 +9963,37 @@
       <c r="H25">
         <v>-1.47</v>
       </c>
-      <c r="I25" s="287">
+      <c r="I25" s="286">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="281">
+      <c r="J25" s="277">
         <v>-4.3</v>
       </c>
       <c r="K25" s="282">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="278">
+      <c r="L25" s="287">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="288">
+      <c r="M25" s="278">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="286">
+      <c r="N25" s="279">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="279">
+      <c r="O25" s="283">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="283">
+      <c r="P25" s="280">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="284">
+      <c r="Q25" s="281">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="277">
+      <c r="R25" s="284">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="280">
+      <c r="S25" s="288">
         <v>-12.95</v>
       </c>
       <c r="T25" s="285">
@@ -10025,40 +10025,40 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="293">
+      <c r="I26" s="295">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="295">
+      <c r="J26" s="296">
         <v>0.56</v>
       </c>
-      <c r="K26" s="298">
+      <c r="K26" s="300">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="294">
+      <c r="L26" s="289">
         <v>-7.91</v>
       </c>
-      <c r="M26" s="300">
+      <c r="M26" s="292">
         <v>1.36</v>
       </c>
-      <c r="N26" s="296">
+      <c r="N26" s="293">
         <v>3.39</v>
       </c>
-      <c r="O26" s="289">
+      <c r="O26" s="297">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="290">
+      <c r="P26" s="294">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="299">
+      <c r="Q26" s="290">
         <v>7.01</v>
       </c>
-      <c r="R26" s="297">
+      <c r="R26" s="298">
         <v>12.66</v>
       </c>
-      <c r="S26" s="291">
+      <c r="S26" s="299">
         <v>6.55</v>
       </c>
-      <c r="T26" s="292">
+      <c r="T26" s="291">
         <v>-10.28</v>
       </c>
     </row>
@@ -10087,40 +10087,40 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="309">
+      <c r="I27" s="303">
         <v>-1.23</v>
       </c>
-      <c r="J27" s="304">
+      <c r="J27" s="310">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="302">
+      <c r="K27" s="304">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="305">
+      <c r="L27" s="311">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="310">
+      <c r="M27" s="306">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="311">
+      <c r="N27" s="307">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="312">
+      <c r="O27" s="301">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="306">
+      <c r="P27" s="302">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="301">
+      <c r="Q27" s="305">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="303">
+      <c r="R27" s="308">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="307">
+      <c r="S27" s="309">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="308">
+      <c r="T27" s="312">
         <v>-12.1</v>
       </c>
     </row>
@@ -10149,40 +10149,40 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="313">
+      <c r="I28" s="316">
         <v>1.28</v>
       </c>
-      <c r="J28" s="319">
+      <c r="J28" s="317">
         <v>2.92</v>
       </c>
-      <c r="K28" s="321">
+      <c r="K28" s="318">
         <v>4.72</v>
       </c>
-      <c r="L28" s="316">
+      <c r="L28" s="320">
         <v>6.25</v>
       </c>
-      <c r="M28" s="314">
+      <c r="M28" s="323">
         <v>16.86</v>
       </c>
-      <c r="N28" s="322">
+      <c r="N28" s="321">
         <v>13.12</v>
       </c>
-      <c r="O28" s="315">
+      <c r="O28" s="319">
         <v>24.45</v>
       </c>
-      <c r="P28" s="323">
+      <c r="P28" s="322">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="320">
+      <c r="Q28" s="324">
         <v>46.03</v>
       </c>
-      <c r="R28" s="324">
+      <c r="R28" s="313">
         <v>45.46</v>
       </c>
-      <c r="S28" s="317">
+      <c r="S28" s="314">
         <v>42.9</v>
       </c>
-      <c r="T28" s="318">
+      <c r="T28" s="315">
         <v>23.63</v>
       </c>
     </row>
@@ -10211,37 +10211,37 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="327">
         <v>3.14</v>
       </c>
-      <c r="J29" s="333">
+      <c r="J29" s="335">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="335">
+      <c r="K29" s="329">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="328">
+      <c r="L29" s="330">
         <v>-0.61</v>
       </c>
       <c r="M29" s="336">
         <v>6.71</v>
       </c>
-      <c r="N29" s="325">
+      <c r="N29" s="328">
         <v>3.47</v>
       </c>
-      <c r="O29" s="329">
+      <c r="O29" s="333">
         <v>-0.94</v>
       </c>
-      <c r="P29" s="326">
+      <c r="P29" s="331">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="330">
+      <c r="Q29" s="325">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="327">
+      <c r="R29" s="326">
         <v>0.11</v>
       </c>
-      <c r="S29" s="331">
+      <c r="S29" s="334">
         <v>2.42</v>
       </c>
       <c r="T29" s="332">
@@ -10273,10 +10273,10 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="344">
+      <c r="I30" s="338">
         <v>1.85</v>
       </c>
-      <c r="J30" s="339">
+      <c r="J30" s="344">
         <v>7.78</v>
       </c>
       <c r="K30" s="348">
@@ -10285,28 +10285,28 @@
       <c r="L30" s="345">
         <v>11.93</v>
       </c>
-      <c r="M30" s="337">
+      <c r="M30" s="339">
         <v>5.23</v>
       </c>
-      <c r="N30" s="340">
+      <c r="N30" s="341">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="341">
+      <c r="O30" s="346">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="342">
+      <c r="P30" s="337">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="338">
+      <c r="Q30" s="347">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="343">
+      <c r="R30" s="342">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="346">
+      <c r="S30" s="343">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="347">
+      <c r="T30" s="340">
         <v>-13.9</v>
       </c>
     </row>
@@ -10335,7 +10335,7 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="354">
+      <c r="I31" s="353">
         <v>1.82</v>
       </c>
       <c r="J31" s="358">
@@ -10347,28 +10347,28 @@
       <c r="L31" s="360">
         <v>1.42</v>
       </c>
-      <c r="M31" s="349">
+      <c r="M31" s="350">
         <v>-7.09</v>
       </c>
-      <c r="N31" s="355">
+      <c r="N31" s="351">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="356">
+      <c r="O31" s="354">
         <v>-10.32</v>
       </c>
-      <c r="P31" s="350">
+      <c r="P31" s="355">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="351">
+      <c r="Q31" s="357">
         <v>-17</v>
       </c>
-      <c r="R31" s="352">
+      <c r="R31" s="349">
         <v>-16.8</v>
       </c>
-      <c r="S31" s="357">
+      <c r="S31" s="352">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="353">
+      <c r="T31" s="356">
         <v>-20.65</v>
       </c>
     </row>
@@ -10397,40 +10397,40 @@
       <c r="H32">
         <v>-1.07</v>
       </c>
-      <c r="I32" s="367">
+      <c r="I32" s="362">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="372">
+      <c r="J32" s="371">
         <v>0.27</v>
       </c>
-      <c r="K32" s="368">
+      <c r="K32" s="365">
         <v>2.99</v>
       </c>
-      <c r="L32" s="369">
+      <c r="L32" s="366">
         <v>2.35</v>
       </c>
-      <c r="M32" s="362">
+      <c r="M32" s="363">
         <v>0.72</v>
       </c>
-      <c r="N32" s="363">
+      <c r="N32" s="367">
         <v>1</v>
       </c>
-      <c r="O32" s="370">
+      <c r="O32" s="368">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="364">
+      <c r="P32" s="372">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="371">
+      <c r="Q32" s="361">
         <v>3.26</v>
       </c>
-      <c r="R32" s="361">
+      <c r="R32" s="369">
         <v>1</v>
       </c>
-      <c r="S32" s="365">
+      <c r="S32" s="364">
         <v>1.45</v>
       </c>
-      <c r="T32" s="366">
+      <c r="T32" s="370">
         <v>7.78</v>
       </c>
     </row>
@@ -10459,40 +10459,40 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="381">
+      <c r="I33" s="377">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="378">
+      <c r="J33" s="374">
         <v>0.57</v>
       </c>
-      <c r="K33" s="373">
+      <c r="K33" s="378">
         <v>-8.88</v>
       </c>
       <c r="L33" s="382">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="374">
+      <c r="M33" s="383">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="379">
+      <c r="N33" s="384">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="380">
+      <c r="O33" s="375">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="375">
+      <c r="P33" s="376">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="376">
+      <c r="Q33" s="380">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="383">
+      <c r="R33" s="379">
         <v>-20.6</v>
       </c>
-      <c r="S33" s="384">
+      <c r="S33" s="373">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="377">
+      <c r="T33" s="381">
         <v>-22.68</v>
       </c>
     </row>
@@ -10521,40 +10521,40 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="391">
+      <c r="I34" s="389">
         <v>-3</v>
       </c>
-      <c r="J34" s="388">
+      <c r="J34" s="393">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="389">
+      <c r="K34" s="394">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="396">
+      <c r="L34" s="385">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="385">
+      <c r="M34" s="390">
         <v>-16.82</v>
       </c>
-      <c r="N34" s="392">
+      <c r="N34" s="396">
         <v>-18.2</v>
       </c>
-      <c r="O34" s="393">
+      <c r="O34" s="386">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="386">
+      <c r="P34" s="395">
         <v>-19.82</v>
       </c>
-      <c r="Q34" s="394">
+      <c r="Q34" s="387">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="390">
+      <c r="R34" s="391">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="395">
+      <c r="S34" s="392">
         <v>-21.43</v>
       </c>
-      <c r="T34" s="387">
+      <c r="T34" s="388">
         <v>-22.12</v>
       </c>
     </row>
@@ -10583,40 +10583,40 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="399">
+      <c r="I35" s="400">
         <v>4.2</v>
       </c>
-      <c r="J35" s="400">
+      <c r="J35" s="407">
         <v>3.72</v>
       </c>
       <c r="K35" s="404">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="401">
+      <c r="L35" s="408">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="405">
+      <c r="M35" s="401">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="408">
+      <c r="N35" s="397">
         <v>6.61</v>
       </c>
-      <c r="O35" s="406">
+      <c r="O35" s="405">
         <v>5.5</v>
       </c>
-      <c r="P35" s="402">
+      <c r="P35" s="398">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="407">
+      <c r="Q35" s="406">
         <v>1.68</v>
       </c>
-      <c r="R35" s="403">
+      <c r="R35" s="402">
         <v>1.37</v>
       </c>
-      <c r="S35" s="397">
+      <c r="S35" s="403">
         <v>0.08</v>
       </c>
-      <c r="T35" s="398">
+      <c r="T35" s="399">
         <v>-0.66</v>
       </c>
     </row>
@@ -10645,40 +10645,40 @@
       <c r="H36">
         <v>-3.03</v>
       </c>
-      <c r="I36" s="418">
+      <c r="I36" s="410">
         <v>5.57</v>
       </c>
-      <c r="J36" s="409">
+      <c r="J36" s="414">
         <v>16.17</v>
       </c>
-      <c r="K36" s="410">
+      <c r="K36" s="411">
         <v>22.01</v>
       </c>
-      <c r="L36" s="419">
+      <c r="L36" s="415">
         <v>16.85</v>
       </c>
-      <c r="M36" s="415">
+      <c r="M36" s="416">
         <v>7.07</v>
       </c>
-      <c r="N36" s="411">
+      <c r="N36" s="418">
         <v>0.27</v>
       </c>
-      <c r="O36" s="416">
+      <c r="O36" s="419">
         <v>2.45</v>
       </c>
-      <c r="P36" s="420">
+      <c r="P36" s="417">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="417">
+      <c r="Q36" s="420">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="412">
+      <c r="R36" s="409">
         <v>9.65</v>
       </c>
-      <c r="S36" s="413">
+      <c r="S36" s="412">
         <v>7.47</v>
       </c>
-      <c r="T36" s="414">
+      <c r="T36" s="413">
         <v>3.26</v>
       </c>
     </row>
@@ -10707,40 +10707,40 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="428">
+      <c r="I37" s="423">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="432">
+      <c r="J37" s="428">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="429">
+      <c r="K37" s="431">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="423">
+      <c r="L37" s="425">
         <v>7.57</v>
       </c>
-      <c r="M37" s="425">
+      <c r="M37" s="432">
         <v>5.6</v>
       </c>
-      <c r="N37" s="430">
+      <c r="N37" s="429">
         <v>4.48</v>
       </c>
       <c r="O37" s="426">
         <v>3.32</v>
       </c>
-      <c r="P37" s="431">
+      <c r="P37" s="421">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="424">
+      <c r="Q37" s="427">
         <v>3.78</v>
       </c>
-      <c r="R37" s="421">
+      <c r="R37" s="430">
         <v>8.07</v>
       </c>
       <c r="S37" s="422">
         <v>11.74</v>
       </c>
-      <c r="T37" s="427">
+      <c r="T37" s="424">
         <v>11.74</v>
       </c>
     </row>
@@ -10772,33 +10772,33 @@
       <c r="I38" s="440">
         <v>6.62</v>
       </c>
-      <c r="J38" s="433">
+      <c r="J38" s="441">
         <v>10.07</v>
       </c>
-      <c r="K38" s="434">
+      <c r="K38" s="433">
         <v>6.26</v>
       </c>
       <c r="L38" s="435">
         <v>2.13</v>
       </c>
-      <c r="M38" s="437">
+      <c r="M38" s="438">
         <v>1.41</v>
       </c>
-      <c r="N38" s="441">
+      <c r="N38" s="439">
         <v>7.72</v>
       </c>
-      <c r="O38" s="442">
+      <c r="O38" s="436">
         <v>5.74</v>
       </c>
-      <c r="P38" s="438">
+      <c r="P38" s="434">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="436">
+      <c r="Q38" s="442">
         <v>14.45</v>
       </c>
       <c r="R38" t="str"/>
       <c r="S38" t="str"/>
-      <c r="T38" s="439">
+      <c r="T38" s="437">
         <v>14.45</v>
       </c>
     </row>
@@ -10827,34 +10827,34 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="443">
+      <c r="I39" s="444">
         <v>7.14</v>
       </c>
-      <c r="J39" s="449">
+      <c r="J39" s="446">
         <v>7.82</v>
       </c>
-      <c r="K39" s="445">
+      <c r="K39" s="451">
         <v>7.68</v>
       </c>
-      <c r="L39" s="450">
+      <c r="L39" s="448">
         <v>8.49</v>
       </c>
-      <c r="M39" s="446">
+      <c r="M39" s="443">
         <v>9.43</v>
       </c>
-      <c r="N39" s="444">
+      <c r="N39" s="449">
         <v>5.39</v>
       </c>
-      <c r="O39" s="451">
+      <c r="O39" s="447">
         <v>8.49</v>
       </c>
-      <c r="P39" s="447">
+      <c r="P39" s="445">
         <v>7.28</v>
       </c>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="448">
+      <c r="T39" s="450">
         <v>7.28</v>
       </c>
     </row>
@@ -10883,32 +10883,32 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="453">
+      <c r="I40" s="459">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="454">
+      <c r="J40" s="452">
         <v>-0.66</v>
       </c>
-      <c r="K40" s="455">
+      <c r="K40" s="453">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="456">
+      <c r="L40" s="454">
         <v>0</v>
       </c>
-      <c r="M40" s="457">
+      <c r="M40" s="455">
         <v>-1.31</v>
       </c>
-      <c r="N40" s="458">
+      <c r="N40" s="456">
         <v>0.33</v>
       </c>
-      <c r="O40" s="459">
+      <c r="O40" s="457">
         <v>0</v>
       </c>
       <c r="P40" t="str"/>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="452">
+      <c r="T40" s="458">
         <v>0</v>
       </c>
     </row>
@@ -10937,22 +10937,22 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="462">
+      <c r="I41" s="461">
         <v>0.59</v>
       </c>
-      <c r="J41" s="463">
+      <c r="J41" s="462">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="464">
+      <c r="K41" s="463">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="465">
+      <c r="L41" s="464">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="466">
+      <c r="M41" s="465">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="460">
+      <c r="N41" s="466">
         <v>-7.55</v>
       </c>
       <c r="O41" t="str"/>
@@ -10960,7 +10960,7 @@
       <c r="Q41" t="str"/>
       <c r="R41" t="str"/>
       <c r="S41" t="str"/>
-      <c r="T41" s="461">
+      <c r="T41" s="460">
         <v>-7.55</v>
       </c>
     </row>
@@ -10989,19 +10989,19 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="468">
+      <c r="I42" s="469">
         <v>2.08</v>
       </c>
-      <c r="J42" s="469">
+      <c r="J42" s="470">
         <v>2.7</v>
       </c>
-      <c r="K42" s="470">
+      <c r="K42" s="471">
         <v>0</v>
       </c>
-      <c r="L42" s="471">
+      <c r="L42" s="472">
         <v>1.25</v>
       </c>
-      <c r="M42" s="472">
+      <c r="M42" s="467">
         <v>1.04</v>
       </c>
       <c r="N42" t="str"/>
@@ -11010,7 +11010,7 @@
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="467">
+      <c r="T42" s="468">
         <v>1.04</v>
       </c>
     </row>
@@ -11039,16 +11039,16 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="477">
+      <c r="I43" s="474">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="473">
+      <c r="J43" s="475">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="474">
+      <c r="K43" s="476">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="475">
+      <c r="L43" s="477">
         <v>8.46</v>
       </c>
       <c r="M43" t="str"/>
@@ -11058,7 +11058,7 @@
       <c r="Q43" t="str"/>
       <c r="R43" t="str"/>
       <c r="S43" t="str"/>
-      <c r="T43" s="476">
+      <c r="T43" s="473">
         <v>8.46</v>
       </c>
     </row>
@@ -11133,10 +11133,10 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="483">
+      <c r="I45" s="484">
         <v>2.03</v>
       </c>
-      <c r="J45" s="484">
+      <c r="J45" s="482">
         <v>5.03</v>
       </c>
       <c r="K45" t="str"/>
@@ -11148,7 +11148,7 @@
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="482">
+      <c r="T45" s="483">
         <v>5.03</v>
       </c>
     </row>
@@ -11211,40 +11211,40 @@
       <c r="F47" t="str"/>
       <c r="G47" t="str"/>
       <c r="H47" t="str"/>
-      <c r="I47" s="489">
+      <c r="I47" s="490">
         <v>59.09</v>
       </c>
-      <c r="J47" s="486">
+      <c r="J47" s="494">
         <v>59.09</v>
       </c>
-      <c r="K47" s="491">
+      <c r="K47" s="485">
         <v>51.16</v>
       </c>
-      <c r="L47" s="494">
+      <c r="L47" s="491">
         <v>57.14</v>
       </c>
-      <c r="M47" s="492">
+      <c r="M47" s="486">
         <v>53.66</v>
       </c>
-      <c r="N47" s="495">
+      <c r="N47" s="492">
         <v>55</v>
       </c>
-      <c r="O47" s="490">
+      <c r="O47" s="487">
         <v>41.03</v>
       </c>
-      <c r="P47" s="496">
+      <c r="P47" s="495">
         <v>42.11</v>
       </c>
-      <c r="Q47" s="487">
+      <c r="Q47" s="488">
         <v>40.54</v>
       </c>
-      <c r="R47" s="485">
+      <c r="R47" s="493">
         <v>44.44</v>
       </c>
-      <c r="S47" s="493">
+      <c r="S47" s="496">
         <v>47.22</v>
       </c>
-      <c r="T47" s="488">
+      <c r="T47" s="489">
         <v>38.64</v>
       </c>
     </row>
@@ -11259,40 +11259,40 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="501">
+      <c r="I48" s="506">
         <v>2.15</v>
       </c>
-      <c r="J48" s="502">
+      <c r="J48" s="501">
         <v>2.44</v>
       </c>
-      <c r="K48" s="503">
+      <c r="K48" s="507">
         <v>1.8</v>
       </c>
-      <c r="L48" s="497">
+      <c r="L48" s="502">
         <v>1.15</v>
       </c>
-      <c r="M48" s="505">
+      <c r="M48" s="498">
         <v>1.23</v>
       </c>
-      <c r="N48" s="498">
+      <c r="N48" s="508">
         <v>-0.15</v>
       </c>
-      <c r="O48" s="508">
+      <c r="O48" s="499">
         <v>-0.24</v>
       </c>
-      <c r="P48" s="499">
+      <c r="P48" s="503">
         <v>-0.26</v>
       </c>
-      <c r="Q48" s="506">
+      <c r="Q48" s="504">
         <v>-0.83</v>
       </c>
-      <c r="R48" s="504">
+      <c r="R48" s="500">
         <v>0.03</v>
       </c>
-      <c r="S48" s="500">
+      <c r="S48" s="505">
         <v>0.34</v>
       </c>
-      <c r="T48" s="507">
+      <c r="T48" s="497">
         <v>-4.09</v>
       </c>
     </row>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -39,19 +39,1189 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF39AE54"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF98D4A6"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,61 +1233,1345 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,43 +2583,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,7 +2649,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
+        <fgColor rgb="FFCE2E3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,25 +2667,265 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,109 +2937,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,1261 +3033,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
+        <fgColor rgb="FFD83342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1605,1477 +3075,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8537,19 +8537,19 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="7">
         <v>4.95</v>
       </c>
       <c r="J2" s="8">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="11">
         <v>1.74</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="2">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="12">
         <v>-2.39</v>
       </c>
       <c r="N2" s="3">
@@ -8558,19 +8558,19 @@
       <c r="O2" s="4">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="1">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="5">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="9">
         <v>-4.59</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="6">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="6">
+      <c r="T2" s="10">
         <v>-15.96</v>
       </c>
     </row>
@@ -8599,40 +8599,40 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="23">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="16">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="18">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="19">
         <v>0.1</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="20">
         <v>3.32</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="13">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="21">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="17">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="24">
         <v>2.8</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="14">
         <v>1.66</v>
       </c>
       <c r="S3" s="22">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="15">
         <v>20.62</v>
       </c>
     </row>
@@ -8661,40 +8661,40 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="29">
         <v>4.19</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="30">
         <v>5.08</v>
       </c>
-      <c r="K4" s="26">
+      <c r="K4" s="25">
         <v>15.59</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="26">
         <v>27.15</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="31">
         <v>36.04</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="35">
         <v>41.33</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="33">
         <v>37.54</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="27">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="32">
         <v>32.33</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="36">
         <v>45.56</v>
       </c>
-      <c r="S4" s="25">
+      <c r="S4" s="28">
         <v>56.03</v>
       </c>
-      <c r="T4" s="29">
+      <c r="T4" s="34">
         <v>27.06</v>
       </c>
     </row>
@@ -8723,40 +8723,40 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="37">
+      <c r="I5" s="44">
         <v>11.97</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="37">
         <v>17.45</v>
       </c>
-      <c r="K5" s="39">
+      <c r="K5" s="38">
         <v>14.27</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="42">
         <v>17.32</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="46">
         <v>25.33</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="43">
         <v>21.54</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="39">
         <v>22.72</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="45">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="40">
         <v>17.54</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="41">
         <v>16.88</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="47">
         <v>11.79</v>
       </c>
-      <c r="T5" s="38">
+      <c r="T5" s="48">
         <v>16.67</v>
       </c>
     </row>
@@ -8785,40 +8785,40 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="55">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="51">
+      <c r="J6" s="56">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="57">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="50">
         <v>-0.66</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="53">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="51">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="52">
+      <c r="O6" s="58">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="60">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="49">
+      <c r="Q6" s="59">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="52">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="54">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="50">
+      <c r="T6" s="49">
         <v>-18.59</v>
       </c>
     </row>
@@ -8847,40 +8847,40 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="68">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="62">
+      <c r="J7" s="69">
         <v>1.8</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="61">
         <v>0.07</v>
       </c>
-      <c r="L7" s="63">
+      <c r="L7" s="64">
         <v>0.63</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="70">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="64">
+      <c r="N7" s="62">
         <v>1.55</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="71">
         <v>0.85</v>
       </c>
-      <c r="P7" s="65">
+      <c r="P7" s="72">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="63">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="61">
+      <c r="R7" s="65">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="70">
+      <c r="S7" s="67">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="66">
         <v>4.01</v>
       </c>
     </row>
@@ -8912,37 +8912,37 @@
       <c r="I8" s="79">
         <v>3.13</v>
       </c>
-      <c r="J8" s="83">
+      <c r="J8" s="84">
         <v>5.21</v>
       </c>
-      <c r="K8" s="75">
+      <c r="K8" s="80">
         <v>0.43</v>
       </c>
-      <c r="L8" s="76">
+      <c r="L8" s="75">
         <v>3.68</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="82">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="83">
         <v>1.66</v>
       </c>
       <c r="O8" s="73">
         <v>1.72</v>
       </c>
-      <c r="P8" s="77">
+      <c r="P8" s="81">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="78">
+      <c r="Q8" s="74">
         <v>15.33</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="76">
         <v>12.57</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="77">
         <v>23.85</v>
       </c>
-      <c r="T8" s="74">
+      <c r="T8" s="78">
         <v>-13.37</v>
       </c>
     </row>
@@ -8974,37 +8974,37 @@
       <c r="I9" s="93">
         <v>1.35</v>
       </c>
-      <c r="J9" s="85">
+      <c r="J9" s="88">
         <v>2.48</v>
       </c>
-      <c r="K9" s="86">
+      <c r="K9" s="89">
         <v>1.58</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="90">
         <v>1.35</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="91">
         <v>2.93</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="86">
         <v>0.23</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="92">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="94">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="88">
+      <c r="Q9" s="96">
         <v>3.83</v>
       </c>
-      <c r="R9" s="91">
+      <c r="R9" s="95">
         <v>7.43</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="87">
         <v>17.12</v>
       </c>
-      <c r="T9" s="92">
+      <c r="T9" s="85">
         <v>3.15</v>
       </c>
     </row>
@@ -9033,40 +9033,40 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="99">
+      <c r="I10" s="107">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="108">
+      <c r="J10" s="99">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="100">
         <v>-7.86</v>
       </c>
-      <c r="L10" s="100">
+      <c r="L10" s="108">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="97">
         <v>-12.37</v>
       </c>
-      <c r="N10" s="103">
+      <c r="N10" s="104">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="104">
+      <c r="O10" s="98">
         <v>-9.15</v>
       </c>
       <c r="P10" s="101">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="105">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="102">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="97">
+      <c r="S10" s="106">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="98">
+      <c r="T10" s="103">
         <v>-10.94</v>
       </c>
     </row>
@@ -9095,40 +9095,40 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="119">
         <v>7.32</v>
       </c>
-      <c r="J11" s="109">
+      <c r="J11" s="115">
         <v>7.76</v>
       </c>
-      <c r="K11" s="110">
+      <c r="K11" s="120">
         <v>15.37</v>
       </c>
-      <c r="L11" s="114">
+      <c r="L11" s="109">
         <v>8.64</v>
       </c>
-      <c r="M11" s="115">
+      <c r="M11" s="110">
         <v>0.59</v>
       </c>
       <c r="N11" s="111">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="116">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="117">
         <v>-2.93</v>
       </c>
       <c r="Q11" s="112">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="113">
+      <c r="R11" s="118">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="116">
+      <c r="S11" s="113">
         <v>0.15</v>
       </c>
-      <c r="T11" s="117">
+      <c r="T11" s="114">
         <v>-21.08</v>
       </c>
     </row>
@@ -9157,40 +9157,40 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="122">
+      <c r="I12" s="125">
         <v>10.48</v>
       </c>
-      <c r="J12" s="126">
+      <c r="J12" s="127">
         <v>13.87</v>
       </c>
-      <c r="K12" s="127">
+      <c r="K12" s="121">
         <v>4.11</v>
       </c>
-      <c r="L12" s="123">
+      <c r="L12" s="128">
         <v>6.13</v>
       </c>
-      <c r="M12" s="130">
+      <c r="M12" s="129">
         <v>9.68</v>
       </c>
-      <c r="N12" s="124">
+      <c r="N12" s="122">
         <v>2.66</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="130">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="126">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="128">
+      <c r="Q12" s="123">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="125">
+      <c r="R12" s="131">
         <v>0.97</v>
       </c>
-      <c r="S12" s="121">
+      <c r="S12" s="132">
         <v>3.06</v>
       </c>
-      <c r="T12" s="129">
+      <c r="T12" s="124">
         <v>-21.53</v>
       </c>
     </row>
@@ -9219,40 +9219,40 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="143">
+      <c r="I13" s="141">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="144">
+      <c r="J13" s="135">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="137">
+      <c r="K13" s="136">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="133">
+      <c r="L13" s="139">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="139">
+      <c r="M13" s="133">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="134">
+      <c r="N13" s="140">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="135">
+      <c r="O13" s="137">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="138">
+      <c r="P13" s="142">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="140">
+      <c r="Q13" s="134">
         <v>-4.93</v>
       </c>
-      <c r="R13" s="141">
+      <c r="R13" s="138">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="142">
+      <c r="S13" s="143">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="136">
+      <c r="T13" s="144">
         <v>-20.66</v>
       </c>
     </row>
@@ -9281,40 +9281,40 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="146">
+      <c r="I14" s="150">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="149">
+      <c r="J14" s="151">
         <v>-5</v>
       </c>
-      <c r="K14" s="155">
+      <c r="K14" s="154">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="156">
+      <c r="L14" s="145">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="150">
+      <c r="M14" s="146">
         <v>-7.37</v>
       </c>
-      <c r="N14" s="145">
+      <c r="N14" s="147">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="152">
+      <c r="O14" s="155">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="147">
+      <c r="P14" s="152">
         <v>-5.63</v>
       </c>
-      <c r="Q14" s="151">
+      <c r="Q14" s="156">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="153">
+      <c r="R14" s="148">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="154">
+      <c r="S14" s="153">
         <v>0</v>
       </c>
-      <c r="T14" s="148">
+      <c r="T14" s="149">
         <v>-8.25</v>
       </c>
     </row>
@@ -9343,40 +9343,40 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="164">
+      <c r="I15" s="165">
         <v>9.9</v>
       </c>
-      <c r="J15" s="165">
+      <c r="J15" s="159">
         <v>9.43</v>
       </c>
-      <c r="K15" s="166">
+      <c r="K15" s="162">
         <v>8.82</v>
       </c>
       <c r="L15" s="167">
         <v>4.15</v>
       </c>
-      <c r="M15" s="160">
+      <c r="M15" s="163">
         <v>7.79</v>
       </c>
       <c r="N15" s="168">
         <v>1.3</v>
       </c>
-      <c r="O15" s="162">
+      <c r="O15" s="166">
         <v>8.69</v>
       </c>
-      <c r="P15" s="163">
+      <c r="P15" s="160">
         <v>6.79</v>
       </c>
       <c r="Q15" s="157">
         <v>5.84</v>
       </c>
-      <c r="R15" s="158">
+      <c r="R15" s="161">
         <v>6.88</v>
       </c>
-      <c r="S15" s="161">
+      <c r="S15" s="158">
         <v>2.34</v>
       </c>
-      <c r="T15" s="159">
+      <c r="T15" s="164">
         <v>-7.35</v>
       </c>
     </row>
@@ -9405,40 +9405,40 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="179">
+      <c r="I16" s="173">
         <v>2.67</v>
       </c>
-      <c r="J16" s="171">
+      <c r="J16" s="174">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="180">
+      <c r="K16" s="175">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="172">
+      <c r="L16" s="176">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="173">
+      <c r="M16" s="177">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="175">
+      <c r="N16" s="169">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="176">
+      <c r="O16" s="178">
         <v>-4.85</v>
       </c>
-      <c r="P16" s="177">
+      <c r="P16" s="179">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="169">
+      <c r="Q16" s="170">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="178">
+      <c r="R16" s="171">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="174">
+      <c r="S16" s="180">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="170">
+      <c r="T16" s="172">
         <v>-21.15</v>
       </c>
     </row>
@@ -9467,40 +9467,40 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="181">
+      <c r="I17" s="189">
         <v>-1.51</v>
       </c>
       <c r="J17" s="186">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="187">
+      <c r="K17" s="182">
         <v>0.2</v>
       </c>
-      <c r="L17" s="182">
+      <c r="L17" s="190">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="188">
+      <c r="M17" s="185">
         <v>0.53</v>
       </c>
-      <c r="N17" s="183">
+      <c r="N17" s="191">
         <v>3.31</v>
       </c>
-      <c r="O17" s="191">
+      <c r="O17" s="183">
         <v>6.89</v>
       </c>
-      <c r="P17" s="184">
+      <c r="P17" s="192">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="192">
+      <c r="Q17" s="181">
         <v>4.09</v>
       </c>
-      <c r="R17" s="189">
+      <c r="R17" s="184">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="190">
+      <c r="S17" s="187">
         <v>-1.45</v>
       </c>
-      <c r="T17" s="185">
+      <c r="T17" s="188">
         <v>-1.47</v>
       </c>
     </row>
@@ -9529,40 +9529,40 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="200">
+      <c r="I18" s="201">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="204">
+      <c r="J18" s="199">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="195">
+      <c r="K18" s="194">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="201">
+      <c r="L18" s="202">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="197">
+      <c r="M18" s="196">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="198">
+      <c r="N18" s="197">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="196">
+      <c r="O18" s="203">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="193">
+      <c r="P18" s="200">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="194">
+      <c r="Q18" s="204">
         <v>-20.52</v>
       </c>
-      <c r="R18" s="202">
+      <c r="R18" s="195">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="203">
+      <c r="S18" s="193">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="199">
+      <c r="T18" s="198">
         <v>-24.97</v>
       </c>
     </row>
@@ -9591,40 +9591,40 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="209">
+      <c r="I19" s="212">
         <v>1.39</v>
       </c>
-      <c r="J19" s="214">
+      <c r="J19" s="205">
         <v>0.39</v>
       </c>
-      <c r="K19" s="210">
+      <c r="K19" s="213">
         <v>1.93</v>
       </c>
-      <c r="L19" s="215">
+      <c r="L19" s="206">
         <v>3.7</v>
       </c>
-      <c r="M19" s="212">
+      <c r="M19" s="214">
         <v>9.45</v>
       </c>
-      <c r="N19" s="216">
+      <c r="N19" s="208">
         <v>5.75</v>
       </c>
-      <c r="O19" s="207">
+      <c r="O19" s="209">
         <v>12.85</v>
       </c>
-      <c r="P19" s="213">
+      <c r="P19" s="207">
         <v>8.68</v>
       </c>
-      <c r="Q19" s="205">
+      <c r="Q19" s="210">
         <v>14.74</v>
       </c>
-      <c r="R19" s="206">
+      <c r="R19" s="215">
         <v>14.89</v>
       </c>
-      <c r="S19" s="211">
+      <c r="S19" s="216">
         <v>9.1</v>
       </c>
-      <c r="T19" s="208">
+      <c r="T19" s="211">
         <v>3.43</v>
       </c>
     </row>
@@ -9653,40 +9653,40 @@
       <c r="H20">
         <v>-1.89</v>
       </c>
-      <c r="I20" s="226">
+      <c r="I20" s="227">
         <v>1.85</v>
       </c>
-      <c r="J20" s="218">
+      <c r="J20" s="219">
         <v>8.14</v>
       </c>
-      <c r="K20" s="219">
+      <c r="K20" s="220">
         <v>2.43</v>
       </c>
-      <c r="L20" s="227">
+      <c r="L20" s="225">
         <v>1.09</v>
       </c>
-      <c r="M20" s="220">
+      <c r="M20" s="223">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="221">
+      <c r="N20" s="228">
         <v>-0.76</v>
       </c>
-      <c r="O20" s="222">
+      <c r="O20" s="217">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="223">
+      <c r="P20" s="221">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="225">
+      <c r="Q20" s="226">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="224">
+      <c r="R20" s="218">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="228">
+      <c r="S20" s="224">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="217">
+      <c r="T20" s="222">
         <v>-8.14</v>
       </c>
     </row>
@@ -9715,40 +9715,40 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="240">
+      <c r="I21" s="238">
         <v>8.65</v>
       </c>
-      <c r="J21" s="237">
+      <c r="J21" s="234">
         <v>9.13</v>
       </c>
-      <c r="K21" s="231">
+      <c r="K21" s="236">
         <v>12.02</v>
       </c>
       <c r="L21" s="229">
         <v>9.13</v>
       </c>
-      <c r="M21" s="232">
+      <c r="M21" s="239">
         <v>12.86</v>
       </c>
       <c r="N21" s="230">
         <v>8.29</v>
       </c>
-      <c r="O21" s="233">
+      <c r="O21" s="231">
         <v>0.36</v>
       </c>
-      <c r="P21" s="238">
+      <c r="P21" s="232">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="234">
+      <c r="Q21" s="237">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="239">
+      <c r="R21" s="233">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="235">
+      <c r="S21" s="240">
         <v>2.04</v>
       </c>
-      <c r="T21" s="236">
+      <c r="T21" s="235">
         <v>-9.86</v>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="243">
+      <c r="I22" s="247">
         <v>9.66</v>
       </c>
       <c r="J22" s="244">
@@ -9786,25 +9786,25 @@
       <c r="K22" s="245">
         <v>19.72</v>
       </c>
-      <c r="L22" s="246">
+      <c r="L22" s="248">
         <v>17.55</v>
       </c>
-      <c r="M22" s="247">
+      <c r="M22" s="252">
         <v>15.78</v>
       </c>
-      <c r="N22" s="248">
+      <c r="N22" s="242">
         <v>6.9</v>
       </c>
-      <c r="O22" s="252">
+      <c r="O22" s="243">
         <v>0.99</v>
       </c>
-      <c r="P22" s="249">
+      <c r="P22" s="246">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="241">
+      <c r="Q22" s="249">
         <v>8.88</v>
       </c>
-      <c r="R22" s="242">
+      <c r="R22" s="241">
         <v>4.73</v>
       </c>
       <c r="S22" s="250">
@@ -9839,40 +9839,40 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="259">
+      <c r="I23" s="257">
         <v>5.78</v>
       </c>
-      <c r="J23" s="260">
+      <c r="J23" s="261">
         <v>3.91</v>
       </c>
-      <c r="K23" s="256">
+      <c r="K23" s="262">
         <v>6.83</v>
       </c>
-      <c r="L23" s="264">
+      <c r="L23" s="263">
         <v>4.79</v>
       </c>
-      <c r="M23" s="257">
+      <c r="M23" s="254">
         <v>5.08</v>
       </c>
-      <c r="N23" s="261">
+      <c r="N23" s="258">
         <v>4.5</v>
       </c>
-      <c r="O23" s="254">
+      <c r="O23" s="264">
         <v>1.4</v>
       </c>
-      <c r="P23" s="262">
+      <c r="P23" s="259">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="258">
+      <c r="Q23" s="255">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="253">
+      <c r="R23" s="256">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="255">
+      <c r="S23" s="260">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="263">
+      <c r="T23" s="253">
         <v>5.95</v>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
       <c r="K24" s="267">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="274">
+      <c r="L24" s="270">
         <v>-12.46</v>
       </c>
       <c r="M24" s="272">
@@ -9919,22 +9919,22 @@
       <c r="N24" s="268">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="269">
+      <c r="O24" s="273">
         <v>-7.66</v>
       </c>
-      <c r="P24" s="270">
+      <c r="P24" s="274">
         <v>-9.54</v>
       </c>
-      <c r="Q24" s="276">
+      <c r="Q24" s="269">
         <v>-15.61</v>
       </c>
       <c r="R24" s="275">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="265">
+      <c r="S24" s="276">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="273">
+      <c r="T24" s="265">
         <v>-10.65</v>
       </c>
     </row>
@@ -9966,37 +9966,37 @@
       <c r="I25" s="286">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="277">
+      <c r="J25" s="287">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="282">
+      <c r="K25" s="283">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="287">
+      <c r="L25" s="288">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="278">
+      <c r="M25" s="280">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="279">
+      <c r="N25" s="284">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="283">
+      <c r="O25" s="277">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="280">
+      <c r="P25" s="281">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="281">
+      <c r="Q25" s="278">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="284">
+      <c r="R25" s="279">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="288">
+      <c r="S25" s="285">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="285">
+      <c r="T25" s="282">
         <v>-12.52</v>
       </c>
     </row>
@@ -10025,40 +10025,40 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="295">
+      <c r="I26" s="293">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="296">
+      <c r="J26" s="294">
         <v>0.56</v>
       </c>
-      <c r="K26" s="300">
+      <c r="K26" s="289">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="289">
+      <c r="L26" s="290">
         <v>-7.91</v>
       </c>
-      <c r="M26" s="292">
+      <c r="M26" s="295">
         <v>1.36</v>
       </c>
-      <c r="N26" s="293">
+      <c r="N26" s="298">
         <v>3.39</v>
       </c>
-      <c r="O26" s="297">
+      <c r="O26" s="299">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="294">
+      <c r="P26" s="291">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="290">
+      <c r="Q26" s="292">
         <v>7.01</v>
       </c>
-      <c r="R26" s="298">
+      <c r="R26" s="300">
         <v>12.66</v>
       </c>
-      <c r="S26" s="299">
+      <c r="S26" s="296">
         <v>6.55</v>
       </c>
-      <c r="T26" s="291">
+      <c r="T26" s="297">
         <v>-10.28</v>
       </c>
     </row>
@@ -10087,40 +10087,40 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="303">
+      <c r="I27" s="308">
         <v>-1.23</v>
       </c>
-      <c r="J27" s="310">
+      <c r="J27" s="302">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="304">
+      <c r="K27" s="311">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="311">
+      <c r="L27" s="303">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="306">
+      <c r="M27" s="304">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="307">
+      <c r="N27" s="305">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="301">
+      <c r="O27" s="312">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="302">
+      <c r="P27" s="306">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="305">
+      <c r="Q27" s="301">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="308">
+      <c r="R27" s="309">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="309">
+      <c r="S27" s="310">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="312">
+      <c r="T27" s="307">
         <v>-12.1</v>
       </c>
     </row>
@@ -10149,40 +10149,40 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="316">
+      <c r="I28" s="322">
         <v>1.28</v>
       </c>
-      <c r="J28" s="317">
+      <c r="J28" s="315">
         <v>2.92</v>
       </c>
-      <c r="K28" s="318">
+      <c r="K28" s="316">
         <v>4.72</v>
       </c>
-      <c r="L28" s="320">
+      <c r="L28" s="318">
         <v>6.25</v>
       </c>
-      <c r="M28" s="323">
+      <c r="M28" s="319">
         <v>16.86</v>
       </c>
-      <c r="N28" s="321">
+      <c r="N28" s="320">
         <v>13.12</v>
       </c>
-      <c r="O28" s="319">
+      <c r="O28" s="321">
         <v>24.45</v>
       </c>
-      <c r="P28" s="322">
+      <c r="P28" s="313">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="324">
+      <c r="Q28" s="323">
         <v>46.03</v>
       </c>
-      <c r="R28" s="313">
+      <c r="R28" s="317">
         <v>45.46</v>
       </c>
-      <c r="S28" s="314">
+      <c r="S28" s="324">
         <v>42.9</v>
       </c>
-      <c r="T28" s="315">
+      <c r="T28" s="314">
         <v>23.63</v>
       </c>
     </row>
@@ -10211,40 +10211,40 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="327">
+      <c r="I29" s="325">
         <v>3.14</v>
       </c>
-      <c r="J29" s="335">
+      <c r="J29" s="330">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="329">
+      <c r="K29" s="331">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="330">
+      <c r="L29" s="326">
         <v>-0.61</v>
       </c>
-      <c r="M29" s="336">
+      <c r="M29" s="327">
         <v>6.71</v>
       </c>
-      <c r="N29" s="328">
+      <c r="N29" s="336">
         <v>3.47</v>
       </c>
-      <c r="O29" s="333">
+      <c r="O29" s="332">
         <v>-0.94</v>
       </c>
-      <c r="P29" s="331">
+      <c r="P29" s="333">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="325">
+      <c r="Q29" s="334">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="326">
+      <c r="R29" s="335">
         <v>0.11</v>
       </c>
-      <c r="S29" s="334">
+      <c r="S29" s="328">
         <v>2.42</v>
       </c>
-      <c r="T29" s="332">
+      <c r="T29" s="329">
         <v>6.88</v>
       </c>
     </row>
@@ -10273,40 +10273,40 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="338">
+      <c r="I30" s="344">
         <v>1.85</v>
       </c>
-      <c r="J30" s="344">
+      <c r="J30" s="345">
         <v>7.78</v>
       </c>
-      <c r="K30" s="348">
+      <c r="K30" s="346">
         <v>13.84</v>
       </c>
-      <c r="L30" s="345">
+      <c r="L30" s="337">
         <v>11.93</v>
       </c>
-      <c r="M30" s="339">
+      <c r="M30" s="338">
         <v>5.23</v>
       </c>
-      <c r="N30" s="341">
+      <c r="N30" s="347">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="346">
+      <c r="O30" s="348">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="337">
+      <c r="P30" s="339">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="347">
+      <c r="Q30" s="340">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="342">
+      <c r="R30" s="341">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="343">
+      <c r="S30" s="342">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="340">
+      <c r="T30" s="343">
         <v>-13.9</v>
       </c>
     </row>
@@ -10335,40 +10335,40 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="353">
+      <c r="I31" s="358">
         <v>1.82</v>
       </c>
-      <c r="J31" s="358">
+      <c r="J31" s="359">
         <v>6.88</v>
       </c>
-      <c r="K31" s="359">
+      <c r="K31" s="353">
         <v>4.25</v>
       </c>
-      <c r="L31" s="360">
+      <c r="L31" s="350">
         <v>1.42</v>
       </c>
-      <c r="M31" s="350">
+      <c r="M31" s="354">
         <v>-7.09</v>
       </c>
-      <c r="N31" s="351">
+      <c r="N31" s="355">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="354">
+      <c r="O31" s="360">
         <v>-10.32</v>
       </c>
-      <c r="P31" s="355">
+      <c r="P31" s="351">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="357">
+      <c r="Q31" s="349">
         <v>-17</v>
       </c>
-      <c r="R31" s="349">
+      <c r="R31" s="356">
         <v>-16.8</v>
       </c>
-      <c r="S31" s="352">
+      <c r="S31" s="357">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="356">
+      <c r="T31" s="352">
         <v>-20.65</v>
       </c>
     </row>
@@ -10397,40 +10397,40 @@
       <c r="H32">
         <v>-1.07</v>
       </c>
-      <c r="I32" s="362">
+      <c r="I32" s="363">
         <v>-1.18</v>
       </c>
       <c r="J32" s="371">
         <v>0.27</v>
       </c>
-      <c r="K32" s="365">
+      <c r="K32" s="369">
         <v>2.99</v>
       </c>
-      <c r="L32" s="366">
+      <c r="L32" s="370">
         <v>2.35</v>
       </c>
-      <c r="M32" s="363">
+      <c r="M32" s="366">
         <v>0.72</v>
       </c>
-      <c r="N32" s="367">
+      <c r="N32" s="364">
         <v>1</v>
       </c>
-      <c r="O32" s="368">
+      <c r="O32" s="365">
         <v>-2.35</v>
       </c>
       <c r="P32" s="372">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="361">
+      <c r="Q32" s="367">
         <v>3.26</v>
       </c>
-      <c r="R32" s="369">
+      <c r="R32" s="361">
         <v>1</v>
       </c>
-      <c r="S32" s="364">
+      <c r="S32" s="362">
         <v>1.45</v>
       </c>
-      <c r="T32" s="370">
+      <c r="T32" s="368">
         <v>7.78</v>
       </c>
     </row>
@@ -10459,31 +10459,31 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="377">
+      <c r="I33" s="376">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="374">
+      <c r="J33" s="382">
         <v>0.57</v>
       </c>
-      <c r="K33" s="378">
+      <c r="K33" s="377">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="382">
+      <c r="L33" s="374">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="383">
+      <c r="M33" s="378">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="384">
+      <c r="N33" s="383">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="375">
+      <c r="O33" s="380">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="376">
+      <c r="P33" s="381">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="380">
+      <c r="Q33" s="384">
         <v>-20.23</v>
       </c>
       <c r="R33" s="379">
@@ -10492,7 +10492,7 @@
       <c r="S33" s="373">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="381">
+      <c r="T33" s="375">
         <v>-22.68</v>
       </c>
     </row>
@@ -10521,37 +10521,37 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="389">
+      <c r="I34" s="396">
         <v>-3</v>
       </c>
-      <c r="J34" s="393">
+      <c r="J34" s="389">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="394">
+      <c r="K34" s="390">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="385">
+      <c r="L34" s="393">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="390">
+      <c r="M34" s="385">
         <v>-16.82</v>
       </c>
-      <c r="N34" s="396">
+      <c r="N34" s="386">
         <v>-18.2</v>
       </c>
-      <c r="O34" s="386">
+      <c r="O34" s="394">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="395">
+      <c r="P34" s="391">
         <v>-19.82</v>
       </c>
       <c r="Q34" s="387">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="391">
+      <c r="R34" s="392">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="392">
+      <c r="S34" s="395">
         <v>-21.43</v>
       </c>
       <c r="T34" s="388">
@@ -10583,40 +10583,40 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="400">
+      <c r="I35" s="398">
         <v>4.2</v>
       </c>
-      <c r="J35" s="407">
+      <c r="J35" s="399">
         <v>3.72</v>
       </c>
-      <c r="K35" s="404">
+      <c r="K35" s="406">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="408">
+      <c r="L35" s="407">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="401">
+      <c r="M35" s="405">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="397">
+      <c r="N35" s="400">
         <v>6.61</v>
       </c>
-      <c r="O35" s="405">
+      <c r="O35" s="401">
         <v>5.5</v>
       </c>
-      <c r="P35" s="398">
+      <c r="P35" s="408">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="406">
+      <c r="Q35" s="403">
         <v>1.68</v>
       </c>
       <c r="R35" s="402">
         <v>1.37</v>
       </c>
-      <c r="S35" s="403">
+      <c r="S35" s="404">
         <v>0.08</v>
       </c>
-      <c r="T35" s="399">
+      <c r="T35" s="397">
         <v>-0.66</v>
       </c>
     </row>
@@ -10645,40 +10645,40 @@
       <c r="H36">
         <v>-3.03</v>
       </c>
-      <c r="I36" s="410">
+      <c r="I36" s="409">
         <v>5.57</v>
       </c>
-      <c r="J36" s="414">
+      <c r="J36" s="410">
         <v>16.17</v>
       </c>
-      <c r="K36" s="411">
+      <c r="K36" s="414">
         <v>22.01</v>
       </c>
-      <c r="L36" s="415">
+      <c r="L36" s="418">
         <v>16.85</v>
       </c>
-      <c r="M36" s="416">
+      <c r="M36" s="412">
         <v>7.07</v>
       </c>
-      <c r="N36" s="418">
+      <c r="N36" s="413">
         <v>0.27</v>
       </c>
       <c r="O36" s="419">
         <v>2.45</v>
       </c>
-      <c r="P36" s="417">
+      <c r="P36" s="415">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="420">
+      <c r="Q36" s="411">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="409">
+      <c r="R36" s="420">
         <v>9.65</v>
       </c>
-      <c r="S36" s="412">
+      <c r="S36" s="416">
         <v>7.47</v>
       </c>
-      <c r="T36" s="413">
+      <c r="T36" s="417">
         <v>3.26</v>
       </c>
     </row>
@@ -10707,40 +10707,40 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="423">
+      <c r="I37" s="430">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="428">
+      <c r="J37" s="425">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="431">
+      <c r="K37" s="428">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="425">
+      <c r="L37" s="431">
         <v>7.57</v>
       </c>
       <c r="M37" s="432">
         <v>5.6</v>
       </c>
-      <c r="N37" s="429">
+      <c r="N37" s="423">
         <v>4.48</v>
       </c>
-      <c r="O37" s="426">
+      <c r="O37" s="424">
         <v>3.32</v>
       </c>
-      <c r="P37" s="421">
+      <c r="P37" s="429">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="427">
+      <c r="Q37" s="426">
         <v>3.78</v>
       </c>
-      <c r="R37" s="430">
+      <c r="R37" s="427">
         <v>8.07</v>
       </c>
-      <c r="S37" s="422">
+      <c r="S37" s="421">
         <v>11.74</v>
       </c>
-      <c r="T37" s="424">
+      <c r="T37" s="422">
         <v>11.74</v>
       </c>
     </row>
@@ -10769,36 +10769,36 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="440">
+      <c r="I38" s="439">
         <v>6.62</v>
       </c>
-      <c r="J38" s="441">
+      <c r="J38" s="435">
         <v>10.07</v>
       </c>
-      <c r="K38" s="433">
+      <c r="K38" s="436">
         <v>6.26</v>
       </c>
-      <c r="L38" s="435">
+      <c r="L38" s="442">
         <v>2.13</v>
       </c>
-      <c r="M38" s="438">
+      <c r="M38" s="433">
         <v>1.41</v>
       </c>
-      <c r="N38" s="439">
+      <c r="N38" s="440">
         <v>7.72</v>
       </c>
-      <c r="O38" s="436">
+      <c r="O38" s="434">
         <v>5.74</v>
       </c>
-      <c r="P38" s="434">
+      <c r="P38" s="437">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="442">
+      <c r="Q38" s="438">
         <v>14.45</v>
       </c>
       <c r="R38" t="str"/>
       <c r="S38" t="str"/>
-      <c r="T38" s="437">
+      <c r="T38" s="441">
         <v>14.45</v>
       </c>
     </row>
@@ -10827,34 +10827,34 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="444">
+      <c r="I39" s="443">
         <v>7.14</v>
       </c>
-      <c r="J39" s="446">
+      <c r="J39" s="444">
         <v>7.82</v>
       </c>
-      <c r="K39" s="451">
+      <c r="K39" s="445">
         <v>7.68</v>
       </c>
-      <c r="L39" s="448">
+      <c r="L39" s="446">
         <v>8.49</v>
       </c>
-      <c r="M39" s="443">
+      <c r="M39" s="447">
         <v>9.43</v>
       </c>
-      <c r="N39" s="449">
+      <c r="N39" s="450">
         <v>5.39</v>
       </c>
-      <c r="O39" s="447">
+      <c r="O39" s="448">
         <v>8.49</v>
       </c>
-      <c r="P39" s="445">
+      <c r="P39" s="451">
         <v>7.28</v>
       </c>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="450">
+      <c r="T39" s="449">
         <v>7.28</v>
       </c>
     </row>
@@ -10883,32 +10883,32 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="459">
+      <c r="I40" s="453">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="452">
+      <c r="J40" s="454">
         <v>-0.66</v>
       </c>
-      <c r="K40" s="453">
+      <c r="K40" s="455">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="454">
+      <c r="L40" s="456">
         <v>0</v>
       </c>
-      <c r="M40" s="455">
+      <c r="M40" s="457">
         <v>-1.31</v>
       </c>
-      <c r="N40" s="456">
+      <c r="N40" s="458">
         <v>0.33</v>
       </c>
-      <c r="O40" s="457">
+      <c r="O40" s="459">
         <v>0</v>
       </c>
       <c r="P40" t="str"/>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="458">
+      <c r="T40" s="452">
         <v>0</v>
       </c>
     </row>
@@ -10989,19 +10989,19 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="469">
+      <c r="I42" s="471">
         <v>2.08</v>
       </c>
-      <c r="J42" s="470">
+      <c r="J42" s="472">
         <v>2.7</v>
       </c>
-      <c r="K42" s="471">
+      <c r="K42" s="467">
         <v>0</v>
       </c>
-      <c r="L42" s="472">
+      <c r="L42" s="468">
         <v>1.25</v>
       </c>
-      <c r="M42" s="467">
+      <c r="M42" s="469">
         <v>1.04</v>
       </c>
       <c r="N42" t="str"/>
@@ -11010,7 +11010,7 @@
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="468">
+      <c r="T42" s="470">
         <v>1.04</v>
       </c>
     </row>
@@ -11039,16 +11039,16 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="474">
+      <c r="I43" s="473">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="475">
+      <c r="J43" s="474">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="476">
+      <c r="K43" s="475">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="477">
+      <c r="L43" s="476">
         <v>8.46</v>
       </c>
       <c r="M43" t="str"/>
@@ -11058,7 +11058,7 @@
       <c r="Q43" t="str"/>
       <c r="R43" t="str"/>
       <c r="S43" t="str"/>
-      <c r="T43" s="473">
+      <c r="T43" s="477">
         <v>8.46</v>
       </c>
     </row>
@@ -11087,13 +11087,13 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="479">
+      <c r="I44" s="478">
         <v>10.68</v>
       </c>
-      <c r="J44" s="480">
+      <c r="J44" s="479">
         <v>1.78</v>
       </c>
-      <c r="K44" s="481">
+      <c r="K44" s="480">
         <v>-1.94</v>
       </c>
       <c r="L44" t="str"/>
@@ -11104,7 +11104,7 @@
       <c r="Q44" t="str"/>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="478">
+      <c r="T44" s="481">
         <v>-1.94</v>
       </c>
     </row>
@@ -11133,10 +11133,10 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="484">
+      <c r="I45" s="482">
         <v>2.03</v>
       </c>
-      <c r="J45" s="482">
+      <c r="J45" s="483">
         <v>5.03</v>
       </c>
       <c r="K45" t="str"/>
@@ -11148,7 +11148,7 @@
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="483">
+      <c r="T45" s="484">
         <v>5.03</v>
       </c>
     </row>
@@ -11211,40 +11211,40 @@
       <c r="F47" t="str"/>
       <c r="G47" t="str"/>
       <c r="H47" t="str"/>
-      <c r="I47" s="490">
+      <c r="I47" s="486">
         <v>59.09</v>
       </c>
-      <c r="J47" s="494">
+      <c r="J47" s="495">
         <v>59.09</v>
       </c>
-      <c r="K47" s="485">
+      <c r="K47" s="490">
         <v>51.16</v>
       </c>
-      <c r="L47" s="491">
+      <c r="L47" s="488">
         <v>57.14</v>
       </c>
-      <c r="M47" s="486">
+      <c r="M47" s="496">
         <v>53.66</v>
       </c>
-      <c r="N47" s="492">
+      <c r="N47" s="491">
         <v>55</v>
       </c>
-      <c r="O47" s="487">
+      <c r="O47" s="489">
         <v>41.03</v>
       </c>
-      <c r="P47" s="495">
+      <c r="P47" s="487">
         <v>42.11</v>
       </c>
-      <c r="Q47" s="488">
+      <c r="Q47" s="492">
         <v>40.54</v>
       </c>
       <c r="R47" s="493">
         <v>44.44</v>
       </c>
-      <c r="S47" s="496">
+      <c r="S47" s="494">
         <v>47.22</v>
       </c>
-      <c r="T47" s="489">
+      <c r="T47" s="485">
         <v>38.64</v>
       </c>
     </row>
@@ -11259,40 +11259,40 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="506">
+      <c r="I48" s="500">
         <v>2.15</v>
       </c>
       <c r="J48" s="501">
         <v>2.44</v>
       </c>
-      <c r="K48" s="507">
+      <c r="K48" s="506">
         <v>1.8</v>
       </c>
       <c r="L48" s="502">
         <v>1.15</v>
       </c>
-      <c r="M48" s="498">
+      <c r="M48" s="507">
         <v>1.23</v>
       </c>
       <c r="N48" s="508">
         <v>-0.15</v>
       </c>
-      <c r="O48" s="499">
+      <c r="O48" s="503">
         <v>-0.24</v>
       </c>
-      <c r="P48" s="503">
+      <c r="P48" s="497">
         <v>-0.26</v>
       </c>
       <c r="Q48" s="504">
         <v>-0.83</v>
       </c>
-      <c r="R48" s="500">
+      <c r="R48" s="505">
         <v>0.03</v>
       </c>
-      <c r="S48" s="505">
+      <c r="S48" s="498">
         <v>0.34</v>
       </c>
-      <c r="T48" s="497">
+      <c r="T48" s="499">
         <v>-4.09</v>
       </c>
     </row>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -39,19 +39,1849 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF259C40"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,61 +1893,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,25 +1917,685 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,42 +2607,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -207,7 +2661,265 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,109 +2931,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CE97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,1249 +3045,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
+        <fgColor rgb="FFD83342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A94"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1587,1501 +3063,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFEFBFC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83342"/>
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5DAB1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8537,40 +8537,40 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="3">
         <v>4.95</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="4">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="8">
         <v>1.74</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="1">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="2">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="5">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="9">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="10">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="11">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="12">
         <v>-4.59</v>
       </c>
       <c r="S2" s="6">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="10">
+      <c r="T2" s="7">
         <v>-15.96</v>
       </c>
     </row>
@@ -8599,31 +8599,31 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="19">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="23">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="15">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="16">
         <v>0.1</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="24">
         <v>3.32</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="17">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="13">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="20">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="21">
         <v>2.8</v>
       </c>
       <c r="R3" s="14">
@@ -8632,7 +8632,7 @@
       <c r="S3" s="22">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="18">
         <v>20.62</v>
       </c>
     </row>
@@ -8661,40 +8661,40 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="31">
         <v>4.19</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="26">
         <v>5.08</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="35">
         <v>15.59</v>
       </c>
-      <c r="L4" s="26">
+      <c r="L4" s="33">
         <v>27.15</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="27">
         <v>36.04</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="34">
         <v>41.33</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="32">
         <v>37.54</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="28">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="29">
         <v>32.33</v>
       </c>
       <c r="R4" s="36">
         <v>45.56</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="30">
         <v>56.03</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="25">
         <v>27.06</v>
       </c>
     </row>
@@ -8723,40 +8723,40 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="42">
         <v>11.97</v>
       </c>
-      <c r="J5" s="37">
+      <c r="J5" s="45">
         <v>17.45</v>
       </c>
-      <c r="K5" s="38">
+      <c r="K5" s="37">
         <v>14.27</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="38">
         <v>17.32</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="39">
         <v>25.33</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="46">
         <v>21.54</v>
       </c>
-      <c r="O5" s="39">
+      <c r="O5" s="40">
         <v>22.72</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="47">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="43">
         <v>17.54</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="48">
         <v>16.88</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="44">
         <v>11.79</v>
       </c>
-      <c r="T5" s="48">
+      <c r="T5" s="41">
         <v>16.67</v>
       </c>
     </row>
@@ -8785,40 +8785,40 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="54">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="58">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="59">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="50">
+      <c r="L6" s="60">
         <v>-0.66</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="55">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="51">
+      <c r="N6" s="50">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="56">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="49">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="51">
         <v>-6.26</v>
       </c>
       <c r="R6" s="52">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="57">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="49">
+      <c r="T6" s="53">
         <v>-18.59</v>
       </c>
     </row>
@@ -8847,40 +8847,40 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="65">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="71">
         <v>1.8</v>
       </c>
       <c r="K7" s="61">
         <v>0.07</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="62">
         <v>0.63</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="63">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="62">
+      <c r="N7" s="69">
         <v>1.55</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="66">
         <v>0.85</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="70">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="63">
+      <c r="Q7" s="67">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="65">
+      <c r="R7" s="64">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="72">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="66">
+      <c r="T7" s="68">
         <v>4.01</v>
       </c>
     </row>
@@ -8909,40 +8909,40 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="78">
         <v>3.13</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="79">
         <v>5.21</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="82">
         <v>0.43</v>
       </c>
-      <c r="L8" s="75">
+      <c r="L8" s="80">
         <v>3.68</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="74">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="75">
         <v>1.66</v>
       </c>
-      <c r="O8" s="73">
+      <c r="O8" s="76">
         <v>1.72</v>
       </c>
       <c r="P8" s="81">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="74">
+      <c r="Q8" s="83">
         <v>15.33</v>
       </c>
-      <c r="R8" s="76">
+      <c r="R8" s="84">
         <v>12.57</v>
       </c>
       <c r="S8" s="77">
         <v>23.85</v>
       </c>
-      <c r="T8" s="78">
+      <c r="T8" s="73">
         <v>-13.37</v>
       </c>
     </row>
@@ -8971,40 +8971,40 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="92">
         <v>1.35</v>
       </c>
       <c r="J9" s="88">
         <v>2.48</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="91">
         <v>1.58</v>
       </c>
-      <c r="L9" s="90">
+      <c r="L9" s="93">
         <v>1.35</v>
       </c>
-      <c r="M9" s="91">
+      <c r="M9" s="85">
         <v>2.93</v>
       </c>
-      <c r="N9" s="86">
+      <c r="N9" s="94">
         <v>0.23</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="89">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="90">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="86">
         <v>3.83</v>
       </c>
       <c r="R9" s="95">
         <v>7.43</v>
       </c>
-      <c r="S9" s="87">
+      <c r="S9" s="96">
         <v>17.12</v>
       </c>
-      <c r="T9" s="85">
+      <c r="T9" s="87">
         <v>3.15</v>
       </c>
     </row>
@@ -9033,40 +9033,40 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="106">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="97">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="100">
+      <c r="K10" s="107">
         <v>-7.86</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="103">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="97">
+      <c r="M10" s="98">
         <v>-12.37</v>
       </c>
       <c r="N10" s="104">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="98">
+      <c r="O10" s="105">
         <v>-9.15</v>
       </c>
       <c r="P10" s="101">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="99">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="102">
+      <c r="R10" s="100">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="106">
+      <c r="S10" s="102">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="103">
+      <c r="T10" s="108">
         <v>-10.94</v>
       </c>
     </row>
@@ -9095,40 +9095,40 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="119">
+      <c r="I11" s="115">
         <v>7.32</v>
       </c>
-      <c r="J11" s="115">
+      <c r="J11" s="120">
         <v>7.76</v>
       </c>
-      <c r="K11" s="120">
+      <c r="K11" s="109">
         <v>15.37</v>
       </c>
-      <c r="L11" s="109">
+      <c r="L11" s="113">
         <v>8.64</v>
       </c>
-      <c r="M11" s="110">
+      <c r="M11" s="111">
         <v>0.59</v>
       </c>
-      <c r="N11" s="111">
+      <c r="N11" s="116">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="116">
+      <c r="O11" s="110">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="117">
+      <c r="P11" s="114">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="112">
+      <c r="Q11" s="117">
         <v>-4.39</v>
       </c>
       <c r="R11" s="118">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="113">
+      <c r="S11" s="119">
         <v>0.15</v>
       </c>
-      <c r="T11" s="114">
+      <c r="T11" s="112">
         <v>-21.08</v>
       </c>
     </row>
@@ -9157,40 +9157,40 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="125">
+      <c r="I12" s="132">
         <v>10.48</v>
       </c>
       <c r="J12" s="127">
         <v>13.87</v>
       </c>
-      <c r="K12" s="121">
+      <c r="K12" s="124">
         <v>4.11</v>
       </c>
       <c r="L12" s="128">
         <v>6.13</v>
       </c>
-      <c r="M12" s="129">
+      <c r="M12" s="125">
         <v>9.68</v>
       </c>
-      <c r="N12" s="122">
+      <c r="N12" s="129">
         <v>2.66</v>
       </c>
-      <c r="O12" s="130">
+      <c r="O12" s="121">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="126">
+      <c r="P12" s="131">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="123">
+      <c r="Q12" s="126">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="130">
         <v>0.97</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="122">
         <v>3.06</v>
       </c>
-      <c r="T12" s="124">
+      <c r="T12" s="123">
         <v>-21.53</v>
       </c>
     </row>
@@ -9219,40 +9219,40 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="141">
+      <c r="I13" s="136">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="135">
+      <c r="J13" s="143">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="136">
+      <c r="K13" s="137">
         <v>-12.58</v>
       </c>
       <c r="L13" s="139">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="133">
+      <c r="M13" s="144">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="140">
+      <c r="N13" s="134">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="137">
+      <c r="O13" s="140">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="142">
+      <c r="P13" s="141">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="134">
+      <c r="Q13" s="133">
         <v>-4.93</v>
       </c>
       <c r="R13" s="138">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="143">
+      <c r="S13" s="135">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="144">
+      <c r="T13" s="142">
         <v>-20.66</v>
       </c>
     </row>
@@ -9281,40 +9281,40 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="150">
+      <c r="I14" s="152">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="151">
+      <c r="J14" s="147">
         <v>-5</v>
       </c>
-      <c r="K14" s="154">
+      <c r="K14" s="148">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="145">
+      <c r="L14" s="150">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="146">
+      <c r="M14" s="149">
         <v>-7.37</v>
       </c>
-      <c r="N14" s="147">
+      <c r="N14" s="153">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="155">
+      <c r="O14" s="151">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="152">
+      <c r="P14" s="154">
         <v>-5.63</v>
       </c>
       <c r="Q14" s="156">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="148">
+      <c r="R14" s="155">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="153">
+      <c r="S14" s="145">
         <v>0</v>
       </c>
-      <c r="T14" s="149">
+      <c r="T14" s="146">
         <v>-8.25</v>
       </c>
     </row>
@@ -9343,40 +9343,40 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="165">
+      <c r="I15" s="166">
         <v>9.9</v>
       </c>
-      <c r="J15" s="159">
+      <c r="J15" s="162">
         <v>9.43</v>
       </c>
-      <c r="K15" s="162">
+      <c r="K15" s="157">
         <v>8.82</v>
       </c>
-      <c r="L15" s="167">
+      <c r="L15" s="163">
         <v>4.15</v>
       </c>
-      <c r="M15" s="163">
+      <c r="M15" s="158">
         <v>7.79</v>
       </c>
-      <c r="N15" s="168">
+      <c r="N15" s="159">
         <v>1.3</v>
       </c>
-      <c r="O15" s="166">
+      <c r="O15" s="164">
         <v>8.69</v>
       </c>
       <c r="P15" s="160">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="157">
+      <c r="Q15" s="165">
         <v>5.84</v>
       </c>
-      <c r="R15" s="161">
+      <c r="R15" s="167">
         <v>6.88</v>
       </c>
-      <c r="S15" s="158">
+      <c r="S15" s="161">
         <v>2.34</v>
       </c>
-      <c r="T15" s="164">
+      <c r="T15" s="168">
         <v>-7.35</v>
       </c>
     </row>
@@ -9411,34 +9411,34 @@
       <c r="J16" s="174">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="175">
+      <c r="K16" s="176">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="176">
+      <c r="L16" s="178">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="177">
+      <c r="M16" s="179">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="169">
+      <c r="N16" s="175">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="178">
+      <c r="O16" s="180">
         <v>-4.85</v>
       </c>
-      <c r="P16" s="179">
+      <c r="P16" s="171">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="170">
+      <c r="Q16" s="177">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="171">
+      <c r="R16" s="172">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="180">
+      <c r="S16" s="169">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="172">
+      <c r="T16" s="170">
         <v>-21.15</v>
       </c>
     </row>
@@ -9467,40 +9467,40 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="189">
+      <c r="I17" s="184">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="186">
+      <c r="J17" s="190">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="182">
+      <c r="K17" s="191">
         <v>0.2</v>
       </c>
-      <c r="L17" s="190">
+      <c r="L17" s="192">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="185">
+      <c r="M17" s="181">
         <v>0.53</v>
       </c>
-      <c r="N17" s="191">
+      <c r="N17" s="182">
         <v>3.31</v>
       </c>
       <c r="O17" s="183">
         <v>6.89</v>
       </c>
-      <c r="P17" s="192">
+      <c r="P17" s="186">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="181">
+      <c r="Q17" s="187">
         <v>4.09</v>
       </c>
-      <c r="R17" s="184">
+      <c r="R17" s="188">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="187">
+      <c r="S17" s="185">
         <v>-1.45</v>
       </c>
-      <c r="T17" s="188">
+      <c r="T17" s="189">
         <v>-1.47</v>
       </c>
     </row>
@@ -9529,40 +9529,40 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="201">
+      <c r="I18" s="195">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="199">
+      <c r="J18" s="203">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="194">
+      <c r="K18" s="197">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="202">
+      <c r="L18" s="198">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="196">
+      <c r="M18" s="199">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="197">
+      <c r="N18" s="204">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="203">
+      <c r="O18" s="200">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="200">
+      <c r="P18" s="193">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="204">
+      <c r="Q18" s="196">
         <v>-20.52</v>
       </c>
-      <c r="R18" s="195">
+      <c r="R18" s="201">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="193">
+      <c r="S18" s="194">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="198">
+      <c r="T18" s="202">
         <v>-24.97</v>
       </c>
     </row>
@@ -9591,40 +9591,40 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="212">
+      <c r="I19" s="214">
         <v>1.39</v>
       </c>
-      <c r="J19" s="205">
+      <c r="J19" s="215">
         <v>0.39</v>
       </c>
-      <c r="K19" s="213">
+      <c r="K19" s="216">
         <v>1.93</v>
       </c>
-      <c r="L19" s="206">
+      <c r="L19" s="211">
         <v>3.7</v>
       </c>
-      <c r="M19" s="214">
+      <c r="M19" s="209">
         <v>9.45</v>
       </c>
-      <c r="N19" s="208">
+      <c r="N19" s="207">
         <v>5.75</v>
       </c>
-      <c r="O19" s="209">
+      <c r="O19" s="205">
         <v>12.85</v>
       </c>
-      <c r="P19" s="207">
+      <c r="P19" s="212">
         <v>8.68</v>
       </c>
       <c r="Q19" s="210">
         <v>14.74</v>
       </c>
-      <c r="R19" s="215">
+      <c r="R19" s="208">
         <v>14.89</v>
       </c>
-      <c r="S19" s="216">
+      <c r="S19" s="206">
         <v>9.1</v>
       </c>
-      <c r="T19" s="211">
+      <c r="T19" s="213">
         <v>3.43</v>
       </c>
     </row>
@@ -9662,31 +9662,31 @@
       <c r="K20" s="220">
         <v>2.43</v>
       </c>
-      <c r="L20" s="225">
+      <c r="L20" s="224">
         <v>1.09</v>
       </c>
-      <c r="M20" s="223">
+      <c r="M20" s="225">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="228">
+      <c r="N20" s="221">
         <v>-0.76</v>
       </c>
-      <c r="O20" s="217">
+      <c r="O20" s="228">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="221">
+      <c r="P20" s="222">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="226">
+      <c r="Q20" s="217">
         <v>-7.39</v>
       </c>
       <c r="R20" s="218">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="224">
+      <c r="S20" s="226">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="222">
+      <c r="T20" s="223">
         <v>-8.14</v>
       </c>
     </row>
@@ -9715,40 +9715,40 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="238">
+      <c r="I21" s="239">
         <v>8.65</v>
       </c>
       <c r="J21" s="234">
         <v>9.13</v>
       </c>
-      <c r="K21" s="236">
+      <c r="K21" s="232">
         <v>12.02</v>
       </c>
-      <c r="L21" s="229">
+      <c r="L21" s="237">
         <v>9.13</v>
       </c>
-      <c r="M21" s="239">
+      <c r="M21" s="235">
         <v>12.86</v>
       </c>
-      <c r="N21" s="230">
+      <c r="N21" s="240">
         <v>8.29</v>
       </c>
-      <c r="O21" s="231">
+      <c r="O21" s="229">
         <v>0.36</v>
       </c>
-      <c r="P21" s="232">
+      <c r="P21" s="233">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="237">
+      <c r="Q21" s="230">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="233">
+      <c r="R21" s="231">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="240">
+      <c r="S21" s="236">
         <v>2.04</v>
       </c>
-      <c r="T21" s="235">
+      <c r="T21" s="238">
         <v>-9.86</v>
       </c>
     </row>
@@ -9777,40 +9777,40 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="247">
+      <c r="I22" s="249">
         <v>9.66</v>
       </c>
-      <c r="J22" s="244">
+      <c r="J22" s="243">
         <v>14</v>
       </c>
-      <c r="K22" s="245">
+      <c r="K22" s="246">
         <v>19.72</v>
       </c>
-      <c r="L22" s="248">
+      <c r="L22" s="251">
         <v>17.55</v>
       </c>
-      <c r="M22" s="252">
+      <c r="M22" s="250">
         <v>15.78</v>
       </c>
-      <c r="N22" s="242">
+      <c r="N22" s="247">
         <v>6.9</v>
       </c>
-      <c r="O22" s="243">
+      <c r="O22" s="248">
         <v>0.99</v>
       </c>
-      <c r="P22" s="246">
+      <c r="P22" s="252">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="249">
+      <c r="Q22" s="241">
         <v>8.88</v>
       </c>
-      <c r="R22" s="241">
+      <c r="R22" s="242">
         <v>4.73</v>
       </c>
-      <c r="S22" s="250">
+      <c r="S22" s="244">
         <v>5.92</v>
       </c>
-      <c r="T22" s="251">
+      <c r="T22" s="245">
         <v>-12.23</v>
       </c>
     </row>
@@ -9839,40 +9839,40 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="257">
+      <c r="I23" s="255">
         <v>5.78</v>
       </c>
-      <c r="J23" s="261">
+      <c r="J23" s="253">
         <v>3.91</v>
       </c>
-      <c r="K23" s="262">
+      <c r="K23" s="256">
         <v>6.83</v>
       </c>
-      <c r="L23" s="263">
+      <c r="L23" s="257">
         <v>4.79</v>
       </c>
-      <c r="M23" s="254">
+      <c r="M23" s="261">
         <v>5.08</v>
       </c>
-      <c r="N23" s="258">
+      <c r="N23" s="262">
         <v>4.5</v>
       </c>
-      <c r="O23" s="264">
+      <c r="O23" s="258">
         <v>1.4</v>
       </c>
-      <c r="P23" s="259">
+      <c r="P23" s="263">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="255">
+      <c r="Q23" s="259">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="256">
+      <c r="R23" s="260">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="260">
+      <c r="S23" s="264">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="253">
+      <c r="T23" s="254">
         <v>5.95</v>
       </c>
     </row>
@@ -9901,16 +9901,16 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="271">
+      <c r="I24" s="270">
         <v>-0.93</v>
       </c>
       <c r="J24" s="266">
         <v>-2.54</v>
       </c>
-      <c r="K24" s="267">
+      <c r="K24" s="271">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="270">
+      <c r="L24" s="275">
         <v>-12.46</v>
       </c>
       <c r="M24" s="272">
@@ -9919,19 +9919,19 @@
       <c r="N24" s="268">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="273">
+      <c r="O24" s="276">
         <v>-7.66</v>
       </c>
-      <c r="P24" s="274">
+      <c r="P24" s="273">
         <v>-9.54</v>
       </c>
       <c r="Q24" s="269">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="275">
+      <c r="R24" s="274">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="276">
+      <c r="S24" s="267">
         <v>-17.03</v>
       </c>
       <c r="T24" s="265">
@@ -9963,40 +9963,40 @@
       <c r="H25">
         <v>-1.47</v>
       </c>
-      <c r="I25" s="286">
+      <c r="I25" s="282">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="287">
+      <c r="J25" s="278">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="283">
+      <c r="K25" s="279">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="288">
+      <c r="L25" s="280">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="280">
+      <c r="M25" s="283">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="284">
+      <c r="N25" s="287">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="277">
+      <c r="O25" s="288">
         <v>-11.42</v>
       </c>
       <c r="P25" s="281">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="278">
+      <c r="Q25" s="284">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="279">
+      <c r="R25" s="285">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="285">
+      <c r="S25" s="286">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="282">
+      <c r="T25" s="277">
         <v>-12.52</v>
       </c>
     </row>
@@ -10025,40 +10025,40 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="293">
+      <c r="I26" s="294">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="294">
+      <c r="J26" s="300">
         <v>0.56</v>
       </c>
       <c r="K26" s="289">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="290">
+      <c r="L26" s="295">
         <v>-7.91</v>
       </c>
-      <c r="M26" s="295">
+      <c r="M26" s="296">
         <v>1.36</v>
       </c>
-      <c r="N26" s="298">
+      <c r="N26" s="291">
         <v>3.39</v>
       </c>
-      <c r="O26" s="299">
+      <c r="O26" s="292">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="291">
+      <c r="P26" s="299">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="292">
+      <c r="Q26" s="293">
         <v>7.01</v>
       </c>
-      <c r="R26" s="300">
+      <c r="R26" s="290">
         <v>12.66</v>
       </c>
-      <c r="S26" s="296">
+      <c r="S26" s="297">
         <v>6.55</v>
       </c>
-      <c r="T26" s="297">
+      <c r="T26" s="298">
         <v>-10.28</v>
       </c>
     </row>
@@ -10087,40 +10087,40 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="308">
+      <c r="I27" s="301">
         <v>-1.23</v>
       </c>
-      <c r="J27" s="302">
+      <c r="J27" s="309">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="311">
+      <c r="K27" s="306">
         <v>-6.09</v>
       </c>
       <c r="L27" s="303">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="304">
+      <c r="M27" s="307">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="305">
+      <c r="N27" s="310">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="312">
+      <c r="O27" s="308">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="306">
+      <c r="P27" s="304">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="301">
+      <c r="Q27" s="305">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="309">
+      <c r="R27" s="311">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="310">
+      <c r="S27" s="312">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="307">
+      <c r="T27" s="302">
         <v>-12.1</v>
       </c>
     </row>
@@ -10149,40 +10149,40 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="322">
+      <c r="I28" s="321">
         <v>1.28</v>
       </c>
-      <c r="J28" s="315">
+      <c r="J28" s="314">
         <v>2.92</v>
       </c>
-      <c r="K28" s="316">
+      <c r="K28" s="322">
         <v>4.72</v>
       </c>
-      <c r="L28" s="318">
+      <c r="L28" s="316">
         <v>6.25</v>
       </c>
-      <c r="M28" s="319">
+      <c r="M28" s="315">
         <v>16.86</v>
       </c>
-      <c r="N28" s="320">
+      <c r="N28" s="318">
         <v>13.12</v>
       </c>
-      <c r="O28" s="321">
+      <c r="O28" s="319">
         <v>24.45</v>
       </c>
-      <c r="P28" s="313">
+      <c r="P28" s="320">
         <v>36.9</v>
       </c>
       <c r="Q28" s="323">
         <v>46.03</v>
       </c>
-      <c r="R28" s="317">
+      <c r="R28" s="324">
         <v>45.46</v>
       </c>
-      <c r="S28" s="324">
+      <c r="S28" s="313">
         <v>42.9</v>
       </c>
-      <c r="T28" s="314">
+      <c r="T28" s="317">
         <v>23.63</v>
       </c>
     </row>
@@ -10211,40 +10211,40 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="325">
+      <c r="I29" s="336">
         <v>3.14</v>
       </c>
-      <c r="J29" s="330">
+      <c r="J29" s="325">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="331">
+      <c r="K29" s="333">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="326">
+      <c r="L29" s="331">
         <v>-0.61</v>
       </c>
-      <c r="M29" s="327">
+      <c r="M29" s="326">
         <v>6.71</v>
       </c>
-      <c r="N29" s="336">
+      <c r="N29" s="334">
         <v>3.47</v>
       </c>
-      <c r="O29" s="332">
+      <c r="O29" s="328">
         <v>-0.94</v>
       </c>
-      <c r="P29" s="333">
+      <c r="P29" s="332">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="334">
+      <c r="Q29" s="335">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="335">
+      <c r="R29" s="327">
         <v>0.11</v>
       </c>
-      <c r="S29" s="328">
+      <c r="S29" s="329">
         <v>2.42</v>
       </c>
-      <c r="T29" s="329">
+      <c r="T29" s="330">
         <v>6.88</v>
       </c>
     </row>
@@ -10273,40 +10273,40 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="344">
+      <c r="I30" s="343">
         <v>1.85</v>
       </c>
-      <c r="J30" s="345">
+      <c r="J30" s="338">
         <v>7.78</v>
       </c>
-      <c r="K30" s="346">
+      <c r="K30" s="344">
         <v>13.84</v>
       </c>
-      <c r="L30" s="337">
+      <c r="L30" s="340">
         <v>11.93</v>
       </c>
-      <c r="M30" s="338">
+      <c r="M30" s="345">
         <v>5.23</v>
       </c>
-      <c r="N30" s="347">
+      <c r="N30" s="339">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="348">
+      <c r="O30" s="346">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="339">
+      <c r="P30" s="347">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="340">
+      <c r="Q30" s="341">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="341">
+      <c r="R30" s="337">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="342">
+      <c r="S30" s="348">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="343">
+      <c r="T30" s="342">
         <v>-13.9</v>
       </c>
     </row>
@@ -10335,40 +10335,40 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="358">
+      <c r="I31" s="351">
         <v>1.82</v>
       </c>
       <c r="J31" s="359">
         <v>6.88</v>
       </c>
-      <c r="K31" s="353">
+      <c r="K31" s="349">
         <v>4.25</v>
       </c>
-      <c r="L31" s="350">
+      <c r="L31" s="356">
         <v>1.42</v>
       </c>
-      <c r="M31" s="354">
+      <c r="M31" s="352">
         <v>-7.09</v>
       </c>
-      <c r="N31" s="355">
+      <c r="N31" s="360">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="360">
+      <c r="O31" s="353">
         <v>-10.32</v>
       </c>
-      <c r="P31" s="351">
+      <c r="P31" s="350">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="349">
+      <c r="Q31" s="354">
         <v>-17</v>
       </c>
-      <c r="R31" s="356">
+      <c r="R31" s="355">
         <v>-16.8</v>
       </c>
       <c r="S31" s="357">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="352">
+      <c r="T31" s="358">
         <v>-20.65</v>
       </c>
     </row>
@@ -10397,40 +10397,40 @@
       <c r="H32">
         <v>-1.07</v>
       </c>
-      <c r="I32" s="363">
+      <c r="I32" s="371">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="371">
+      <c r="J32" s="372">
         <v>0.27</v>
       </c>
-      <c r="K32" s="369">
+      <c r="K32" s="366">
         <v>2.99</v>
       </c>
-      <c r="L32" s="370">
+      <c r="L32" s="369">
         <v>2.35</v>
       </c>
-      <c r="M32" s="366">
+      <c r="M32" s="361">
         <v>0.72</v>
       </c>
-      <c r="N32" s="364">
+      <c r="N32" s="362">
         <v>1</v>
       </c>
-      <c r="O32" s="365">
+      <c r="O32" s="363">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="372">
+      <c r="P32" s="368">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="367">
+      <c r="Q32" s="364">
         <v>3.26</v>
       </c>
-      <c r="R32" s="361">
+      <c r="R32" s="365">
         <v>1</v>
       </c>
-      <c r="S32" s="362">
+      <c r="S32" s="370">
         <v>1.45</v>
       </c>
-      <c r="T32" s="368">
+      <c r="T32" s="367">
         <v>7.78</v>
       </c>
     </row>
@@ -10459,40 +10459,40 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="376">
+      <c r="I33" s="383">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="382">
+      <c r="J33" s="374">
         <v>0.57</v>
       </c>
-      <c r="K33" s="377">
+      <c r="K33" s="380">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="374">
+      <c r="L33" s="378">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="378">
+      <c r="M33" s="379">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="383">
+      <c r="N33" s="384">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="380">
+      <c r="O33" s="375">
         <v>-19.47</v>
       </c>
       <c r="P33" s="381">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="384">
+      <c r="Q33" s="382">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="379">
+      <c r="R33" s="373">
         <v>-20.6</v>
       </c>
-      <c r="S33" s="373">
+      <c r="S33" s="376">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="375">
+      <c r="T33" s="377">
         <v>-22.68</v>
       </c>
     </row>
@@ -10521,28 +10521,28 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="396">
+      <c r="I34" s="389">
         <v>-3</v>
       </c>
-      <c r="J34" s="389">
+      <c r="J34" s="390">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="390">
+      <c r="K34" s="385">
         <v>-11.52</v>
       </c>
       <c r="L34" s="393">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="385">
+      <c r="M34" s="386">
         <v>-16.82</v>
       </c>
-      <c r="N34" s="386">
+      <c r="N34" s="391">
         <v>-18.2</v>
       </c>
       <c r="O34" s="394">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="391">
+      <c r="P34" s="388">
         <v>-19.82</v>
       </c>
       <c r="Q34" s="387">
@@ -10554,7 +10554,7 @@
       <c r="S34" s="395">
         <v>-21.43</v>
       </c>
-      <c r="T34" s="388">
+      <c r="T34" s="396">
         <v>-22.12</v>
       </c>
     </row>
@@ -10583,40 +10583,40 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="398">
+      <c r="I35" s="401">
         <v>4.2</v>
       </c>
-      <c r="J35" s="399">
+      <c r="J35" s="403">
         <v>3.72</v>
       </c>
-      <c r="K35" s="406">
+      <c r="K35" s="404">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="407">
+      <c r="L35" s="405">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="405">
+      <c r="M35" s="406">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="400">
+      <c r="N35" s="407">
         <v>6.61</v>
       </c>
-      <c r="O35" s="401">
+      <c r="O35" s="397">
         <v>5.5</v>
       </c>
-      <c r="P35" s="408">
+      <c r="P35" s="399">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="403">
+      <c r="Q35" s="398">
         <v>1.68</v>
       </c>
-      <c r="R35" s="402">
+      <c r="R35" s="400">
         <v>1.37</v>
       </c>
-      <c r="S35" s="404">
+      <c r="S35" s="408">
         <v>0.08</v>
       </c>
-      <c r="T35" s="397">
+      <c r="T35" s="402">
         <v>-0.66</v>
       </c>
     </row>
@@ -10645,31 +10645,31 @@
       <c r="H36">
         <v>-3.03</v>
       </c>
-      <c r="I36" s="409">
+      <c r="I36" s="417">
         <v>5.57</v>
       </c>
-      <c r="J36" s="410">
+      <c r="J36" s="418">
         <v>16.17</v>
       </c>
-      <c r="K36" s="414">
+      <c r="K36" s="419">
         <v>22.01</v>
       </c>
-      <c r="L36" s="418">
+      <c r="L36" s="409">
         <v>16.85</v>
       </c>
-      <c r="M36" s="412">
+      <c r="M36" s="414">
         <v>7.07</v>
       </c>
-      <c r="N36" s="413">
+      <c r="N36" s="410">
         <v>0.27</v>
       </c>
-      <c r="O36" s="419">
+      <c r="O36" s="415">
         <v>2.45</v>
       </c>
-      <c r="P36" s="415">
+      <c r="P36" s="411">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="411">
+      <c r="Q36" s="412">
         <v>-0.27</v>
       </c>
       <c r="R36" s="420">
@@ -10678,7 +10678,7 @@
       <c r="S36" s="416">
         <v>7.47</v>
       </c>
-      <c r="T36" s="417">
+      <c r="T36" s="413">
         <v>3.26</v>
       </c>
     </row>
@@ -10710,37 +10710,37 @@
       <c r="I37" s="430">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="425">
+      <c r="J37" s="424">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="428">
+      <c r="K37" s="431">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="431">
+      <c r="L37" s="427">
         <v>7.57</v>
       </c>
-      <c r="M37" s="432">
+      <c r="M37" s="425">
         <v>5.6</v>
       </c>
-      <c r="N37" s="423">
+      <c r="N37" s="421">
         <v>4.48</v>
       </c>
-      <c r="O37" s="424">
+      <c r="O37" s="428">
         <v>3.32</v>
       </c>
-      <c r="P37" s="429">
+      <c r="P37" s="422">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="426">
+      <c r="Q37" s="432">
         <v>3.78</v>
       </c>
-      <c r="R37" s="427">
+      <c r="R37" s="423">
         <v>8.07</v>
       </c>
-      <c r="S37" s="421">
+      <c r="S37" s="429">
         <v>11.74</v>
       </c>
-      <c r="T37" s="422">
+      <c r="T37" s="426">
         <v>11.74</v>
       </c>
     </row>
@@ -10769,36 +10769,36 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="439">
+      <c r="I38" s="435">
         <v>6.62</v>
       </c>
-      <c r="J38" s="435">
+      <c r="J38" s="439">
         <v>10.07</v>
       </c>
-      <c r="K38" s="436">
+      <c r="K38" s="440">
         <v>6.26</v>
       </c>
-      <c r="L38" s="442">
+      <c r="L38" s="441">
         <v>2.13</v>
       </c>
-      <c r="M38" s="433">
+      <c r="M38" s="442">
         <v>1.41</v>
       </c>
-      <c r="N38" s="440">
+      <c r="N38" s="438">
         <v>7.72</v>
       </c>
-      <c r="O38" s="434">
+      <c r="O38" s="433">
         <v>5.74</v>
       </c>
-      <c r="P38" s="437">
+      <c r="P38" s="436">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="438">
+      <c r="Q38" s="437">
         <v>14.45</v>
       </c>
       <c r="R38" t="str"/>
       <c r="S38" t="str"/>
-      <c r="T38" s="441">
+      <c r="T38" s="434">
         <v>14.45</v>
       </c>
     </row>
@@ -10827,34 +10827,34 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="443">
+      <c r="I39" s="451">
         <v>7.14</v>
       </c>
-      <c r="J39" s="444">
+      <c r="J39" s="448">
         <v>7.82</v>
       </c>
-      <c r="K39" s="445">
+      <c r="K39" s="443">
         <v>7.68</v>
       </c>
-      <c r="L39" s="446">
+      <c r="L39" s="444">
         <v>8.49</v>
       </c>
-      <c r="M39" s="447">
+      <c r="M39" s="446">
         <v>9.43</v>
       </c>
-      <c r="N39" s="450">
+      <c r="N39" s="449">
         <v>5.39</v>
       </c>
-      <c r="O39" s="448">
+      <c r="O39" s="445">
         <v>8.49</v>
       </c>
-      <c r="P39" s="451">
+      <c r="P39" s="450">
         <v>7.28</v>
       </c>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="449">
+      <c r="T39" s="447">
         <v>7.28</v>
       </c>
     </row>
@@ -10937,22 +10937,22 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="461">
+      <c r="I41" s="462">
         <v>0.59</v>
       </c>
-      <c r="J41" s="462">
+      <c r="J41" s="463">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="463">
+      <c r="K41" s="464">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="464">
+      <c r="L41" s="465">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="465">
+      <c r="M41" s="466">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="466">
+      <c r="N41" s="460">
         <v>-7.55</v>
       </c>
       <c r="O41" t="str"/>
@@ -10960,7 +10960,7 @@
       <c r="Q41" t="str"/>
       <c r="R41" t="str"/>
       <c r="S41" t="str"/>
-      <c r="T41" s="460">
+      <c r="T41" s="461">
         <v>-7.55</v>
       </c>
     </row>
@@ -10989,19 +10989,19 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="471">
+      <c r="I42" s="467">
         <v>2.08</v>
       </c>
-      <c r="J42" s="472">
+      <c r="J42" s="468">
         <v>2.7</v>
       </c>
-      <c r="K42" s="467">
+      <c r="K42" s="469">
         <v>0</v>
       </c>
-      <c r="L42" s="468">
+      <c r="L42" s="470">
         <v>1.25</v>
       </c>
-      <c r="M42" s="469">
+      <c r="M42" s="471">
         <v>1.04</v>
       </c>
       <c r="N42" t="str"/>
@@ -11010,7 +11010,7 @@
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="470">
+      <c r="T42" s="472">
         <v>1.04</v>
       </c>
     </row>
@@ -11039,16 +11039,16 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="473">
+      <c r="I43" s="477">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="474">
+      <c r="J43" s="473">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="475">
+      <c r="K43" s="474">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="476">
+      <c r="L43" s="475">
         <v>8.46</v>
       </c>
       <c r="M43" t="str"/>
@@ -11058,7 +11058,7 @@
       <c r="Q43" t="str"/>
       <c r="R43" t="str"/>
       <c r="S43" t="str"/>
-      <c r="T43" s="477">
+      <c r="T43" s="476">
         <v>8.46</v>
       </c>
     </row>
@@ -11087,13 +11087,13 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="478">
+      <c r="I44" s="480">
         <v>10.68</v>
       </c>
-      <c r="J44" s="479">
+      <c r="J44" s="481">
         <v>1.78</v>
       </c>
-      <c r="K44" s="480">
+      <c r="K44" s="478">
         <v>-1.94</v>
       </c>
       <c r="L44" t="str"/>
@@ -11104,7 +11104,7 @@
       <c r="Q44" t="str"/>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="481">
+      <c r="T44" s="479">
         <v>-1.94</v>
       </c>
     </row>
@@ -11133,10 +11133,10 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="482">
+      <c r="I45" s="483">
         <v>2.03</v>
       </c>
-      <c r="J45" s="483">
+      <c r="J45" s="484">
         <v>5.03</v>
       </c>
       <c r="K45" t="str"/>
@@ -11148,7 +11148,7 @@
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="484">
+      <c r="T45" s="482">
         <v>5.03</v>
       </c>
     </row>
@@ -11214,37 +11214,37 @@
       <c r="I47" s="486">
         <v>59.09</v>
       </c>
-      <c r="J47" s="495">
+      <c r="J47" s="494">
         <v>59.09</v>
       </c>
-      <c r="K47" s="490">
+      <c r="K47" s="489">
         <v>51.16</v>
       </c>
-      <c r="L47" s="488">
+      <c r="L47" s="491">
         <v>57.14</v>
       </c>
-      <c r="M47" s="496">
+      <c r="M47" s="492">
         <v>53.66</v>
       </c>
-      <c r="N47" s="491">
+      <c r="N47" s="490">
         <v>55</v>
       </c>
-      <c r="O47" s="489">
+      <c r="O47" s="495">
         <v>41.03</v>
       </c>
-      <c r="P47" s="487">
+      <c r="P47" s="493">
         <v>42.11</v>
       </c>
-      <c r="Q47" s="492">
+      <c r="Q47" s="496">
         <v>40.54</v>
       </c>
-      <c r="R47" s="493">
+      <c r="R47" s="487">
         <v>44.44</v>
       </c>
-      <c r="S47" s="494">
+      <c r="S47" s="485">
         <v>47.22</v>
       </c>
-      <c r="T47" s="485">
+      <c r="T47" s="488">
         <v>38.64</v>
       </c>
     </row>
@@ -11259,40 +11259,40 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="500">
+      <c r="I48" s="502">
         <v>2.15</v>
       </c>
-      <c r="J48" s="501">
+      <c r="J48" s="508">
         <v>2.44</v>
       </c>
-      <c r="K48" s="506">
+      <c r="K48" s="504">
         <v>1.8</v>
       </c>
-      <c r="L48" s="502">
+      <c r="L48" s="503">
         <v>1.15</v>
       </c>
-      <c r="M48" s="507">
+      <c r="M48" s="506">
         <v>1.23</v>
       </c>
-      <c r="N48" s="508">
+      <c r="N48" s="497">
         <v>-0.15</v>
       </c>
-      <c r="O48" s="503">
+      <c r="O48" s="498">
         <v>-0.24</v>
       </c>
-      <c r="P48" s="497">
+      <c r="P48" s="499">
         <v>-0.26</v>
       </c>
-      <c r="Q48" s="504">
+      <c r="Q48" s="507">
         <v>-0.83</v>
       </c>
       <c r="R48" s="505">
         <v>0.03</v>
       </c>
-      <c r="S48" s="498">
+      <c r="S48" s="500">
         <v>0.34</v>
       </c>
-      <c r="T48" s="499">
+      <c r="T48" s="501">
         <v>-4.09</v>
       </c>
     </row>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="510">
+  <fills count="519">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,19 +39,1435 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF98D4A6"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,13 +1479,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,7 +1635,211 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,49 +1851,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,31 +1917,691 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,247 +2613,487 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDB3444"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -435,1531 +3105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
+        <fgColor rgb="FFD83342"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1971,535 +3117,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
+        <fgColor rgb="FFE56B77"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2511,571 +3129,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF87CE97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8A94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5DAB1"/>
+        <fgColor rgb="FFE9F6EC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3086,7 +3140,70 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="509">
+  <borders count="518">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6654,7 +6771,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="509">
+  <cellXfs count="518">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8178,6 +8295,33 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="508" fillId="509" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="509" fillId="510" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="510" fillId="511" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="511" fillId="512" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="512" fillId="513" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="513" fillId="514" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="514" fillId="515" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="515" fillId="516" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="516" fillId="517" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="517" fillId="518" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8537,41 +8681,41 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="7">
         <v>4.95</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="10">
         <v>1.74</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="8">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="11">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="12">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="6">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="4">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="5">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="9">
         <v>-4.59</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="1">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="7">
-        <v>-15.96</v>
+      <c r="T2" s="2">
+        <v>-15.78</v>
       </c>
     </row>
     <row r="3">
@@ -8599,41 +8743,41 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="14">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="24">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="23">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="18">
         <v>0.1</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="19">
         <v>3.32</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="20">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="21">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="15">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="22">
         <v>2.8</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="16">
         <v>1.66</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="17">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="18">
-        <v>20.62</v>
+      <c r="T3" s="13">
+        <v>18.65</v>
       </c>
     </row>
     <row r="4">
@@ -8661,41 +8805,41 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="30">
         <v>4.19</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="31">
         <v>5.08</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="25">
         <v>15.59</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="27">
         <v>27.15</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="32">
         <v>36.04</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="26">
         <v>41.33</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="28">
         <v>37.54</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="35">
         <v>45.14</v>
       </c>
       <c r="Q4" s="29">
         <v>32.33</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="33">
         <v>45.56</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="36">
         <v>56.03</v>
       </c>
-      <c r="T4" s="25">
-        <v>27.06</v>
+      <c r="T4" s="34">
+        <v>25.44</v>
       </c>
     </row>
     <row r="5">
@@ -8723,41 +8867,41 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="47">
         <v>11.97</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="44">
         <v>17.45</v>
       </c>
-      <c r="K5" s="37">
+      <c r="K5" s="41">
         <v>14.27</v>
       </c>
-      <c r="L5" s="38">
+      <c r="L5" s="43">
         <v>17.32</v>
       </c>
-      <c r="M5" s="39">
+      <c r="M5" s="48">
         <v>25.33</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="42">
         <v>21.54</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="45">
         <v>22.72</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="37">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="46">
         <v>17.54</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="38">
         <v>16.88</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="39">
         <v>11.79</v>
       </c>
-      <c r="T5" s="41">
-        <v>16.67</v>
+      <c r="T5" s="40">
+        <v>24.67</v>
       </c>
     </row>
     <row r="6">
@@ -8785,41 +8929,41 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="56">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="49">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="50">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="51">
         <v>-0.66</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="57">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="50">
+      <c r="N6" s="58">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="52">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="49">
+      <c r="P6" s="59">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="51">
+      <c r="Q6" s="53">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="52">
+      <c r="R6" s="54">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="60">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="53">
-        <v>-18.59</v>
+      <c r="T6" s="55">
+        <v>-18.2</v>
       </c>
     </row>
     <row r="7">
@@ -8847,41 +8991,41 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="62">
         <v>-1.99</v>
       </c>
       <c r="J7" s="71">
         <v>1.8</v>
       </c>
-      <c r="K7" s="61">
+      <c r="K7" s="72">
         <v>0.07</v>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="63">
         <v>0.63</v>
       </c>
-      <c r="M7" s="63">
+      <c r="M7" s="64">
         <v>-0.33</v>
       </c>
       <c r="N7" s="69">
         <v>1.55</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="65">
         <v>0.85</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="66">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="70">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="64">
+      <c r="R7" s="61">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="67">
         <v>-6.29</v>
       </c>
       <c r="T7" s="68">
-        <v>4.01</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="8">
@@ -8909,41 +9053,41 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="78">
+      <c r="I8" s="76">
         <v>3.13</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="81">
         <v>5.21</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="74">
         <v>0.43</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="78">
         <v>3.68</v>
       </c>
-      <c r="M8" s="74">
+      <c r="M8" s="79">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="75">
+      <c r="N8" s="77">
         <v>1.66</v>
       </c>
-      <c r="O8" s="76">
+      <c r="O8" s="82">
         <v>1.72</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="83">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="80">
         <v>15.33</v>
       </c>
       <c r="R8" s="84">
         <v>12.57</v>
       </c>
-      <c r="S8" s="77">
+      <c r="S8" s="73">
         <v>23.85</v>
       </c>
-      <c r="T8" s="73">
-        <v>-13.37</v>
+      <c r="T8" s="75">
+        <v>-13.24</v>
       </c>
     </row>
     <row r="9">
@@ -8971,41 +9115,41 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="89">
         <v>1.35</v>
       </c>
-      <c r="J9" s="88">
+      <c r="J9" s="95">
         <v>2.48</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9" s="86">
         <v>1.58</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="90">
         <v>1.35</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="96">
         <v>2.93</v>
       </c>
-      <c r="N9" s="94">
+      <c r="N9" s="91">
         <v>0.23</v>
       </c>
-      <c r="O9" s="89">
+      <c r="O9" s="92">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="90">
+      <c r="P9" s="94">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="86">
+      <c r="Q9" s="85">
         <v>3.83</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="87">
         <v>7.43</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="88">
         <v>17.12</v>
       </c>
-      <c r="T9" s="87">
-        <v>3.15</v>
+      <c r="T9" s="93">
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
@@ -9033,41 +9177,41 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="105">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="97">
+      <c r="J10" s="106">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="108">
         <v>-7.86</v>
       </c>
       <c r="L10" s="103">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="98">
+      <c r="M10" s="107">
         <v>-12.37</v>
       </c>
       <c r="N10" s="104">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="101">
         <v>-9.15</v>
       </c>
-      <c r="P10" s="101">
+      <c r="P10" s="97">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="99">
+      <c r="Q10" s="102">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="100">
+      <c r="R10" s="98">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="102">
+      <c r="S10" s="99">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="108">
-        <v>-10.94</v>
+      <c r="T10" s="100">
+        <v>-12.01</v>
       </c>
     </row>
     <row r="11">
@@ -9095,41 +9239,41 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="115">
+      <c r="I11" s="120">
         <v>7.32</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="110">
         <v>7.76</v>
       </c>
-      <c r="K11" s="109">
+      <c r="K11" s="115">
         <v>15.37</v>
       </c>
-      <c r="L11" s="113">
+      <c r="L11" s="111">
         <v>8.64</v>
       </c>
-      <c r="M11" s="111">
+      <c r="M11" s="112">
         <v>0.59</v>
       </c>
-      <c r="N11" s="116">
+      <c r="N11" s="109">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="110">
+      <c r="O11" s="117">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="114">
+      <c r="P11" s="113">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="117">
+      <c r="Q11" s="118">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="118">
+      <c r="R11" s="119">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="119">
+      <c r="S11" s="114">
         <v>0.15</v>
       </c>
-      <c r="T11" s="112">
-        <v>-21.08</v>
+      <c r="T11" s="116">
+        <v>-21.52</v>
       </c>
     </row>
     <row r="12">
@@ -9157,41 +9301,41 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="131">
         <v>10.48</v>
       </c>
-      <c r="J12" s="127">
+      <c r="J12" s="132">
         <v>13.87</v>
       </c>
-      <c r="K12" s="124">
+      <c r="K12" s="128">
         <v>4.11</v>
       </c>
-      <c r="L12" s="128">
+      <c r="L12" s="121">
         <v>6.13</v>
       </c>
-      <c r="M12" s="125">
+      <c r="M12" s="124">
         <v>9.68</v>
       </c>
-      <c r="N12" s="129">
+      <c r="N12" s="125">
         <v>2.66</v>
       </c>
-      <c r="O12" s="121">
+      <c r="O12" s="129">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="122">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="126">
+      <c r="Q12" s="123">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="130">
+      <c r="R12" s="126">
         <v>0.97</v>
       </c>
-      <c r="S12" s="122">
+      <c r="S12" s="127">
         <v>3.06</v>
       </c>
-      <c r="T12" s="123">
-        <v>-21.53</v>
+      <c r="T12" s="130">
+        <v>-21.13</v>
       </c>
     </row>
     <row r="13">
@@ -9219,41 +9363,41 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="136">
+      <c r="I13" s="133">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="143">
+      <c r="J13" s="137">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="137">
+      <c r="K13" s="135">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="139">
+      <c r="L13" s="141">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="136">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="134">
+      <c r="N13" s="138">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="140">
+      <c r="O13" s="139">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="141">
+      <c r="P13" s="142">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="133">
+      <c r="Q13" s="134">
         <v>-4.93</v>
       </c>
-      <c r="R13" s="138">
+      <c r="R13" s="140">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="135">
+      <c r="S13" s="143">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="142">
-        <v>-20.66</v>
+      <c r="T13" s="144">
+        <v>-17.08</v>
       </c>
     </row>
     <row r="14">
@@ -9281,41 +9425,41 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="152">
+      <c r="I14" s="150">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="147">
+      <c r="J14" s="156">
         <v>-5</v>
       </c>
-      <c r="K14" s="148">
+      <c r="K14" s="151">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="150">
+      <c r="L14" s="152">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="149">
+      <c r="M14" s="147">
         <v>-7.37</v>
       </c>
       <c r="N14" s="153">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="151">
+      <c r="O14" s="154">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="154">
+      <c r="P14" s="145">
         <v>-5.63</v>
       </c>
-      <c r="Q14" s="156">
+      <c r="Q14" s="155">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="155">
+      <c r="R14" s="148">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="145">
+      <c r="S14" s="149">
         <v>0</v>
       </c>
       <c r="T14" s="146">
-        <v>-8.25</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="15">
@@ -9343,41 +9487,41 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="166">
+      <c r="I15" s="161">
         <v>9.9</v>
       </c>
-      <c r="J15" s="162">
+      <c r="J15" s="157">
         <v>9.43</v>
       </c>
-      <c r="K15" s="157">
+      <c r="K15" s="167">
         <v>8.82</v>
       </c>
-      <c r="L15" s="163">
+      <c r="L15" s="159">
         <v>4.15</v>
       </c>
-      <c r="M15" s="158">
+      <c r="M15" s="162">
         <v>7.79</v>
       </c>
-      <c r="N15" s="159">
+      <c r="N15" s="168">
         <v>1.3</v>
       </c>
-      <c r="O15" s="164">
+      <c r="O15" s="163">
         <v>8.69</v>
       </c>
       <c r="P15" s="160">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="165">
+      <c r="Q15" s="164">
         <v>5.84</v>
       </c>
-      <c r="R15" s="167">
+      <c r="R15" s="165">
         <v>6.88</v>
       </c>
-      <c r="S15" s="161">
+      <c r="S15" s="158">
         <v>2.34</v>
       </c>
-      <c r="T15" s="168">
-        <v>-7.35</v>
+      <c r="T15" s="166">
+        <v>-4.33</v>
       </c>
     </row>
     <row r="16">
@@ -9405,41 +9549,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="173">
+      <c r="I16" s="177">
         <v>2.67</v>
       </c>
-      <c r="J16" s="174">
+      <c r="J16" s="170">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="176">
+      <c r="K16" s="172">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="178">
+      <c r="L16" s="175">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="179">
+      <c r="M16" s="173">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="175">
+      <c r="N16" s="171">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="180">
+      <c r="O16" s="178">
         <v>-4.85</v>
       </c>
-      <c r="P16" s="171">
+      <c r="P16" s="179">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="177">
+      <c r="Q16" s="180">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="172">
+      <c r="R16" s="174">
         <v>-10.42</v>
       </c>
       <c r="S16" s="169">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="170">
-        <v>-21.15</v>
+      <c r="T16" s="176">
+        <v>-20.06</v>
       </c>
     </row>
     <row r="17">
@@ -9470,38 +9614,38 @@
       <c r="I17" s="184">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="190">
+      <c r="J17" s="187">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="191">
+      <c r="K17" s="181">
         <v>0.2</v>
       </c>
-      <c r="L17" s="192">
+      <c r="L17" s="185">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="181">
+      <c r="M17" s="188">
         <v>0.53</v>
       </c>
-      <c r="N17" s="182">
+      <c r="N17" s="190">
         <v>3.31</v>
       </c>
-      <c r="O17" s="183">
+      <c r="O17" s="191">
         <v>6.89</v>
       </c>
-      <c r="P17" s="186">
+      <c r="P17" s="189">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="187">
+      <c r="Q17" s="192">
         <v>4.09</v>
       </c>
-      <c r="R17" s="188">
+      <c r="R17" s="182">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="185">
+      <c r="S17" s="186">
         <v>-1.45</v>
       </c>
-      <c r="T17" s="189">
-        <v>-1.47</v>
+      <c r="T17" s="183">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="18">
@@ -9529,41 +9673,41 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="195">
+      <c r="I18" s="198">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="203">
+      <c r="J18" s="194">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="197">
+      <c r="K18" s="203">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="198">
+      <c r="L18" s="201">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="199">
+      <c r="M18" s="195">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="204">
+      <c r="N18" s="199">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="200">
+      <c r="O18" s="196">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="193">
+      <c r="P18" s="197">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="196">
+      <c r="Q18" s="200">
         <v>-20.52</v>
       </c>
-      <c r="R18" s="201">
+      <c r="R18" s="204">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="194">
+      <c r="S18" s="202">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="202">
-        <v>-24.97</v>
+      <c r="T18" s="193">
+        <v>-23.66</v>
       </c>
     </row>
     <row r="19">
@@ -9591,41 +9735,41 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="214">
+      <c r="I19" s="212">
         <v>1.39</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="213">
         <v>0.39</v>
       </c>
-      <c r="K19" s="216">
+      <c r="K19" s="207">
         <v>1.93</v>
       </c>
-      <c r="L19" s="211">
+      <c r="L19" s="214">
         <v>3.7</v>
       </c>
-      <c r="M19" s="209">
+      <c r="M19" s="208">
         <v>9.45</v>
       </c>
-      <c r="N19" s="207">
+      <c r="N19" s="215">
         <v>5.75</v>
       </c>
-      <c r="O19" s="205">
+      <c r="O19" s="216">
         <v>12.85</v>
       </c>
-      <c r="P19" s="212">
+      <c r="P19" s="209">
         <v>8.68</v>
       </c>
       <c r="Q19" s="210">
         <v>14.74</v>
       </c>
-      <c r="R19" s="208">
+      <c r="R19" s="206">
         <v>14.89</v>
       </c>
-      <c r="S19" s="206">
+      <c r="S19" s="205">
         <v>9.1</v>
       </c>
-      <c r="T19" s="213">
-        <v>3.43</v>
+      <c r="T19" s="211">
+        <v>10.53</v>
       </c>
     </row>
     <row r="20">
@@ -9653,41 +9797,41 @@
       <c r="H20">
         <v>-1.89</v>
       </c>
-      <c r="I20" s="227">
+      <c r="I20" s="220">
         <v>1.85</v>
       </c>
-      <c r="J20" s="219">
+      <c r="J20" s="223">
         <v>8.14</v>
       </c>
-      <c r="K20" s="220">
+      <c r="K20" s="226">
         <v>2.43</v>
       </c>
-      <c r="L20" s="224">
+      <c r="L20" s="218">
         <v>1.09</v>
       </c>
-      <c r="M20" s="225">
+      <c r="M20" s="219">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="221">
+      <c r="N20" s="227">
         <v>-0.76</v>
       </c>
-      <c r="O20" s="228">
+      <c r="O20" s="221">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="222">
+      <c r="P20" s="224">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="217">
+      <c r="Q20" s="222">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="218">
+      <c r="R20" s="225">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="226">
+      <c r="S20" s="228">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="223">
-        <v>-8.14</v>
+      <c r="T20" s="217">
+        <v>-4.28</v>
       </c>
     </row>
     <row r="21">
@@ -9715,41 +9859,41 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="239">
+      <c r="I21" s="233">
         <v>8.65</v>
       </c>
-      <c r="J21" s="234">
+      <c r="J21" s="229">
         <v>9.13</v>
       </c>
-      <c r="K21" s="232">
+      <c r="K21" s="234">
         <v>12.02</v>
       </c>
-      <c r="L21" s="237">
+      <c r="L21" s="230">
         <v>9.13</v>
       </c>
-      <c r="M21" s="235">
+      <c r="M21" s="237">
         <v>12.86</v>
       </c>
-      <c r="N21" s="240">
+      <c r="N21" s="238">
         <v>8.29</v>
       </c>
-      <c r="O21" s="229">
+      <c r="O21" s="239">
         <v>0.36</v>
       </c>
-      <c r="P21" s="233">
+      <c r="P21" s="236">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="230">
+      <c r="Q21" s="235">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="231">
+      <c r="R21" s="240">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="236">
+      <c r="S21" s="231">
         <v>2.04</v>
       </c>
-      <c r="T21" s="238">
-        <v>-9.86</v>
+      <c r="T21" s="232">
+        <v>-2.88</v>
       </c>
     </row>
     <row r="22">
@@ -9780,38 +9924,38 @@
       <c r="I22" s="249">
         <v>9.66</v>
       </c>
-      <c r="J22" s="243">
+      <c r="J22" s="248">
         <v>14</v>
       </c>
-      <c r="K22" s="246">
+      <c r="K22" s="252">
         <v>19.72</v>
       </c>
-      <c r="L22" s="251">
+      <c r="L22" s="243">
         <v>17.55</v>
       </c>
-      <c r="M22" s="250">
+      <c r="M22" s="241">
         <v>15.78</v>
       </c>
-      <c r="N22" s="247">
+      <c r="N22" s="244">
         <v>6.9</v>
       </c>
-      <c r="O22" s="248">
+      <c r="O22" s="242">
         <v>0.99</v>
       </c>
-      <c r="P22" s="252">
+      <c r="P22" s="245">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="241">
+      <c r="Q22" s="246">
         <v>8.88</v>
       </c>
-      <c r="R22" s="242">
+      <c r="R22" s="250">
         <v>4.73</v>
       </c>
-      <c r="S22" s="244">
+      <c r="S22" s="251">
         <v>5.92</v>
       </c>
-      <c r="T22" s="245">
-        <v>-12.23</v>
+      <c r="T22" s="247">
+        <v>-8.28</v>
       </c>
     </row>
     <row r="23">
@@ -9839,41 +9983,41 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="255">
+      <c r="I23" s="257">
         <v>5.78</v>
       </c>
-      <c r="J23" s="253">
+      <c r="J23" s="254">
         <v>3.91</v>
       </c>
-      <c r="K23" s="256">
+      <c r="K23" s="258">
         <v>6.83</v>
       </c>
-      <c r="L23" s="257">
+      <c r="L23" s="255">
         <v>4.79</v>
       </c>
-      <c r="M23" s="261">
+      <c r="M23" s="262">
         <v>5.08</v>
       </c>
-      <c r="N23" s="262">
+      <c r="N23" s="259">
         <v>4.5</v>
       </c>
-      <c r="O23" s="258">
+      <c r="O23" s="260">
         <v>1.4</v>
       </c>
       <c r="P23" s="263">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="259">
+      <c r="Q23" s="256">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="260">
+      <c r="R23" s="261">
         <v>-4.9</v>
       </c>
       <c r="S23" s="264">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="254">
-        <v>5.95</v>
+      <c r="T23" s="253">
+        <v>6.07</v>
       </c>
     </row>
     <row r="24">
@@ -9901,41 +10045,41 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="270">
+      <c r="I24" s="267">
         <v>-0.93</v>
       </c>
-      <c r="J24" s="266">
+      <c r="J24" s="273">
         <v>-2.54</v>
       </c>
-      <c r="K24" s="271">
+      <c r="K24" s="268">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="275">
+      <c r="L24" s="269">
         <v>-12.46</v>
       </c>
-      <c r="M24" s="272">
+      <c r="M24" s="275">
         <v>-11.46</v>
       </c>
-      <c r="N24" s="268">
+      <c r="N24" s="276">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="276">
+      <c r="O24" s="274">
         <v>-7.66</v>
       </c>
-      <c r="P24" s="273">
+      <c r="P24" s="265">
         <v>-9.54</v>
       </c>
-      <c r="Q24" s="269">
+      <c r="Q24" s="266">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="274">
+      <c r="R24" s="270">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="267">
+      <c r="S24" s="271">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="265">
-        <v>-10.65</v>
+      <c r="T24" s="272">
+        <v>-10.63</v>
       </c>
     </row>
     <row r="25">
@@ -9963,41 +10107,41 @@
       <c r="H25">
         <v>-1.47</v>
       </c>
-      <c r="I25" s="282">
+      <c r="I25" s="283">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="278">
+      <c r="J25" s="284">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="279">
+      <c r="K25" s="280">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="280">
+      <c r="L25" s="285">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="283">
+      <c r="M25" s="288">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="287">
+      <c r="N25" s="281">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="288">
+      <c r="O25" s="286">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="281">
+      <c r="P25" s="287">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="284">
+      <c r="Q25" s="277">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="285">
+      <c r="R25" s="278">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="286">
+      <c r="S25" s="279">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="277">
-        <v>-12.52</v>
+      <c r="T25" s="282">
+        <v>-11.78</v>
       </c>
     </row>
     <row r="26">
@@ -10025,41 +10169,41 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="294">
+      <c r="I26" s="290">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="300">
+      <c r="J26" s="291">
         <v>0.56</v>
       </c>
-      <c r="K26" s="289">
+      <c r="K26" s="299">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="295">
+      <c r="L26" s="292">
         <v>-7.91</v>
       </c>
-      <c r="M26" s="296">
+      <c r="M26" s="293">
         <v>1.36</v>
       </c>
-      <c r="N26" s="291">
+      <c r="N26" s="298">
         <v>3.39</v>
       </c>
-      <c r="O26" s="292">
+      <c r="O26" s="300">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="299">
+      <c r="P26" s="295">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="293">
+      <c r="Q26" s="296">
         <v>7.01</v>
       </c>
-      <c r="R26" s="290">
+      <c r="R26" s="289">
         <v>12.66</v>
       </c>
       <c r="S26" s="297">
         <v>6.55</v>
       </c>
-      <c r="T26" s="298">
-        <v>-10.28</v>
+      <c r="T26" s="294">
+        <v>-7.46</v>
       </c>
     </row>
     <row r="27">
@@ -10087,41 +10231,41 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="301">
+      <c r="I27" s="308">
         <v>-1.23</v>
       </c>
-      <c r="J27" s="309">
+      <c r="J27" s="302">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="306">
+      <c r="K27" s="303">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="303">
+      <c r="L27" s="309">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="307">
+      <c r="M27" s="312">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="310">
+      <c r="N27" s="304">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="308">
+      <c r="O27" s="301">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="304">
+      <c r="P27" s="310">
         <v>-14.1</v>
       </c>
       <c r="Q27" s="305">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="311">
+      <c r="R27" s="306">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="312">
+      <c r="S27" s="307">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="302">
-        <v>-12.1</v>
+      <c r="T27" s="311">
+        <v>-12.56</v>
       </c>
     </row>
     <row r="28">
@@ -10155,25 +10299,25 @@
       <c r="J28" s="314">
         <v>2.92</v>
       </c>
-      <c r="K28" s="322">
+      <c r="K28" s="317">
         <v>4.72</v>
       </c>
-      <c r="L28" s="316">
+      <c r="L28" s="315">
         <v>6.25</v>
       </c>
-      <c r="M28" s="315">
+      <c r="M28" s="322">
         <v>16.86</v>
       </c>
-      <c r="N28" s="318">
+      <c r="N28" s="323">
         <v>13.12</v>
       </c>
-      <c r="O28" s="319">
+      <c r="O28" s="318">
         <v>24.45</v>
       </c>
-      <c r="P28" s="320">
+      <c r="P28" s="319">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="323">
+      <c r="Q28" s="316">
         <v>46.03</v>
       </c>
       <c r="R28" s="324">
@@ -10182,8 +10326,8 @@
       <c r="S28" s="313">
         <v>42.9</v>
       </c>
-      <c r="T28" s="317">
-        <v>23.63</v>
+      <c r="T28" s="320">
+        <v>30.39</v>
       </c>
     </row>
     <row r="29">
@@ -10211,41 +10355,41 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="336">
+      <c r="I29" s="325">
         <v>3.14</v>
       </c>
-      <c r="J29" s="325">
+      <c r="J29" s="329">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="333">
+      <c r="K29" s="326">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="331">
+      <c r="L29" s="330">
         <v>-0.61</v>
       </c>
-      <c r="M29" s="326">
+      <c r="M29" s="327">
         <v>6.71</v>
       </c>
-      <c r="N29" s="334">
+      <c r="N29" s="332">
         <v>3.47</v>
       </c>
-      <c r="O29" s="328">
+      <c r="O29" s="333">
         <v>-0.94</v>
       </c>
-      <c r="P29" s="332">
+      <c r="P29" s="328">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="335">
+      <c r="Q29" s="334">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="327">
+      <c r="R29" s="331">
         <v>0.11</v>
       </c>
-      <c r="S29" s="329">
+      <c r="S29" s="335">
         <v>2.42</v>
       </c>
-      <c r="T29" s="330">
-        <v>6.88</v>
+      <c r="T29" s="336">
+        <v>9.85</v>
       </c>
     </row>
     <row r="30">
@@ -10273,41 +10417,41 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="343">
+      <c r="I30" s="339">
         <v>1.85</v>
       </c>
-      <c r="J30" s="338">
+      <c r="J30" s="348">
         <v>7.78</v>
       </c>
-      <c r="K30" s="344">
+      <c r="K30" s="340">
         <v>13.84</v>
       </c>
-      <c r="L30" s="340">
+      <c r="L30" s="337">
         <v>11.93</v>
       </c>
-      <c r="M30" s="345">
+      <c r="M30" s="343">
         <v>5.23</v>
       </c>
-      <c r="N30" s="339">
+      <c r="N30" s="344">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="346">
+      <c r="O30" s="345">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="347">
+      <c r="P30" s="341">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="341">
+      <c r="Q30" s="342">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="337">
+      <c r="R30" s="338">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="348">
+      <c r="S30" s="346">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="342">
-        <v>-13.9</v>
+      <c r="T30" s="347">
+        <v>-12.82</v>
       </c>
     </row>
     <row r="31">
@@ -10335,41 +10479,41 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="351">
+      <c r="I31" s="350">
         <v>1.82</v>
       </c>
-      <c r="J31" s="359">
+      <c r="J31" s="353">
         <v>6.88</v>
       </c>
-      <c r="K31" s="349">
+      <c r="K31" s="360">
         <v>4.25</v>
       </c>
-      <c r="L31" s="356">
+      <c r="L31" s="351">
         <v>1.42</v>
       </c>
       <c r="M31" s="352">
         <v>-7.09</v>
       </c>
-      <c r="N31" s="360">
+      <c r="N31" s="354">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="353">
+      <c r="O31" s="355">
         <v>-10.32</v>
       </c>
-      <c r="P31" s="350">
+      <c r="P31" s="356">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="354">
+      <c r="Q31" s="357">
         <v>-17</v>
       </c>
-      <c r="R31" s="355">
+      <c r="R31" s="358">
         <v>-16.8</v>
       </c>
-      <c r="S31" s="357">
+      <c r="S31" s="359">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="358">
-        <v>-20.65</v>
+      <c r="T31" s="349">
+        <v>-19.84</v>
       </c>
     </row>
     <row r="32">
@@ -10397,41 +10541,41 @@
       <c r="H32">
         <v>-1.07</v>
       </c>
-      <c r="I32" s="371">
+      <c r="I32" s="361">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="372">
+      <c r="J32" s="371">
         <v>0.27</v>
       </c>
-      <c r="K32" s="366">
+      <c r="K32" s="363">
         <v>2.99</v>
       </c>
-      <c r="L32" s="369">
+      <c r="L32" s="372">
         <v>2.35</v>
       </c>
-      <c r="M32" s="361">
+      <c r="M32" s="369">
         <v>0.72</v>
       </c>
-      <c r="N32" s="362">
+      <c r="N32" s="364">
         <v>1</v>
       </c>
-      <c r="O32" s="363">
+      <c r="O32" s="365">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="368">
+      <c r="P32" s="362">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="364">
+      <c r="Q32" s="366">
         <v>3.26</v>
       </c>
-      <c r="R32" s="365">
+      <c r="R32" s="367">
         <v>1</v>
       </c>
       <c r="S32" s="370">
         <v>1.45</v>
       </c>
-      <c r="T32" s="367">
-        <v>7.78</v>
+      <c r="T32" s="368">
+        <v>8.6</v>
       </c>
     </row>
     <row r="33">
@@ -10462,38 +10606,38 @@
       <c r="I33" s="383">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="374">
+      <c r="J33" s="373">
         <v>0.57</v>
       </c>
-      <c r="K33" s="380">
+      <c r="K33" s="378">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="378">
+      <c r="L33" s="374">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="379">
+      <c r="M33" s="375">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="384">
+      <c r="N33" s="379">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="375">
+      <c r="O33" s="376">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="381">
+      <c r="P33" s="380">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="382">
+      <c r="Q33" s="384">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="373">
+      <c r="R33" s="381">
         <v>-20.6</v>
       </c>
-      <c r="S33" s="376">
+      <c r="S33" s="377">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="377">
-        <v>-22.68</v>
+      <c r="T33" s="382">
+        <v>-21.17</v>
       </c>
     </row>
     <row r="34">
@@ -10521,41 +10665,41 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="389">
+      <c r="I34" s="385">
         <v>-3</v>
       </c>
-      <c r="J34" s="390">
+      <c r="J34" s="392">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="385">
+      <c r="K34" s="388">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="393">
+      <c r="L34" s="386">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="386">
+      <c r="M34" s="389">
         <v>-16.82</v>
       </c>
-      <c r="N34" s="391">
+      <c r="N34" s="393">
         <v>-18.2</v>
       </c>
       <c r="O34" s="394">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="388">
+      <c r="P34" s="390">
         <v>-19.82</v>
       </c>
-      <c r="Q34" s="387">
+      <c r="Q34" s="395">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="392">
+      <c r="R34" s="396">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="395">
+      <c r="S34" s="387">
         <v>-21.43</v>
       </c>
-      <c r="T34" s="396">
-        <v>-22.12</v>
+      <c r="T34" s="391">
+        <v>-21.43</v>
       </c>
     </row>
     <row r="35">
@@ -10583,41 +10727,41 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="401">
+      <c r="I35" s="403">
         <v>4.2</v>
       </c>
-      <c r="J35" s="403">
+      <c r="J35" s="398">
         <v>3.72</v>
       </c>
       <c r="K35" s="404">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="405">
+      <c r="L35" s="407">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="406">
+      <c r="M35" s="405">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="407">
+      <c r="N35" s="408">
         <v>6.61</v>
       </c>
-      <c r="O35" s="397">
+      <c r="O35" s="400">
         <v>5.5</v>
       </c>
-      <c r="P35" s="399">
+      <c r="P35" s="401">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="398">
+      <c r="Q35" s="402">
         <v>1.68</v>
       </c>
-      <c r="R35" s="400">
+      <c r="R35" s="406">
         <v>1.37</v>
       </c>
-      <c r="S35" s="408">
+      <c r="S35" s="397">
         <v>0.08</v>
       </c>
-      <c r="T35" s="402">
-        <v>-0.66</v>
+      <c r="T35" s="399">
+        <v>0.66</v>
       </c>
     </row>
     <row r="36">
@@ -10645,41 +10789,41 @@
       <c r="H36">
         <v>-3.03</v>
       </c>
-      <c r="I36" s="417">
+      <c r="I36" s="414">
         <v>5.57</v>
       </c>
-      <c r="J36" s="418">
+      <c r="J36" s="420">
         <v>16.17</v>
       </c>
-      <c r="K36" s="419">
+      <c r="K36" s="415">
         <v>22.01</v>
       </c>
-      <c r="L36" s="409">
+      <c r="L36" s="416">
         <v>16.85</v>
       </c>
-      <c r="M36" s="414">
+      <c r="M36" s="409">
         <v>7.07</v>
       </c>
-      <c r="N36" s="410">
+      <c r="N36" s="417">
         <v>0.27</v>
       </c>
-      <c r="O36" s="415">
+      <c r="O36" s="410">
         <v>2.45</v>
       </c>
       <c r="P36" s="411">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="412">
+      <c r="Q36" s="418">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="420">
+      <c r="R36" s="412">
         <v>9.65</v>
       </c>
-      <c r="S36" s="416">
+      <c r="S36" s="413">
         <v>7.47</v>
       </c>
-      <c r="T36" s="413">
-        <v>3.26</v>
+      <c r="T36" s="419">
+        <v>3.4</v>
       </c>
     </row>
     <row r="37">
@@ -10707,41 +10851,41 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="430">
+      <c r="I37" s="432">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="424">
+      <c r="J37" s="430">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="431">
+      <c r="K37" s="428">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="427">
+      <c r="L37" s="421">
         <v>7.57</v>
       </c>
-      <c r="M37" s="425">
+      <c r="M37" s="422">
         <v>5.6</v>
       </c>
-      <c r="N37" s="421">
+      <c r="N37" s="431">
         <v>4.48</v>
       </c>
-      <c r="O37" s="428">
+      <c r="O37" s="429">
         <v>3.32</v>
       </c>
-      <c r="P37" s="422">
+      <c r="P37" s="424">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="432">
+      <c r="Q37" s="425">
         <v>3.78</v>
       </c>
-      <c r="R37" s="423">
+      <c r="R37" s="426">
         <v>8.07</v>
       </c>
-      <c r="S37" s="429">
+      <c r="S37" s="427">
         <v>11.74</v>
       </c>
-      <c r="T37" s="426">
-        <v>11.74</v>
+      <c r="T37" s="423">
+        <v>11.93</v>
       </c>
     </row>
     <row r="38">
@@ -10769,37 +10913,39 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="435">
+      <c r="I38" s="441">
         <v>6.62</v>
       </c>
-      <c r="J38" s="439">
+      <c r="J38" s="433">
         <v>10.07</v>
       </c>
-      <c r="K38" s="440">
+      <c r="K38" s="434">
         <v>6.26</v>
       </c>
-      <c r="L38" s="441">
+      <c r="L38" s="435">
         <v>2.13</v>
       </c>
-      <c r="M38" s="442">
+      <c r="M38" s="439">
         <v>1.41</v>
       </c>
-      <c r="N38" s="438">
+      <c r="N38" s="442">
         <v>7.72</v>
       </c>
-      <c r="O38" s="433">
+      <c r="O38" s="436">
         <v>5.74</v>
       </c>
-      <c r="P38" s="436">
+      <c r="P38" s="443">
         <v>10.77</v>
       </c>
       <c r="Q38" s="437">
         <v>14.45</v>
       </c>
-      <c r="R38" t="str"/>
+      <c r="R38" s="438">
+        <v>18.62</v>
+      </c>
       <c r="S38" t="str"/>
-      <c r="T38" s="434">
-        <v>14.45</v>
+      <c r="T38" s="440">
+        <v>18.62</v>
       </c>
     </row>
     <row r="39">
@@ -10827,35 +10973,37 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="451">
+      <c r="I39" s="449">
         <v>7.14</v>
       </c>
-      <c r="J39" s="448">
+      <c r="J39" s="444">
         <v>7.82</v>
       </c>
-      <c r="K39" s="443">
+      <c r="K39" s="452">
         <v>7.68</v>
       </c>
-      <c r="L39" s="444">
+      <c r="L39" s="447">
         <v>8.49</v>
       </c>
-      <c r="M39" s="446">
+      <c r="M39" s="450">
         <v>9.43</v>
       </c>
-      <c r="N39" s="449">
+      <c r="N39" s="445">
         <v>5.39</v>
       </c>
-      <c r="O39" s="445">
+      <c r="O39" s="446">
         <v>8.49</v>
       </c>
-      <c r="P39" s="450">
+      <c r="P39" s="453">
         <v>7.28</v>
       </c>
-      <c r="Q39" t="str"/>
+      <c r="Q39" s="451">
+        <v>11.99</v>
+      </c>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="447">
-        <v>7.28</v>
+      <c r="T39" s="448">
+        <v>11.99</v>
       </c>
     </row>
     <row r="40">
@@ -10883,16 +11031,16 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="453">
+      <c r="I40" s="455">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="454">
+      <c r="J40" s="460">
         <v>-0.66</v>
       </c>
-      <c r="K40" s="455">
+      <c r="K40" s="456">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="456">
+      <c r="L40" s="461">
         <v>0</v>
       </c>
       <c r="M40" s="457">
@@ -10904,12 +11052,14 @@
       <c r="O40" s="459">
         <v>0</v>
       </c>
-      <c r="P40" t="str"/>
+      <c r="P40" s="462">
+        <v>1.97</v>
+      </c>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="452">
-        <v>0</v>
+      <c r="T40" s="454">
+        <v>1.97</v>
       </c>
     </row>
     <row r="41">
@@ -10937,31 +11087,33 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="462">
+      <c r="I41" s="464">
         <v>0.59</v>
       </c>
-      <c r="J41" s="463">
+      <c r="J41" s="465">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="464">
+      <c r="K41" s="466">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="465">
+      <c r="L41" s="467">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="466">
+      <c r="M41" s="468">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="460">
+      <c r="N41" s="469">
         <v>-7.55</v>
       </c>
-      <c r="O41" t="str"/>
+      <c r="O41" s="470">
+        <v>-6.76</v>
+      </c>
       <c r="P41" t="str"/>
       <c r="Q41" t="str"/>
       <c r="R41" t="str"/>
       <c r="S41" t="str"/>
-      <c r="T41" s="461">
-        <v>-7.55</v>
+      <c r="T41" s="463">
+        <v>-6.76</v>
       </c>
     </row>
     <row r="42">
@@ -10989,29 +11141,31 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="467">
+      <c r="I42" s="476">
         <v>2.08</v>
       </c>
-      <c r="J42" s="468">
+      <c r="J42" s="477">
         <v>2.7</v>
       </c>
-      <c r="K42" s="469">
+      <c r="K42" s="471">
         <v>0</v>
       </c>
-      <c r="L42" s="470">
+      <c r="L42" s="472">
         <v>1.25</v>
       </c>
-      <c r="M42" s="471">
+      <c r="M42" s="473">
         <v>1.04</v>
       </c>
-      <c r="N42" t="str"/>
+      <c r="N42" s="474">
+        <v>1.56</v>
+      </c>
       <c r="O42" t="str"/>
       <c r="P42" t="str"/>
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="472">
-        <v>1.04</v>
+      <c r="T42" s="475">
+        <v>1.56</v>
       </c>
     </row>
     <row r="43">
@@ -11039,27 +11193,29 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="477">
+      <c r="I43" s="479">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="473">
+      <c r="J43" s="480">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="474">
+      <c r="K43" s="481">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="475">
+      <c r="L43" s="482">
         <v>8.46</v>
       </c>
-      <c r="M43" t="str"/>
+      <c r="M43" s="483">
+        <v>10.98</v>
+      </c>
       <c r="N43" t="str"/>
       <c r="O43" t="str"/>
       <c r="P43" t="str"/>
       <c r="Q43" t="str"/>
       <c r="R43" t="str"/>
       <c r="S43" t="str"/>
-      <c r="T43" s="476">
-        <v>8.46</v>
+      <c r="T43" s="478">
+        <v>10.98</v>
       </c>
     </row>
     <row r="44">
@@ -11087,16 +11243,18 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="480">
+      <c r="I44" s="487">
         <v>10.68</v>
       </c>
-      <c r="J44" s="481">
+      <c r="J44" s="488">
         <v>1.78</v>
       </c>
-      <c r="K44" s="478">
+      <c r="K44" s="484">
         <v>-1.94</v>
       </c>
-      <c r="L44" t="str"/>
+      <c r="L44" s="485">
+        <v>3.72</v>
+      </c>
       <c r="M44" t="str"/>
       <c r="N44" t="str"/>
       <c r="O44" t="str"/>
@@ -11104,8 +11262,8 @@
       <c r="Q44" t="str"/>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="479">
-        <v>-1.94</v>
+      <c r="T44" s="486">
+        <v>3.72</v>
       </c>
     </row>
     <row r="45">
@@ -11133,13 +11291,15 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="483">
+      <c r="I45" s="490">
         <v>2.03</v>
       </c>
-      <c r="J45" s="484">
+      <c r="J45" s="491">
         <v>5.03</v>
       </c>
-      <c r="K45" t="str"/>
+      <c r="K45" s="492">
+        <v>5.82</v>
+      </c>
       <c r="L45" t="str"/>
       <c r="M45" t="str"/>
       <c r="N45" t="str"/>
@@ -11148,61 +11308,53 @@
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="482">
-        <v>5.03</v>
+      <c r="T45" s="489">
+        <v>5.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B46" t="str"/>
-      <c r="C46" t="str"/>
-      <c r="D46" t="str"/>
-      <c r="E46" t="str"/>
-      <c r="F46" t="str"/>
-      <c r="G46" t="str"/>
-      <c r="H46" t="str"/>
-      <c r="I46">
-        <v>44</v>
-      </c>
-      <c r="J46">
-        <v>44</v>
-      </c>
-      <c r="K46">
-        <v>43</v>
-      </c>
-      <c r="L46">
-        <v>42</v>
-      </c>
-      <c r="M46">
-        <v>41</v>
-      </c>
-      <c r="N46">
-        <v>40</v>
-      </c>
-      <c r="O46">
-        <v>39</v>
-      </c>
-      <c r="P46">
-        <v>38</v>
-      </c>
-      <c r="Q46">
-        <v>37</v>
-      </c>
-      <c r="R46">
-        <v>36</v>
-      </c>
-      <c r="S46">
-        <v>36</v>
-      </c>
-      <c r="T46">
-        <v>44</v>
-      </c>
+        <v>2026-04-20</v>
+      </c>
+      <c r="B46" t="str">
+        <v>海特高新</v>
+      </c>
+      <c r="C46" t="str">
+        <v>002023</v>
+      </c>
+      <c r="D46" t="str">
+        <v>(09:27:00)加入光，跑步进场海特高新</v>
+      </c>
+      <c r="E46">
+        <v>12.81</v>
+      </c>
+      <c r="F46">
+        <v>13.04</v>
+      </c>
+      <c r="G46">
+        <v>12.81</v>
+      </c>
+      <c r="H46">
+        <v>-0.93</v>
+      </c>
+      <c r="I46" s="493">
+        <v>1.8</v>
+      </c>
+      <c r="J46" t="str"/>
+      <c r="K46" t="str"/>
+      <c r="L46" t="str"/>
+      <c r="M46" t="str"/>
+      <c r="N46" t="str"/>
+      <c r="O46" t="str"/>
+      <c r="P46" t="str"/>
+      <c r="Q46" t="str"/>
+      <c r="R46" t="str"/>
+      <c r="S46" t="str"/>
+      <c r="T46" t="str"/>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B47" t="str"/>
       <c r="C47" t="str"/>
@@ -11211,46 +11363,46 @@
       <c r="F47" t="str"/>
       <c r="G47" t="str"/>
       <c r="H47" t="str"/>
-      <c r="I47" s="486">
-        <v>59.09</v>
-      </c>
-      <c r="J47" s="494">
-        <v>59.09</v>
-      </c>
-      <c r="K47" s="489">
-        <v>51.16</v>
-      </c>
-      <c r="L47" s="491">
-        <v>57.14</v>
-      </c>
-      <c r="M47" s="492">
-        <v>53.66</v>
-      </c>
-      <c r="N47" s="490">
-        <v>55</v>
-      </c>
-      <c r="O47" s="495">
-        <v>41.03</v>
-      </c>
-      <c r="P47" s="493">
-        <v>42.11</v>
-      </c>
-      <c r="Q47" s="496">
-        <v>40.54</v>
-      </c>
-      <c r="R47" s="487">
-        <v>44.44</v>
-      </c>
-      <c r="S47" s="485">
-        <v>47.22</v>
-      </c>
-      <c r="T47" s="488">
-        <v>38.64</v>
+      <c r="I47">
+        <v>45</v>
+      </c>
+      <c r="J47">
+        <v>44</v>
+      </c>
+      <c r="K47">
+        <v>44</v>
+      </c>
+      <c r="L47">
+        <v>43</v>
+      </c>
+      <c r="M47">
+        <v>42</v>
+      </c>
+      <c r="N47">
+        <v>41</v>
+      </c>
+      <c r="O47">
+        <v>40</v>
+      </c>
+      <c r="P47">
+        <v>39</v>
+      </c>
+      <c r="Q47">
+        <v>38</v>
+      </c>
+      <c r="R47">
+        <v>37</v>
+      </c>
+      <c r="S47">
+        <v>36</v>
+      </c>
+      <c r="T47">
+        <v>44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B48" t="str"/>
       <c r="C48" t="str"/>
@@ -11259,41 +11411,89 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="502">
+      <c r="I48" s="500">
+        <v>60</v>
+      </c>
+      <c r="J48" s="503">
+        <v>59.09</v>
+      </c>
+      <c r="K48" s="496">
+        <v>52.27</v>
+      </c>
+      <c r="L48" s="504">
+        <v>58.14</v>
+      </c>
+      <c r="M48" s="497">
+        <v>54.76</v>
+      </c>
+      <c r="N48" s="498">
+        <v>56.1</v>
+      </c>
+      <c r="O48" s="501">
+        <v>40</v>
+      </c>
+      <c r="P48" s="505">
+        <v>43.59</v>
+      </c>
+      <c r="Q48" s="494">
+        <v>42.11</v>
+      </c>
+      <c r="R48" s="495">
+        <v>45.95</v>
+      </c>
+      <c r="S48" s="499">
+        <v>47.22</v>
+      </c>
+      <c r="T48" s="502">
+        <v>45.45</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B49" t="str"/>
+      <c r="C49" t="str"/>
+      <c r="D49" t="str"/>
+      <c r="E49" t="str"/>
+      <c r="F49" t="str"/>
+      <c r="G49" t="str"/>
+      <c r="H49" t="str"/>
+      <c r="I49" s="512">
         <v>2.15</v>
       </c>
-      <c r="J48" s="508">
+      <c r="J49" s="517">
         <v>2.44</v>
       </c>
-      <c r="K48" s="504">
-        <v>1.8</v>
-      </c>
-      <c r="L48" s="503">
-        <v>1.15</v>
-      </c>
-      <c r="M48" s="506">
-        <v>1.23</v>
-      </c>
-      <c r="N48" s="497">
-        <v>-0.15</v>
-      </c>
-      <c r="O48" s="498">
-        <v>-0.24</v>
-      </c>
-      <c r="P48" s="499">
-        <v>-0.26</v>
-      </c>
-      <c r="Q48" s="507">
-        <v>-0.83</v>
-      </c>
-      <c r="R48" s="505">
-        <v>0.03</v>
-      </c>
-      <c r="S48" s="500">
+      <c r="K49" s="513">
+        <v>1.89</v>
+      </c>
+      <c r="L49" s="508">
+        <v>1.21</v>
+      </c>
+      <c r="M49" s="514">
+        <v>1.46</v>
+      </c>
+      <c r="N49" s="515">
+        <v>-0.11</v>
+      </c>
+      <c r="O49" s="506">
+        <v>-0.41</v>
+      </c>
+      <c r="P49" s="516">
+        <v>-0.2</v>
+      </c>
+      <c r="Q49" s="507">
+        <v>-0.49</v>
+      </c>
+      <c r="R49" s="510">
+        <v>0.53</v>
+      </c>
+      <c r="S49" s="511">
         <v>0.34</v>
       </c>
-      <c r="T48" s="501">
-        <v>-4.09</v>
+      <c r="T49" s="509">
+        <v>-2.31</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -45,6 +45,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -57,7 +93,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,13 +111,1537 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF0DF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF45B35E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,25 +1653,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,31 +1791,829 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE4E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,31 +2625,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,12 +2643,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -213,7 +2679,295 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,199 +2979,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9EA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55B96C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD6AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B77"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -429,1123 +3105,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD83342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1557,1585 +3135,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8681,40 +8681,40 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="2">
         <v>4.95</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="9">
         <v>-0.37</v>
       </c>
       <c r="K2" s="10">
         <v>1.74</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="3">
         <v>-0.92</v>
       </c>
       <c r="M2" s="11">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="6">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="7">
         <v>-4.31</v>
       </c>
       <c r="P2" s="4">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="12">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="5">
         <v>-4.59</v>
       </c>
       <c r="S2" s="1">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="8">
         <v>-15.78</v>
       </c>
     </row>
@@ -8746,37 +8746,37 @@
       <c r="I3" s="14">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="15">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="19">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="23">
         <v>0.1</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="16">
         <v>3.32</v>
       </c>
       <c r="N3" s="20">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="17">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="24">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3" s="13">
         <v>2.8</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="21">
         <v>1.66</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="22">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="13">
+      <c r="T3" s="18">
         <v>18.65</v>
       </c>
     </row>
@@ -8805,40 +8805,40 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="26">
         <v>4.19</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="34">
         <v>5.08</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="27">
         <v>15.59</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="28">
         <v>27.15</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="33">
         <v>36.04</v>
       </c>
-      <c r="N4" s="26">
+      <c r="N4" s="35">
         <v>41.33</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="29">
         <v>37.54</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="36">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="30">
         <v>32.33</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="31">
         <v>45.56</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="32">
         <v>56.03</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="25">
         <v>25.44</v>
       </c>
     </row>
@@ -8867,40 +8867,40 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="37">
         <v>11.97</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="38">
         <v>17.45</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="40">
         <v>14.27</v>
       </c>
       <c r="L5" s="43">
         <v>17.32</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="44">
         <v>25.33</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="46">
         <v>21.54</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="47">
         <v>22.72</v>
       </c>
-      <c r="P5" s="37">
+      <c r="P5" s="41">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="39">
         <v>17.54</v>
       </c>
-      <c r="R5" s="38">
+      <c r="R5" s="42">
         <v>16.88</v>
       </c>
-      <c r="S5" s="39">
+      <c r="S5" s="45">
         <v>11.79</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="48">
         <v>24.67</v>
       </c>
     </row>
@@ -8929,40 +8929,40 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="59">
         <v>-0.02</v>
       </c>
       <c r="J6" s="49">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="50">
+      <c r="K6" s="54">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="51">
+      <c r="L6" s="56">
         <v>-0.66</v>
       </c>
       <c r="M6" s="57">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="50">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="52">
+      <c r="O6" s="60">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="51">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="52">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="55">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="58">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="55">
+      <c r="T6" s="53">
         <v>-18.2</v>
       </c>
     </row>
@@ -8991,40 +8991,40 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="62">
+      <c r="I7" s="64">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="70">
         <v>1.8</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="71">
         <v>0.07</v>
       </c>
-      <c r="L7" s="63">
+      <c r="L7" s="61">
         <v>0.63</v>
       </c>
-      <c r="M7" s="64">
+      <c r="M7" s="65">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="66">
         <v>1.55</v>
       </c>
-      <c r="O7" s="65">
+      <c r="O7" s="72">
         <v>0.85</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="62">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="67">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="61">
+      <c r="R7" s="63">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="68">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="68">
+      <c r="T7" s="69">
         <v>4.78</v>
       </c>
     </row>
@@ -9053,40 +9053,40 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="76">
+      <c r="I8" s="82">
         <v>3.13</v>
       </c>
-      <c r="J8" s="81">
+      <c r="J8" s="77">
         <v>5.21</v>
       </c>
-      <c r="K8" s="74">
+      <c r="K8" s="80">
         <v>0.43</v>
       </c>
-      <c r="L8" s="78">
+      <c r="L8" s="74">
         <v>3.68</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="83">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="77">
+      <c r="N8" s="75">
         <v>1.66</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="78">
         <v>1.72</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="84">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="76">
         <v>15.33</v>
       </c>
-      <c r="R8" s="84">
+      <c r="R8" s="73">
         <v>12.57</v>
       </c>
-      <c r="S8" s="73">
+      <c r="S8" s="81">
         <v>23.85</v>
       </c>
-      <c r="T8" s="75">
+      <c r="T8" s="79">
         <v>-13.24</v>
       </c>
     </row>
@@ -9115,37 +9115,37 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="89">
+      <c r="I9" s="85">
         <v>1.35</v>
       </c>
-      <c r="J9" s="95">
+      <c r="J9" s="90">
         <v>2.48</v>
       </c>
       <c r="K9" s="86">
         <v>1.58</v>
       </c>
-      <c r="L9" s="90">
+      <c r="L9" s="91">
         <v>1.35</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="94">
         <v>2.93</v>
       </c>
-      <c r="N9" s="91">
+      <c r="N9" s="95">
         <v>0.23</v>
       </c>
       <c r="O9" s="92">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="87">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="85">
+      <c r="Q9" s="88">
         <v>3.83</v>
       </c>
-      <c r="R9" s="87">
+      <c r="R9" s="96">
         <v>7.43</v>
       </c>
-      <c r="S9" s="88">
+      <c r="S9" s="89">
         <v>17.12</v>
       </c>
       <c r="T9" s="93">
@@ -9177,40 +9177,40 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="98">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="101">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="105">
         <v>-7.86</v>
       </c>
-      <c r="L10" s="103">
+      <c r="L10" s="102">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="103">
         <v>-12.37</v>
       </c>
       <c r="N10" s="104">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="101">
+      <c r="O10" s="106">
         <v>-9.15</v>
       </c>
-      <c r="P10" s="97">
+      <c r="P10" s="99">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="102">
+      <c r="Q10" s="100">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="98">
+      <c r="R10" s="107">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="99">
+      <c r="S10" s="108">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="100">
+      <c r="T10" s="97">
         <v>-12.01</v>
       </c>
     </row>
@@ -9239,10 +9239,10 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="110">
         <v>7.32</v>
       </c>
-      <c r="J11" s="110">
+      <c r="J11" s="117">
         <v>7.76</v>
       </c>
       <c r="K11" s="115">
@@ -9251,28 +9251,28 @@
       <c r="L11" s="111">
         <v>8.64</v>
       </c>
-      <c r="M11" s="112">
+      <c r="M11" s="118">
         <v>0.59</v>
       </c>
-      <c r="N11" s="109">
+      <c r="N11" s="114">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="117">
+      <c r="O11" s="112">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="113">
+      <c r="P11" s="119">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="118">
+      <c r="Q11" s="116">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="119">
+      <c r="R11" s="120">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="114">
+      <c r="S11" s="109">
         <v>0.15</v>
       </c>
-      <c r="T11" s="116">
+      <c r="T11" s="113">
         <v>-21.52</v>
       </c>
     </row>
@@ -9301,40 +9301,40 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="125">
         <v>10.48</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="126">
         <v>13.87</v>
       </c>
-      <c r="K12" s="128">
+      <c r="K12" s="127">
         <v>4.11</v>
       </c>
-      <c r="L12" s="121">
+      <c r="L12" s="132">
         <v>6.13</v>
       </c>
-      <c r="M12" s="124">
+      <c r="M12" s="121">
         <v>9.68</v>
       </c>
-      <c r="N12" s="125">
+      <c r="N12" s="122">
         <v>2.66</v>
       </c>
-      <c r="O12" s="129">
+      <c r="O12" s="123">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="122">
+      <c r="P12" s="131">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="123">
+      <c r="Q12" s="128">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="126">
+      <c r="R12" s="129">
         <v>0.97</v>
       </c>
-      <c r="S12" s="127">
+      <c r="S12" s="130">
         <v>3.06</v>
       </c>
-      <c r="T12" s="130">
+      <c r="T12" s="124">
         <v>-21.13</v>
       </c>
     </row>
@@ -9363,40 +9363,40 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="133">
+      <c r="I13" s="136">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="137">
+      <c r="J13" s="142">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="135">
+      <c r="K13" s="137">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="141">
+      <c r="L13" s="138">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="136">
+      <c r="M13" s="140">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="138">
+      <c r="N13" s="143">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="139">
+      <c r="O13" s="144">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="142">
+      <c r="P13" s="133">
         <v>-11.98</v>
       </c>
       <c r="Q13" s="134">
         <v>-4.93</v>
       </c>
-      <c r="R13" s="140">
+      <c r="R13" s="135">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="143">
+      <c r="S13" s="141">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="144">
+      <c r="T13" s="139">
         <v>-17.08</v>
       </c>
     </row>
@@ -9425,40 +9425,40 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="150">
+      <c r="I14" s="156">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="156">
+      <c r="J14" s="145">
         <v>-5</v>
       </c>
-      <c r="K14" s="151">
+      <c r="K14" s="152">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="152">
+      <c r="L14" s="153">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="147">
+      <c r="M14" s="146">
         <v>-7.37</v>
       </c>
-      <c r="N14" s="153">
+      <c r="N14" s="147">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="154">
+      <c r="O14" s="148">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="145">
+      <c r="P14" s="154">
         <v>-5.63</v>
       </c>
-      <c r="Q14" s="155">
+      <c r="Q14" s="149">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="148">
+      <c r="R14" s="155">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="149">
+      <c r="S14" s="151">
         <v>0</v>
       </c>
-      <c r="T14" s="146">
+      <c r="T14" s="150">
         <v>-7</v>
       </c>
     </row>
@@ -9487,40 +9487,40 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="161">
+      <c r="I15" s="165">
         <v>9.9</v>
       </c>
-      <c r="J15" s="157">
+      <c r="J15" s="160">
         <v>9.43</v>
       </c>
-      <c r="K15" s="167">
+      <c r="K15" s="166">
         <v>8.82</v>
       </c>
-      <c r="L15" s="159">
+      <c r="L15" s="158">
         <v>4.15</v>
       </c>
-      <c r="M15" s="162">
+      <c r="M15" s="167">
         <v>7.79</v>
       </c>
-      <c r="N15" s="168">
+      <c r="N15" s="161">
         <v>1.3</v>
       </c>
-      <c r="O15" s="163">
+      <c r="O15" s="162">
         <v>8.69</v>
       </c>
-      <c r="P15" s="160">
+      <c r="P15" s="159">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="164">
+      <c r="Q15" s="168">
         <v>5.84</v>
       </c>
-      <c r="R15" s="165">
+      <c r="R15" s="163">
         <v>6.88</v>
       </c>
-      <c r="S15" s="158">
+      <c r="S15" s="157">
         <v>2.34</v>
       </c>
-      <c r="T15" s="166">
+      <c r="T15" s="164">
         <v>-4.33</v>
       </c>
     </row>
@@ -9549,40 +9549,40 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="177">
+      <c r="I16" s="174">
         <v>2.67</v>
       </c>
-      <c r="J16" s="170">
+      <c r="J16" s="169">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="172">
+      <c r="K16" s="179">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="175">
+      <c r="L16" s="178">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="173">
+      <c r="M16" s="175">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="171">
+      <c r="N16" s="170">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="178">
+      <c r="O16" s="171">
         <v>-4.85</v>
       </c>
-      <c r="P16" s="179">
+      <c r="P16" s="176">
         <v>-7.82</v>
       </c>
       <c r="Q16" s="180">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="174">
+      <c r="R16" s="172">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="169">
+      <c r="S16" s="177">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="176">
+      <c r="T16" s="173">
         <v>-20.06</v>
       </c>
     </row>
@@ -9611,40 +9611,40 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="184">
+      <c r="I17" s="189">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="187">
+      <c r="J17" s="181">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="181">
+      <c r="K17" s="185">
         <v>0.2</v>
       </c>
-      <c r="L17" s="185">
+      <c r="L17" s="190">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="188">
+      <c r="M17" s="191">
         <v>0.53</v>
       </c>
-      <c r="N17" s="190">
+      <c r="N17" s="186">
         <v>3.31</v>
       </c>
-      <c r="O17" s="191">
+      <c r="O17" s="182">
         <v>6.89</v>
       </c>
-      <c r="P17" s="189">
+      <c r="P17" s="183">
         <v>6.36</v>
       </c>
       <c r="Q17" s="192">
         <v>4.09</v>
       </c>
-      <c r="R17" s="182">
+      <c r="R17" s="187">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="186">
+      <c r="S17" s="184">
         <v>-1.45</v>
       </c>
-      <c r="T17" s="183">
+      <c r="T17" s="188">
         <v>-0.84</v>
       </c>
     </row>
@@ -9673,40 +9673,40 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="198">
+      <c r="I18" s="199">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="194">
+      <c r="J18" s="193">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="203">
+      <c r="K18" s="194">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="201">
+      <c r="L18" s="200">
         <v>-11.63</v>
       </c>
       <c r="M18" s="195">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="199">
+      <c r="N18" s="201">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="196">
+      <c r="O18" s="202">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="197">
+      <c r="P18" s="203">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="200">
+      <c r="Q18" s="198">
         <v>-20.52</v>
       </c>
       <c r="R18" s="204">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="202">
+      <c r="S18" s="196">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="193">
+      <c r="T18" s="197">
         <v>-23.66</v>
       </c>
     </row>
@@ -9735,37 +9735,37 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="212">
+      <c r="I19" s="209">
         <v>1.39</v>
       </c>
       <c r="J19" s="213">
         <v>0.39</v>
       </c>
-      <c r="K19" s="207">
+      <c r="K19" s="205">
         <v>1.93</v>
       </c>
       <c r="L19" s="214">
         <v>3.7</v>
       </c>
-      <c r="M19" s="208">
+      <c r="M19" s="206">
         <v>9.45</v>
       </c>
-      <c r="N19" s="215">
+      <c r="N19" s="210">
         <v>5.75</v>
       </c>
-      <c r="O19" s="216">
+      <c r="O19" s="215">
         <v>12.85</v>
       </c>
-      <c r="P19" s="209">
+      <c r="P19" s="216">
         <v>8.68</v>
       </c>
-      <c r="Q19" s="210">
+      <c r="Q19" s="207">
         <v>14.74</v>
       </c>
-      <c r="R19" s="206">
+      <c r="R19" s="208">
         <v>14.89</v>
       </c>
-      <c r="S19" s="205">
+      <c r="S19" s="212">
         <v>9.1</v>
       </c>
       <c r="T19" s="211">
@@ -9797,40 +9797,40 @@
       <c r="H20">
         <v>-1.89</v>
       </c>
-      <c r="I20" s="220">
+      <c r="I20" s="219">
         <v>1.85</v>
       </c>
-      <c r="J20" s="223">
+      <c r="J20" s="228">
         <v>8.14</v>
       </c>
-      <c r="K20" s="226">
+      <c r="K20" s="227">
         <v>2.43</v>
       </c>
-      <c r="L20" s="218">
+      <c r="L20" s="220">
         <v>1.09</v>
       </c>
-      <c r="M20" s="219">
+      <c r="M20" s="225">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="227">
+      <c r="N20" s="217">
         <v>-0.76</v>
       </c>
       <c r="O20" s="221">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="224">
+      <c r="P20" s="218">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="222">
+      <c r="Q20" s="226">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="225">
+      <c r="R20" s="222">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="228">
+      <c r="S20" s="223">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="217">
+      <c r="T20" s="224">
         <v>-4.28</v>
       </c>
     </row>
@@ -9859,40 +9859,40 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="233">
+      <c r="I21" s="237">
         <v>8.65</v>
       </c>
-      <c r="J21" s="229">
+      <c r="J21" s="233">
         <v>9.13</v>
       </c>
-      <c r="K21" s="234">
+      <c r="K21" s="229">
         <v>12.02</v>
       </c>
       <c r="L21" s="230">
         <v>9.13</v>
       </c>
-      <c r="M21" s="237">
+      <c r="M21" s="231">
         <v>12.86</v>
       </c>
       <c r="N21" s="238">
         <v>8.29</v>
       </c>
-      <c r="O21" s="239">
+      <c r="O21" s="240">
         <v>0.36</v>
       </c>
-      <c r="P21" s="236">
+      <c r="P21" s="234">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="235">
+      <c r="Q21" s="232">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="240">
+      <c r="R21" s="235">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="231">
+      <c r="S21" s="239">
         <v>2.04</v>
       </c>
-      <c r="T21" s="232">
+      <c r="T21" s="236">
         <v>-2.88</v>
       </c>
     </row>
@@ -9921,40 +9921,40 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="249">
+      <c r="I22" s="246">
         <v>9.66</v>
       </c>
-      <c r="J22" s="248">
+      <c r="J22" s="247">
         <v>14</v>
       </c>
-      <c r="K22" s="252">
+      <c r="K22" s="250">
         <v>19.72</v>
       </c>
-      <c r="L22" s="243">
+      <c r="L22" s="248">
         <v>17.55</v>
       </c>
-      <c r="M22" s="241">
+      <c r="M22" s="251">
         <v>15.78</v>
       </c>
-      <c r="N22" s="244">
+      <c r="N22" s="243">
         <v>6.9</v>
       </c>
-      <c r="O22" s="242">
+      <c r="O22" s="252">
         <v>0.99</v>
       </c>
-      <c r="P22" s="245">
+      <c r="P22" s="244">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="246">
+      <c r="Q22" s="241">
         <v>8.88</v>
       </c>
-      <c r="R22" s="250">
+      <c r="R22" s="245">
         <v>4.73</v>
       </c>
-      <c r="S22" s="251">
+      <c r="S22" s="249">
         <v>5.92</v>
       </c>
-      <c r="T22" s="247">
+      <c r="T22" s="242">
         <v>-8.28</v>
       </c>
     </row>
@@ -9983,19 +9983,19 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="257">
+      <c r="I23" s="256">
         <v>5.78</v>
       </c>
-      <c r="J23" s="254">
+      <c r="J23" s="253">
         <v>3.91</v>
       </c>
-      <c r="K23" s="258">
+      <c r="K23" s="263">
         <v>6.83</v>
       </c>
-      <c r="L23" s="255">
+      <c r="L23" s="254">
         <v>4.79</v>
       </c>
-      <c r="M23" s="262">
+      <c r="M23" s="258">
         <v>5.08</v>
       </c>
       <c r="N23" s="259">
@@ -10004,19 +10004,19 @@
       <c r="O23" s="260">
         <v>1.4</v>
       </c>
-      <c r="P23" s="263">
+      <c r="P23" s="261">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="256">
+      <c r="Q23" s="262">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="261">
+      <c r="R23" s="264">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="264">
+      <c r="S23" s="255">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="253">
+      <c r="T23" s="257">
         <v>6.07</v>
       </c>
     </row>
@@ -10045,40 +10045,40 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="267">
+      <c r="I24" s="269">
         <v>-0.93</v>
       </c>
-      <c r="J24" s="273">
+      <c r="J24" s="275">
         <v>-2.54</v>
       </c>
-      <c r="K24" s="268">
+      <c r="K24" s="272">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="269">
+      <c r="L24" s="274">
         <v>-12.46</v>
       </c>
-      <c r="M24" s="275">
+      <c r="M24" s="276">
         <v>-11.46</v>
       </c>
-      <c r="N24" s="276">
+      <c r="N24" s="265">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="274">
+      <c r="O24" s="266">
         <v>-7.66</v>
       </c>
-      <c r="P24" s="265">
+      <c r="P24" s="267">
         <v>-9.54</v>
       </c>
-      <c r="Q24" s="266">
+      <c r="Q24" s="270">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="270">
+      <c r="R24" s="268">
         <v>-18.67</v>
       </c>
       <c r="S24" s="271">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="272">
+      <c r="T24" s="273">
         <v>-10.63</v>
       </c>
     </row>
@@ -10110,37 +10110,37 @@
       <c r="I25" s="283">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="284">
+      <c r="J25" s="281">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="280">
+      <c r="K25" s="279">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="285">
+      <c r="L25" s="286">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="288">
+      <c r="M25" s="284">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="281">
+      <c r="N25" s="280">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="286">
+      <c r="O25" s="285">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="287">
+      <c r="P25" s="282">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="277">
+      <c r="Q25" s="287">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="278">
+      <c r="R25" s="288">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="279">
+      <c r="S25" s="277">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="282">
+      <c r="T25" s="278">
         <v>-11.78</v>
       </c>
     </row>
@@ -10169,40 +10169,40 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="290">
+      <c r="I26" s="299">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="291">
+      <c r="J26" s="300">
         <v>0.56</v>
       </c>
-      <c r="K26" s="299">
+      <c r="K26" s="297">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="292">
+      <c r="L26" s="290">
         <v>-7.91</v>
       </c>
-      <c r="M26" s="293">
+      <c r="M26" s="298">
         <v>1.36</v>
       </c>
-      <c r="N26" s="298">
+      <c r="N26" s="294">
         <v>3.39</v>
       </c>
-      <c r="O26" s="300">
+      <c r="O26" s="289">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="295">
+      <c r="P26" s="291">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="296">
+      <c r="Q26" s="295">
         <v>7.01</v>
       </c>
-      <c r="R26" s="289">
+      <c r="R26" s="292">
         <v>12.66</v>
       </c>
-      <c r="S26" s="297">
+      <c r="S26" s="296">
         <v>6.55</v>
       </c>
-      <c r="T26" s="294">
+      <c r="T26" s="293">
         <v>-7.46</v>
       </c>
     </row>
@@ -10231,40 +10231,40 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="308">
+      <c r="I27" s="304">
         <v>-1.23</v>
       </c>
-      <c r="J27" s="302">
+      <c r="J27" s="309">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="303">
+      <c r="K27" s="305">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="309">
+      <c r="L27" s="310">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="312">
+      <c r="M27" s="311">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="304">
+      <c r="N27" s="306">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="301">
+      <c r="O27" s="307">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="310">
+      <c r="P27" s="308">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="305">
+      <c r="Q27" s="301">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="306">
+      <c r="R27" s="302">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="307">
+      <c r="S27" s="303">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="311">
+      <c r="T27" s="312">
         <v>-12.56</v>
       </c>
     </row>
@@ -10293,37 +10293,37 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="321">
+      <c r="I28" s="314">
         <v>1.28</v>
       </c>
-      <c r="J28" s="314">
+      <c r="J28" s="321">
         <v>2.92</v>
       </c>
-      <c r="K28" s="317">
+      <c r="K28" s="324">
         <v>4.72</v>
       </c>
-      <c r="L28" s="315">
+      <c r="L28" s="317">
         <v>6.25</v>
       </c>
-      <c r="M28" s="322">
+      <c r="M28" s="313">
         <v>16.86</v>
       </c>
-      <c r="N28" s="323">
+      <c r="N28" s="315">
         <v>13.12</v>
       </c>
-      <c r="O28" s="318">
+      <c r="O28" s="322">
         <v>24.45</v>
       </c>
-      <c r="P28" s="319">
+      <c r="P28" s="323">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="316">
+      <c r="Q28" s="318">
         <v>46.03</v>
       </c>
-      <c r="R28" s="324">
+      <c r="R28" s="319">
         <v>45.46</v>
       </c>
-      <c r="S28" s="313">
+      <c r="S28" s="316">
         <v>42.9</v>
       </c>
       <c r="T28" s="320">
@@ -10355,40 +10355,40 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="325">
+      <c r="I29" s="333">
         <v>3.14</v>
       </c>
-      <c r="J29" s="329">
+      <c r="J29" s="325">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="326">
+      <c r="K29" s="331">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="330">
+      <c r="L29" s="334">
         <v>-0.61</v>
       </c>
-      <c r="M29" s="327">
+      <c r="M29" s="329">
         <v>6.71</v>
       </c>
-      <c r="N29" s="332">
+      <c r="N29" s="326">
         <v>3.47</v>
       </c>
-      <c r="O29" s="333">
+      <c r="O29" s="327">
         <v>-0.94</v>
       </c>
       <c r="P29" s="328">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="334">
+      <c r="Q29" s="335">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="331">
+      <c r="R29" s="336">
         <v>0.11</v>
       </c>
-      <c r="S29" s="335">
+      <c r="S29" s="330">
         <v>2.42</v>
       </c>
-      <c r="T29" s="336">
+      <c r="T29" s="332">
         <v>9.85</v>
       </c>
     </row>
@@ -10417,40 +10417,40 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="339">
+      <c r="I30" s="344">
         <v>1.85</v>
       </c>
       <c r="J30" s="348">
         <v>7.78</v>
       </c>
-      <c r="K30" s="340">
+      <c r="K30" s="345">
         <v>13.84</v>
       </c>
-      <c r="L30" s="337">
+      <c r="L30" s="341">
         <v>11.93</v>
       </c>
-      <c r="M30" s="343">
+      <c r="M30" s="338">
         <v>5.23</v>
       </c>
-      <c r="N30" s="344">
+      <c r="N30" s="342">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="345">
+      <c r="O30" s="346">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="341">
+      <c r="P30" s="343">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="342">
+      <c r="Q30" s="339">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="338">
+      <c r="R30" s="337">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="346">
+      <c r="S30" s="347">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="347">
+      <c r="T30" s="340">
         <v>-12.82</v>
       </c>
     </row>
@@ -10479,40 +10479,40 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="350">
+      <c r="I31" s="360">
         <v>1.82</v>
       </c>
-      <c r="J31" s="353">
+      <c r="J31" s="352">
         <v>6.88</v>
       </c>
-      <c r="K31" s="360">
+      <c r="K31" s="353">
         <v>4.25</v>
       </c>
-      <c r="L31" s="351">
+      <c r="L31" s="357">
         <v>1.42</v>
       </c>
-      <c r="M31" s="352">
+      <c r="M31" s="358">
         <v>-7.09</v>
       </c>
-      <c r="N31" s="354">
+      <c r="N31" s="349">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="355">
+      <c r="O31" s="350">
         <v>-10.32</v>
       </c>
-      <c r="P31" s="356">
+      <c r="P31" s="351">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="357">
+      <c r="Q31" s="359">
         <v>-17</v>
       </c>
-      <c r="R31" s="358">
+      <c r="R31" s="354">
         <v>-16.8</v>
       </c>
-      <c r="S31" s="359">
+      <c r="S31" s="355">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="349">
+      <c r="T31" s="356">
         <v>-19.84</v>
       </c>
     </row>
@@ -10544,37 +10544,37 @@
       <c r="I32" s="361">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="371">
+      <c r="J32" s="366">
         <v>0.27</v>
       </c>
-      <c r="K32" s="363">
+      <c r="K32" s="367">
         <v>2.99</v>
       </c>
-      <c r="L32" s="372">
+      <c r="L32" s="371">
         <v>2.35</v>
       </c>
-      <c r="M32" s="369">
+      <c r="M32" s="362">
         <v>0.72</v>
       </c>
-      <c r="N32" s="364">
+      <c r="N32" s="368">
         <v>1</v>
       </c>
-      <c r="O32" s="365">
+      <c r="O32" s="364">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="362">
+      <c r="P32" s="369">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="366">
+      <c r="Q32" s="365">
         <v>3.26</v>
       </c>
-      <c r="R32" s="367">
+      <c r="R32" s="372">
         <v>1</v>
       </c>
       <c r="S32" s="370">
         <v>1.45</v>
       </c>
-      <c r="T32" s="368">
+      <c r="T32" s="363">
         <v>8.6</v>
       </c>
     </row>
@@ -10603,40 +10603,40 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="383">
+      <c r="I33" s="380">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="373">
+      <c r="J33" s="381">
         <v>0.57</v>
       </c>
-      <c r="K33" s="378">
+      <c r="K33" s="377">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="374">
+      <c r="L33" s="373">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="375">
+      <c r="M33" s="382">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="379">
+      <c r="N33" s="383">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="376">
+      <c r="O33" s="374">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="380">
+      <c r="P33" s="375">
         <v>-18.9</v>
       </c>
       <c r="Q33" s="384">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="381">
+      <c r="R33" s="378">
         <v>-20.6</v>
       </c>
-      <c r="S33" s="377">
+      <c r="S33" s="379">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="382">
+      <c r="T33" s="376">
         <v>-21.17</v>
       </c>
     </row>
@@ -10665,19 +10665,19 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="385">
+      <c r="I34" s="389">
         <v>-3</v>
       </c>
       <c r="J34" s="392">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="388">
+      <c r="K34" s="390">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="386">
+      <c r="L34" s="385">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="389">
+      <c r="M34" s="386">
         <v>-16.82</v>
       </c>
       <c r="N34" s="393">
@@ -10686,19 +10686,19 @@
       <c r="O34" s="394">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="390">
+      <c r="P34" s="387">
         <v>-19.82</v>
       </c>
-      <c r="Q34" s="395">
+      <c r="Q34" s="388">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="396">
+      <c r="R34" s="391">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="387">
+      <c r="S34" s="395">
         <v>-21.43</v>
       </c>
-      <c r="T34" s="391">
+      <c r="T34" s="396">
         <v>-21.43</v>
       </c>
     </row>
@@ -10727,40 +10727,40 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="403">
+      <c r="I35" s="406">
         <v>4.2</v>
       </c>
-      <c r="J35" s="398">
+      <c r="J35" s="399">
         <v>3.72</v>
       </c>
-      <c r="K35" s="404">
+      <c r="K35" s="407">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="407">
+      <c r="L35" s="400">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="405">
+      <c r="M35" s="401">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="408">
+      <c r="N35" s="405">
         <v>6.61</v>
       </c>
-      <c r="O35" s="400">
+      <c r="O35" s="408">
         <v>5.5</v>
       </c>
-      <c r="P35" s="401">
+      <c r="P35" s="402">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="402">
+      <c r="Q35" s="397">
         <v>1.68</v>
       </c>
-      <c r="R35" s="406">
+      <c r="R35" s="398">
         <v>1.37</v>
       </c>
-      <c r="S35" s="397">
+      <c r="S35" s="403">
         <v>0.08</v>
       </c>
-      <c r="T35" s="399">
+      <c r="T35" s="404">
         <v>0.66</v>
       </c>
     </row>
@@ -10792,37 +10792,37 @@
       <c r="I36" s="414">
         <v>5.57</v>
       </c>
-      <c r="J36" s="420">
+      <c r="J36" s="409">
         <v>16.17</v>
       </c>
-      <c r="K36" s="415">
+      <c r="K36" s="410">
         <v>22.01</v>
       </c>
       <c r="L36" s="416">
         <v>16.85</v>
       </c>
-      <c r="M36" s="409">
+      <c r="M36" s="411">
         <v>7.07</v>
       </c>
-      <c r="N36" s="417">
+      <c r="N36" s="419">
         <v>0.27</v>
       </c>
-      <c r="O36" s="410">
+      <c r="O36" s="412">
         <v>2.45</v>
       </c>
-      <c r="P36" s="411">
+      <c r="P36" s="420">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="418">
+      <c r="Q36" s="415">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="412">
+      <c r="R36" s="413">
         <v>9.65</v>
       </c>
-      <c r="S36" s="413">
+      <c r="S36" s="417">
         <v>7.47</v>
       </c>
-      <c r="T36" s="419">
+      <c r="T36" s="418">
         <v>3.4</v>
       </c>
     </row>
@@ -10851,40 +10851,40 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="432">
+      <c r="I37" s="421">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="430">
+      <c r="J37" s="426">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="428">
+      <c r="K37" s="422">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="421">
+      <c r="L37" s="423">
         <v>7.57</v>
       </c>
-      <c r="M37" s="422">
+      <c r="M37" s="427">
         <v>5.6</v>
       </c>
-      <c r="N37" s="431">
+      <c r="N37" s="428">
         <v>4.48</v>
       </c>
-      <c r="O37" s="429">
+      <c r="O37" s="431">
         <v>3.32</v>
       </c>
-      <c r="P37" s="424">
+      <c r="P37" s="429">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="425">
+      <c r="Q37" s="432">
         <v>3.78</v>
       </c>
-      <c r="R37" s="426">
+      <c r="R37" s="424">
         <v>8.07</v>
       </c>
-      <c r="S37" s="427">
+      <c r="S37" s="430">
         <v>11.74</v>
       </c>
-      <c r="T37" s="423">
+      <c r="T37" s="425">
         <v>11.93</v>
       </c>
     </row>
@@ -10913,38 +10913,38 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="441">
+      <c r="I38" s="437">
         <v>6.62</v>
       </c>
-      <c r="J38" s="433">
+      <c r="J38" s="440">
         <v>10.07</v>
       </c>
-      <c r="K38" s="434">
+      <c r="K38" s="435">
         <v>6.26</v>
       </c>
-      <c r="L38" s="435">
+      <c r="L38" s="441">
         <v>2.13</v>
       </c>
-      <c r="M38" s="439">
+      <c r="M38" s="442">
         <v>1.41</v>
       </c>
-      <c r="N38" s="442">
+      <c r="N38" s="443">
         <v>7.72</v>
       </c>
-      <c r="O38" s="436">
+      <c r="O38" s="433">
         <v>5.74</v>
       </c>
-      <c r="P38" s="443">
+      <c r="P38" s="438">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="437">
+      <c r="Q38" s="436">
         <v>14.45</v>
       </c>
-      <c r="R38" s="438">
+      <c r="R38" s="439">
         <v>18.62</v>
       </c>
       <c r="S38" t="str"/>
-      <c r="T38" s="440">
+      <c r="T38" s="434">
         <v>18.62</v>
       </c>
     </row>
@@ -10973,28 +10973,28 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="449">
+      <c r="I39" s="448">
         <v>7.14</v>
       </c>
-      <c r="J39" s="444">
+      <c r="J39" s="453">
         <v>7.82</v>
       </c>
-      <c r="K39" s="452">
+      <c r="K39" s="444">
         <v>7.68</v>
       </c>
-      <c r="L39" s="447">
+      <c r="L39" s="445">
         <v>8.49</v>
       </c>
-      <c r="M39" s="450">
+      <c r="M39" s="446">
         <v>9.43</v>
       </c>
-      <c r="N39" s="445">
+      <c r="N39" s="450">
         <v>5.39</v>
       </c>
-      <c r="O39" s="446">
+      <c r="O39" s="447">
         <v>8.49</v>
       </c>
-      <c r="P39" s="453">
+      <c r="P39" s="449">
         <v>7.28</v>
       </c>
       <c r="Q39" s="451">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="448">
+      <c r="T39" s="452">
         <v>11.99</v>
       </c>
     </row>
@@ -11031,34 +11031,34 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="455">
+      <c r="I40" s="454">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="460">
+      <c r="J40" s="455">
         <v>-0.66</v>
       </c>
-      <c r="K40" s="456">
+      <c r="K40" s="459">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="461">
+      <c r="L40" s="460">
         <v>0</v>
       </c>
-      <c r="M40" s="457">
+      <c r="M40" s="461">
         <v>-1.31</v>
       </c>
-      <c r="N40" s="458">
+      <c r="N40" s="457">
         <v>0.33</v>
       </c>
-      <c r="O40" s="459">
+      <c r="O40" s="456">
         <v>0</v>
       </c>
-      <c r="P40" s="462">
+      <c r="P40" s="458">
         <v>1.97</v>
       </c>
       <c r="Q40" t="str"/>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="454">
+      <c r="T40" s="462">
         <v>1.97</v>
       </c>
     </row>
@@ -11087,32 +11087,32 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="464">
+      <c r="I41" s="466">
         <v>0.59</v>
       </c>
-      <c r="J41" s="465">
+      <c r="J41" s="467">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="466">
+      <c r="K41" s="468">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="467">
+      <c r="L41" s="469">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="468">
+      <c r="M41" s="470">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="469">
+      <c r="N41" s="463">
         <v>-7.55</v>
       </c>
-      <c r="O41" s="470">
+      <c r="O41" s="464">
         <v>-6.76</v>
       </c>
       <c r="P41" t="str"/>
       <c r="Q41" t="str"/>
       <c r="R41" t="str"/>
       <c r="S41" t="str"/>
-      <c r="T41" s="463">
+      <c r="T41" s="465">
         <v>-6.76</v>
       </c>
     </row>
@@ -11141,22 +11141,22 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="476">
+      <c r="I42" s="472">
         <v>2.08</v>
       </c>
-      <c r="J42" s="477">
+      <c r="J42" s="473">
         <v>2.7</v>
       </c>
-      <c r="K42" s="471">
+      <c r="K42" s="474">
         <v>0</v>
       </c>
-      <c r="L42" s="472">
+      <c r="L42" s="475">
         <v>1.25</v>
       </c>
-      <c r="M42" s="473">
+      <c r="M42" s="476">
         <v>1.04</v>
       </c>
-      <c r="N42" s="474">
+      <c r="N42" s="477">
         <v>1.56</v>
       </c>
       <c r="O42" t="str"/>
@@ -11164,7 +11164,7 @@
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="475">
+      <c r="T42" s="471">
         <v>1.56</v>
       </c>
     </row>
@@ -11193,19 +11193,19 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="479">
+      <c r="I43" s="480">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="480">
+      <c r="J43" s="481">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="481">
+      <c r="K43" s="482">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="482">
+      <c r="L43" s="483">
         <v>8.46</v>
       </c>
-      <c r="M43" s="483">
+      <c r="M43" s="478">
         <v>10.98</v>
       </c>
       <c r="N43" t="str"/>
@@ -11214,7 +11214,7 @@
       <c r="Q43" t="str"/>
       <c r="R43" t="str"/>
       <c r="S43" t="str"/>
-      <c r="T43" s="478">
+      <c r="T43" s="479">
         <v>10.98</v>
       </c>
     </row>
@@ -11243,16 +11243,16 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="487">
+      <c r="I44" s="488">
         <v>10.68</v>
       </c>
-      <c r="J44" s="488">
+      <c r="J44" s="484">
         <v>1.78</v>
       </c>
-      <c r="K44" s="484">
+      <c r="K44" s="485">
         <v>-1.94</v>
       </c>
-      <c r="L44" s="485">
+      <c r="L44" s="486">
         <v>3.72</v>
       </c>
       <c r="M44" t="str"/>
@@ -11262,7 +11262,7 @@
       <c r="Q44" t="str"/>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="486">
+      <c r="T44" s="487">
         <v>3.72</v>
       </c>
     </row>
@@ -11291,13 +11291,13 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="490">
+      <c r="I45" s="489">
         <v>2.03</v>
       </c>
-      <c r="J45" s="491">
+      <c r="J45" s="490">
         <v>5.03</v>
       </c>
-      <c r="K45" s="492">
+      <c r="K45" s="491">
         <v>5.82</v>
       </c>
       <c r="L45" t="str"/>
@@ -11308,7 +11308,7 @@
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="489">
+      <c r="T45" s="492">
         <v>5.82</v>
       </c>
     </row>
@@ -11414,37 +11414,37 @@
       <c r="I48" s="500">
         <v>60</v>
       </c>
-      <c r="J48" s="503">
+      <c r="J48" s="494">
         <v>59.09</v>
       </c>
-      <c r="K48" s="496">
+      <c r="K48" s="495">
         <v>52.27</v>
       </c>
-      <c r="L48" s="504">
+      <c r="L48" s="496">
         <v>58.14</v>
       </c>
       <c r="M48" s="497">
         <v>54.76</v>
       </c>
-      <c r="N48" s="498">
+      <c r="N48" s="501">
         <v>56.1</v>
       </c>
-      <c r="O48" s="501">
+      <c r="O48" s="504">
         <v>40</v>
       </c>
-      <c r="P48" s="505">
+      <c r="P48" s="498">
         <v>43.59</v>
       </c>
-      <c r="Q48" s="494">
+      <c r="Q48" s="502">
         <v>42.11</v>
       </c>
-      <c r="R48" s="495">
+      <c r="R48" s="499">
         <v>45.95</v>
       </c>
-      <c r="S48" s="499">
+      <c r="S48" s="505">
         <v>47.22</v>
       </c>
-      <c r="T48" s="502">
+      <c r="T48" s="503">
         <v>45.45</v>
       </c>
     </row>
@@ -11462,28 +11462,28 @@
       <c r="I49" s="512">
         <v>2.15</v>
       </c>
-      <c r="J49" s="517">
+      <c r="J49" s="516">
         <v>2.44</v>
       </c>
       <c r="K49" s="513">
         <v>1.89</v>
       </c>
-      <c r="L49" s="508">
+      <c r="L49" s="514">
         <v>1.21</v>
       </c>
-      <c r="M49" s="514">
+      <c r="M49" s="507">
         <v>1.46</v>
       </c>
       <c r="N49" s="515">
         <v>-0.11</v>
       </c>
-      <c r="O49" s="506">
+      <c r="O49" s="508">
         <v>-0.41</v>
       </c>
-      <c r="P49" s="516">
+      <c r="P49" s="517">
         <v>-0.2</v>
       </c>
-      <c r="Q49" s="507">
+      <c r="Q49" s="509">
         <v>-0.49</v>
       </c>
       <c r="R49" s="510">
@@ -11492,7 +11492,7 @@
       <c r="S49" s="511">
         <v>0.34</v>
       </c>
-      <c r="T49" s="509">
+      <c r="T49" s="506">
         <v>-2.31</v>
       </c>
     </row>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="519">
+  <fills count="530">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,13 +39,1615 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,19 +1659,229 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,43 +1899,727 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C2C7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,7 +2631,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,7 +2649,253 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,25 +2907,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,12 +2949,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -207,31 +2961,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,169 +3021,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3EB058"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,109 +3177,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,1327 +3195,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAF0DF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFD2ECD8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1861,1286 +3205,85 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE4E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9EA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF55B96C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD6AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B77"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9F6EC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="518">
+  <borders count="529">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6771,7 +6914,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="518">
+  <cellXfs count="529">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8322,6 +8465,39 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="517" fillId="518" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="518" fillId="519" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="519" fillId="520" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="520" fillId="521" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="521" fillId="522" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="522" fillId="523" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="523" fillId="524" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="524" fillId="525" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="525" fillId="526" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="526" fillId="527" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="527" fillId="528" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="528" fillId="529" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8681,41 +8857,41 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="8">
         <v>4.95</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="3">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="9">
         <v>1.74</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="1">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="10">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="4">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="5">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="6">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="11">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="7">
         <v>-4.59</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="12">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="8">
-        <v>-15.78</v>
+      <c r="T2" s="2">
+        <v>-17.71</v>
       </c>
     </row>
     <row r="3">
@@ -8743,41 +8919,41 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="23">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="18">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="16">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="19">
         <v>0.1</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="24">
         <v>3.32</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="13">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="20">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="14">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="15">
         <v>2.8</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="17">
         <v>1.66</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="21">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="18">
-        <v>18.65</v>
+      <c r="T3" s="22">
+        <v>17.62</v>
       </c>
     </row>
     <row r="4">
@@ -8805,41 +8981,41 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="29">
         <v>4.19</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="26">
         <v>5.08</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="34">
         <v>15.59</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="35">
         <v>27.15</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="30">
         <v>36.04</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="36">
         <v>41.33</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="33">
         <v>37.54</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="31">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="25">
         <v>32.33</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="27">
         <v>45.56</v>
       </c>
       <c r="S4" s="32">
         <v>56.03</v>
       </c>
-      <c r="T4" s="25">
-        <v>25.44</v>
+      <c r="T4" s="28">
+        <v>28.86</v>
       </c>
     </row>
     <row r="5">
@@ -8867,41 +9043,41 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="37">
+      <c r="I5" s="38">
         <v>11.97</v>
       </c>
-      <c r="J5" s="38">
+      <c r="J5" s="47">
         <v>17.45</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="48">
         <v>14.27</v>
       </c>
       <c r="L5" s="43">
         <v>17.32</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="42">
         <v>25.33</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="44">
         <v>21.54</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="37">
         <v>22.72</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="39">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="39">
+      <c r="Q5" s="45">
         <v>17.54</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="40">
         <v>16.88</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="41">
         <v>11.79</v>
       </c>
-      <c r="T5" s="48">
-        <v>24.67</v>
+      <c r="T5" s="46">
+        <v>26.94</v>
       </c>
     </row>
     <row r="6">
@@ -8929,41 +9105,41 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="49">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="49">
+      <c r="J6" s="50">
         <v>-1.34</v>
       </c>
       <c r="K6" s="54">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="51">
         <v>-0.66</v>
       </c>
       <c r="M6" s="57">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="50">
+      <c r="N6" s="55">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="52">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="51">
+      <c r="P6" s="53">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="52">
+      <c r="Q6" s="59">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="60">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="56">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="53">
-        <v>-18.2</v>
+      <c r="T6" s="58">
+        <v>-17.05</v>
       </c>
     </row>
     <row r="7">
@@ -8991,41 +9167,41 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="65">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="66">
         <v>1.8</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="67">
         <v>0.07</v>
       </c>
-      <c r="L7" s="61">
+      <c r="L7" s="72">
         <v>0.63</v>
       </c>
-      <c r="M7" s="65">
+      <c r="M7" s="69">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="61">
         <v>1.55</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="68">
         <v>0.85</v>
       </c>
-      <c r="P7" s="62">
+      <c r="P7" s="70">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="62">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="63">
+      <c r="R7" s="71">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="63">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="69">
-        <v>4.78</v>
+      <c r="T7" s="64">
+        <v>10.63</v>
       </c>
     </row>
     <row r="8">
@@ -9053,41 +9229,41 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="83">
         <v>3.13</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="84">
         <v>5.21</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="73">
         <v>0.43</v>
       </c>
       <c r="L8" s="74">
         <v>3.68</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="78">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="75">
+      <c r="N8" s="79">
         <v>1.66</v>
       </c>
-      <c r="O8" s="78">
+      <c r="O8" s="75">
         <v>1.72</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="81">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="76">
+      <c r="Q8" s="80">
         <v>15.33</v>
       </c>
-      <c r="R8" s="73">
+      <c r="R8" s="82">
         <v>12.57</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="76">
         <v>23.85</v>
       </c>
-      <c r="T8" s="79">
-        <v>-13.24</v>
+      <c r="T8" s="77">
+        <v>-13.18</v>
       </c>
     </row>
     <row r="9">
@@ -9115,41 +9291,41 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="85">
+      <c r="I9" s="91">
         <v>1.35</v>
       </c>
-      <c r="J9" s="90">
+      <c r="J9" s="92">
         <v>2.48</v>
       </c>
-      <c r="K9" s="86">
+      <c r="K9" s="88">
         <v>1.58</v>
       </c>
-      <c r="L9" s="91">
+      <c r="L9" s="96">
         <v>1.35</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="85">
         <v>2.93</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="93">
         <v>0.23</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="86">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="87">
+      <c r="P9" s="94">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="88">
+      <c r="Q9" s="95">
         <v>3.83</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="87">
         <v>7.43</v>
       </c>
       <c r="S9" s="89">
         <v>17.12</v>
       </c>
-      <c r="T9" s="93">
-        <v>3.6</v>
+      <c r="T9" s="90">
+        <v>5.18</v>
       </c>
     </row>
     <row r="10">
@@ -9177,41 +9353,41 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="98">
+      <c r="I10" s="103">
         <v>-3.57</v>
       </c>
       <c r="J10" s="101">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="105">
+      <c r="K10" s="102">
         <v>-7.86</v>
       </c>
-      <c r="L10" s="102">
+      <c r="L10" s="107">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="103">
+      <c r="M10" s="108">
         <v>-12.37</v>
       </c>
       <c r="N10" s="104">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="105">
         <v>-9.15</v>
       </c>
-      <c r="P10" s="99">
+      <c r="P10" s="97">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="100">
+      <c r="Q10" s="106">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="98">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="99">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="97">
-        <v>-12.01</v>
+      <c r="T10" s="100">
+        <v>-13.87</v>
       </c>
     </row>
     <row r="11">
@@ -9239,41 +9415,41 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="110">
+      <c r="I11" s="109">
         <v>7.32</v>
       </c>
-      <c r="J11" s="117">
+      <c r="J11" s="114">
         <v>7.76</v>
       </c>
       <c r="K11" s="115">
         <v>15.37</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="117">
         <v>8.64</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="110">
         <v>0.59</v>
       </c>
-      <c r="N11" s="114">
+      <c r="N11" s="116">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="112">
+      <c r="O11" s="111">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="119">
+      <c r="P11" s="118">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="116">
+      <c r="Q11" s="119">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="120">
+      <c r="R11" s="112">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="109">
+      <c r="S11" s="113">
         <v>0.15</v>
       </c>
-      <c r="T11" s="113">
-        <v>-21.52</v>
+      <c r="T11" s="120">
+        <v>-22.25</v>
       </c>
     </row>
     <row r="12">
@@ -9301,41 +9477,41 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="125">
+      <c r="I12" s="132">
         <v>10.48</v>
       </c>
-      <c r="J12" s="126">
+      <c r="J12" s="121">
         <v>13.87</v>
       </c>
       <c r="K12" s="127">
         <v>4.11</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="130">
         <v>6.13</v>
       </c>
-      <c r="M12" s="121">
+      <c r="M12" s="123">
         <v>9.68</v>
       </c>
-      <c r="N12" s="122">
+      <c r="N12" s="124">
         <v>2.66</v>
       </c>
-      <c r="O12" s="123">
+      <c r="O12" s="128">
         <v>-1.61</v>
       </c>
       <c r="P12" s="131">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="128">
+      <c r="Q12" s="125">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="129">
+      <c r="R12" s="122">
         <v>0.97</v>
       </c>
-      <c r="S12" s="130">
+      <c r="S12" s="129">
         <v>3.06</v>
       </c>
-      <c r="T12" s="124">
-        <v>-21.13</v>
+      <c r="T12" s="126">
+        <v>-22.74</v>
       </c>
     </row>
     <row r="13">
@@ -9363,41 +9539,41 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="136">
+      <c r="I13" s="139">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="142">
+      <c r="J13" s="140">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="137">
+      <c r="K13" s="143">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="138">
+      <c r="L13" s="135">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="140">
+      <c r="M13" s="144">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="143">
+      <c r="N13" s="136">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="141">
         <v>-9.38</v>
       </c>
       <c r="P13" s="133">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="134">
+      <c r="Q13" s="137">
         <v>-4.93</v>
       </c>
-      <c r="R13" s="135">
+      <c r="R13" s="138">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="141">
+      <c r="S13" s="134">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="139">
-        <v>-17.08</v>
+      <c r="T13" s="142">
+        <v>-16.65</v>
       </c>
     </row>
     <row r="14">
@@ -9425,41 +9601,41 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="156">
+      <c r="I14" s="146">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="145">
+      <c r="J14" s="154">
         <v>-5</v>
       </c>
-      <c r="K14" s="152">
+      <c r="K14" s="147">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="153">
+      <c r="L14" s="155">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="146">
+      <c r="M14" s="148">
         <v>-7.37</v>
       </c>
-      <c r="N14" s="147">
+      <c r="N14" s="150">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="148">
+      <c r="O14" s="151">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="154">
+      <c r="P14" s="153">
         <v>-5.63</v>
       </c>
       <c r="Q14" s="149">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="155">
+      <c r="R14" s="156">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="151">
+      <c r="S14" s="152">
         <v>0</v>
       </c>
-      <c r="T14" s="150">
-        <v>-7</v>
+      <c r="T14" s="145">
+        <v>-6.75</v>
       </c>
     </row>
     <row r="15">
@@ -9487,19 +9663,19 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="165">
+      <c r="I15" s="168">
         <v>9.9</v>
       </c>
-      <c r="J15" s="160">
+      <c r="J15" s="157">
         <v>9.43</v>
       </c>
-      <c r="K15" s="166">
+      <c r="K15" s="165">
         <v>8.82</v>
       </c>
-      <c r="L15" s="158">
+      <c r="L15" s="166">
         <v>4.15</v>
       </c>
-      <c r="M15" s="167">
+      <c r="M15" s="158">
         <v>7.79</v>
       </c>
       <c r="N15" s="161">
@@ -9508,20 +9684,20 @@
       <c r="O15" s="162">
         <v>8.69</v>
       </c>
-      <c r="P15" s="159">
+      <c r="P15" s="163">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="168">
+      <c r="Q15" s="167">
         <v>5.84</v>
       </c>
-      <c r="R15" s="163">
+      <c r="R15" s="164">
         <v>6.88</v>
       </c>
-      <c r="S15" s="157">
+      <c r="S15" s="159">
         <v>2.34</v>
       </c>
-      <c r="T15" s="164">
-        <v>-4.33</v>
+      <c r="T15" s="160">
+        <v>-7.31</v>
       </c>
     </row>
     <row r="16">
@@ -9549,41 +9725,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="174">
+      <c r="I16" s="175">
         <v>2.67</v>
       </c>
-      <c r="J16" s="169">
+      <c r="J16" s="170">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="179">
+      <c r="K16" s="171">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="178">
+      <c r="L16" s="179">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="175">
+      <c r="M16" s="172">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="170">
+      <c r="N16" s="177">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="171">
+      <c r="O16" s="180">
         <v>-4.85</v>
       </c>
       <c r="P16" s="176">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="180">
+      <c r="Q16" s="173">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="172">
+      <c r="R16" s="178">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="177">
+      <c r="S16" s="174">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="173">
-        <v>-20.06</v>
+      <c r="T16" s="169">
+        <v>-21.76</v>
       </c>
     </row>
     <row r="17">
@@ -9611,41 +9787,41 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="189">
+      <c r="I17" s="184">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="181">
+      <c r="J17" s="188">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="185">
+      <c r="K17" s="182">
         <v>0.2</v>
       </c>
-      <c r="L17" s="190">
+      <c r="L17" s="189">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="191">
+      <c r="M17" s="185">
         <v>0.53</v>
       </c>
       <c r="N17" s="186">
         <v>3.31</v>
       </c>
-      <c r="O17" s="182">
+      <c r="O17" s="183">
         <v>6.89</v>
       </c>
-      <c r="P17" s="183">
+      <c r="P17" s="192">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="192">
+      <c r="Q17" s="187">
         <v>4.09</v>
       </c>
-      <c r="R17" s="187">
+      <c r="R17" s="190">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="184">
+      <c r="S17" s="191">
         <v>-1.45</v>
       </c>
-      <c r="T17" s="188">
-        <v>-0.84</v>
+      <c r="T17" s="181">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="18">
@@ -9673,41 +9849,41 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="199">
+      <c r="I18" s="201">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="193">
+      <c r="J18" s="195">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="194">
+      <c r="K18" s="203">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="200">
+      <c r="L18" s="196">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="195">
+      <c r="M18" s="197">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="201">
+      <c r="N18" s="204">
         <v>-13.2</v>
       </c>
       <c r="O18" s="202">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="203">
+      <c r="P18" s="200">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="198">
+      <c r="Q18" s="193">
         <v>-20.52</v>
       </c>
-      <c r="R18" s="204">
+      <c r="R18" s="194">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="196">
+      <c r="S18" s="198">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="197">
-        <v>-23.66</v>
+      <c r="T18" s="199">
+        <v>-25.88</v>
       </c>
     </row>
     <row r="19">
@@ -9735,41 +9911,41 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="209">
+      <c r="I19" s="207">
         <v>1.39</v>
       </c>
-      <c r="J19" s="213">
+      <c r="J19" s="208">
         <v>0.39</v>
       </c>
-      <c r="K19" s="205">
+      <c r="K19" s="209">
         <v>1.93</v>
       </c>
-      <c r="L19" s="214">
+      <c r="L19" s="215">
         <v>3.7</v>
       </c>
-      <c r="M19" s="206">
+      <c r="M19" s="210">
         <v>9.45</v>
       </c>
-      <c r="N19" s="210">
+      <c r="N19" s="212">
         <v>5.75</v>
       </c>
-      <c r="O19" s="215">
+      <c r="O19" s="205">
         <v>12.85</v>
       </c>
-      <c r="P19" s="216">
+      <c r="P19" s="213">
         <v>8.68</v>
       </c>
-      <c r="Q19" s="207">
+      <c r="Q19" s="216">
         <v>14.74</v>
       </c>
-      <c r="R19" s="208">
+      <c r="R19" s="211">
         <v>14.89</v>
       </c>
-      <c r="S19" s="212">
+      <c r="S19" s="206">
         <v>9.1</v>
       </c>
-      <c r="T19" s="211">
-        <v>10.53</v>
+      <c r="T19" s="214">
+        <v>12.54</v>
       </c>
     </row>
     <row r="20">
@@ -9797,41 +9973,41 @@
       <c r="H20">
         <v>-1.89</v>
       </c>
-      <c r="I20" s="219">
+      <c r="I20" s="222">
         <v>1.85</v>
       </c>
-      <c r="J20" s="228">
+      <c r="J20" s="217">
         <v>8.14</v>
       </c>
-      <c r="K20" s="227">
+      <c r="K20" s="218">
         <v>2.43</v>
       </c>
-      <c r="L20" s="220">
+      <c r="L20" s="227">
         <v>1.09</v>
       </c>
-      <c r="M20" s="225">
+      <c r="M20" s="228">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="217">
+      <c r="N20" s="219">
         <v>-0.76</v>
       </c>
-      <c r="O20" s="221">
+      <c r="O20" s="220">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="218">
+      <c r="P20" s="223">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="226">
+      <c r="Q20" s="224">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="222">
+      <c r="R20" s="225">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="223">
+      <c r="S20" s="226">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="224">
-        <v>-4.28</v>
+      <c r="T20" s="221">
+        <v>-7.39</v>
       </c>
     </row>
     <row r="21">
@@ -9859,41 +10035,41 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="237">
+      <c r="I21" s="238">
         <v>8.65</v>
       </c>
-      <c r="J21" s="233">
+      <c r="J21" s="229">
         <v>9.13</v>
       </c>
-      <c r="K21" s="229">
+      <c r="K21" s="235">
         <v>12.02</v>
       </c>
       <c r="L21" s="230">
         <v>9.13</v>
       </c>
-      <c r="M21" s="231">
+      <c r="M21" s="236">
         <v>12.86</v>
       </c>
-      <c r="N21" s="238">
+      <c r="N21" s="231">
         <v>8.29</v>
       </c>
-      <c r="O21" s="240">
+      <c r="O21" s="239">
         <v>0.36</v>
       </c>
-      <c r="P21" s="234">
+      <c r="P21" s="232">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="232">
+      <c r="Q21" s="234">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="235">
+      <c r="R21" s="237">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="239">
+      <c r="S21" s="233">
         <v>2.04</v>
       </c>
-      <c r="T21" s="236">
-        <v>-2.88</v>
+      <c r="T21" s="240">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="22">
@@ -9921,41 +10097,41 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="246">
+      <c r="I22" s="249">
         <v>9.66</v>
       </c>
-      <c r="J22" s="247">
+      <c r="J22" s="245">
         <v>14</v>
       </c>
       <c r="K22" s="250">
         <v>19.72</v>
       </c>
-      <c r="L22" s="248">
+      <c r="L22" s="242">
         <v>17.55</v>
       </c>
-      <c r="M22" s="251">
+      <c r="M22" s="248">
         <v>15.78</v>
       </c>
-      <c r="N22" s="243">
+      <c r="N22" s="246">
         <v>6.9</v>
       </c>
-      <c r="O22" s="252">
+      <c r="O22" s="243">
         <v>0.99</v>
       </c>
-      <c r="P22" s="244">
+      <c r="P22" s="251">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="241">
+      <c r="Q22" s="252">
         <v>8.88</v>
       </c>
-      <c r="R22" s="245">
+      <c r="R22" s="244">
         <v>4.73</v>
       </c>
-      <c r="S22" s="249">
+      <c r="S22" s="241">
         <v>5.92</v>
       </c>
-      <c r="T22" s="242">
-        <v>-8.28</v>
+      <c r="T22" s="247">
+        <v>-3.75</v>
       </c>
     </row>
     <row r="23">
@@ -9983,41 +10159,41 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="256">
+      <c r="I23" s="257">
         <v>5.78</v>
       </c>
-      <c r="J23" s="253">
+      <c r="J23" s="262">
         <v>3.91</v>
       </c>
       <c r="K23" s="263">
         <v>6.83</v>
       </c>
-      <c r="L23" s="254">
+      <c r="L23" s="260">
         <v>4.79</v>
       </c>
-      <c r="M23" s="258">
+      <c r="M23" s="264">
         <v>5.08</v>
       </c>
-      <c r="N23" s="259">
+      <c r="N23" s="253">
         <v>4.5</v>
       </c>
-      <c r="O23" s="260">
+      <c r="O23" s="255">
         <v>1.4</v>
       </c>
-      <c r="P23" s="261">
+      <c r="P23" s="254">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="262">
+      <c r="Q23" s="261">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="264">
+      <c r="R23" s="258">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="255">
+      <c r="S23" s="259">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="257">
-        <v>6.07</v>
+      <c r="T23" s="256">
+        <v>4.79</v>
       </c>
     </row>
     <row r="24">
@@ -10045,22 +10221,22 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="269">
+      <c r="I24" s="270">
         <v>-0.93</v>
       </c>
       <c r="J24" s="275">
         <v>-2.54</v>
       </c>
-      <c r="K24" s="272">
+      <c r="K24" s="276">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="274">
+      <c r="L24" s="265">
         <v>-12.46</v>
       </c>
-      <c r="M24" s="276">
+      <c r="M24" s="272">
         <v>-11.46</v>
       </c>
-      <c r="N24" s="265">
+      <c r="N24" s="271">
         <v>-11.81</v>
       </c>
       <c r="O24" s="266">
@@ -10069,17 +10245,17 @@
       <c r="P24" s="267">
         <v>-9.54</v>
       </c>
-      <c r="Q24" s="270">
+      <c r="Q24" s="268">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="268">
+      <c r="R24" s="273">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="271">
+      <c r="S24" s="274">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="273">
-        <v>-10.63</v>
+      <c r="T24" s="269">
+        <v>-14.23</v>
       </c>
     </row>
     <row r="25">
@@ -10107,41 +10283,41 @@
       <c r="H25">
         <v>-1.47</v>
       </c>
-      <c r="I25" s="283">
+      <c r="I25" s="277">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="281">
+      <c r="J25" s="282">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="279">
+      <c r="K25" s="278">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="286">
+      <c r="L25" s="283">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="284">
+      <c r="M25" s="287">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="280">
+      <c r="N25" s="279">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="285">
+      <c r="O25" s="288">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="282">
+      <c r="P25" s="284">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="287">
+      <c r="Q25" s="286">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="288">
+      <c r="R25" s="280">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="277">
+      <c r="S25" s="285">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="278">
-        <v>-11.78</v>
+      <c r="T25" s="281">
+        <v>-10.71</v>
       </c>
     </row>
     <row r="26">
@@ -10169,41 +10345,41 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="299">
+      <c r="I26" s="296">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="300">
+      <c r="J26" s="299">
         <v>0.56</v>
       </c>
       <c r="K26" s="297">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="290">
+      <c r="L26" s="291">
         <v>-7.91</v>
       </c>
       <c r="M26" s="298">
         <v>1.36</v>
       </c>
-      <c r="N26" s="294">
+      <c r="N26" s="300">
         <v>3.39</v>
       </c>
       <c r="O26" s="289">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="291">
+      <c r="P26" s="290">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="295">
+      <c r="Q26" s="292">
         <v>7.01</v>
       </c>
-      <c r="R26" s="292">
+      <c r="R26" s="294">
         <v>12.66</v>
       </c>
-      <c r="S26" s="296">
+      <c r="S26" s="293">
         <v>6.55</v>
       </c>
-      <c r="T26" s="293">
-        <v>-7.46</v>
+      <c r="T26" s="295">
+        <v>-9.04</v>
       </c>
     </row>
     <row r="27">
@@ -10237,25 +10413,25 @@
       <c r="J27" s="309">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="305">
+      <c r="K27" s="306">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="310">
+      <c r="L27" s="311">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="311">
+      <c r="M27" s="312">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="306">
+      <c r="N27" s="305">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="307">
+      <c r="O27" s="301">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="308">
+      <c r="P27" s="310">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="301">
+      <c r="Q27" s="307">
         <v>-9.78</v>
       </c>
       <c r="R27" s="302">
@@ -10264,8 +10440,8 @@
       <c r="S27" s="303">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="312">
-        <v>-12.56</v>
+      <c r="T27" s="308">
+        <v>-13.48</v>
       </c>
     </row>
     <row r="28">
@@ -10293,41 +10469,41 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="314">
+      <c r="I28" s="322">
         <v>1.28</v>
       </c>
-      <c r="J28" s="321">
+      <c r="J28" s="313">
         <v>2.92</v>
       </c>
-      <c r="K28" s="324">
+      <c r="K28" s="316">
         <v>4.72</v>
       </c>
       <c r="L28" s="317">
         <v>6.25</v>
       </c>
-      <c r="M28" s="313">
+      <c r="M28" s="323">
         <v>16.86</v>
       </c>
-      <c r="N28" s="315">
+      <c r="N28" s="314">
         <v>13.12</v>
       </c>
-      <c r="O28" s="322">
+      <c r="O28" s="318">
         <v>24.45</v>
       </c>
-      <c r="P28" s="323">
+      <c r="P28" s="319">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="318">
+      <c r="Q28" s="324">
         <v>46.03</v>
       </c>
-      <c r="R28" s="319">
+      <c r="R28" s="320">
         <v>45.46</v>
       </c>
-      <c r="S28" s="316">
+      <c r="S28" s="315">
         <v>42.9</v>
       </c>
-      <c r="T28" s="320">
-        <v>30.39</v>
+      <c r="T28" s="321">
+        <v>33.01</v>
       </c>
     </row>
     <row r="29">
@@ -10355,41 +10531,41 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="333">
+      <c r="I29" s="336">
         <v>3.14</v>
       </c>
-      <c r="J29" s="325">
+      <c r="J29" s="334">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="331">
+      <c r="K29" s="330">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="332">
         <v>-0.61</v>
       </c>
-      <c r="M29" s="329">
+      <c r="M29" s="325">
         <v>6.71</v>
       </c>
-      <c r="N29" s="326">
+      <c r="N29" s="331">
         <v>3.47</v>
       </c>
-      <c r="O29" s="327">
+      <c r="O29" s="326">
         <v>-0.94</v>
       </c>
-      <c r="P29" s="328">
+      <c r="P29" s="335">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="335">
+      <c r="Q29" s="327">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="336">
+      <c r="R29" s="333">
         <v>0.11</v>
       </c>
-      <c r="S29" s="330">
+      <c r="S29" s="328">
         <v>2.42</v>
       </c>
-      <c r="T29" s="332">
-        <v>9.85</v>
+      <c r="T29" s="329">
+        <v>13.65</v>
       </c>
     </row>
     <row r="30">
@@ -10417,41 +10593,41 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="344">
+      <c r="I30" s="338">
         <v>1.85</v>
       </c>
-      <c r="J30" s="348">
+      <c r="J30" s="340">
         <v>7.78</v>
       </c>
-      <c r="K30" s="345">
+      <c r="K30" s="339">
         <v>13.84</v>
       </c>
-      <c r="L30" s="341">
+      <c r="L30" s="342">
         <v>11.93</v>
       </c>
-      <c r="M30" s="338">
+      <c r="M30" s="347">
         <v>5.23</v>
       </c>
-      <c r="N30" s="342">
+      <c r="N30" s="343">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="346">
+      <c r="O30" s="348">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="343">
+      <c r="P30" s="337">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="339">
+      <c r="Q30" s="344">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="337">
+      <c r="R30" s="341">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="347">
+      <c r="S30" s="345">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="340">
-        <v>-12.82</v>
+      <c r="T30" s="346">
+        <v>-14.22</v>
       </c>
     </row>
     <row r="31">
@@ -10479,41 +10655,41 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="360">
+      <c r="I31" s="349">
         <v>1.82</v>
       </c>
-      <c r="J31" s="352">
+      <c r="J31" s="356">
         <v>6.88</v>
       </c>
-      <c r="K31" s="353">
+      <c r="K31" s="357">
         <v>4.25</v>
       </c>
-      <c r="L31" s="357">
+      <c r="L31" s="358">
         <v>1.42</v>
       </c>
-      <c r="M31" s="358">
+      <c r="M31" s="359">
         <v>-7.09</v>
       </c>
-      <c r="N31" s="349">
+      <c r="N31" s="350">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="350">
+      <c r="O31" s="353">
         <v>-10.32</v>
       </c>
       <c r="P31" s="351">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="359">
+      <c r="Q31" s="354">
         <v>-17</v>
       </c>
-      <c r="R31" s="354">
+      <c r="R31" s="355">
         <v>-16.8</v>
       </c>
-      <c r="S31" s="355">
+      <c r="S31" s="352">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="356">
-        <v>-19.84</v>
+      <c r="T31" s="360">
+        <v>-18.62</v>
       </c>
     </row>
     <row r="32">
@@ -10544,16 +10720,16 @@
       <c r="I32" s="361">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="366">
+      <c r="J32" s="363">
         <v>0.27</v>
       </c>
-      <c r="K32" s="367">
+      <c r="K32" s="362">
         <v>2.99</v>
       </c>
-      <c r="L32" s="371">
+      <c r="L32" s="370">
         <v>2.35</v>
       </c>
-      <c r="M32" s="362">
+      <c r="M32" s="367">
         <v>0.72</v>
       </c>
       <c r="N32" s="368">
@@ -10562,20 +10738,20 @@
       <c r="O32" s="364">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="369">
+      <c r="P32" s="365">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="365">
+      <c r="Q32" s="369">
         <v>3.26</v>
       </c>
-      <c r="R32" s="372">
+      <c r="R32" s="366">
         <v>1</v>
       </c>
-      <c r="S32" s="370">
+      <c r="S32" s="371">
         <v>1.45</v>
       </c>
-      <c r="T32" s="363">
-        <v>8.6</v>
+      <c r="T32" s="372">
+        <v>5.88</v>
       </c>
     </row>
     <row r="33">
@@ -10603,41 +10779,41 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="380">
+      <c r="I33" s="376">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="381">
+      <c r="J33" s="380">
         <v>0.57</v>
       </c>
       <c r="K33" s="377">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="373">
+      <c r="L33" s="378">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="382">
+      <c r="M33" s="384">
         <v>-13.04</v>
       </c>
       <c r="N33" s="383">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="374">
+      <c r="O33" s="379">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="375">
+      <c r="P33" s="381">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="384">
+      <c r="Q33" s="382">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="378">
+      <c r="R33" s="373">
         <v>-20.6</v>
       </c>
-      <c r="S33" s="379">
+      <c r="S33" s="374">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="376">
-        <v>-21.17</v>
+      <c r="T33" s="375">
+        <v>-20.98</v>
       </c>
     </row>
     <row r="34">
@@ -10665,25 +10841,25 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="389">
+      <c r="I34" s="393">
         <v>-3</v>
       </c>
-      <c r="J34" s="392">
+      <c r="J34" s="394">
         <v>-7.14</v>
       </c>
       <c r="K34" s="390">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="385">
+      <c r="L34" s="395">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="386">
+      <c r="M34" s="391">
         <v>-16.82</v>
       </c>
-      <c r="N34" s="393">
+      <c r="N34" s="396">
         <v>-18.2</v>
       </c>
-      <c r="O34" s="394">
+      <c r="O34" s="392">
         <v>-16.59</v>
       </c>
       <c r="P34" s="387">
@@ -10692,14 +10868,14 @@
       <c r="Q34" s="388">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="391">
+      <c r="R34" s="389">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="395">
+      <c r="S34" s="385">
         <v>-21.43</v>
       </c>
-      <c r="T34" s="396">
-        <v>-21.43</v>
+      <c r="T34" s="386">
+        <v>-20.51</v>
       </c>
     </row>
     <row r="35">
@@ -10727,41 +10903,41 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="406">
+      <c r="I35" s="402">
         <v>4.2</v>
       </c>
-      <c r="J35" s="399">
+      <c r="J35" s="400">
         <v>3.72</v>
       </c>
-      <c r="K35" s="407">
+      <c r="K35" s="403">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="400">
+      <c r="L35" s="404">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="401">
+      <c r="M35" s="397">
         <v>-3.1</v>
       </c>
       <c r="N35" s="405">
         <v>6.61</v>
       </c>
-      <c r="O35" s="408">
+      <c r="O35" s="406">
         <v>5.5</v>
       </c>
-      <c r="P35" s="402">
+      <c r="P35" s="407">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="397">
+      <c r="Q35" s="408">
         <v>1.68</v>
       </c>
-      <c r="R35" s="398">
+      <c r="R35" s="401">
         <v>1.37</v>
       </c>
-      <c r="S35" s="403">
+      <c r="S35" s="398">
         <v>0.08</v>
       </c>
-      <c r="T35" s="404">
-        <v>0.66</v>
+      <c r="T35" s="399">
+        <v>0.85</v>
       </c>
     </row>
     <row r="36">
@@ -10789,41 +10965,41 @@
       <c r="H36">
         <v>-3.03</v>
       </c>
-      <c r="I36" s="414">
+      <c r="I36" s="410">
         <v>5.57</v>
       </c>
-      <c r="J36" s="409">
+      <c r="J36" s="411">
         <v>16.17</v>
       </c>
-      <c r="K36" s="410">
+      <c r="K36" s="416">
         <v>22.01</v>
       </c>
-      <c r="L36" s="416">
+      <c r="L36" s="413">
         <v>16.85</v>
       </c>
-      <c r="M36" s="411">
+      <c r="M36" s="417">
         <v>7.07</v>
       </c>
-      <c r="N36" s="419">
+      <c r="N36" s="420">
         <v>0.27</v>
       </c>
-      <c r="O36" s="412">
+      <c r="O36" s="414">
         <v>2.45</v>
       </c>
-      <c r="P36" s="420">
+      <c r="P36" s="415">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="415">
+      <c r="Q36" s="418">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="413">
+      <c r="R36" s="409">
         <v>9.65</v>
       </c>
-      <c r="S36" s="417">
+      <c r="S36" s="412">
         <v>7.47</v>
       </c>
-      <c r="T36" s="418">
-        <v>3.4</v>
+      <c r="T36" s="419">
+        <v>1.49</v>
       </c>
     </row>
     <row r="37">
@@ -10851,41 +11027,41 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="421">
+      <c r="I37" s="425">
         <v>-2.93</v>
       </c>
       <c r="J37" s="426">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="422">
+      <c r="K37" s="427">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="423">
+      <c r="L37" s="430">
         <v>7.57</v>
       </c>
-      <c r="M37" s="427">
+      <c r="M37" s="423">
         <v>5.6</v>
       </c>
-      <c r="N37" s="428">
+      <c r="N37" s="431">
         <v>4.48</v>
       </c>
-      <c r="O37" s="431">
+      <c r="O37" s="432">
         <v>3.32</v>
       </c>
-      <c r="P37" s="429">
+      <c r="P37" s="428">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="432">
+      <c r="Q37" s="429">
         <v>3.78</v>
       </c>
-      <c r="R37" s="424">
+      <c r="R37" s="421">
         <v>8.07</v>
       </c>
-      <c r="S37" s="430">
+      <c r="S37" s="422">
         <v>11.74</v>
       </c>
-      <c r="T37" s="425">
-        <v>11.93</v>
+      <c r="T37" s="424">
+        <v>7.72</v>
       </c>
     </row>
     <row r="38">
@@ -10913,39 +11089,41 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="437">
+      <c r="I38" s="441">
         <v>6.62</v>
       </c>
       <c r="J38" s="440">
         <v>10.07</v>
       </c>
-      <c r="K38" s="435">
+      <c r="K38" s="442">
         <v>6.26</v>
       </c>
-      <c r="L38" s="441">
+      <c r="L38" s="443">
         <v>2.13</v>
       </c>
-      <c r="M38" s="442">
+      <c r="M38" s="444">
         <v>1.41</v>
       </c>
-      <c r="N38" s="443">
+      <c r="N38" s="433">
         <v>7.72</v>
       </c>
-      <c r="O38" s="433">
+      <c r="O38" s="434">
         <v>5.74</v>
       </c>
-      <c r="P38" s="438">
+      <c r="P38" s="436">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="436">
+      <c r="Q38" s="435">
         <v>14.45</v>
       </c>
-      <c r="R38" s="439">
+      <c r="R38" s="437">
         <v>18.62</v>
       </c>
-      <c r="S38" t="str"/>
-      <c r="T38" s="434">
-        <v>18.62</v>
+      <c r="S38" s="438">
+        <v>14.8</v>
+      </c>
+      <c r="T38" s="439">
+        <v>14.8</v>
       </c>
     </row>
     <row r="39">
@@ -10973,37 +11151,39 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="448">
+      <c r="I39" s="452">
         <v>7.14</v>
       </c>
       <c r="J39" s="453">
         <v>7.82</v>
       </c>
-      <c r="K39" s="444">
+      <c r="K39" s="449">
         <v>7.68</v>
       </c>
-      <c r="L39" s="445">
+      <c r="L39" s="454">
         <v>8.49</v>
       </c>
-      <c r="M39" s="446">
+      <c r="M39" s="450">
         <v>9.43</v>
       </c>
-      <c r="N39" s="450">
+      <c r="N39" s="451">
         <v>5.39</v>
       </c>
-      <c r="O39" s="447">
+      <c r="O39" s="455">
         <v>8.49</v>
       </c>
-      <c r="P39" s="449">
+      <c r="P39" s="448">
         <v>7.28</v>
       </c>
-      <c r="Q39" s="451">
+      <c r="Q39" s="446">
         <v>11.99</v>
       </c>
-      <c r="R39" t="str"/>
+      <c r="R39" s="447">
+        <v>7.95</v>
+      </c>
       <c r="S39" t="str"/>
-      <c r="T39" s="452">
-        <v>11.99</v>
+      <c r="T39" s="445">
+        <v>7.95</v>
       </c>
     </row>
     <row r="40">
@@ -11031,35 +11211,37 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="454">
+      <c r="I40" s="462">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="455">
+      <c r="J40" s="459">
         <v>-0.66</v>
       </c>
-      <c r="K40" s="459">
+      <c r="K40" s="463">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="460">
+      <c r="L40" s="458">
         <v>0</v>
       </c>
       <c r="M40" s="461">
         <v>-1.31</v>
       </c>
-      <c r="N40" s="457">
+      <c r="N40" s="464">
         <v>0.33</v>
       </c>
-      <c r="O40" s="456">
+      <c r="O40" s="465">
         <v>0</v>
       </c>
-      <c r="P40" s="458">
+      <c r="P40" s="460">
         <v>1.97</v>
       </c>
-      <c r="Q40" t="str"/>
+      <c r="Q40" s="456">
+        <v>-0.22</v>
+      </c>
       <c r="R40" t="str"/>
       <c r="S40" t="str"/>
-      <c r="T40" s="462">
-        <v>1.97</v>
+      <c r="T40" s="457">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="41">
@@ -11087,33 +11269,35 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="466">
+      <c r="I41" s="467">
         <v>0.59</v>
       </c>
-      <c r="J41" s="467">
+      <c r="J41" s="471">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="468">
+      <c r="K41" s="469">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="469">
+      <c r="L41" s="470">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="470">
+      <c r="M41" s="468">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="463">
+      <c r="N41" s="474">
         <v>-7.55</v>
       </c>
-      <c r="O41" s="464">
+      <c r="O41" s="466">
         <v>-6.76</v>
       </c>
-      <c r="P41" t="str"/>
+      <c r="P41" s="472">
+        <v>-8.43</v>
+      </c>
       <c r="Q41" t="str"/>
       <c r="R41" t="str"/>
       <c r="S41" t="str"/>
-      <c r="T41" s="465">
-        <v>-6.76</v>
+      <c r="T41" s="473">
+        <v>-8.43</v>
       </c>
     </row>
     <row r="42">
@@ -11141,13 +11325,13 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="472">
+      <c r="I42" s="480">
         <v>2.08</v>
       </c>
-      <c r="J42" s="473">
+      <c r="J42" s="481">
         <v>2.7</v>
       </c>
-      <c r="K42" s="474">
+      <c r="K42" s="482">
         <v>0</v>
       </c>
       <c r="L42" s="475">
@@ -11159,13 +11343,15 @@
       <c r="N42" s="477">
         <v>1.56</v>
       </c>
-      <c r="O42" t="str"/>
+      <c r="O42" s="478">
+        <v>-0.52</v>
+      </c>
       <c r="P42" t="str"/>
       <c r="Q42" t="str"/>
       <c r="R42" t="str"/>
       <c r="S42" t="str"/>
-      <c r="T42" s="471">
-        <v>1.56</v>
+      <c r="T42" s="479">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="43">
@@ -11193,29 +11379,31 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="480">
+      <c r="I43" s="488">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="481">
+      <c r="J43" s="489">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="482">
+      <c r="K43" s="483">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="483">
+      <c r="L43" s="484">
         <v>8.46</v>
       </c>
-      <c r="M43" s="478">
+      <c r="M43" s="485">
         <v>10.98</v>
       </c>
-      <c r="N43" t="str"/>
+      <c r="N43" s="486">
+        <v>10.41</v>
+      </c>
       <c r="O43" t="str"/>
       <c r="P43" t="str"/>
       <c r="Q43" t="str"/>
       <c r="R43" t="str"/>
       <c r="S43" t="str"/>
-      <c r="T43" s="479">
-        <v>10.98</v>
+      <c r="T43" s="487">
+        <v>10.41</v>
       </c>
     </row>
     <row r="44">
@@ -11243,27 +11431,29 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="488">
+      <c r="I44" s="494">
         <v>10.68</v>
       </c>
-      <c r="J44" s="484">
+      <c r="J44" s="495">
         <v>1.78</v>
       </c>
-      <c r="K44" s="485">
+      <c r="K44" s="490">
         <v>-1.94</v>
       </c>
-      <c r="L44" s="486">
+      <c r="L44" s="491">
         <v>3.72</v>
       </c>
-      <c r="M44" t="str"/>
+      <c r="M44" s="492">
+        <v>2.1</v>
+      </c>
       <c r="N44" t="str"/>
       <c r="O44" t="str"/>
       <c r="P44" t="str"/>
       <c r="Q44" t="str"/>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="487">
-        <v>3.72</v>
+      <c r="T44" s="493">
+        <v>2.1</v>
       </c>
     </row>
     <row r="45">
@@ -11291,16 +11481,18 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="489">
+      <c r="I45" s="496">
         <v>2.03</v>
       </c>
-      <c r="J45" s="490">
+      <c r="J45" s="497">
         <v>5.03</v>
       </c>
-      <c r="K45" s="491">
+      <c r="K45" s="498">
         <v>5.82</v>
       </c>
-      <c r="L45" t="str"/>
+      <c r="L45" s="499">
+        <v>3.17</v>
+      </c>
       <c r="M45" t="str"/>
       <c r="N45" t="str"/>
       <c r="O45" t="str"/>
@@ -11308,8 +11500,8 @@
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="492">
-        <v>5.82</v>
+      <c r="T45" s="500">
+        <v>3.17</v>
       </c>
     </row>
     <row r="46">
@@ -11337,10 +11529,12 @@
       <c r="H46">
         <v>-0.93</v>
       </c>
-      <c r="I46" s="493">
+      <c r="I46" s="501">
         <v>1.8</v>
       </c>
-      <c r="J46" t="str"/>
+      <c r="J46" s="502">
+        <v>0.31</v>
+      </c>
       <c r="K46" t="str"/>
       <c r="L46" t="str"/>
       <c r="M46" t="str"/>
@@ -11350,59 +11544,53 @@
       <c r="Q46" t="str"/>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" t="str"/>
+      <c r="T46" s="503">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B47" t="str"/>
-      <c r="C47" t="str"/>
-      <c r="D47" t="str"/>
-      <c r="E47" t="str"/>
-      <c r="F47" t="str"/>
-      <c r="G47" t="str"/>
-      <c r="H47" t="str"/>
-      <c r="I47">
-        <v>45</v>
-      </c>
-      <c r="J47">
-        <v>44</v>
-      </c>
-      <c r="K47">
-        <v>44</v>
-      </c>
-      <c r="L47">
-        <v>43</v>
-      </c>
-      <c r="M47">
-        <v>42</v>
-      </c>
-      <c r="N47">
-        <v>41</v>
-      </c>
-      <c r="O47">
-        <v>40</v>
-      </c>
-      <c r="P47">
-        <v>39</v>
-      </c>
-      <c r="Q47">
-        <v>38</v>
-      </c>
-      <c r="R47">
-        <v>37</v>
-      </c>
-      <c r="S47">
-        <v>36</v>
-      </c>
-      <c r="T47">
-        <v>44</v>
-      </c>
+        <v>2026-04-21</v>
+      </c>
+      <c r="B47" t="str">
+        <v>可川科技</v>
+      </c>
+      <c r="C47" t="str">
+        <v>603052</v>
+      </c>
+      <c r="D47" t="str">
+        <v>(09:27:00)跑步进场可川科技</v>
+      </c>
+      <c r="E47">
+        <v>92.02</v>
+      </c>
+      <c r="F47">
+        <v>90.3</v>
+      </c>
+      <c r="G47">
+        <v>92.02</v>
+      </c>
+      <c r="H47">
+        <v>0.36</v>
+      </c>
+      <c r="I47" s="504">
+        <v>-1.87</v>
+      </c>
+      <c r="J47" t="str"/>
+      <c r="K47" t="str"/>
+      <c r="L47" t="str"/>
+      <c r="M47" t="str"/>
+      <c r="N47" t="str"/>
+      <c r="O47" t="str"/>
+      <c r="P47" t="str"/>
+      <c r="Q47" t="str"/>
+      <c r="R47" t="str"/>
+      <c r="S47" t="str"/>
+      <c r="T47" t="str"/>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B48" t="str"/>
       <c r="C48" t="str"/>
@@ -11411,46 +11599,46 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="500">
-        <v>60</v>
-      </c>
-      <c r="J48" s="494">
-        <v>59.09</v>
-      </c>
-      <c r="K48" s="495">
-        <v>52.27</v>
-      </c>
-      <c r="L48" s="496">
-        <v>58.14</v>
-      </c>
-      <c r="M48" s="497">
-        <v>54.76</v>
-      </c>
-      <c r="N48" s="501">
-        <v>56.1</v>
-      </c>
-      <c r="O48" s="504">
+      <c r="I48">
+        <v>46</v>
+      </c>
+      <c r="J48">
+        <v>45</v>
+      </c>
+      <c r="K48">
+        <v>44</v>
+      </c>
+      <c r="L48">
+        <v>44</v>
+      </c>
+      <c r="M48">
+        <v>43</v>
+      </c>
+      <c r="N48">
+        <v>42</v>
+      </c>
+      <c r="O48">
+        <v>41</v>
+      </c>
+      <c r="P48">
         <v>40</v>
       </c>
-      <c r="P48" s="498">
-        <v>43.59</v>
-      </c>
-      <c r="Q48" s="502">
-        <v>42.11</v>
-      </c>
-      <c r="R48" s="499">
-        <v>45.95</v>
-      </c>
-      <c r="S48" s="505">
-        <v>47.22</v>
-      </c>
-      <c r="T48" s="503">
-        <v>45.45</v>
+      <c r="Q48">
+        <v>39</v>
+      </c>
+      <c r="R48">
+        <v>38</v>
+      </c>
+      <c r="S48">
+        <v>37</v>
+      </c>
+      <c r="T48">
+        <v>45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B49" t="str"/>
       <c r="C49" t="str"/>
@@ -11459,41 +11647,89 @@
       <c r="F49" t="str"/>
       <c r="G49" t="str"/>
       <c r="H49" t="str"/>
-      <c r="I49" s="512">
-        <v>2.15</v>
-      </c>
-      <c r="J49" s="516">
-        <v>2.44</v>
-      </c>
-      <c r="K49" s="513">
+      <c r="I49" s="516">
+        <v>58.7</v>
+      </c>
+      <c r="J49" s="508">
+        <v>60</v>
+      </c>
+      <c r="K49" s="509">
+        <v>52.27</v>
+      </c>
+      <c r="L49" s="505">
+        <v>59.09</v>
+      </c>
+      <c r="M49" s="512">
+        <v>55.81</v>
+      </c>
+      <c r="N49" s="506">
+        <v>57.14</v>
+      </c>
+      <c r="O49" s="510">
+        <v>39.02</v>
+      </c>
+      <c r="P49" s="513">
+        <v>42.5</v>
+      </c>
+      <c r="Q49" s="511">
+        <v>41.03</v>
+      </c>
+      <c r="R49" s="507">
+        <v>47.37</v>
+      </c>
+      <c r="S49" s="514">
+        <v>48.65</v>
+      </c>
+      <c r="T49" s="515">
+        <v>42.22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B50" t="str"/>
+      <c r="C50" t="str"/>
+      <c r="D50" t="str"/>
+      <c r="E50" t="str"/>
+      <c r="F50" t="str"/>
+      <c r="G50" t="str"/>
+      <c r="H50" t="str"/>
+      <c r="I50" s="524">
+        <v>2.06</v>
+      </c>
+      <c r="J50" s="518">
+        <v>2.39</v>
+      </c>
+      <c r="K50" s="525">
         <v>1.89</v>
       </c>
-      <c r="L49" s="514">
-        <v>1.21</v>
-      </c>
-      <c r="M49" s="507">
-        <v>1.46</v>
-      </c>
-      <c r="N49" s="515">
-        <v>-0.11</v>
-      </c>
-      <c r="O49" s="508">
+      <c r="L50" s="526">
+        <v>1.25</v>
+      </c>
+      <c r="M50" s="521">
+        <v>1.47</v>
+      </c>
+      <c r="N50" s="519">
+        <v>0.14</v>
+      </c>
+      <c r="O50" s="527">
         <v>-0.41</v>
       </c>
-      <c r="P49" s="517">
-        <v>-0.2</v>
-      </c>
-      <c r="Q49" s="509">
+      <c r="P50" s="520">
+        <v>-0.41</v>
+      </c>
+      <c r="Q50" s="528">
         <v>-0.49</v>
       </c>
-      <c r="R49" s="510">
-        <v>0.53</v>
-      </c>
-      <c r="S49" s="511">
-        <v>0.34</v>
-      </c>
-      <c r="T49" s="506">
-        <v>-2.31</v>
+      <c r="R50" s="522">
+        <v>0.73</v>
+      </c>
+      <c r="S50" s="517">
+        <v>0.73</v>
+      </c>
+      <c r="T50" s="523">
+        <v>-2.74</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="530">
+  <fills count="566">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,97 +39,3307 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEFF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAADCB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE66E7A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0DEBA"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BEC3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF32AB4D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,37 +3351,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,391 +3399,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF7D4D7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -579,2634 +3411,270 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C2C7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3EB058"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8690"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="529">
+  <borders count="565">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6914,7 +7382,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="529">
+  <cellXfs count="565">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8498,6 +8966,114 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="528" fillId="529" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="529" fillId="530" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="530" fillId="531" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="531" fillId="532" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="532" fillId="533" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="533" fillId="534" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="534" fillId="535" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="535" fillId="536" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="536" fillId="537" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="537" fillId="538" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="538" fillId="539" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="539" fillId="540" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="540" fillId="541" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="541" fillId="542" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="542" fillId="543" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="543" fillId="544" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="544" fillId="545" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="545" fillId="546" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="546" fillId="547" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="547" fillId="548" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="548" fillId="549" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="549" fillId="550" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="550" fillId="551" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="551" fillId="552" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="552" fillId="553" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="553" fillId="554" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="554" fillId="555" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="555" fillId="556" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="556" fillId="557" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="557" fillId="558" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="558" fillId="559" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="559" fillId="560" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="560" fillId="561" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="561" fillId="562" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="562" fillId="563" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="563" fillId="564" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="564" fillId="565" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8857,41 +9433,41 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="5">
         <v>4.95</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="6">
         <v>1.74</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="7">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="12">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="8">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="9">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="3">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="10">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="1">
         <v>-4.59</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="4">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="2">
-        <v>-17.71</v>
+      <c r="T2" s="11">
+        <v>-17.8</v>
       </c>
     </row>
     <row r="3">
@@ -8919,10 +9495,10 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="15">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="20">
         <v>-0.41</v>
       </c>
       <c r="K3" s="16">
@@ -8931,29 +9507,29 @@
       <c r="L3" s="19">
         <v>0.1</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="17">
         <v>3.32</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="21">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="18">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="23">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="24">
         <v>2.8</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="13">
         <v>1.66</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="14">
         <v>-0.1</v>
       </c>
       <c r="T3" s="22">
-        <v>17.62</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="4">
@@ -8981,41 +9557,41 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="27">
         <v>4.19</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="36">
         <v>5.08</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="28">
         <v>15.59</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="29">
         <v>27.15</v>
       </c>
       <c r="M4" s="30">
         <v>36.04</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="34">
         <v>41.33</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="31">
         <v>37.54</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="35">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="25">
+      <c r="Q4" s="32">
         <v>32.33</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="25">
         <v>45.56</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="33">
         <v>56.03</v>
       </c>
-      <c r="T4" s="28">
-        <v>28.86</v>
+      <c r="T4" s="26">
+        <v>29.51</v>
       </c>
     </row>
     <row r="5">
@@ -9043,41 +9619,41 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="38">
+      <c r="I5" s="48">
         <v>11.97</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="44">
         <v>17.45</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="45">
         <v>14.27</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="37">
         <v>17.32</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="40">
         <v>25.33</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="46">
         <v>21.54</v>
       </c>
-      <c r="O5" s="37">
+      <c r="O5" s="41">
         <v>22.72</v>
       </c>
-      <c r="P5" s="39">
+      <c r="P5" s="42">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="38">
         <v>17.54</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="43">
         <v>16.88</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="47">
         <v>11.79</v>
       </c>
-      <c r="T5" s="46">
-        <v>26.94</v>
+      <c r="T5" s="39">
+        <v>29.59</v>
       </c>
     </row>
     <row r="6">
@@ -9105,41 +9681,41 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="54">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="50">
+      <c r="J6" s="55">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="49">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="51">
+      <c r="L6" s="50">
         <v>-0.66</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="52">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="55">
+      <c r="N6" s="51">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="52">
+      <c r="O6" s="59">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="56">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="57">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="60">
+      <c r="R6" s="58">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="53">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="58">
-        <v>-17.05</v>
+      <c r="T6" s="60">
+        <v>-18.9</v>
       </c>
     </row>
     <row r="7">
@@ -9167,41 +9743,41 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="65">
+      <c r="I7" s="66">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="61">
         <v>1.8</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="70">
         <v>0.07</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="62">
         <v>0.63</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="67">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="61">
+      <c r="N7" s="64">
         <v>1.55</v>
       </c>
       <c r="O7" s="68">
         <v>0.85</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="65">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="62">
+      <c r="Q7" s="71">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="72">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="63">
+      <c r="S7" s="69">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="64">
-        <v>10.63</v>
+      <c r="T7" s="63">
+        <v>10.34</v>
       </c>
     </row>
     <row r="8">
@@ -9229,41 +9805,41 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="79">
         <v>3.13</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="75">
         <v>5.21</v>
       </c>
-      <c r="K8" s="73">
+      <c r="K8" s="76">
         <v>0.43</v>
       </c>
-      <c r="L8" s="74">
+      <c r="L8" s="77">
         <v>3.68</v>
       </c>
-      <c r="M8" s="78">
+      <c r="M8" s="84">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="82">
         <v>1.66</v>
       </c>
-      <c r="O8" s="75">
+      <c r="O8" s="83">
         <v>1.72</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="73">
         <v>7.79</v>
       </c>
       <c r="Q8" s="80">
         <v>15.33</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="78">
         <v>12.57</v>
       </c>
-      <c r="S8" s="76">
+      <c r="S8" s="81">
         <v>23.85</v>
       </c>
-      <c r="T8" s="77">
-        <v>-13.18</v>
+      <c r="T8" s="74">
+        <v>-17.35</v>
       </c>
     </row>
     <row r="9">
@@ -9291,41 +9867,41 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="91">
+      <c r="I9" s="93">
         <v>1.35</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="90">
         <v>2.48</v>
       </c>
-      <c r="K9" s="88">
+      <c r="K9" s="91">
         <v>1.58</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="94">
         <v>1.35</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="95">
         <v>2.93</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="86">
         <v>0.23</v>
       </c>
-      <c r="O9" s="86">
+      <c r="O9" s="87">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="96">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="95">
+      <c r="Q9" s="85">
         <v>3.83</v>
       </c>
-      <c r="R9" s="87">
+      <c r="R9" s="92">
         <v>7.43</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="88">
         <v>17.12</v>
       </c>
-      <c r="T9" s="90">
-        <v>5.18</v>
+      <c r="T9" s="89">
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -9353,41 +9929,41 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="103">
+      <c r="I10" s="97">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="104">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="98">
         <v>-7.86</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="105">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="106">
         <v>-12.37</v>
       </c>
-      <c r="N10" s="104">
+      <c r="N10" s="107">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="99">
         <v>-9.15</v>
       </c>
-      <c r="P10" s="97">
+      <c r="P10" s="100">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="106">
+      <c r="Q10" s="101">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="98">
+      <c r="R10" s="102">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="99">
+      <c r="S10" s="103">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="100">
-        <v>-13.87</v>
+      <c r="T10" s="108">
+        <v>-15.08</v>
       </c>
     </row>
     <row r="11">
@@ -9415,41 +9991,41 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="109">
+      <c r="I11" s="113">
         <v>7.32</v>
       </c>
       <c r="J11" s="114">
         <v>7.76</v>
       </c>
-      <c r="K11" s="115">
+      <c r="K11" s="119">
         <v>15.37</v>
       </c>
-      <c r="L11" s="117">
+      <c r="L11" s="115">
         <v>8.64</v>
       </c>
       <c r="M11" s="110">
         <v>0.59</v>
       </c>
-      <c r="N11" s="116">
+      <c r="N11" s="111">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="111">
+      <c r="O11" s="120">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="118">
+      <c r="P11" s="116">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="109">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="112">
+      <c r="R11" s="117">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="113">
+      <c r="S11" s="112">
         <v>0.15</v>
       </c>
-      <c r="T11" s="120">
-        <v>-22.25</v>
+      <c r="T11" s="118">
+        <v>-22.55</v>
       </c>
     </row>
     <row r="12">
@@ -9477,41 +10053,41 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="124">
         <v>10.48</v>
       </c>
       <c r="J12" s="121">
         <v>13.87</v>
       </c>
-      <c r="K12" s="127">
+      <c r="K12" s="125">
         <v>4.11</v>
       </c>
-      <c r="L12" s="130">
+      <c r="L12" s="122">
         <v>6.13</v>
       </c>
-      <c r="M12" s="123">
+      <c r="M12" s="132">
         <v>9.68</v>
       </c>
-      <c r="N12" s="124">
+      <c r="N12" s="129">
         <v>2.66</v>
       </c>
-      <c r="O12" s="128">
+      <c r="O12" s="130">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="123">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="125">
+      <c r="Q12" s="126">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="122">
+      <c r="R12" s="131">
         <v>0.97</v>
       </c>
-      <c r="S12" s="129">
+      <c r="S12" s="127">
         <v>3.06</v>
       </c>
-      <c r="T12" s="126">
-        <v>-22.74</v>
+      <c r="T12" s="128">
+        <v>-26.69</v>
       </c>
     </row>
     <row r="13">
@@ -9539,41 +10115,41 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="139">
+      <c r="I13" s="135">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="140">
+      <c r="J13" s="136">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="143">
+      <c r="K13" s="139">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="135">
+      <c r="L13" s="137">
         <v>-8.03</v>
       </c>
       <c r="M13" s="144">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="136">
+      <c r="N13" s="133">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="141">
+      <c r="O13" s="140">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="133">
+      <c r="P13" s="141">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="137">
+      <c r="Q13" s="138">
         <v>-4.93</v>
       </c>
-      <c r="R13" s="138">
+      <c r="R13" s="143">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="134">
+      <c r="S13" s="142">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="142">
-        <v>-16.65</v>
+      <c r="T13" s="134">
+        <v>-15.62</v>
       </c>
     </row>
     <row r="14">
@@ -9601,41 +10177,41 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="146">
+      <c r="I14" s="155">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="154">
+      <c r="J14" s="151">
         <v>-5</v>
       </c>
-      <c r="K14" s="147">
+      <c r="K14" s="146">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="155">
+      <c r="L14" s="149">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="148">
+      <c r="M14" s="152">
         <v>-7.37</v>
       </c>
       <c r="N14" s="150">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="151">
+      <c r="O14" s="156">
         <v>-9.38</v>
       </c>
       <c r="P14" s="153">
         <v>-5.63</v>
       </c>
-      <c r="Q14" s="149">
+      <c r="Q14" s="154">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="156">
+      <c r="R14" s="147">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="152">
+      <c r="S14" s="148">
         <v>0</v>
       </c>
       <c r="T14" s="145">
-        <v>-6.75</v>
+        <v>-9.38</v>
       </c>
     </row>
     <row r="15">
@@ -9663,41 +10239,41 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="168">
+      <c r="I15" s="166">
         <v>9.9</v>
       </c>
       <c r="J15" s="157">
         <v>9.43</v>
       </c>
-      <c r="K15" s="165">
+      <c r="K15" s="160">
         <v>8.82</v>
       </c>
-      <c r="L15" s="166">
+      <c r="L15" s="163">
         <v>4.15</v>
       </c>
-      <c r="M15" s="158">
+      <c r="M15" s="167">
         <v>7.79</v>
       </c>
-      <c r="N15" s="161">
+      <c r="N15" s="164">
         <v>1.3</v>
       </c>
-      <c r="O15" s="162">
+      <c r="O15" s="158">
         <v>8.69</v>
       </c>
-      <c r="P15" s="163">
+      <c r="P15" s="168">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="167">
+      <c r="Q15" s="159">
         <v>5.84</v>
       </c>
-      <c r="R15" s="164">
+      <c r="R15" s="161">
         <v>6.88</v>
       </c>
-      <c r="S15" s="159">
+      <c r="S15" s="165">
         <v>2.34</v>
       </c>
-      <c r="T15" s="160">
-        <v>-7.31</v>
+      <c r="T15" s="162">
+        <v>-13.41</v>
       </c>
     </row>
     <row r="16">
@@ -9728,38 +10304,38 @@
       <c r="I16" s="175">
         <v>2.67</v>
       </c>
-      <c r="J16" s="170">
+      <c r="J16" s="169">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="171">
+      <c r="K16" s="170">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="179">
+      <c r="L16" s="178">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="172">
+      <c r="M16" s="176">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="177">
+      <c r="N16" s="179">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="180">
+      <c r="O16" s="171">
         <v>-4.85</v>
       </c>
-      <c r="P16" s="176">
+      <c r="P16" s="174">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="173">
+      <c r="Q16" s="172">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="178">
+      <c r="R16" s="173">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="174">
+      <c r="S16" s="177">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="169">
-        <v>-21.76</v>
+      <c r="T16" s="180">
+        <v>-28.24</v>
       </c>
     </row>
     <row r="17">
@@ -9787,41 +10363,41 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="184">
+      <c r="I17" s="188">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="188">
+      <c r="J17" s="182">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="182">
+      <c r="K17" s="189">
         <v>0.2</v>
       </c>
-      <c r="L17" s="189">
+      <c r="L17" s="181">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="185">
+      <c r="M17" s="183">
         <v>0.53</v>
       </c>
-      <c r="N17" s="186">
+      <c r="N17" s="184">
         <v>3.31</v>
       </c>
-      <c r="O17" s="183">
+      <c r="O17" s="190">
         <v>6.89</v>
       </c>
-      <c r="P17" s="192">
+      <c r="P17" s="191">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="187">
+      <c r="Q17" s="192">
         <v>4.09</v>
       </c>
-      <c r="R17" s="190">
+      <c r="R17" s="185">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="191">
+      <c r="S17" s="186">
         <v>-1.45</v>
       </c>
-      <c r="T17" s="181">
-        <v>-3.42</v>
+      <c r="T17" s="187">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="18">
@@ -9849,41 +10425,41 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="201">
+      <c r="I18" s="200">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="195">
+      <c r="J18" s="203">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="203">
+      <c r="K18" s="201">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="196">
+      <c r="L18" s="194">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="197">
+      <c r="M18" s="195">
         <v>-11.63</v>
       </c>
       <c r="N18" s="204">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="202">
+      <c r="O18" s="198">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="200">
+      <c r="P18" s="196">
         <v>-16.73</v>
       </c>
       <c r="Q18" s="193">
         <v>-20.52</v>
       </c>
-      <c r="R18" s="194">
+      <c r="R18" s="202">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="198">
+      <c r="S18" s="199">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="199">
-        <v>-25.88</v>
+      <c r="T18" s="197">
+        <v>-27.32</v>
       </c>
     </row>
     <row r="19">
@@ -9911,41 +10487,41 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="207">
+      <c r="I19" s="213">
         <v>1.39</v>
       </c>
-      <c r="J19" s="208">
+      <c r="J19" s="212">
         <v>0.39</v>
       </c>
-      <c r="K19" s="209">
+      <c r="K19" s="206">
         <v>1.93</v>
       </c>
-      <c r="L19" s="215">
+      <c r="L19" s="207">
         <v>3.7</v>
       </c>
-      <c r="M19" s="210">
+      <c r="M19" s="208">
         <v>9.45</v>
       </c>
-      <c r="N19" s="212">
+      <c r="N19" s="209">
         <v>5.75</v>
       </c>
-      <c r="O19" s="205">
+      <c r="O19" s="210">
         <v>12.85</v>
       </c>
-      <c r="P19" s="213">
+      <c r="P19" s="214">
         <v>8.68</v>
       </c>
-      <c r="Q19" s="216">
+      <c r="Q19" s="211">
         <v>14.74</v>
       </c>
-      <c r="R19" s="211">
+      <c r="R19" s="215">
         <v>14.89</v>
       </c>
-      <c r="S19" s="206">
+      <c r="S19" s="216">
         <v>9.1</v>
       </c>
-      <c r="T19" s="214">
-        <v>12.54</v>
+      <c r="T19" s="205">
+        <v>14.89</v>
       </c>
     </row>
     <row r="20">
@@ -9973,41 +10549,41 @@
       <c r="H20">
         <v>-1.89</v>
       </c>
-      <c r="I20" s="222">
+      <c r="I20" s="228">
         <v>1.85</v>
       </c>
       <c r="J20" s="217">
         <v>8.14</v>
       </c>
-      <c r="K20" s="218">
+      <c r="K20" s="226">
         <v>2.43</v>
       </c>
       <c r="L20" s="227">
         <v>1.09</v>
       </c>
-      <c r="M20" s="228">
+      <c r="M20" s="222">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="219">
+      <c r="N20" s="218">
         <v>-0.76</v>
       </c>
-      <c r="O20" s="220">
+      <c r="O20" s="223">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="223">
+      <c r="P20" s="219">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="224">
+      <c r="Q20" s="220">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="225">
+      <c r="R20" s="221">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="226">
+      <c r="S20" s="224">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="221">
-        <v>-7.39</v>
+      <c r="T20" s="225">
+        <v>-9.91</v>
       </c>
     </row>
     <row r="21">
@@ -10035,41 +10611,41 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="238">
+      <c r="I21" s="231">
         <v>8.65</v>
       </c>
-      <c r="J21" s="229">
+      <c r="J21" s="240">
         <v>9.13</v>
       </c>
-      <c r="K21" s="235">
+      <c r="K21" s="229">
         <v>12.02</v>
       </c>
-      <c r="L21" s="230">
+      <c r="L21" s="232">
         <v>9.13</v>
       </c>
-      <c r="M21" s="236">
+      <c r="M21" s="233">
         <v>12.86</v>
       </c>
-      <c r="N21" s="231">
+      <c r="N21" s="236">
         <v>8.29</v>
       </c>
-      <c r="O21" s="239">
+      <c r="O21" s="237">
         <v>0.36</v>
       </c>
-      <c r="P21" s="232">
+      <c r="P21" s="238">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="234">
+      <c r="Q21" s="239">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="237">
+      <c r="R21" s="230">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="233">
+      <c r="S21" s="234">
         <v>2.04</v>
       </c>
-      <c r="T21" s="240">
-        <v>-0.72</v>
+      <c r="T21" s="235">
+        <v>-3.73</v>
       </c>
     </row>
     <row r="22">
@@ -10097,41 +10673,41 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="249">
+      <c r="I22" s="243">
         <v>9.66</v>
       </c>
-      <c r="J22" s="245">
+      <c r="J22" s="252">
         <v>14</v>
       </c>
-      <c r="K22" s="250">
+      <c r="K22" s="241">
         <v>19.72</v>
       </c>
-      <c r="L22" s="242">
+      <c r="L22" s="249">
         <v>17.55</v>
       </c>
-      <c r="M22" s="248">
+      <c r="M22" s="242">
         <v>15.78</v>
       </c>
-      <c r="N22" s="246">
+      <c r="N22" s="245">
         <v>6.9</v>
       </c>
-      <c r="O22" s="243">
+      <c r="O22" s="246">
         <v>0.99</v>
       </c>
-      <c r="P22" s="251">
+      <c r="P22" s="247">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="252">
+      <c r="Q22" s="250">
         <v>8.88</v>
       </c>
-      <c r="R22" s="244">
+      <c r="R22" s="251">
         <v>4.73</v>
       </c>
-      <c r="S22" s="241">
+      <c r="S22" s="248">
         <v>5.92</v>
       </c>
-      <c r="T22" s="247">
-        <v>-3.75</v>
+      <c r="T22" s="244">
+        <v>-14</v>
       </c>
     </row>
     <row r="23">
@@ -10159,41 +10735,41 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="257">
+      <c r="I23" s="260">
         <v>5.78</v>
       </c>
-      <c r="J23" s="262">
+      <c r="J23" s="261">
         <v>3.91</v>
       </c>
-      <c r="K23" s="263">
+      <c r="K23" s="258">
         <v>6.83</v>
       </c>
-      <c r="L23" s="260">
+      <c r="L23" s="264">
         <v>4.79</v>
       </c>
-      <c r="M23" s="264">
+      <c r="M23" s="259">
         <v>5.08</v>
       </c>
       <c r="N23" s="253">
         <v>4.5</v>
       </c>
-      <c r="O23" s="255">
+      <c r="O23" s="262">
         <v>1.4</v>
       </c>
       <c r="P23" s="254">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="261">
+      <c r="Q23" s="263">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="258">
+      <c r="R23" s="255">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="259">
+      <c r="S23" s="256">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="256">
-        <v>4.79</v>
+      <c r="T23" s="257">
+        <v>6.42</v>
       </c>
     </row>
     <row r="24">
@@ -10221,25 +10797,25 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="270">
+      <c r="I24" s="271">
         <v>-0.93</v>
       </c>
       <c r="J24" s="275">
         <v>-2.54</v>
       </c>
-      <c r="K24" s="276">
+      <c r="K24" s="265">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="265">
+      <c r="L24" s="276">
         <v>-12.46</v>
       </c>
-      <c r="M24" s="272">
+      <c r="M24" s="274">
         <v>-11.46</v>
       </c>
-      <c r="N24" s="271">
+      <c r="N24" s="266">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="266">
+      <c r="O24" s="272">
         <v>-7.66</v>
       </c>
       <c r="P24" s="267">
@@ -10248,14 +10824,14 @@
       <c r="Q24" s="268">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="273">
+      <c r="R24" s="269">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="274">
+      <c r="S24" s="273">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="269">
-        <v>-14.23</v>
+      <c r="T24" s="270">
+        <v>-6.33</v>
       </c>
     </row>
     <row r="25">
@@ -10283,41 +10859,41 @@
       <c r="H25">
         <v>-1.47</v>
       </c>
-      <c r="I25" s="277">
+      <c r="I25" s="285">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="282">
+      <c r="J25" s="287">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="278">
+      <c r="K25" s="286">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="283">
+      <c r="L25" s="280">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="287">
+      <c r="M25" s="281">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="279">
+      <c r="N25" s="278">
         <v>-8.15</v>
       </c>
       <c r="O25" s="288">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="284">
+      <c r="P25" s="277">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="286">
+      <c r="Q25" s="279">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="280">
+      <c r="R25" s="282">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="285">
+      <c r="S25" s="283">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="281">
-        <v>-10.71</v>
+      <c r="T25" s="284">
+        <v>-15.3</v>
       </c>
     </row>
     <row r="26">
@@ -10345,41 +10921,41 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="296">
+      <c r="I26" s="295">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="299">
+      <c r="J26" s="296">
         <v>0.56</v>
       </c>
       <c r="K26" s="297">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="291">
+      <c r="L26" s="290">
         <v>-7.91</v>
       </c>
       <c r="M26" s="298">
         <v>1.36</v>
       </c>
-      <c r="N26" s="300">
+      <c r="N26" s="291">
         <v>3.39</v>
       </c>
-      <c r="O26" s="289">
+      <c r="O26" s="292">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="290">
+      <c r="P26" s="293">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="292">
+      <c r="Q26" s="289">
         <v>7.01</v>
       </c>
-      <c r="R26" s="294">
+      <c r="R26" s="299">
         <v>12.66</v>
       </c>
-      <c r="S26" s="293">
+      <c r="S26" s="294">
         <v>6.55</v>
       </c>
-      <c r="T26" s="295">
-        <v>-9.04</v>
+      <c r="T26" s="300">
+        <v>-12.2</v>
       </c>
     </row>
     <row r="27">
@@ -10407,41 +10983,41 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="304">
+      <c r="I27" s="308">
         <v>-1.23</v>
       </c>
-      <c r="J27" s="309">
+      <c r="J27" s="301">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="306">
+      <c r="K27" s="304">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="311">
+      <c r="L27" s="305">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="312">
+      <c r="M27" s="306">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="305">
+      <c r="N27" s="309">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="301">
+      <c r="O27" s="310">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="310">
+      <c r="P27" s="311">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="307">
+      <c r="Q27" s="302">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="302">
+      <c r="R27" s="307">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="303">
+      <c r="S27" s="312">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="308">
-        <v>-13.48</v>
+      <c r="T27" s="303">
+        <v>-12.17</v>
       </c>
     </row>
     <row r="28">
@@ -10469,41 +11045,41 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="322">
+      <c r="I28" s="324">
         <v>1.28</v>
       </c>
-      <c r="J28" s="313">
+      <c r="J28" s="318">
         <v>2.92</v>
       </c>
-      <c r="K28" s="316">
+      <c r="K28" s="319">
         <v>4.72</v>
       </c>
-      <c r="L28" s="317">
+      <c r="L28" s="314">
         <v>6.25</v>
       </c>
-      <c r="M28" s="323">
+      <c r="M28" s="316">
         <v>16.86</v>
       </c>
-      <c r="N28" s="314">
+      <c r="N28" s="320">
         <v>13.12</v>
       </c>
-      <c r="O28" s="318">
+      <c r="O28" s="321">
         <v>24.45</v>
       </c>
-      <c r="P28" s="319">
+      <c r="P28" s="317">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="324">
+      <c r="Q28" s="322">
         <v>46.03</v>
       </c>
-      <c r="R28" s="320">
+      <c r="R28" s="315">
         <v>45.46</v>
       </c>
-      <c r="S28" s="315">
+      <c r="S28" s="313">
         <v>42.9</v>
       </c>
-      <c r="T28" s="321">
-        <v>33.01</v>
+      <c r="T28" s="323">
+        <v>56.64</v>
       </c>
     </row>
     <row r="29">
@@ -10531,41 +11107,41 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="336">
+      <c r="I29" s="333">
         <v>3.14</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="336">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="330">
+      <c r="K29" s="325">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="332">
+      <c r="L29" s="334">
         <v>-0.61</v>
       </c>
-      <c r="M29" s="325">
+      <c r="M29" s="331">
         <v>6.71</v>
       </c>
-      <c r="N29" s="331">
+      <c r="N29" s="327">
         <v>3.47</v>
       </c>
       <c r="O29" s="326">
         <v>-0.94</v>
       </c>
-      <c r="P29" s="335">
+      <c r="P29" s="328">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="327">
+      <c r="Q29" s="335">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="333">
+      <c r="R29" s="329">
         <v>0.11</v>
       </c>
-      <c r="S29" s="328">
+      <c r="S29" s="332">
         <v>2.42</v>
       </c>
-      <c r="T29" s="329">
-        <v>13.65</v>
+      <c r="T29" s="330">
+        <v>9.96</v>
       </c>
     </row>
     <row r="30">
@@ -10593,41 +11169,41 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="338">
+      <c r="I30" s="347">
         <v>1.85</v>
       </c>
-      <c r="J30" s="340">
+      <c r="J30" s="348">
         <v>7.78</v>
       </c>
-      <c r="K30" s="339">
+      <c r="K30" s="337">
         <v>13.84</v>
       </c>
-      <c r="L30" s="342">
+      <c r="L30" s="340">
         <v>11.93</v>
       </c>
-      <c r="M30" s="347">
+      <c r="M30" s="344">
         <v>5.23</v>
       </c>
-      <c r="N30" s="343">
+      <c r="N30" s="338">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="348">
+      <c r="O30" s="339">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="337">
+      <c r="P30" s="341">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="344">
+      <c r="Q30" s="342">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="341">
+      <c r="R30" s="343">
         <v>-7.4</v>
       </c>
       <c r="S30" s="345">
         <v>-5.36</v>
       </c>
       <c r="T30" s="346">
-        <v>-14.22</v>
+        <v>-10.78</v>
       </c>
     </row>
     <row r="31">
@@ -10655,41 +11231,41 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="349">
+      <c r="I31" s="357">
         <v>1.82</v>
       </c>
-      <c r="J31" s="356">
+      <c r="J31" s="358">
         <v>6.88</v>
       </c>
-      <c r="K31" s="357">
+      <c r="K31" s="360">
         <v>4.25</v>
       </c>
-      <c r="L31" s="358">
+      <c r="L31" s="352">
         <v>1.42</v>
       </c>
-      <c r="M31" s="359">
+      <c r="M31" s="349">
         <v>-7.09</v>
       </c>
       <c r="N31" s="350">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="353">
+      <c r="O31" s="355">
         <v>-10.32</v>
       </c>
       <c r="P31" s="351">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="354">
+      <c r="Q31" s="353">
         <v>-17</v>
       </c>
-      <c r="R31" s="355">
+      <c r="R31" s="354">
         <v>-16.8</v>
       </c>
-      <c r="S31" s="352">
+      <c r="S31" s="359">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="360">
-        <v>-18.62</v>
+      <c r="T31" s="356">
+        <v>-15.18</v>
       </c>
     </row>
     <row r="32">
@@ -10717,41 +11293,41 @@
       <c r="H32">
         <v>-1.07</v>
       </c>
-      <c r="I32" s="361">
+      <c r="I32" s="371">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="363">
+      <c r="J32" s="366">
         <v>0.27</v>
       </c>
-      <c r="K32" s="362">
+      <c r="K32" s="372">
         <v>2.99</v>
       </c>
-      <c r="L32" s="370">
+      <c r="L32" s="367">
         <v>2.35</v>
       </c>
-      <c r="M32" s="367">
+      <c r="M32" s="361">
         <v>0.72</v>
       </c>
-      <c r="N32" s="368">
+      <c r="N32" s="362">
         <v>1</v>
       </c>
-      <c r="O32" s="364">
+      <c r="O32" s="368">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="365">
+      <c r="P32" s="363">
         <v>-0.09</v>
       </c>
       <c r="Q32" s="369">
         <v>3.26</v>
       </c>
-      <c r="R32" s="366">
+      <c r="R32" s="364">
         <v>1</v>
       </c>
-      <c r="S32" s="371">
+      <c r="S32" s="370">
         <v>1.45</v>
       </c>
-      <c r="T32" s="372">
-        <v>5.88</v>
+      <c r="T32" s="365">
+        <v>-5.16</v>
       </c>
     </row>
     <row r="33">
@@ -10779,41 +11355,41 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="376">
+      <c r="I33" s="375">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="380">
+      <c r="J33" s="382">
         <v>0.57</v>
       </c>
-      <c r="K33" s="377">
+      <c r="K33" s="376">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="378">
+      <c r="L33" s="379">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="384">
+      <c r="M33" s="383">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="383">
+      <c r="N33" s="380">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="379">
+      <c r="O33" s="384">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="381">
+      <c r="P33" s="373">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="382">
+      <c r="Q33" s="381">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="373">
+      <c r="R33" s="374">
         <v>-20.6</v>
       </c>
-      <c r="S33" s="374">
+      <c r="S33" s="377">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="375">
-        <v>-20.98</v>
+      <c r="T33" s="378">
+        <v>-21.17</v>
       </c>
     </row>
     <row r="34">
@@ -10841,41 +11417,41 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="393">
+      <c r="I34" s="386">
         <v>-3</v>
       </c>
-      <c r="J34" s="394">
+      <c r="J34" s="387">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="390">
+      <c r="K34" s="395">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="395">
+      <c r="L34" s="391">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="391">
+      <c r="M34" s="392">
         <v>-16.82</v>
       </c>
       <c r="N34" s="396">
         <v>-18.2</v>
       </c>
-      <c r="O34" s="392">
+      <c r="O34" s="388">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="387">
+      <c r="P34" s="385">
         <v>-19.82</v>
       </c>
-      <c r="Q34" s="388">
+      <c r="Q34" s="389">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="389">
+      <c r="R34" s="390">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="385">
+      <c r="S34" s="393">
         <v>-21.43</v>
       </c>
-      <c r="T34" s="386">
-        <v>-20.51</v>
+      <c r="T34" s="394">
+        <v>-18.2</v>
       </c>
     </row>
     <row r="35">
@@ -10903,41 +11479,41 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="402">
+      <c r="I35" s="403">
         <v>4.2</v>
       </c>
-      <c r="J35" s="400">
+      <c r="J35" s="399">
         <v>3.72</v>
       </c>
-      <c r="K35" s="403">
+      <c r="K35" s="401">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="404">
+      <c r="L35" s="402">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="397">
+      <c r="M35" s="404">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="405">
+      <c r="N35" s="406">
         <v>6.61</v>
       </c>
-      <c r="O35" s="406">
+      <c r="O35" s="407">
         <v>5.5</v>
       </c>
-      <c r="P35" s="407">
+      <c r="P35" s="408">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="408">
+      <c r="Q35" s="397">
         <v>1.68</v>
       </c>
-      <c r="R35" s="401">
+      <c r="R35" s="400">
         <v>1.37</v>
       </c>
       <c r="S35" s="398">
         <v>0.08</v>
       </c>
-      <c r="T35" s="399">
-        <v>0.85</v>
+      <c r="T35" s="405">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="36">
@@ -10968,38 +11544,38 @@
       <c r="I36" s="410">
         <v>5.57</v>
       </c>
-      <c r="J36" s="411">
+      <c r="J36" s="415">
         <v>16.17</v>
       </c>
-      <c r="K36" s="416">
+      <c r="K36" s="411">
         <v>22.01</v>
       </c>
-      <c r="L36" s="413">
+      <c r="L36" s="419">
         <v>16.85</v>
       </c>
-      <c r="M36" s="417">
+      <c r="M36" s="412">
         <v>7.07</v>
       </c>
-      <c r="N36" s="420">
+      <c r="N36" s="417">
         <v>0.27</v>
       </c>
-      <c r="O36" s="414">
+      <c r="O36" s="420">
         <v>2.45</v>
       </c>
-      <c r="P36" s="415">
+      <c r="P36" s="413">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="418">
+      <c r="Q36" s="409">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="409">
+      <c r="R36" s="414">
         <v>9.65</v>
       </c>
-      <c r="S36" s="412">
+      <c r="S36" s="418">
         <v>7.47</v>
       </c>
-      <c r="T36" s="419">
-        <v>1.49</v>
+      <c r="T36" s="416">
+        <v>-5.57</v>
       </c>
     </row>
     <row r="37">
@@ -11027,41 +11603,41 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="425">
+      <c r="I37" s="426">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="426">
+      <c r="J37" s="430">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="427">
+      <c r="K37" s="428">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="430">
+      <c r="L37" s="431">
         <v>7.57</v>
       </c>
-      <c r="M37" s="423">
+      <c r="M37" s="424">
         <v>5.6</v>
       </c>
-      <c r="N37" s="431">
+      <c r="N37" s="432">
         <v>4.48</v>
       </c>
-      <c r="O37" s="432">
+      <c r="O37" s="427">
         <v>3.32</v>
       </c>
-      <c r="P37" s="428">
+      <c r="P37" s="421">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="429">
+      <c r="Q37" s="422">
         <v>3.78</v>
       </c>
-      <c r="R37" s="421">
+      <c r="R37" s="429">
         <v>8.07</v>
       </c>
-      <c r="S37" s="422">
+      <c r="S37" s="423">
         <v>11.74</v>
       </c>
-      <c r="T37" s="424">
-        <v>7.72</v>
+      <c r="T37" s="425">
+        <v>4.98</v>
       </c>
     </row>
     <row r="38">
@@ -11089,41 +11665,41 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="441">
+      <c r="I38" s="436">
         <v>6.62</v>
       </c>
-      <c r="J38" s="440">
+      <c r="J38" s="437">
         <v>10.07</v>
       </c>
-      <c r="K38" s="442">
+      <c r="K38" s="438">
         <v>6.26</v>
       </c>
-      <c r="L38" s="443">
+      <c r="L38" s="440">
         <v>2.13</v>
       </c>
-      <c r="M38" s="444">
+      <c r="M38" s="441">
         <v>1.41</v>
       </c>
-      <c r="N38" s="433">
+      <c r="N38" s="442">
         <v>7.72</v>
       </c>
-      <c r="O38" s="434">
+      <c r="O38" s="439">
         <v>5.74</v>
       </c>
-      <c r="P38" s="436">
+      <c r="P38" s="435">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="435">
+      <c r="Q38" s="433">
         <v>14.45</v>
       </c>
-      <c r="R38" s="437">
+      <c r="R38" s="443">
         <v>18.62</v>
       </c>
-      <c r="S38" s="438">
+      <c r="S38" s="434">
         <v>14.8</v>
       </c>
-      <c r="T38" s="439">
-        <v>14.8</v>
+      <c r="T38" s="444">
+        <v>2.33</v>
       </c>
     </row>
     <row r="39">
@@ -11151,39 +11727,41 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="452">
+      <c r="I39" s="454">
         <v>7.14</v>
       </c>
-      <c r="J39" s="453">
+      <c r="J39" s="455">
         <v>7.82</v>
       </c>
-      <c r="K39" s="449">
+      <c r="K39" s="447">
         <v>7.68</v>
       </c>
-      <c r="L39" s="454">
+      <c r="L39" s="448">
         <v>8.49</v>
       </c>
-      <c r="M39" s="450">
+      <c r="M39" s="456">
         <v>9.43</v>
       </c>
-      <c r="N39" s="451">
+      <c r="N39" s="450">
         <v>5.39</v>
       </c>
-      <c r="O39" s="455">
+      <c r="O39" s="451">
         <v>8.49</v>
       </c>
-      <c r="P39" s="448">
+      <c r="P39" s="452">
         <v>7.28</v>
       </c>
-      <c r="Q39" s="446">
+      <c r="Q39" s="453">
         <v>11.99</v>
       </c>
-      <c r="R39" s="447">
+      <c r="R39" s="449">
         <v>7.95</v>
       </c>
-      <c r="S39" t="str"/>
-      <c r="T39" s="445">
-        <v>7.95</v>
+      <c r="S39" s="445">
+        <v>7.55</v>
+      </c>
+      <c r="T39" s="446">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="40">
@@ -11211,37 +11789,41 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="462">
+      <c r="I40" s="459">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="459">
+      <c r="J40" s="463">
         <v>-0.66</v>
       </c>
-      <c r="K40" s="463">
+      <c r="K40" s="468">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="458">
+      <c r="L40" s="464">
         <v>0</v>
       </c>
-      <c r="M40" s="461">
+      <c r="M40" s="457">
         <v>-1.31</v>
       </c>
-      <c r="N40" s="464">
+      <c r="N40" s="460">
         <v>0.33</v>
       </c>
-      <c r="O40" s="465">
+      <c r="O40" s="466">
         <v>0</v>
       </c>
-      <c r="P40" s="460">
+      <c r="P40" s="461">
         <v>1.97</v>
       </c>
-      <c r="Q40" s="456">
+      <c r="Q40" s="462">
         <v>-0.22</v>
       </c>
-      <c r="R40" t="str"/>
-      <c r="S40" t="str"/>
-      <c r="T40" s="457">
-        <v>-0.22</v>
+      <c r="R40" s="465">
+        <v>2.51</v>
+      </c>
+      <c r="S40" s="458">
+        <v>-0.55</v>
+      </c>
+      <c r="T40" s="467">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="41">
@@ -11269,35 +11851,41 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="467">
+      <c r="I41" s="470">
         <v>0.59</v>
       </c>
       <c r="J41" s="471">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="469">
+      <c r="K41" s="477">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="470">
+      <c r="L41" s="473">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="468">
+      <c r="M41" s="474">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="474">
+      <c r="N41" s="478">
         <v>-7.55</v>
       </c>
-      <c r="O41" s="466">
+      <c r="O41" s="479">
         <v>-6.76</v>
       </c>
-      <c r="P41" s="472">
+      <c r="P41" s="480">
         <v>-8.43</v>
       </c>
-      <c r="Q41" t="str"/>
-      <c r="R41" t="str"/>
-      <c r="S41" t="str"/>
-      <c r="T41" s="473">
-        <v>-8.43</v>
+      <c r="Q41" s="475">
+        <v>-9.51</v>
+      </c>
+      <c r="R41" s="472">
+        <v>-7.55</v>
+      </c>
+      <c r="S41" s="469">
+        <v>-9.12</v>
+      </c>
+      <c r="T41" s="476">
+        <v>-9.12</v>
       </c>
     </row>
     <row r="42">
@@ -11325,33 +11913,39 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="480">
+      <c r="I42" s="487">
         <v>2.08</v>
       </c>
-      <c r="J42" s="481">
+      <c r="J42" s="491">
         <v>2.7</v>
       </c>
-      <c r="K42" s="482">
+      <c r="K42" s="484">
         <v>0</v>
       </c>
-      <c r="L42" s="475">
+      <c r="L42" s="488">
         <v>1.25</v>
       </c>
-      <c r="M42" s="476">
+      <c r="M42" s="483">
         <v>1.04</v>
       </c>
-      <c r="N42" s="477">
+      <c r="N42" s="489">
         <v>1.56</v>
       </c>
-      <c r="O42" s="478">
+      <c r="O42" s="485">
         <v>-0.52</v>
       </c>
-      <c r="P42" t="str"/>
-      <c r="Q42" t="str"/>
-      <c r="R42" t="str"/>
+      <c r="P42" s="486">
+        <v>-1.56</v>
+      </c>
+      <c r="Q42" s="481">
+        <v>-6.75</v>
+      </c>
+      <c r="R42" s="482">
+        <v>-5.61</v>
+      </c>
       <c r="S42" t="str"/>
-      <c r="T42" s="479">
-        <v>-0.52</v>
+      <c r="T42" s="490">
+        <v>-5.61</v>
       </c>
     </row>
     <row r="43">
@@ -11379,31 +11973,37 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="488">
+      <c r="I43" s="499">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="489">
+      <c r="J43" s="493">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="483">
+      <c r="K43" s="494">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="484">
+      <c r="L43" s="495">
         <v>8.46</v>
       </c>
-      <c r="M43" s="485">
+      <c r="M43" s="498">
         <v>10.98</v>
       </c>
-      <c r="N43" s="486">
+      <c r="N43" s="496">
         <v>10.41</v>
       </c>
-      <c r="O43" t="str"/>
-      <c r="P43" t="str"/>
-      <c r="Q43" t="str"/>
+      <c r="O43" s="500">
+        <v>21.46</v>
+      </c>
+      <c r="P43" s="501">
+        <v>26.1</v>
+      </c>
+      <c r="Q43" s="497">
+        <v>22.85</v>
+      </c>
       <c r="R43" t="str"/>
       <c r="S43" t="str"/>
-      <c r="T43" s="487">
-        <v>10.41</v>
+      <c r="T43" s="492">
+        <v>22.85</v>
       </c>
     </row>
     <row r="44">
@@ -11431,29 +12031,35 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="494">
+      <c r="I44" s="510">
         <v>10.68</v>
       </c>
-      <c r="J44" s="495">
+      <c r="J44" s="505">
         <v>1.78</v>
       </c>
-      <c r="K44" s="490">
+      <c r="K44" s="506">
         <v>-1.94</v>
       </c>
-      <c r="L44" s="491">
+      <c r="L44" s="507">
         <v>3.72</v>
       </c>
-      <c r="M44" s="492">
+      <c r="M44" s="503">
         <v>2.1</v>
       </c>
-      <c r="N44" t="str"/>
-      <c r="O44" t="str"/>
-      <c r="P44" t="str"/>
+      <c r="N44" s="502">
+        <v>6.15</v>
+      </c>
+      <c r="O44" s="508">
+        <v>9.06</v>
+      </c>
+      <c r="P44" s="509">
+        <v>-0.97</v>
+      </c>
       <c r="Q44" t="str"/>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="493">
-        <v>2.1</v>
+      <c r="T44" s="504">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="45">
@@ -11481,27 +12087,33 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="496">
+      <c r="I45" s="517">
         <v>2.03</v>
       </c>
-      <c r="J45" s="497">
+      <c r="J45" s="512">
         <v>5.03</v>
       </c>
-      <c r="K45" s="498">
+      <c r="K45" s="513">
         <v>5.82</v>
       </c>
-      <c r="L45" s="499">
+      <c r="L45" s="518">
         <v>3.17</v>
       </c>
-      <c r="M45" t="str"/>
-      <c r="N45" t="str"/>
-      <c r="O45" t="str"/>
+      <c r="M45" s="511">
+        <v>-0.26</v>
+      </c>
+      <c r="N45" s="514">
+        <v>-2.65</v>
+      </c>
+      <c r="O45" s="515">
+        <v>-7.58</v>
+      </c>
       <c r="P45" t="str"/>
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="500">
-        <v>3.17</v>
+      <c r="T45" s="516">
+        <v>-7.58</v>
       </c>
     </row>
     <row r="46">
@@ -11529,23 +12141,29 @@
       <c r="H46">
         <v>-0.93</v>
       </c>
-      <c r="I46" s="501">
+      <c r="I46" s="521">
         <v>1.8</v>
       </c>
-      <c r="J46" s="502">
+      <c r="J46" s="522">
         <v>0.31</v>
       </c>
-      <c r="K46" t="str"/>
-      <c r="L46" t="str"/>
-      <c r="M46" t="str"/>
+      <c r="K46" s="523">
+        <v>3.04</v>
+      </c>
+      <c r="L46" s="524">
+        <v>0.78</v>
+      </c>
+      <c r="M46" s="519">
+        <v>-3.2</v>
+      </c>
       <c r="N46" t="str"/>
       <c r="O46" t="str"/>
       <c r="P46" t="str"/>
       <c r="Q46" t="str"/>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" s="503">
-        <v>0.31</v>
+      <c r="T46" s="520">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="47">
@@ -11573,12 +12191,18 @@
       <c r="H47">
         <v>0.36</v>
       </c>
-      <c r="I47" s="504">
+      <c r="I47" s="525">
         <v>-1.87</v>
       </c>
-      <c r="J47" t="str"/>
-      <c r="K47" t="str"/>
-      <c r="L47" t="str"/>
+      <c r="J47" s="526">
+        <v>-0.72</v>
+      </c>
+      <c r="K47" s="527">
+        <v>2.87</v>
+      </c>
+      <c r="L47" s="528">
+        <v>-1.03</v>
+      </c>
       <c r="M47" t="str"/>
       <c r="N47" t="str"/>
       <c r="O47" t="str"/>
@@ -11586,150 +12210,326 @@
       <c r="Q47" t="str"/>
       <c r="R47" t="str"/>
       <c r="S47" t="str"/>
-      <c r="T47" t="str"/>
+      <c r="T47" s="529">
+        <v>-1.03</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B48" t="str"/>
-      <c r="C48" t="str"/>
-      <c r="D48" t="str"/>
-      <c r="E48" t="str"/>
-      <c r="F48" t="str"/>
-      <c r="G48" t="str"/>
-      <c r="H48" t="str"/>
-      <c r="I48">
-        <v>46</v>
-      </c>
-      <c r="J48">
-        <v>45</v>
-      </c>
-      <c r="K48">
-        <v>44</v>
-      </c>
-      <c r="L48">
-        <v>44</v>
-      </c>
-      <c r="M48">
-        <v>43</v>
-      </c>
-      <c r="N48">
-        <v>42</v>
-      </c>
-      <c r="O48">
-        <v>41</v>
-      </c>
-      <c r="P48">
-        <v>40</v>
-      </c>
-      <c r="Q48">
-        <v>39</v>
-      </c>
-      <c r="R48">
-        <v>38</v>
-      </c>
-      <c r="S48">
-        <v>37</v>
-      </c>
-      <c r="T48">
-        <v>45</v>
+        <v>2026-04-22</v>
+      </c>
+      <c r="B48" t="str">
+        <v>豫能控股</v>
+      </c>
+      <c r="C48" t="str">
+        <v>001896</v>
+      </c>
+      <c r="D48" t="str">
+        <v>(09:25:00)豫能控股</v>
+      </c>
+      <c r="E48">
+        <v>16.88</v>
+      </c>
+      <c r="F48">
+        <v>17.5</v>
+      </c>
+      <c r="G48">
+        <v>16.88</v>
+      </c>
+      <c r="H48">
+        <v>-1.29</v>
+      </c>
+      <c r="I48" s="533">
+        <v>3.67</v>
+      </c>
+      <c r="J48" s="530">
+        <v>6.46</v>
+      </c>
+      <c r="K48" s="531">
+        <v>-0.77</v>
+      </c>
+      <c r="L48" t="str"/>
+      <c r="M48" t="str"/>
+      <c r="N48" t="str"/>
+      <c r="O48" t="str"/>
+      <c r="P48" t="str"/>
+      <c r="Q48" t="str"/>
+      <c r="R48" t="str"/>
+      <c r="S48" t="str"/>
+      <c r="T48" s="532">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>上涨比例</v>
-      </c>
-      <c r="B49" t="str"/>
-      <c r="C49" t="str"/>
-      <c r="D49" t="str"/>
-      <c r="E49" t="str"/>
-      <c r="F49" t="str"/>
-      <c r="G49" t="str"/>
-      <c r="H49" t="str"/>
-      <c r="I49" s="516">
-        <v>58.7</v>
-      </c>
-      <c r="J49" s="508">
-        <v>60</v>
-      </c>
-      <c r="K49" s="509">
-        <v>52.27</v>
-      </c>
-      <c r="L49" s="505">
-        <v>59.09</v>
-      </c>
-      <c r="M49" s="512">
-        <v>55.81</v>
-      </c>
-      <c r="N49" s="506">
-        <v>57.14</v>
-      </c>
-      <c r="O49" s="510">
-        <v>39.02</v>
-      </c>
-      <c r="P49" s="513">
-        <v>42.5</v>
-      </c>
-      <c r="Q49" s="511">
-        <v>41.03</v>
-      </c>
-      <c r="R49" s="507">
-        <v>47.37</v>
-      </c>
-      <c r="S49" s="514">
-        <v>48.65</v>
-      </c>
-      <c r="T49" s="515">
-        <v>42.22</v>
+        <v>2026-04-23</v>
+      </c>
+      <c r="B49" t="str">
+        <v>四川黄金</v>
+      </c>
+      <c r="C49" t="str">
+        <v>001337</v>
+      </c>
+      <c r="D49" t="str">
+        <v>(09:25:00)不用去油了, 去四川黄金</v>
+      </c>
+      <c r="E49">
+        <v>49.29</v>
+      </c>
+      <c r="F49">
+        <v>47.55</v>
+      </c>
+      <c r="G49">
+        <v>49.29</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49" s="535">
+        <v>-3.53</v>
+      </c>
+      <c r="J49" s="536">
+        <v>-3.9</v>
+      </c>
+      <c r="K49" t="str"/>
+      <c r="L49" t="str"/>
+      <c r="M49" t="str"/>
+      <c r="N49" t="str"/>
+      <c r="O49" t="str"/>
+      <c r="P49" t="str"/>
+      <c r="Q49" t="str"/>
+      <c r="R49" t="str"/>
+      <c r="S49" t="str"/>
+      <c r="T49" s="534">
+        <v>-3.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="B50" t="str">
+        <v>武汉凡谷</v>
+      </c>
+      <c r="C50" t="str">
+        <v>002194</v>
+      </c>
+      <c r="D50" t="str">
+        <v>(09:25:00)武汉凡谷给缝就塞</v>
+      </c>
+      <c r="E50">
+        <v>12.3</v>
+      </c>
+      <c r="F50">
+        <v>12.36</v>
+      </c>
+      <c r="G50">
+        <v>12.3</v>
+      </c>
+      <c r="H50">
+        <v>3.71</v>
+      </c>
+      <c r="I50" s="537">
+        <v>0.49</v>
+      </c>
+      <c r="J50" s="538">
+        <v>-8.37</v>
+      </c>
+      <c r="K50" t="str"/>
+      <c r="L50" t="str"/>
+      <c r="M50" t="str"/>
+      <c r="N50" t="str"/>
+      <c r="O50" t="str"/>
+      <c r="P50" t="str"/>
+      <c r="Q50" t="str"/>
+      <c r="R50" t="str"/>
+      <c r="S50" t="str"/>
+      <c r="T50" s="539">
+        <v>-8.37</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="B51" t="str">
+        <v>小商品城</v>
+      </c>
+      <c r="C51" t="str">
+        <v>600415</v>
+      </c>
+      <c r="D51" t="str">
+        <v>(09:25:00)底部放量，注意低吸小商品城</v>
+      </c>
+      <c r="E51">
+        <v>13.5</v>
+      </c>
+      <c r="F51">
+        <v>13.25</v>
+      </c>
+      <c r="G51">
+        <v>13.5</v>
+      </c>
+      <c r="H51">
+        <v>-0.95</v>
+      </c>
+      <c r="I51" s="540">
+        <v>-1.85</v>
+      </c>
+      <c r="J51" t="str"/>
+      <c r="K51" t="str"/>
+      <c r="L51" t="str"/>
+      <c r="M51" t="str"/>
+      <c r="N51" t="str"/>
+      <c r="O51" t="str"/>
+      <c r="P51" t="str"/>
+      <c r="Q51" t="str"/>
+      <c r="R51" t="str"/>
+      <c r="S51" t="str"/>
+      <c r="T51" t="str"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>纪录总数</v>
+      </c>
+      <c r="B52" t="str"/>
+      <c r="C52" t="str"/>
+      <c r="D52" t="str"/>
+      <c r="E52" t="str"/>
+      <c r="F52" t="str"/>
+      <c r="G52" t="str"/>
+      <c r="H52" t="str"/>
+      <c r="I52">
+        <v>50</v>
+      </c>
+      <c r="J52">
+        <v>49</v>
+      </c>
+      <c r="K52">
+        <v>47</v>
+      </c>
+      <c r="L52">
+        <v>46</v>
+      </c>
+      <c r="M52">
+        <v>45</v>
+      </c>
+      <c r="N52">
+        <v>44</v>
+      </c>
+      <c r="O52">
+        <v>44</v>
+      </c>
+      <c r="P52">
+        <v>43</v>
+      </c>
+      <c r="Q52">
+        <v>42</v>
+      </c>
+      <c r="R52">
+        <v>41</v>
+      </c>
+      <c r="S52">
+        <v>40</v>
+      </c>
+      <c r="T52">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>上涨比例</v>
+      </c>
+      <c r="B53" t="str"/>
+      <c r="C53" t="str"/>
+      <c r="D53" t="str"/>
+      <c r="E53" t="str"/>
+      <c r="F53" t="str"/>
+      <c r="G53" t="str"/>
+      <c r="H53" t="str"/>
+      <c r="I53" s="542">
+        <v>58</v>
+      </c>
+      <c r="J53" s="544">
+        <v>57.14</v>
+      </c>
+      <c r="K53" s="549">
+        <v>53.19</v>
+      </c>
+      <c r="L53" s="545">
+        <v>58.7</v>
+      </c>
+      <c r="M53" s="552">
+        <v>53.33</v>
+      </c>
+      <c r="N53" s="546">
+        <v>56.82</v>
+      </c>
+      <c r="O53" s="541">
+        <v>40.91</v>
+      </c>
+      <c r="P53" s="550">
+        <v>41.86</v>
+      </c>
+      <c r="Q53" s="551">
+        <v>40.48</v>
+      </c>
+      <c r="R53" s="547">
+        <v>46.34</v>
+      </c>
+      <c r="S53" s="543">
+        <v>47.5</v>
+      </c>
+      <c r="T53" s="548">
+        <v>24.49</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>平均涨幅</v>
       </c>
-      <c r="B50" t="str"/>
-      <c r="C50" t="str"/>
-      <c r="D50" t="str"/>
-      <c r="E50" t="str"/>
-      <c r="F50" t="str"/>
-      <c r="G50" t="str"/>
-      <c r="H50" t="str"/>
-      <c r="I50" s="524">
+      <c r="B54" t="str"/>
+      <c r="C54" t="str"/>
+      <c r="D54" t="str"/>
+      <c r="E54" t="str"/>
+      <c r="F54" t="str"/>
+      <c r="G54" t="str"/>
+      <c r="H54" t="str"/>
+      <c r="I54" s="556">
+        <v>1.87</v>
+      </c>
+      <c r="J54" s="562">
         <v>2.06</v>
       </c>
-      <c r="J50" s="518">
-        <v>2.39</v>
-      </c>
-      <c r="K50" s="525">
-        <v>1.89</v>
-      </c>
-      <c r="L50" s="526">
-        <v>1.25</v>
-      </c>
-      <c r="M50" s="521">
-        <v>1.47</v>
-      </c>
-      <c r="N50" s="519">
+      <c r="K54" s="563">
+        <v>1.88</v>
+      </c>
+      <c r="L54" s="564">
+        <v>1.19</v>
+      </c>
+      <c r="M54" s="560">
+        <v>1.33</v>
+      </c>
+      <c r="N54" s="557">
+        <v>0.21</v>
+      </c>
+      <c r="O54" s="553">
         <v>0.14</v>
       </c>
-      <c r="O50" s="527">
-        <v>-0.41</v>
-      </c>
-      <c r="P50" s="520">
-        <v>-0.41</v>
-      </c>
-      <c r="Q50" s="528">
-        <v>-0.49</v>
-      </c>
-      <c r="R50" s="522">
-        <v>0.73</v>
-      </c>
-      <c r="S50" s="517">
-        <v>0.73</v>
-      </c>
-      <c r="T50" s="523">
-        <v>-2.74</v>
+      <c r="P54" s="558">
+        <v>0.17</v>
+      </c>
+      <c r="Q54" s="554">
+        <v>-0.3</v>
+      </c>
+      <c r="R54" s="561">
+        <v>0.42</v>
+      </c>
+      <c r="S54" s="559">
+        <v>0.62</v>
+      </c>
+      <c r="T54" s="555">
+        <v>-4.13</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="566">
+  <fills count="578">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -45,31 +45,1633 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEFF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF259C40"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,19 +1683,1759 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0DEBA"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,715 +3447,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -825,2604 +3471,114 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAADCB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE66E7A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BEC3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF32AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8690"/>
+        <fgColor rgb="FFDE4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9828C"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="565">
+  <borders count="577">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7382,7 +7538,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="565">
+  <cellXfs count="577">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -9074,6 +9230,42 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="564" fillId="565" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="565" fillId="566" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="566" fillId="567" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="567" fillId="568" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="568" fillId="569" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="569" fillId="570" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="570" fillId="571" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="571" fillId="572" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="572" fillId="573" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="573" fillId="574" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="574" fillId="575" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="575" fillId="576" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="576" fillId="577" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9433,41 +9625,41 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="2">
         <v>4.95</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="5">
         <v>-0.37</v>
       </c>
       <c r="K2" s="6">
         <v>1.74</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="9">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="3">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="7">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="10">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="11">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="12">
         <v>-4.86</v>
       </c>
       <c r="R2" s="1">
         <v>-4.59</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="8">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="11">
-        <v>-17.8</v>
+      <c r="T2" s="4">
+        <v>-21.83</v>
       </c>
     </row>
     <row r="3">
@@ -9495,41 +9687,41 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="21">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="16">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="17">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="22">
         <v>0.1</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="23">
         <v>3.32</v>
       </c>
-      <c r="N3" s="21">
+      <c r="N3" s="18">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="24">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="13">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="14">
         <v>2.8</v>
       </c>
-      <c r="R3" s="13">
+      <c r="R3" s="19">
         <v>1.66</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="15">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="22">
-        <v>15.13</v>
+      <c r="T3" s="20">
+        <v>15.65</v>
       </c>
     </row>
     <row r="4">
@@ -9557,13 +9749,13 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="33">
         <v>4.19</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="32">
         <v>5.08</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="34">
         <v>15.59</v>
       </c>
       <c r="L4" s="29">
@@ -9572,26 +9764,26 @@
       <c r="M4" s="30">
         <v>36.04</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="35">
         <v>41.33</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="26">
         <v>37.54</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="36">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="27">
         <v>32.33</v>
       </c>
       <c r="R4" s="25">
         <v>45.56</v>
       </c>
-      <c r="S4" s="33">
+      <c r="S4" s="31">
         <v>56.03</v>
       </c>
-      <c r="T4" s="26">
-        <v>29.51</v>
+      <c r="T4" s="28">
+        <v>33.03</v>
       </c>
     </row>
     <row r="5">
@@ -9619,41 +9811,41 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="39">
         <v>11.97</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="40">
         <v>17.45</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="41">
         <v>14.27</v>
       </c>
-      <c r="L5" s="37">
+      <c r="L5" s="43">
         <v>17.32</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="44">
         <v>25.33</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="45">
         <v>21.54</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="46">
         <v>22.72</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="48">
         <v>20.84</v>
       </c>
-      <c r="Q5" s="38">
+      <c r="Q5" s="47">
         <v>17.54</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="37">
         <v>16.88</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="42">
         <v>11.79</v>
       </c>
-      <c r="T5" s="39">
-        <v>29.59</v>
+      <c r="T5" s="38">
+        <v>31.29</v>
       </c>
     </row>
     <row r="6">
@@ -9681,41 +9873,41 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="49">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="53">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="49">
+      <c r="K6" s="54">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="50">
+      <c r="L6" s="59">
         <v>-0.66</v>
       </c>
-      <c r="M6" s="52">
+      <c r="M6" s="60">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="51">
+      <c r="N6" s="56">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="50">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="51">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="52">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="57">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="55">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="60">
-        <v>-18.9</v>
+      <c r="T6" s="58">
+        <v>-21.16</v>
       </c>
     </row>
     <row r="7">
@@ -9743,41 +9935,41 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="71">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="61">
+      <c r="J7" s="66">
         <v>1.8</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="67">
         <v>0.07</v>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="63">
         <v>0.63</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="72">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="64">
+      <c r="N7" s="61">
         <v>1.55</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="62">
         <v>0.85</v>
       </c>
-      <c r="P7" s="65">
+      <c r="P7" s="68">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="69">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="64">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="65">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="63">
-        <v>10.34</v>
+      <c r="T7" s="70">
+        <v>8.61</v>
       </c>
     </row>
     <row r="8">
@@ -9805,41 +9997,41 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="81">
         <v>3.13</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="77">
         <v>5.21</v>
       </c>
-      <c r="K8" s="76">
+      <c r="K8" s="82">
         <v>0.43</v>
       </c>
-      <c r="L8" s="77">
+      <c r="L8" s="73">
         <v>3.68</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="74">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="75">
         <v>1.66</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="78">
         <v>1.72</v>
       </c>
-      <c r="P8" s="73">
+      <c r="P8" s="83">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="84">
         <v>15.33</v>
       </c>
-      <c r="R8" s="78">
+      <c r="R8" s="79">
         <v>12.57</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="80">
         <v>23.85</v>
       </c>
-      <c r="T8" s="74">
-        <v>-17.35</v>
+      <c r="T8" s="76">
+        <v>-13.49</v>
       </c>
     </row>
     <row r="9">
@@ -9867,41 +10059,41 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="90">
         <v>1.35</v>
       </c>
-      <c r="J9" s="90">
+      <c r="J9" s="91">
         <v>2.48</v>
       </c>
-      <c r="K9" s="91">
+      <c r="K9" s="93">
         <v>1.58</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="85">
         <v>1.35</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="94">
         <v>2.93</v>
       </c>
       <c r="N9" s="86">
         <v>0.23</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="92">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="95">
         <v>-0.68</v>
       </c>
-      <c r="Q9" s="85">
+      <c r="Q9" s="87">
         <v>3.83</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="96">
         <v>7.43</v>
       </c>
       <c r="S9" s="88">
         <v>17.12</v>
       </c>
       <c r="T9" s="89">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="10">
@@ -9929,41 +10121,41 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="97">
+      <c r="I10" s="108">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="104">
+      <c r="J10" s="99">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="98">
+      <c r="K10" s="101">
         <v>-7.86</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="97">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="102">
         <v>-12.37</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="100">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="99">
+      <c r="O10" s="104">
         <v>-9.15</v>
       </c>
-      <c r="P10" s="100">
+      <c r="P10" s="103">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="101">
+      <c r="Q10" s="105">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="102">
+      <c r="R10" s="98">
         <v>-11.08</v>
       </c>
-      <c r="S10" s="103">
+      <c r="S10" s="106">
         <v>-11.72</v>
       </c>
-      <c r="T10" s="108">
-        <v>-15.08</v>
+      <c r="T10" s="107">
+        <v>-14.58</v>
       </c>
     </row>
     <row r="11">
@@ -9991,41 +10183,41 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="113">
+      <c r="I11" s="114">
         <v>7.32</v>
       </c>
-      <c r="J11" s="114">
+      <c r="J11" s="118">
         <v>7.76</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="115">
         <v>15.37</v>
       </c>
-      <c r="L11" s="115">
+      <c r="L11" s="110">
         <v>8.64</v>
       </c>
-      <c r="M11" s="110">
+      <c r="M11" s="116">
         <v>0.59</v>
       </c>
       <c r="N11" s="111">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="119">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="116">
+      <c r="P11" s="112">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="109">
+      <c r="Q11" s="120">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="117">
+      <c r="R11" s="113">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="112">
+      <c r="S11" s="109">
         <v>0.15</v>
       </c>
-      <c r="T11" s="118">
-        <v>-22.55</v>
+      <c r="T11" s="117">
+        <v>-21.82</v>
       </c>
     </row>
     <row r="12">
@@ -10062,32 +10254,32 @@
       <c r="K12" s="125">
         <v>4.11</v>
       </c>
-      <c r="L12" s="122">
+      <c r="L12" s="126">
         <v>6.13</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="123">
         <v>9.68</v>
       </c>
-      <c r="N12" s="129">
+      <c r="N12" s="122">
         <v>2.66</v>
       </c>
-      <c r="O12" s="130">
+      <c r="O12" s="127">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="123">
+      <c r="P12" s="129">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="126">
+      <c r="Q12" s="130">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="128">
         <v>0.97</v>
       </c>
-      <c r="S12" s="127">
+      <c r="S12" s="131">
         <v>3.06</v>
       </c>
-      <c r="T12" s="128">
-        <v>-26.69</v>
+      <c r="T12" s="132">
+        <v>-29.27</v>
       </c>
     </row>
     <row r="13">
@@ -10115,41 +10307,41 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="135">
+      <c r="I13" s="133">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="136">
+      <c r="J13" s="140">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="139">
+      <c r="K13" s="134">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="137">
+      <c r="L13" s="141">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="136">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="133">
+      <c r="N13" s="138">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="140">
+      <c r="O13" s="142">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="141">
+      <c r="P13" s="135">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="138">
+      <c r="Q13" s="139">
         <v>-4.93</v>
       </c>
       <c r="R13" s="143">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="142">
+      <c r="S13" s="144">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="134">
-        <v>-15.62</v>
+      <c r="T13" s="137">
+        <v>-14.21</v>
       </c>
     </row>
     <row r="14">
@@ -10180,38 +10372,38 @@
       <c r="I14" s="155">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="151">
+      <c r="J14" s="153">
         <v>-5</v>
       </c>
-      <c r="K14" s="146">
+      <c r="K14" s="149">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="149">
+      <c r="L14" s="147">
         <v>-7.13</v>
       </c>
-      <c r="M14" s="152">
+      <c r="M14" s="156">
         <v>-7.37</v>
       </c>
       <c r="N14" s="150">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="156">
+      <c r="O14" s="154">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="153">
+      <c r="P14" s="151">
         <v>-5.63</v>
       </c>
-      <c r="Q14" s="154">
+      <c r="Q14" s="148">
         <v>-1.62</v>
       </c>
-      <c r="R14" s="147">
+      <c r="R14" s="145">
         <v>-2.75</v>
       </c>
-      <c r="S14" s="148">
+      <c r="S14" s="146">
         <v>0</v>
       </c>
-      <c r="T14" s="145">
-        <v>-9.38</v>
+      <c r="T14" s="152">
+        <v>-12</v>
       </c>
     </row>
     <row r="15">
@@ -10239,41 +10431,41 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="166">
+      <c r="I15" s="159">
         <v>9.9</v>
       </c>
-      <c r="J15" s="157">
+      <c r="J15" s="160">
         <v>9.43</v>
       </c>
-      <c r="K15" s="160">
+      <c r="K15" s="167">
         <v>8.82</v>
       </c>
-      <c r="L15" s="163">
+      <c r="L15" s="161">
         <v>4.15</v>
       </c>
-      <c r="M15" s="167">
+      <c r="M15" s="168">
         <v>7.79</v>
       </c>
-      <c r="N15" s="164">
+      <c r="N15" s="163">
         <v>1.3</v>
       </c>
-      <c r="O15" s="158">
+      <c r="O15" s="164">
         <v>8.69</v>
       </c>
-      <c r="P15" s="168">
+      <c r="P15" s="157">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="159">
+      <c r="Q15" s="165">
         <v>5.84</v>
       </c>
-      <c r="R15" s="161">
+      <c r="R15" s="158">
         <v>6.88</v>
       </c>
-      <c r="S15" s="165">
+      <c r="S15" s="162">
         <v>2.34</v>
       </c>
-      <c r="T15" s="162">
-        <v>-13.41</v>
+      <c r="T15" s="166">
+        <v>-14.75</v>
       </c>
     </row>
     <row r="16">
@@ -10301,41 +10493,41 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="175">
+      <c r="I16" s="171">
         <v>2.67</v>
       </c>
-      <c r="J16" s="169">
+      <c r="J16" s="176">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="170">
+      <c r="K16" s="180">
         <v>-2.48</v>
       </c>
-      <c r="L16" s="178">
+      <c r="L16" s="172">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="176">
+      <c r="M16" s="169">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="179">
+      <c r="N16" s="170">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="171">
+      <c r="O16" s="177">
         <v>-4.85</v>
       </c>
-      <c r="P16" s="174">
+      <c r="P16" s="178">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="172">
+      <c r="Q16" s="173">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="173">
+      <c r="R16" s="174">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="177">
+      <c r="S16" s="175">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="180">
-        <v>-28.24</v>
+      <c r="T16" s="179">
+        <v>-27.7</v>
       </c>
     </row>
     <row r="17">
@@ -10363,41 +10555,41 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="188">
+      <c r="I17" s="192">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="182">
+      <c r="J17" s="188">
         <v>-2.31</v>
       </c>
       <c r="K17" s="189">
         <v>0.2</v>
       </c>
-      <c r="L17" s="181">
+      <c r="L17" s="184">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="183">
+      <c r="M17" s="190">
         <v>0.53</v>
       </c>
-      <c r="N17" s="184">
+      <c r="N17" s="181">
         <v>3.31</v>
       </c>
-      <c r="O17" s="190">
+      <c r="O17" s="185">
         <v>6.89</v>
       </c>
-      <c r="P17" s="191">
+      <c r="P17" s="182">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="192">
+      <c r="Q17" s="183">
         <v>4.09</v>
       </c>
-      <c r="R17" s="185">
+      <c r="R17" s="186">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="186">
+      <c r="S17" s="191">
         <v>-1.45</v>
       </c>
       <c r="T17" s="187">
-        <v>-0.98</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="18">
@@ -10425,41 +10617,41 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="200">
+      <c r="I18" s="201">
         <v>-3.66</v>
       </c>
-      <c r="J18" s="203">
+      <c r="J18" s="198">
         <v>-4.31</v>
       </c>
-      <c r="K18" s="201">
+      <c r="K18" s="199">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="194">
+      <c r="L18" s="196">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="195">
+      <c r="M18" s="197">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="204">
+      <c r="N18" s="202">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="198">
+      <c r="O18" s="203">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="196">
+      <c r="P18" s="204">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="193">
+      <c r="Q18" s="195">
         <v>-20.52</v>
       </c>
-      <c r="R18" s="202">
+      <c r="R18" s="193">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="199">
+      <c r="S18" s="200">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="197">
-        <v>-27.32</v>
+      <c r="T18" s="194">
+        <v>-26.93</v>
       </c>
     </row>
     <row r="19">
@@ -10487,41 +10679,41 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="213">
+      <c r="I19" s="210">
         <v>1.39</v>
       </c>
-      <c r="J19" s="212">
+      <c r="J19" s="215">
         <v>0.39</v>
       </c>
       <c r="K19" s="206">
         <v>1.93</v>
       </c>
-      <c r="L19" s="207">
+      <c r="L19" s="216">
         <v>3.7</v>
       </c>
-      <c r="M19" s="208">
+      <c r="M19" s="207">
         <v>9.45</v>
       </c>
-      <c r="N19" s="209">
+      <c r="N19" s="211">
         <v>5.75</v>
       </c>
-      <c r="O19" s="210">
+      <c r="O19" s="212">
         <v>12.85</v>
       </c>
-      <c r="P19" s="214">
+      <c r="P19" s="213">
         <v>8.68</v>
       </c>
-      <c r="Q19" s="211">
+      <c r="Q19" s="214">
         <v>14.74</v>
       </c>
-      <c r="R19" s="215">
+      <c r="R19" s="208">
         <v>14.89</v>
       </c>
-      <c r="S19" s="216">
+      <c r="S19" s="205">
         <v>9.1</v>
       </c>
-      <c r="T19" s="205">
-        <v>14.89</v>
+      <c r="T19" s="209">
+        <v>16.4</v>
       </c>
     </row>
     <row r="20">
@@ -10549,41 +10741,41 @@
       <c r="H20">
         <v>-1.89</v>
       </c>
-      <c r="I20" s="228">
+      <c r="I20" s="220">
         <v>1.85</v>
       </c>
-      <c r="J20" s="217">
+      <c r="J20" s="228">
         <v>8.14</v>
       </c>
-      <c r="K20" s="226">
+      <c r="K20" s="221">
         <v>2.43</v>
       </c>
-      <c r="L20" s="227">
+      <c r="L20" s="217">
         <v>1.09</v>
       </c>
-      <c r="M20" s="222">
+      <c r="M20" s="218">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="218">
+      <c r="N20" s="227">
         <v>-0.76</v>
       </c>
       <c r="O20" s="223">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="219">
+      <c r="P20" s="224">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="220">
+      <c r="Q20" s="219">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="221">
+      <c r="R20" s="225">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="224">
+      <c r="S20" s="222">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="225">
-        <v>-9.91</v>
+      <c r="T20" s="226">
+        <v>-9.57</v>
       </c>
     </row>
     <row r="21">
@@ -10611,41 +10803,41 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="231">
+      <c r="I21" s="232">
         <v>8.65</v>
       </c>
-      <c r="J21" s="240">
+      <c r="J21" s="229">
         <v>9.13</v>
       </c>
-      <c r="K21" s="229">
+      <c r="K21" s="237">
         <v>12.02</v>
       </c>
-      <c r="L21" s="232">
+      <c r="L21" s="238">
         <v>9.13</v>
       </c>
       <c r="M21" s="233">
         <v>12.86</v>
       </c>
-      <c r="N21" s="236">
+      <c r="N21" s="239">
         <v>8.29</v>
       </c>
-      <c r="O21" s="237">
+      <c r="O21" s="240">
         <v>0.36</v>
       </c>
-      <c r="P21" s="238">
+      <c r="P21" s="234">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="239">
+      <c r="Q21" s="230">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="230">
+      <c r="R21" s="235">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="234">
+      <c r="S21" s="231">
         <v>2.04</v>
       </c>
-      <c r="T21" s="235">
-        <v>-3.73</v>
+      <c r="T21" s="236">
+        <v>-5.29</v>
       </c>
     </row>
     <row r="22">
@@ -10673,41 +10865,41 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="243">
+      <c r="I22" s="249">
         <v>9.66</v>
       </c>
-      <c r="J22" s="252">
+      <c r="J22" s="241">
         <v>14</v>
       </c>
-      <c r="K22" s="241">
+      <c r="K22" s="242">
         <v>19.72</v>
       </c>
-      <c r="L22" s="249">
+      <c r="L22" s="247">
         <v>17.55</v>
       </c>
-      <c r="M22" s="242">
+      <c r="M22" s="243">
         <v>15.78</v>
       </c>
-      <c r="N22" s="245">
+      <c r="N22" s="250">
         <v>6.9</v>
       </c>
-      <c r="O22" s="246">
+      <c r="O22" s="244">
         <v>0.99</v>
       </c>
-      <c r="P22" s="247">
+      <c r="P22" s="248">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="250">
+      <c r="Q22" s="246">
         <v>8.88</v>
       </c>
-      <c r="R22" s="251">
+      <c r="R22" s="245">
         <v>4.73</v>
       </c>
-      <c r="S22" s="248">
+      <c r="S22" s="251">
         <v>5.92</v>
       </c>
-      <c r="T22" s="244">
-        <v>-14</v>
+      <c r="T22" s="252">
+        <v>-13.81</v>
       </c>
     </row>
     <row r="23">
@@ -10735,41 +10927,41 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="260">
+      <c r="I23" s="258">
         <v>5.78</v>
       </c>
-      <c r="J23" s="261">
+      <c r="J23" s="263">
         <v>3.91</v>
       </c>
-      <c r="K23" s="258">
+      <c r="K23" s="259">
         <v>6.83</v>
       </c>
-      <c r="L23" s="264">
+      <c r="L23" s="255">
         <v>4.79</v>
       </c>
-      <c r="M23" s="259">
+      <c r="M23" s="260">
         <v>5.08</v>
       </c>
-      <c r="N23" s="253">
+      <c r="N23" s="256">
         <v>4.5</v>
       </c>
-      <c r="O23" s="262">
+      <c r="O23" s="264">
         <v>1.4</v>
       </c>
-      <c r="P23" s="254">
+      <c r="P23" s="262">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="263">
+      <c r="Q23" s="253">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="255">
+      <c r="R23" s="261">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="256">
+      <c r="S23" s="254">
         <v>-3.33</v>
       </c>
       <c r="T23" s="257">
-        <v>6.42</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="24">
@@ -10797,41 +10989,41 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="271">
+      <c r="I24" s="274">
         <v>-0.93</v>
       </c>
-      <c r="J24" s="275">
+      <c r="J24" s="269">
         <v>-2.54</v>
       </c>
-      <c r="K24" s="265">
+      <c r="K24" s="276">
         <v>-5.77</v>
       </c>
-      <c r="L24" s="276">
+      <c r="L24" s="270">
         <v>-12.46</v>
       </c>
-      <c r="M24" s="274">
+      <c r="M24" s="265">
         <v>-11.46</v>
       </c>
       <c r="N24" s="266">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="272">
+      <c r="O24" s="267">
         <v>-7.66</v>
       </c>
-      <c r="P24" s="267">
+      <c r="P24" s="268">
         <v>-9.54</v>
       </c>
-      <c r="Q24" s="268">
+      <c r="Q24" s="275">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="269">
+      <c r="R24" s="271">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="273">
+      <c r="S24" s="272">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="270">
-        <v>-6.33</v>
+      <c r="T24" s="273">
+        <v>-9.13</v>
       </c>
     </row>
     <row r="25">
@@ -10859,41 +11051,41 @@
       <c r="H25">
         <v>-1.47</v>
       </c>
-      <c r="I25" s="285">
+      <c r="I25" s="288">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="287">
+      <c r="J25" s="283">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="286">
+      <c r="K25" s="279">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="280">
+      <c r="L25" s="284">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="281">
+      <c r="M25" s="280">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="278">
+      <c r="N25" s="285">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="288">
+      <c r="O25" s="277">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="277">
+      <c r="P25" s="287">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="279">
+      <c r="Q25" s="281">
         <v>-17.04</v>
       </c>
       <c r="R25" s="282">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="283">
+      <c r="S25" s="278">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="284">
-        <v>-15.3</v>
+      <c r="T25" s="286">
+        <v>-15.69</v>
       </c>
     </row>
     <row r="26">
@@ -10921,41 +11113,41 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="295">
+      <c r="I26" s="293">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="296">
+      <c r="J26" s="297">
         <v>0.56</v>
       </c>
-      <c r="K26" s="297">
+      <c r="K26" s="291">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="290">
+      <c r="L26" s="299">
         <v>-7.91</v>
       </c>
-      <c r="M26" s="298">
+      <c r="M26" s="294">
         <v>1.36</v>
       </c>
-      <c r="N26" s="291">
+      <c r="N26" s="292">
         <v>3.39</v>
       </c>
-      <c r="O26" s="292">
+      <c r="O26" s="295">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="293">
+      <c r="P26" s="300">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="289">
+      <c r="Q26" s="296">
         <v>7.01</v>
       </c>
-      <c r="R26" s="299">
+      <c r="R26" s="289">
         <v>12.66</v>
       </c>
-      <c r="S26" s="294">
+      <c r="S26" s="298">
         <v>6.55</v>
       </c>
-      <c r="T26" s="300">
-        <v>-12.2</v>
+      <c r="T26" s="290">
+        <v>-12.09</v>
       </c>
     </row>
     <row r="27">
@@ -10983,41 +11175,41 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="308">
+      <c r="I27" s="312">
         <v>-1.23</v>
       </c>
       <c r="J27" s="301">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="304">
+      <c r="K27" s="305">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="305">
+      <c r="L27" s="306">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="306">
+      <c r="M27" s="308">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="309">
+      <c r="N27" s="302">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="310">
+      <c r="O27" s="303">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="311">
+      <c r="P27" s="307">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="302">
+      <c r="Q27" s="309">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="307">
+      <c r="R27" s="304">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="312">
+      <c r="S27" s="310">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="303">
-        <v>-12.17</v>
+      <c r="T27" s="311">
+        <v>-12.02</v>
       </c>
     </row>
     <row r="28">
@@ -11045,41 +11237,41 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="324">
+      <c r="I28" s="321">
         <v>1.28</v>
       </c>
-      <c r="J28" s="318">
+      <c r="J28" s="316">
         <v>2.92</v>
       </c>
-      <c r="K28" s="319">
+      <c r="K28" s="317">
         <v>4.72</v>
       </c>
-      <c r="L28" s="314">
+      <c r="L28" s="324">
         <v>6.25</v>
       </c>
-      <c r="M28" s="316">
+      <c r="M28" s="322">
         <v>16.86</v>
       </c>
-      <c r="N28" s="320">
+      <c r="N28" s="313">
         <v>13.12</v>
       </c>
-      <c r="O28" s="321">
+      <c r="O28" s="318">
         <v>24.45</v>
       </c>
-      <c r="P28" s="317">
+      <c r="P28" s="319">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="322">
+      <c r="Q28" s="323">
         <v>46.03</v>
       </c>
-      <c r="R28" s="315">
+      <c r="R28" s="314">
         <v>45.46</v>
       </c>
-      <c r="S28" s="313">
+      <c r="S28" s="320">
         <v>42.9</v>
       </c>
-      <c r="T28" s="323">
-        <v>56.64</v>
+      <c r="T28" s="315">
+        <v>55.61</v>
       </c>
     </row>
     <row r="29">
@@ -11107,41 +11299,41 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="333">
+      <c r="I29" s="326">
         <v>3.14</v>
       </c>
-      <c r="J29" s="336">
+      <c r="J29" s="331">
         <v>-1.16</v>
       </c>
-      <c r="K29" s="325">
+      <c r="K29" s="335">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="332">
         <v>-0.61</v>
       </c>
-      <c r="M29" s="331">
+      <c r="M29" s="336">
         <v>6.71</v>
       </c>
       <c r="N29" s="327">
         <v>3.47</v>
       </c>
-      <c r="O29" s="326">
+      <c r="O29" s="328">
         <v>-0.94</v>
       </c>
-      <c r="P29" s="328">
+      <c r="P29" s="333">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="335">
+      <c r="Q29" s="329">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="329">
+      <c r="R29" s="325">
         <v>0.11</v>
       </c>
-      <c r="S29" s="332">
+      <c r="S29" s="334">
         <v>2.42</v>
       </c>
       <c r="T29" s="330">
-        <v>9.96</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="30">
@@ -11175,35 +11367,35 @@
       <c r="J30" s="348">
         <v>7.78</v>
       </c>
-      <c r="K30" s="337">
+      <c r="K30" s="339">
         <v>13.84</v>
       </c>
-      <c r="L30" s="340">
+      <c r="L30" s="341">
         <v>11.93</v>
       </c>
-      <c r="M30" s="344">
+      <c r="M30" s="337">
         <v>5.23</v>
       </c>
-      <c r="N30" s="338">
+      <c r="N30" s="342">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="339">
+      <c r="O30" s="343">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="341">
+      <c r="P30" s="344">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="342">
+      <c r="Q30" s="345">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="343">
+      <c r="R30" s="346">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="345">
+      <c r="S30" s="338">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="346">
-        <v>-10.78</v>
+      <c r="T30" s="340">
+        <v>-16.45</v>
       </c>
     </row>
     <row r="31">
@@ -11231,41 +11423,41 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="357">
+      <c r="I31" s="360">
         <v>1.82</v>
       </c>
-      <c r="J31" s="358">
+      <c r="J31" s="351">
         <v>6.88</v>
       </c>
-      <c r="K31" s="360">
+      <c r="K31" s="349">
         <v>4.25</v>
       </c>
-      <c r="L31" s="352">
+      <c r="L31" s="356">
         <v>1.42</v>
       </c>
-      <c r="M31" s="349">
+      <c r="M31" s="357">
         <v>-7.09</v>
       </c>
       <c r="N31" s="350">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="355">
+      <c r="O31" s="358">
         <v>-10.32</v>
       </c>
-      <c r="P31" s="351">
+      <c r="P31" s="352">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="353">
+      <c r="Q31" s="359">
         <v>-17</v>
       </c>
-      <c r="R31" s="354">
+      <c r="R31" s="353">
         <v>-16.8</v>
       </c>
-      <c r="S31" s="359">
+      <c r="S31" s="354">
         <v>-17.41</v>
       </c>
-      <c r="T31" s="356">
-        <v>-15.18</v>
+      <c r="T31" s="355">
+        <v>-12.35</v>
       </c>
     </row>
     <row r="32">
@@ -11293,41 +11485,41 @@
       <c r="H32">
         <v>-1.07</v>
       </c>
-      <c r="I32" s="371">
+      <c r="I32" s="361">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="366">
+      <c r="J32" s="365">
         <v>0.27</v>
       </c>
-      <c r="K32" s="372">
+      <c r="K32" s="362">
         <v>2.99</v>
       </c>
-      <c r="L32" s="367">
+      <c r="L32" s="366">
         <v>2.35</v>
       </c>
-      <c r="M32" s="361">
+      <c r="M32" s="363">
         <v>0.72</v>
       </c>
-      <c r="N32" s="362">
+      <c r="N32" s="367">
         <v>1</v>
       </c>
       <c r="O32" s="368">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="363">
+      <c r="P32" s="371">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="369">
+      <c r="Q32" s="364">
         <v>3.26</v>
       </c>
-      <c r="R32" s="364">
+      <c r="R32" s="369">
         <v>1</v>
       </c>
       <c r="S32" s="370">
         <v>1.45</v>
       </c>
-      <c r="T32" s="365">
-        <v>-5.16</v>
+      <c r="T32" s="372">
+        <v>4.34</v>
       </c>
     </row>
     <row r="33">
@@ -11355,41 +11547,41 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="375">
+      <c r="I33" s="382">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="382">
+      <c r="J33" s="383">
         <v>0.57</v>
       </c>
-      <c r="K33" s="376">
+      <c r="K33" s="374">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="379">
+      <c r="L33" s="384">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="383">
+      <c r="M33" s="373">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="380">
+      <c r="N33" s="375">
         <v>-20.6</v>
       </c>
-      <c r="O33" s="384">
+      <c r="O33" s="376">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="373">
+      <c r="P33" s="378">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="381">
+      <c r="Q33" s="379">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="374">
+      <c r="R33" s="380">
         <v>-20.6</v>
       </c>
       <c r="S33" s="377">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="378">
-        <v>-21.17</v>
+      <c r="T33" s="381">
+        <v>-21.55</v>
       </c>
     </row>
     <row r="34">
@@ -11420,38 +11612,38 @@
       <c r="I34" s="386">
         <v>-3</v>
       </c>
-      <c r="J34" s="387">
+      <c r="J34" s="393">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="395">
+      <c r="K34" s="394">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="391">
+      <c r="L34" s="390">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="392">
+      <c r="M34" s="387">
         <v>-16.82</v>
       </c>
-      <c r="N34" s="396">
+      <c r="N34" s="385">
         <v>-18.2</v>
       </c>
-      <c r="O34" s="388">
+      <c r="O34" s="395">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="385">
+      <c r="P34" s="388">
         <v>-19.82</v>
       </c>
       <c r="Q34" s="389">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="390">
+      <c r="R34" s="396">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="393">
+      <c r="S34" s="391">
         <v>-21.43</v>
       </c>
-      <c r="T34" s="394">
-        <v>-18.2</v>
+      <c r="T34" s="392">
+        <v>-12.67</v>
       </c>
     </row>
     <row r="35">
@@ -11479,41 +11671,41 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="403">
+      <c r="I35" s="406">
         <v>4.2</v>
       </c>
-      <c r="J35" s="399">
+      <c r="J35" s="401">
         <v>3.72</v>
       </c>
-      <c r="K35" s="401">
+      <c r="K35" s="407">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="402">
+      <c r="L35" s="398">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="404">
+      <c r="M35" s="402">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="406">
+      <c r="N35" s="408">
         <v>6.61</v>
       </c>
-      <c r="O35" s="407">
+      <c r="O35" s="403">
         <v>5.5</v>
       </c>
-      <c r="P35" s="408">
+      <c r="P35" s="399">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="397">
+      <c r="Q35" s="404">
         <v>1.68</v>
       </c>
-      <c r="R35" s="400">
+      <c r="R35" s="397">
         <v>1.37</v>
       </c>
-      <c r="S35" s="398">
+      <c r="S35" s="400">
         <v>0.08</v>
       </c>
       <c r="T35" s="405">
-        <v>-1.6</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="36">
@@ -11544,38 +11736,38 @@
       <c r="I36" s="410">
         <v>5.57</v>
       </c>
-      <c r="J36" s="415">
+      <c r="J36" s="411">
         <v>16.17</v>
       </c>
-      <c r="K36" s="411">
+      <c r="K36" s="412">
         <v>22.01</v>
       </c>
-      <c r="L36" s="419">
+      <c r="L36" s="417">
         <v>16.85</v>
       </c>
-      <c r="M36" s="412">
+      <c r="M36" s="418">
         <v>7.07</v>
       </c>
-      <c r="N36" s="417">
+      <c r="N36" s="419">
         <v>0.27</v>
       </c>
-      <c r="O36" s="420">
+      <c r="O36" s="413">
         <v>2.45</v>
       </c>
-      <c r="P36" s="413">
+      <c r="P36" s="420">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="409">
+      <c r="Q36" s="414">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="414">
+      <c r="R36" s="415">
         <v>9.65</v>
       </c>
-      <c r="S36" s="418">
+      <c r="S36" s="409">
         <v>7.47</v>
       </c>
       <c r="T36" s="416">
-        <v>-5.57</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="37">
@@ -11603,41 +11795,41 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="426">
+      <c r="I37" s="425">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="430">
+      <c r="J37" s="423">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="428">
+      <c r="K37" s="426">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="431">
+      <c r="L37" s="421">
         <v>7.57</v>
       </c>
       <c r="M37" s="424">
         <v>5.6</v>
       </c>
-      <c r="N37" s="432">
+      <c r="N37" s="429">
         <v>4.48</v>
       </c>
-      <c r="O37" s="427">
+      <c r="O37" s="430">
         <v>3.32</v>
       </c>
-      <c r="P37" s="421">
+      <c r="P37" s="422">
         <v>5.48</v>
       </c>
-      <c r="Q37" s="422">
+      <c r="Q37" s="427">
         <v>3.78</v>
       </c>
-      <c r="R37" s="429">
+      <c r="R37" s="428">
         <v>8.07</v>
       </c>
-      <c r="S37" s="423">
+      <c r="S37" s="431">
         <v>11.74</v>
       </c>
-      <c r="T37" s="425">
-        <v>4.98</v>
+      <c r="T37" s="432">
+        <v>0.39</v>
       </c>
     </row>
     <row r="38">
@@ -11665,41 +11857,41 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="436">
+      <c r="I38" s="441">
         <v>6.62</v>
       </c>
-      <c r="J38" s="437">
+      <c r="J38" s="436">
         <v>10.07</v>
       </c>
-      <c r="K38" s="438">
+      <c r="K38" s="434">
         <v>6.26</v>
       </c>
-      <c r="L38" s="440">
+      <c r="L38" s="442">
         <v>2.13</v>
       </c>
-      <c r="M38" s="441">
+      <c r="M38" s="437">
         <v>1.41</v>
       </c>
-      <c r="N38" s="442">
+      <c r="N38" s="438">
         <v>7.72</v>
       </c>
-      <c r="O38" s="439">
+      <c r="O38" s="444">
         <v>5.74</v>
       </c>
       <c r="P38" s="435">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="433">
+      <c r="Q38" s="443">
         <v>14.45</v>
       </c>
-      <c r="R38" s="443">
+      <c r="R38" s="433">
         <v>18.62</v>
       </c>
-      <c r="S38" s="434">
+      <c r="S38" s="439">
         <v>14.8</v>
       </c>
-      <c r="T38" s="444">
-        <v>2.33</v>
+      <c r="T38" s="440">
+        <v>1.05</v>
       </c>
     </row>
     <row r="39">
@@ -11727,41 +11919,41 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="454">
+      <c r="I39" s="449">
         <v>7.14</v>
       </c>
-      <c r="J39" s="455">
+      <c r="J39" s="446">
         <v>7.82</v>
       </c>
-      <c r="K39" s="447">
+      <c r="K39" s="453">
         <v>7.68</v>
       </c>
-      <c r="L39" s="448">
+      <c r="L39" s="447">
         <v>8.49</v>
       </c>
-      <c r="M39" s="456">
+      <c r="M39" s="454">
         <v>9.43</v>
       </c>
       <c r="N39" s="450">
         <v>5.39</v>
       </c>
-      <c r="O39" s="451">
+      <c r="O39" s="452">
         <v>8.49</v>
       </c>
-      <c r="P39" s="452">
+      <c r="P39" s="455">
         <v>7.28</v>
       </c>
-      <c r="Q39" s="453">
+      <c r="Q39" s="448">
         <v>11.99</v>
       </c>
-      <c r="R39" s="449">
+      <c r="R39" s="451">
         <v>7.95</v>
       </c>
-      <c r="S39" s="445">
+      <c r="S39" s="456">
         <v>7.55</v>
       </c>
-      <c r="T39" s="446">
-        <v>-0.67</v>
+      <c r="T39" s="445">
+        <v>-8.36</v>
       </c>
     </row>
     <row r="40">
@@ -11789,41 +11981,41 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="459">
+      <c r="I40" s="461">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="463">
+      <c r="J40" s="458">
         <v>-0.66</v>
       </c>
-      <c r="K40" s="468">
+      <c r="K40" s="462">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="464">
+      <c r="L40" s="463">
         <v>0</v>
       </c>
-      <c r="M40" s="457">
+      <c r="M40" s="464">
         <v>-1.31</v>
       </c>
-      <c r="N40" s="460">
+      <c r="N40" s="457">
         <v>0.33</v>
       </c>
-      <c r="O40" s="466">
+      <c r="O40" s="468">
         <v>0</v>
       </c>
-      <c r="P40" s="461">
+      <c r="P40" s="459">
         <v>1.97</v>
       </c>
-      <c r="Q40" s="462">
+      <c r="Q40" s="465">
         <v>-0.22</v>
       </c>
-      <c r="R40" s="465">
+      <c r="R40" s="466">
         <v>2.51</v>
       </c>
-      <c r="S40" s="458">
+      <c r="S40" s="467">
         <v>-0.55</v>
       </c>
-      <c r="T40" s="467">
-        <v>-1.97</v>
+      <c r="T40" s="460">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="41">
@@ -11851,41 +12043,41 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="470">
+      <c r="I41" s="472">
         <v>0.59</v>
       </c>
-      <c r="J41" s="471">
+      <c r="J41" s="473">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="477">
+      <c r="K41" s="470">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="473">
+      <c r="L41" s="474">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="474">
+      <c r="M41" s="477">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="478">
+      <c r="N41" s="471">
         <v>-7.55</v>
       </c>
       <c r="O41" s="479">
         <v>-6.76</v>
       </c>
-      <c r="P41" s="480">
+      <c r="P41" s="475">
         <v>-8.43</v>
       </c>
-      <c r="Q41" s="475">
+      <c r="Q41" s="480">
         <v>-9.51</v>
       </c>
-      <c r="R41" s="472">
+      <c r="R41" s="469">
         <v>-7.55</v>
       </c>
-      <c r="S41" s="469">
+      <c r="S41" s="476">
         <v>-9.12</v>
       </c>
-      <c r="T41" s="476">
-        <v>-9.12</v>
+      <c r="T41" s="478">
+        <v>-8.33</v>
       </c>
     </row>
     <row r="42">
@@ -11913,39 +12105,41 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="487">
+      <c r="I42" s="485">
         <v>2.08</v>
       </c>
-      <c r="J42" s="491">
+      <c r="J42" s="492">
         <v>2.7</v>
       </c>
-      <c r="K42" s="484">
+      <c r="K42" s="486">
         <v>0</v>
       </c>
-      <c r="L42" s="488">
+      <c r="L42" s="487">
         <v>1.25</v>
       </c>
-      <c r="M42" s="483">
+      <c r="M42" s="482">
         <v>1.04</v>
       </c>
-      <c r="N42" s="489">
+      <c r="N42" s="488">
         <v>1.56</v>
       </c>
-      <c r="O42" s="485">
+      <c r="O42" s="489">
         <v>-0.52</v>
       </c>
-      <c r="P42" s="486">
+      <c r="P42" s="483">
         <v>-1.56</v>
       </c>
       <c r="Q42" s="481">
         <v>-6.75</v>
       </c>
-      <c r="R42" s="482">
+      <c r="R42" s="490">
         <v>-5.61</v>
       </c>
-      <c r="S42" t="str"/>
-      <c r="T42" s="490">
-        <v>-5.61</v>
+      <c r="S42" s="484">
+        <v>-8.93</v>
+      </c>
+      <c r="T42" s="491">
+        <v>-8.93</v>
       </c>
     </row>
     <row r="43">
@@ -11973,37 +12167,39 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="499">
+      <c r="I43" s="495">
         <v>-0.65</v>
       </c>
-      <c r="J43" s="493">
+      <c r="J43" s="496">
         <v>-1.3</v>
       </c>
-      <c r="K43" s="494">
+      <c r="K43" s="497">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="495">
+      <c r="L43" s="501">
         <v>8.46</v>
       </c>
-      <c r="M43" s="498">
+      <c r="M43" s="500">
         <v>10.98</v>
       </c>
-      <c r="N43" s="496">
+      <c r="N43" s="493">
         <v>10.41</v>
       </c>
-      <c r="O43" s="500">
+      <c r="O43" s="498">
         <v>21.46</v>
       </c>
-      <c r="P43" s="501">
+      <c r="P43" s="499">
         <v>26.1</v>
       </c>
-      <c r="Q43" s="497">
+      <c r="Q43" s="494">
         <v>22.85</v>
       </c>
-      <c r="R43" t="str"/>
+      <c r="R43" s="502">
+        <v>19.76</v>
+      </c>
       <c r="S43" t="str"/>
-      <c r="T43" s="492">
-        <v>22.85</v>
+      <c r="T43" s="503">
+        <v>19.76</v>
       </c>
     </row>
     <row r="44">
@@ -12031,35 +12227,37 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="510">
+      <c r="I44" s="504">
         <v>10.68</v>
       </c>
-      <c r="J44" s="505">
+      <c r="J44" s="507">
         <v>1.78</v>
       </c>
-      <c r="K44" s="506">
+      <c r="K44" s="505">
         <v>-1.94</v>
       </c>
-      <c r="L44" s="507">
+      <c r="L44" s="508">
         <v>3.72</v>
       </c>
-      <c r="M44" s="503">
+      <c r="M44" s="509">
         <v>2.1</v>
       </c>
-      <c r="N44" s="502">
+      <c r="N44" s="513">
         <v>6.15</v>
       </c>
-      <c r="O44" s="508">
+      <c r="O44" s="506">
         <v>9.06</v>
       </c>
-      <c r="P44" s="509">
+      <c r="P44" s="510">
         <v>-0.97</v>
       </c>
-      <c r="Q44" t="str"/>
+      <c r="Q44" s="511">
+        <v>-9.06</v>
+      </c>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="504">
-        <v>-0.97</v>
+      <c r="T44" s="512">
+        <v>-9.06</v>
       </c>
     </row>
     <row r="45">
@@ -12087,33 +12285,35 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="517">
+      <c r="I45" s="514">
         <v>2.03</v>
       </c>
-      <c r="J45" s="512">
+      <c r="J45" s="515">
         <v>5.03</v>
       </c>
-      <c r="K45" s="513">
+      <c r="K45" s="517">
         <v>5.82</v>
       </c>
       <c r="L45" s="518">
         <v>3.17</v>
       </c>
-      <c r="M45" s="511">
+      <c r="M45" s="522">
         <v>-0.26</v>
       </c>
-      <c r="N45" s="514">
+      <c r="N45" s="516">
         <v>-2.65</v>
       </c>
-      <c r="O45" s="515">
+      <c r="O45" s="521">
         <v>-7.58</v>
       </c>
-      <c r="P45" t="str"/>
+      <c r="P45" s="519">
+        <v>1.68</v>
+      </c>
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="516">
-        <v>-7.58</v>
+      <c r="T45" s="520">
+        <v>1.68</v>
       </c>
     </row>
     <row r="46">
@@ -12141,29 +12341,31 @@
       <c r="H46">
         <v>-0.93</v>
       </c>
-      <c r="I46" s="521">
+      <c r="I46" s="526">
         <v>1.8</v>
       </c>
-      <c r="J46" s="522">
+      <c r="J46" s="527">
         <v>0.31</v>
       </c>
-      <c r="K46" s="523">
+      <c r="K46" s="528">
         <v>3.04</v>
       </c>
-      <c r="L46" s="524">
+      <c r="L46" s="529">
         <v>0.78</v>
       </c>
-      <c r="M46" s="519">
+      <c r="M46" s="523">
         <v>-3.2</v>
       </c>
-      <c r="N46" t="str"/>
+      <c r="N46" s="524">
+        <v>-0.47</v>
+      </c>
       <c r="O46" t="str"/>
       <c r="P46" t="str"/>
       <c r="Q46" t="str"/>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" s="520">
-        <v>-3.2</v>
+      <c r="T46" s="525">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="47">
@@ -12191,27 +12393,29 @@
       <c r="H47">
         <v>0.36</v>
       </c>
-      <c r="I47" s="525">
+      <c r="I47" s="530">
         <v>-1.87</v>
       </c>
-      <c r="J47" s="526">
+      <c r="J47" s="531">
         <v>-0.72</v>
       </c>
-      <c r="K47" s="527">
+      <c r="K47" s="532">
         <v>2.87</v>
       </c>
-      <c r="L47" s="528">
+      <c r="L47" s="533">
         <v>-1.03</v>
       </c>
-      <c r="M47" t="str"/>
+      <c r="M47" s="534">
+        <v>-3.37</v>
+      </c>
       <c r="N47" t="str"/>
       <c r="O47" t="str"/>
       <c r="P47" t="str"/>
       <c r="Q47" t="str"/>
       <c r="R47" t="str"/>
       <c r="S47" t="str"/>
-      <c r="T47" s="529">
-        <v>-1.03</v>
+      <c r="T47" s="535">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="48">
@@ -12239,16 +12443,18 @@
       <c r="H48">
         <v>-1.29</v>
       </c>
-      <c r="I48" s="533">
+      <c r="I48" s="540">
         <v>3.67</v>
       </c>
-      <c r="J48" s="530">
+      <c r="J48" s="536">
         <v>6.46</v>
       </c>
-      <c r="K48" s="531">
+      <c r="K48" s="537">
         <v>-0.77</v>
       </c>
-      <c r="L48" t="str"/>
+      <c r="L48" s="538">
+        <v>-2.9</v>
+      </c>
       <c r="M48" t="str"/>
       <c r="N48" t="str"/>
       <c r="O48" t="str"/>
@@ -12256,8 +12462,8 @@
       <c r="Q48" t="str"/>
       <c r="R48" t="str"/>
       <c r="S48" t="str"/>
-      <c r="T48" s="532">
-        <v>-0.77</v>
+      <c r="T48" s="539">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="49">
@@ -12285,13 +12491,15 @@
       <c r="H49">
         <v>0</v>
       </c>
-      <c r="I49" s="535">
+      <c r="I49" s="541">
         <v>-3.53</v>
       </c>
-      <c r="J49" s="536">
+      <c r="J49" s="542">
         <v>-3.9</v>
       </c>
-      <c r="K49" t="str"/>
+      <c r="K49" s="543">
+        <v>-2.8</v>
+      </c>
       <c r="L49" t="str"/>
       <c r="M49" t="str"/>
       <c r="N49" t="str"/>
@@ -12300,8 +12508,8 @@
       <c r="Q49" t="str"/>
       <c r="R49" t="str"/>
       <c r="S49" t="str"/>
-      <c r="T49" s="534">
-        <v>-3.9</v>
+      <c r="T49" s="544">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="50">
@@ -12329,13 +12537,15 @@
       <c r="H50">
         <v>3.71</v>
       </c>
-      <c r="I50" s="537">
+      <c r="I50" s="545">
         <v>0.49</v>
       </c>
-      <c r="J50" s="538">
+      <c r="J50" s="546">
         <v>-8.37</v>
       </c>
-      <c r="K50" t="str"/>
+      <c r="K50" s="547">
+        <v>-7.56</v>
+      </c>
       <c r="L50" t="str"/>
       <c r="M50" t="str"/>
       <c r="N50" t="str"/>
@@ -12344,8 +12554,8 @@
       <c r="Q50" t="str"/>
       <c r="R50" t="str"/>
       <c r="S50" t="str"/>
-      <c r="T50" s="539">
-        <v>-8.37</v>
+      <c r="T50" s="548">
+        <v>-7.56</v>
       </c>
     </row>
     <row r="51">
@@ -12373,10 +12583,12 @@
       <c r="H51">
         <v>-0.95</v>
       </c>
-      <c r="I51" s="540">
+      <c r="I51" s="549">
         <v>-1.85</v>
       </c>
-      <c r="J51" t="str"/>
+      <c r="J51" s="550">
+        <v>2.81</v>
+      </c>
       <c r="K51" t="str"/>
       <c r="L51" t="str"/>
       <c r="M51" t="str"/>
@@ -12386,59 +12598,53 @@
       <c r="Q51" t="str"/>
       <c r="R51" t="str"/>
       <c r="S51" t="str"/>
-      <c r="T51" t="str"/>
+      <c r="T51" s="551">
+        <v>2.81</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B52" t="str"/>
-      <c r="C52" t="str"/>
-      <c r="D52" t="str"/>
-      <c r="E52" t="str"/>
-      <c r="F52" t="str"/>
-      <c r="G52" t="str"/>
-      <c r="H52" t="str"/>
-      <c r="I52">
-        <v>50</v>
-      </c>
-      <c r="J52">
-        <v>49</v>
-      </c>
-      <c r="K52">
-        <v>47</v>
-      </c>
-      <c r="L52">
-        <v>46</v>
-      </c>
-      <c r="M52">
-        <v>45</v>
-      </c>
-      <c r="N52">
-        <v>44</v>
-      </c>
-      <c r="O52">
-        <v>44</v>
-      </c>
-      <c r="P52">
-        <v>43</v>
-      </c>
-      <c r="Q52">
-        <v>42</v>
-      </c>
-      <c r="R52">
-        <v>41</v>
-      </c>
-      <c r="S52">
-        <v>40</v>
-      </c>
-      <c r="T52">
-        <v>49</v>
-      </c>
+        <v>2026-04-27</v>
+      </c>
+      <c r="B52" t="str">
+        <v>应流股份</v>
+      </c>
+      <c r="C52" t="str">
+        <v>603308</v>
+      </c>
+      <c r="D52" t="str">
+        <v>(09:25:00)好股不嫌贵, 跑步进场应流股份</v>
+      </c>
+      <c r="E52">
+        <v>80.56</v>
+      </c>
+      <c r="F52">
+        <v>80.4</v>
+      </c>
+      <c r="G52">
+        <v>80.56</v>
+      </c>
+      <c r="H52">
+        <v>-1.98</v>
+      </c>
+      <c r="I52" s="552">
+        <v>-0.2</v>
+      </c>
+      <c r="J52" t="str"/>
+      <c r="K52" t="str"/>
+      <c r="L52" t="str"/>
+      <c r="M52" t="str"/>
+      <c r="N52" t="str"/>
+      <c r="O52" t="str"/>
+      <c r="P52" t="str"/>
+      <c r="Q52" t="str"/>
+      <c r="R52" t="str"/>
+      <c r="S52" t="str"/>
+      <c r="T52" t="str"/>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B53" t="str"/>
       <c r="C53" t="str"/>
@@ -12447,46 +12653,46 @@
       <c r="F53" t="str"/>
       <c r="G53" t="str"/>
       <c r="H53" t="str"/>
-      <c r="I53" s="542">
-        <v>58</v>
-      </c>
-      <c r="J53" s="544">
-        <v>57.14</v>
-      </c>
-      <c r="K53" s="549">
-        <v>53.19</v>
-      </c>
-      <c r="L53" s="545">
-        <v>58.7</v>
-      </c>
-      <c r="M53" s="552">
-        <v>53.33</v>
-      </c>
-      <c r="N53" s="546">
-        <v>56.82</v>
-      </c>
-      <c r="O53" s="541">
-        <v>40.91</v>
-      </c>
-      <c r="P53" s="550">
-        <v>41.86</v>
-      </c>
-      <c r="Q53" s="551">
-        <v>40.48</v>
-      </c>
-      <c r="R53" s="547">
-        <v>46.34</v>
-      </c>
-      <c r="S53" s="543">
-        <v>47.5</v>
-      </c>
-      <c r="T53" s="548">
-        <v>24.49</v>
+      <c r="I53">
+        <v>51</v>
+      </c>
+      <c r="J53">
+        <v>50</v>
+      </c>
+      <c r="K53">
+        <v>49</v>
+      </c>
+      <c r="L53">
+        <v>47</v>
+      </c>
+      <c r="M53">
+        <v>46</v>
+      </c>
+      <c r="N53">
+        <v>45</v>
+      </c>
+      <c r="O53">
+        <v>44</v>
+      </c>
+      <c r="P53">
+        <v>44</v>
+      </c>
+      <c r="Q53">
+        <v>43</v>
+      </c>
+      <c r="R53">
+        <v>42</v>
+      </c>
+      <c r="S53">
+        <v>41</v>
+      </c>
+      <c r="T53">
+        <v>50</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B54" t="str"/>
       <c r="C54" t="str"/>
@@ -12495,41 +12701,89 @@
       <c r="F54" t="str"/>
       <c r="G54" t="str"/>
       <c r="H54" t="str"/>
-      <c r="I54" s="556">
-        <v>1.87</v>
-      </c>
-      <c r="J54" s="562">
-        <v>2.06</v>
-      </c>
-      <c r="K54" s="563">
-        <v>1.88</v>
-      </c>
-      <c r="L54" s="564">
-        <v>1.19</v>
+      <c r="I54" s="563">
+        <v>56.86</v>
+      </c>
+      <c r="J54" s="564">
+        <v>58</v>
+      </c>
+      <c r="K54" s="559">
+        <v>51.02</v>
+      </c>
+      <c r="L54" s="553">
+        <v>57.45</v>
       </c>
       <c r="M54" s="560">
-        <v>1.33</v>
-      </c>
-      <c r="N54" s="557">
-        <v>0.21</v>
-      </c>
-      <c r="O54" s="553">
+        <v>52.17</v>
+      </c>
+      <c r="N54" s="561">
+        <v>55.56</v>
+      </c>
+      <c r="O54" s="555">
+        <v>40.91</v>
+      </c>
+      <c r="P54" s="562">
+        <v>43.18</v>
+      </c>
+      <c r="Q54" s="556">
+        <v>39.53</v>
+      </c>
+      <c r="R54" s="554">
+        <v>47.62</v>
+      </c>
+      <c r="S54" s="557">
+        <v>46.34</v>
+      </c>
+      <c r="T54" s="558">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B55" t="str"/>
+      <c r="C55" t="str"/>
+      <c r="D55" t="str"/>
+      <c r="E55" t="str"/>
+      <c r="F55" t="str"/>
+      <c r="G55" t="str"/>
+      <c r="H55" t="str"/>
+      <c r="I55" s="573">
+        <v>1.83</v>
+      </c>
+      <c r="J55" s="566">
+        <v>2.08</v>
+      </c>
+      <c r="K55" s="567">
+        <v>1.59</v>
+      </c>
+      <c r="L55" s="569">
+        <v>1.1</v>
+      </c>
+      <c r="M55" s="576">
+        <v>1.23</v>
+      </c>
+      <c r="N55" s="570">
+        <v>0.2</v>
+      </c>
+      <c r="O55" s="571">
         <v>0.14</v>
       </c>
-      <c r="P54" s="558">
-        <v>0.17</v>
-      </c>
-      <c r="Q54" s="554">
-        <v>-0.3</v>
-      </c>
-      <c r="R54" s="561">
-        <v>0.42</v>
-      </c>
-      <c r="S54" s="559">
-        <v>0.62</v>
-      </c>
-      <c r="T54" s="555">
-        <v>-4.13</v>
+      <c r="P55" s="574">
+        <v>0.2</v>
+      </c>
+      <c r="Q55" s="565">
+        <v>-0.5</v>
+      </c>
+      <c r="R55" s="575">
+        <v>0.88</v>
+      </c>
+      <c r="S55" s="572">
+        <v>0.39</v>
+      </c>
+      <c r="T55" s="568">
+        <v>-4.03</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -39,19 +39,289 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D4A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF39AE54"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D4A6"/>
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,13 +333,3019 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEFF8F1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,79 +3357,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8E97"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4654"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,637 +3453,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
+        <fgColor rgb="FFD93443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -807,2689 +3477,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
+        <fgColor rgb="FFE9828C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA6AD"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9625,40 +9625,40 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="7">
         <v>4.95</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="9">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="11">
         <v>1.74</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L2" s="2">
         <v>-0.92</v>
       </c>
       <c r="M2" s="3">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="10">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="10">
+      <c r="O2" s="4">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="5">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="8">
         <v>-4.86</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="12">
         <v>-4.59</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="6">
         <v>-6.79</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="1">
         <v>-21.83</v>
       </c>
     </row>
@@ -9687,40 +9687,40 @@
       <c r="H3">
         <v>0.21</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="16">
         <v>-1.24</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="13">
         <v>-0.41</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="14">
         <v>-0.21</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="23">
         <v>0.1</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="20">
         <v>3.32</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="24">
         <v>-0.52</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="15">
         <v>-0.31</v>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="17">
         <v>2.59</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="21">
         <v>2.8</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="18">
         <v>1.66</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="22">
         <v>-0.1</v>
       </c>
-      <c r="T3" s="20">
+      <c r="T3" s="19">
         <v>15.65</v>
       </c>
     </row>
@@ -9749,40 +9749,40 @@
       <c r="H4">
         <v>0.43</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="36">
         <v>4.19</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="27">
         <v>5.08</v>
       </c>
       <c r="K4" s="34">
         <v>15.59</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="25">
         <v>27.15</v>
       </c>
       <c r="M4" s="30">
         <v>36.04</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="31">
         <v>41.33</v>
       </c>
-      <c r="O4" s="26">
+      <c r="O4" s="32">
         <v>37.54</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="28">
         <v>45.14</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="26">
         <v>32.33</v>
       </c>
-      <c r="R4" s="25">
+      <c r="R4" s="29">
         <v>45.56</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="35">
         <v>56.03</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="33">
         <v>33.03</v>
       </c>
     </row>
@@ -9811,40 +9811,40 @@
       <c r="H5">
         <v>-1.75</v>
       </c>
-      <c r="I5" s="39">
+      <c r="I5" s="37">
         <v>11.97</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="38">
         <v>17.45</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="39">
         <v>14.27</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="41">
         <v>17.32</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="42">
         <v>25.33</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="46">
         <v>21.54</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="43">
         <v>22.72</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="40">
         <v>20.84</v>
       </c>
       <c r="Q5" s="47">
         <v>17.54</v>
       </c>
-      <c r="R5" s="37">
+      <c r="R5" s="44">
         <v>16.88</v>
       </c>
-      <c r="S5" s="42">
+      <c r="S5" s="48">
         <v>11.79</v>
       </c>
-      <c r="T5" s="38">
+      <c r="T5" s="45">
         <v>31.29</v>
       </c>
     </row>
@@ -9873,40 +9873,40 @@
       <c r="H6">
         <v>1.18</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="50">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="53">
+      <c r="J6" s="51">
         <v>-1.34</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="52">
         <v>-2.2</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="53">
         <v>-0.66</v>
       </c>
-      <c r="M6" s="60">
+      <c r="M6" s="59">
         <v>-2.59</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="54">
         <v>-0.79</v>
       </c>
-      <c r="O6" s="50">
+      <c r="O6" s="55">
         <v>-4.92</v>
       </c>
-      <c r="P6" s="51">
+      <c r="P6" s="56">
         <v>-4.97</v>
       </c>
-      <c r="Q6" s="52">
+      <c r="Q6" s="57">
         <v>-6.26</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="58">
         <v>-6.97</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="60">
         <v>-8.64</v>
       </c>
-      <c r="T6" s="58">
+      <c r="T6" s="49">
         <v>-21.16</v>
       </c>
     </row>
@@ -9935,40 +9935,40 @@
       <c r="H7">
         <v>-0.11</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="62">
         <v>-1.99</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="72">
         <v>1.8</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="70">
         <v>0.07</v>
       </c>
-      <c r="L7" s="63">
+      <c r="L7" s="61">
         <v>0.63</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="63">
         <v>-0.33</v>
       </c>
-      <c r="N7" s="61">
+      <c r="N7" s="64">
         <v>1.55</v>
       </c>
-      <c r="O7" s="62">
+      <c r="O7" s="67">
         <v>0.85</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="65">
         <v>0.88</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="68">
         <v>-9.2</v>
       </c>
-      <c r="R7" s="64">
+      <c r="R7" s="71">
         <v>-6.84</v>
       </c>
-      <c r="S7" s="65">
+      <c r="S7" s="66">
         <v>-6.29</v>
       </c>
-      <c r="T7" s="70">
+      <c r="T7" s="69">
         <v>8.61</v>
       </c>
     </row>
@@ -9997,40 +9997,40 @@
       <c r="H8">
         <v>-1.27</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="73">
         <v>3.13</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="74">
         <v>5.21</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="81">
         <v>0.43</v>
       </c>
-      <c r="L8" s="73">
+      <c r="L8" s="82">
         <v>3.68</v>
       </c>
-      <c r="M8" s="74">
+      <c r="M8" s="77">
         <v>-1.47</v>
       </c>
-      <c r="N8" s="75">
+      <c r="N8" s="78">
         <v>1.66</v>
       </c>
-      <c r="O8" s="78">
+      <c r="O8" s="75">
         <v>1.72</v>
       </c>
       <c r="P8" s="83">
         <v>7.79</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="79">
         <v>15.33</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="76">
         <v>12.57</v>
       </c>
       <c r="S8" s="80">
         <v>23.85</v>
       </c>
-      <c r="T8" s="76">
+      <c r="T8" s="84">
         <v>-13.49</v>
       </c>
     </row>
@@ -10059,40 +10059,40 @@
       <c r="H9">
         <v>0.23</v>
       </c>
-      <c r="I9" s="90">
+      <c r="I9" s="88">
         <v>1.35</v>
       </c>
-      <c r="J9" s="91">
+      <c r="J9" s="89">
         <v>2.48</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="95">
         <v>1.58</v>
       </c>
-      <c r="L9" s="85">
+      <c r="L9" s="90">
         <v>1.35</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="96">
         <v>2.93</v>
       </c>
-      <c r="N9" s="86">
+      <c r="N9" s="85">
         <v>0.23</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="91">
         <v>-2.48</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="86">
         <v>-0.68</v>
       </c>
       <c r="Q9" s="87">
         <v>3.83</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="93">
         <v>7.43</v>
       </c>
-      <c r="S9" s="88">
+      <c r="S9" s="94">
         <v>17.12</v>
       </c>
-      <c r="T9" s="89">
+      <c r="T9" s="92">
         <v>4.05</v>
       </c>
     </row>
@@ -10121,34 +10121,34 @@
       <c r="H10">
         <v>-3.38</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="102">
         <v>-3.57</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="104">
         <v>-6.79</v>
       </c>
-      <c r="K10" s="101">
+      <c r="K10" s="108">
         <v>-7.86</v>
       </c>
       <c r="L10" s="97">
         <v>-9.72</v>
       </c>
-      <c r="M10" s="102">
+      <c r="M10" s="98">
         <v>-12.37</v>
       </c>
-      <c r="N10" s="100">
+      <c r="N10" s="105">
         <v>-10.86</v>
       </c>
-      <c r="O10" s="104">
+      <c r="O10" s="103">
         <v>-9.15</v>
       </c>
-      <c r="P10" s="103">
+      <c r="P10" s="99">
         <v>-10.15</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="101">
         <v>-11.44</v>
       </c>
-      <c r="R10" s="98">
+      <c r="R10" s="100">
         <v>-11.08</v>
       </c>
       <c r="S10" s="106">
@@ -10183,40 +10183,40 @@
       <c r="H11">
         <v>-2.01</v>
       </c>
-      <c r="I11" s="114">
+      <c r="I11" s="109">
         <v>7.32</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="117">
         <v>7.76</v>
       </c>
-      <c r="K11" s="115">
+      <c r="K11" s="110">
         <v>15.37</v>
       </c>
-      <c r="L11" s="110">
+      <c r="L11" s="112">
         <v>8.64</v>
       </c>
-      <c r="M11" s="116">
+      <c r="M11" s="119">
         <v>0.59</v>
       </c>
-      <c r="N11" s="111">
+      <c r="N11" s="113">
         <v>-0.59</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="114">
         <v>-0.15</v>
       </c>
-      <c r="P11" s="112">
+      <c r="P11" s="111">
         <v>-2.93</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="118">
         <v>-4.39</v>
       </c>
-      <c r="R11" s="113">
+      <c r="R11" s="115">
         <v>-2.49</v>
       </c>
-      <c r="S11" s="109">
+      <c r="S11" s="120">
         <v>0.15</v>
       </c>
-      <c r="T11" s="117">
+      <c r="T11" s="116">
         <v>-21.82</v>
       </c>
     </row>
@@ -10245,40 +10245,40 @@
       <c r="H12">
         <v>-0.4</v>
       </c>
-      <c r="I12" s="124">
+      <c r="I12" s="127">
         <v>10.48</v>
       </c>
-      <c r="J12" s="121">
+      <c r="J12" s="123">
         <v>13.87</v>
       </c>
-      <c r="K12" s="125">
+      <c r="K12" s="124">
         <v>4.11</v>
       </c>
-      <c r="L12" s="126">
+      <c r="L12" s="131">
         <v>6.13</v>
       </c>
-      <c r="M12" s="123">
+      <c r="M12" s="125">
         <v>9.68</v>
       </c>
-      <c r="N12" s="122">
+      <c r="N12" s="132">
         <v>2.66</v>
       </c>
-      <c r="O12" s="127">
+      <c r="O12" s="128">
         <v>-1.61</v>
       </c>
-      <c r="P12" s="129">
+      <c r="P12" s="121">
         <v>-4.92</v>
       </c>
-      <c r="Q12" s="130">
+      <c r="Q12" s="126">
         <v>-8.23</v>
       </c>
-      <c r="R12" s="128">
+      <c r="R12" s="129">
         <v>0.97</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="130">
         <v>3.06</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="122">
         <v>-29.27</v>
       </c>
     </row>
@@ -10307,40 +10307,40 @@
       <c r="H13">
         <v>2.05</v>
       </c>
-      <c r="I13" s="133">
+      <c r="I13" s="142">
         <v>-2.49</v>
       </c>
-      <c r="J13" s="140">
+      <c r="J13" s="134">
         <v>-10.3</v>
       </c>
-      <c r="K13" s="134">
+      <c r="K13" s="135">
         <v>-12.58</v>
       </c>
-      <c r="L13" s="141">
+      <c r="L13" s="138">
         <v>-8.03</v>
       </c>
-      <c r="M13" s="136">
+      <c r="M13" s="139">
         <v>-9.98</v>
       </c>
-      <c r="N13" s="138">
+      <c r="N13" s="143">
         <v>-8.95</v>
       </c>
-      <c r="O13" s="142">
+      <c r="O13" s="136">
         <v>-9.38</v>
       </c>
-      <c r="P13" s="135">
+      <c r="P13" s="144">
         <v>-11.98</v>
       </c>
-      <c r="Q13" s="139">
+      <c r="Q13" s="137">
         <v>-4.93</v>
       </c>
-      <c r="R13" s="143">
+      <c r="R13" s="133">
         <v>-3.09</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="141">
         <v>-4.99</v>
       </c>
-      <c r="T13" s="137">
+      <c r="T13" s="140">
         <v>-14.21</v>
       </c>
     </row>
@@ -10369,31 +10369,31 @@
       <c r="H14">
         <v>-3.03</v>
       </c>
-      <c r="I14" s="155">
+      <c r="I14" s="150">
         <v>-3.37</v>
       </c>
-      <c r="J14" s="153">
+      <c r="J14" s="151">
         <v>-5</v>
       </c>
-      <c r="K14" s="149">
+      <c r="K14" s="154">
         <v>-4.87</v>
       </c>
-      <c r="L14" s="147">
+      <c r="L14" s="155">
         <v>-7.13</v>
       </c>
       <c r="M14" s="156">
         <v>-7.37</v>
       </c>
-      <c r="N14" s="150">
+      <c r="N14" s="152">
         <v>-9.88</v>
       </c>
-      <c r="O14" s="154">
+      <c r="O14" s="153">
         <v>-9.38</v>
       </c>
-      <c r="P14" s="151">
+      <c r="P14" s="148">
         <v>-5.63</v>
       </c>
-      <c r="Q14" s="148">
+      <c r="Q14" s="149">
         <v>-1.62</v>
       </c>
       <c r="R14" s="145">
@@ -10402,7 +10402,7 @@
       <c r="S14" s="146">
         <v>0</v>
       </c>
-      <c r="T14" s="152">
+      <c r="T14" s="147">
         <v>-12</v>
       </c>
     </row>
@@ -10431,40 +10431,40 @@
       <c r="H15">
         <v>0.09</v>
       </c>
-      <c r="I15" s="159">
+      <c r="I15" s="168">
         <v>9.9</v>
       </c>
       <c r="J15" s="160">
         <v>9.43</v>
       </c>
-      <c r="K15" s="167">
+      <c r="K15" s="161">
         <v>8.82</v>
       </c>
-      <c r="L15" s="161">
+      <c r="L15" s="164">
         <v>4.15</v>
       </c>
-      <c r="M15" s="168">
+      <c r="M15" s="166">
         <v>7.79</v>
       </c>
-      <c r="N15" s="163">
+      <c r="N15" s="157">
         <v>1.3</v>
       </c>
-      <c r="O15" s="164">
+      <c r="O15" s="158">
         <v>8.69</v>
       </c>
-      <c r="P15" s="157">
+      <c r="P15" s="167">
         <v>6.79</v>
       </c>
-      <c r="Q15" s="165">
+      <c r="Q15" s="159">
         <v>5.84</v>
       </c>
-      <c r="R15" s="158">
+      <c r="R15" s="162">
         <v>6.88</v>
       </c>
-      <c r="S15" s="162">
+      <c r="S15" s="165">
         <v>2.34</v>
       </c>
-      <c r="T15" s="166">
+      <c r="T15" s="163">
         <v>-14.75</v>
       </c>
     </row>
@@ -10493,40 +10493,40 @@
       <c r="H16">
         <v>0</v>
       </c>
-      <c r="I16" s="171">
+      <c r="I16" s="177">
         <v>2.67</v>
       </c>
-      <c r="J16" s="176">
+      <c r="J16" s="169">
         <v>-1.27</v>
       </c>
-      <c r="K16" s="180">
+      <c r="K16" s="178">
         <v>-2.48</v>
       </c>
       <c r="L16" s="172">
         <v>-6.67</v>
       </c>
-      <c r="M16" s="169">
+      <c r="M16" s="179">
         <v>-3.15</v>
       </c>
-      <c r="N16" s="170">
+      <c r="N16" s="173">
         <v>-5.82</v>
       </c>
-      <c r="O16" s="177">
+      <c r="O16" s="174">
         <v>-4.85</v>
       </c>
-      <c r="P16" s="178">
+      <c r="P16" s="175">
         <v>-7.82</v>
       </c>
-      <c r="Q16" s="173">
+      <c r="Q16" s="170">
         <v>-6.61</v>
       </c>
-      <c r="R16" s="174">
+      <c r="R16" s="176">
         <v>-10.42</v>
       </c>
-      <c r="S16" s="175">
+      <c r="S16" s="180">
         <v>-14.06</v>
       </c>
-      <c r="T16" s="179">
+      <c r="T16" s="171">
         <v>-27.7</v>
       </c>
     </row>
@@ -10555,40 +10555,40 @@
       <c r="H17">
         <v>0.12</v>
       </c>
-      <c r="I17" s="192">
+      <c r="I17" s="181">
         <v>-1.51</v>
       </c>
-      <c r="J17" s="188">
+      <c r="J17" s="191">
         <v>-2.31</v>
       </c>
-      <c r="K17" s="189">
+      <c r="K17" s="187">
         <v>0.2</v>
       </c>
-      <c r="L17" s="184">
+      <c r="L17" s="188">
         <v>-0.8</v>
       </c>
-      <c r="M17" s="190">
+      <c r="M17" s="183">
         <v>0.53</v>
       </c>
-      <c r="N17" s="181">
+      <c r="N17" s="184">
         <v>3.31</v>
       </c>
       <c r="O17" s="185">
         <v>6.89</v>
       </c>
-      <c r="P17" s="182">
+      <c r="P17" s="189">
         <v>6.36</v>
       </c>
-      <c r="Q17" s="183">
+      <c r="Q17" s="186">
         <v>4.09</v>
       </c>
-      <c r="R17" s="186">
+      <c r="R17" s="182">
         <v>-1.76</v>
       </c>
-      <c r="S17" s="191">
+      <c r="S17" s="190">
         <v>-1.45</v>
       </c>
-      <c r="T17" s="187">
+      <c r="T17" s="192">
         <v>4.7</v>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       <c r="H18">
         <v>-0.13</v>
       </c>
-      <c r="I18" s="201">
+      <c r="I18" s="196">
         <v>-3.66</v>
       </c>
       <c r="J18" s="198">
@@ -10626,31 +10626,31 @@
       <c r="K18" s="199">
         <v>-6.14</v>
       </c>
-      <c r="L18" s="196">
+      <c r="L18" s="200">
         <v>-11.63</v>
       </c>
-      <c r="M18" s="197">
+      <c r="M18" s="202">
         <v>-11.63</v>
       </c>
-      <c r="N18" s="202">
+      <c r="N18" s="203">
         <v>-13.2</v>
       </c>
-      <c r="O18" s="203">
+      <c r="O18" s="204">
         <v>-12.16</v>
       </c>
-      <c r="P18" s="204">
+      <c r="P18" s="197">
         <v>-16.73</v>
       </c>
-      <c r="Q18" s="195">
+      <c r="Q18" s="201">
         <v>-20.52</v>
       </c>
       <c r="R18" s="193">
         <v>-20.78</v>
       </c>
-      <c r="S18" s="200">
+      <c r="S18" s="194">
         <v>-18.56</v>
       </c>
-      <c r="T18" s="194">
+      <c r="T18" s="195">
         <v>-26.93</v>
       </c>
     </row>
@@ -10679,40 +10679,40 @@
       <c r="H19">
         <v>0.39</v>
       </c>
-      <c r="I19" s="210">
+      <c r="I19" s="214">
         <v>1.39</v>
       </c>
-      <c r="J19" s="215">
+      <c r="J19" s="216">
         <v>0.39</v>
       </c>
-      <c r="K19" s="206">
+      <c r="K19" s="215">
         <v>1.93</v>
       </c>
-      <c r="L19" s="216">
+      <c r="L19" s="209">
         <v>3.7</v>
       </c>
-      <c r="M19" s="207">
+      <c r="M19" s="210">
         <v>9.45</v>
       </c>
-      <c r="N19" s="211">
+      <c r="N19" s="205">
         <v>5.75</v>
       </c>
-      <c r="O19" s="212">
+      <c r="O19" s="207">
         <v>12.85</v>
       </c>
-      <c r="P19" s="213">
+      <c r="P19" s="208">
         <v>8.68</v>
       </c>
-      <c r="Q19" s="214">
+      <c r="Q19" s="206">
         <v>14.74</v>
       </c>
-      <c r="R19" s="208">
+      <c r="R19" s="211">
         <v>14.89</v>
       </c>
-      <c r="S19" s="205">
+      <c r="S19" s="212">
         <v>9.1</v>
       </c>
-      <c r="T19" s="209">
+      <c r="T19" s="213">
         <v>16.4</v>
       </c>
     </row>
@@ -10744,37 +10744,37 @@
       <c r="I20" s="220">
         <v>1.85</v>
       </c>
-      <c r="J20" s="228">
+      <c r="J20" s="218">
         <v>8.14</v>
       </c>
       <c r="K20" s="221">
         <v>2.43</v>
       </c>
-      <c r="L20" s="217">
+      <c r="L20" s="222">
         <v>1.09</v>
       </c>
-      <c r="M20" s="218">
+      <c r="M20" s="224">
         <v>-2.43</v>
       </c>
-      <c r="N20" s="227">
+      <c r="N20" s="225">
         <v>-0.76</v>
       </c>
-      <c r="O20" s="223">
+      <c r="O20" s="219">
         <v>-3.78</v>
       </c>
-      <c r="P20" s="224">
+      <c r="P20" s="223">
         <v>-6.8</v>
       </c>
-      <c r="Q20" s="219">
+      <c r="Q20" s="228">
         <v>-7.39</v>
       </c>
-      <c r="R20" s="225">
+      <c r="R20" s="226">
         <v>-6.38</v>
       </c>
-      <c r="S20" s="222">
+      <c r="S20" s="217">
         <v>-10.58</v>
       </c>
-      <c r="T20" s="226">
+      <c r="T20" s="227">
         <v>-9.57</v>
       </c>
     </row>
@@ -10803,40 +10803,40 @@
       <c r="H21">
         <v>1.22</v>
       </c>
-      <c r="I21" s="232">
+      <c r="I21" s="238">
         <v>8.65</v>
       </c>
-      <c r="J21" s="229">
+      <c r="J21" s="239">
         <v>9.13</v>
       </c>
-      <c r="K21" s="237">
+      <c r="K21" s="230">
         <v>12.02</v>
       </c>
-      <c r="L21" s="238">
+      <c r="L21" s="235">
         <v>9.13</v>
       </c>
-      <c r="M21" s="233">
+      <c r="M21" s="232">
         <v>12.86</v>
       </c>
-      <c r="N21" s="239">
+      <c r="N21" s="240">
         <v>8.29</v>
       </c>
-      <c r="O21" s="240">
+      <c r="O21" s="229">
         <v>0.36</v>
       </c>
-      <c r="P21" s="234">
+      <c r="P21" s="231">
         <v>-1.32</v>
       </c>
-      <c r="Q21" s="230">
+      <c r="Q21" s="236">
         <v>-4.81</v>
       </c>
-      <c r="R21" s="235">
+      <c r="R21" s="233">
         <v>-0.36</v>
       </c>
-      <c r="S21" s="231">
+      <c r="S21" s="234">
         <v>2.04</v>
       </c>
-      <c r="T21" s="236">
+      <c r="T21" s="237">
         <v>-5.29</v>
       </c>
     </row>
@@ -10865,40 +10865,40 @@
       <c r="H22">
         <v>0.4</v>
       </c>
-      <c r="I22" s="249">
+      <c r="I22" s="246">
         <v>9.66</v>
       </c>
-      <c r="J22" s="241">
+      <c r="J22" s="247">
         <v>14</v>
       </c>
-      <c r="K22" s="242">
+      <c r="K22" s="243">
         <v>19.72</v>
       </c>
-      <c r="L22" s="247">
+      <c r="L22" s="244">
         <v>17.55</v>
       </c>
-      <c r="M22" s="243">
+      <c r="M22" s="250">
         <v>15.78</v>
       </c>
-      <c r="N22" s="250">
+      <c r="N22" s="248">
         <v>6.9</v>
       </c>
-      <c r="O22" s="244">
+      <c r="O22" s="251">
         <v>0.99</v>
       </c>
-      <c r="P22" s="248">
+      <c r="P22" s="252">
         <v>11.05</v>
       </c>
-      <c r="Q22" s="246">
+      <c r="Q22" s="249">
         <v>8.88</v>
       </c>
-      <c r="R22" s="245">
+      <c r="R22" s="241">
         <v>4.73</v>
       </c>
-      <c r="S22" s="251">
+      <c r="S22" s="242">
         <v>5.92</v>
       </c>
-      <c r="T22" s="252">
+      <c r="T22" s="245">
         <v>-13.81</v>
       </c>
     </row>
@@ -10927,40 +10927,40 @@
       <c r="H23">
         <v>-3.87</v>
       </c>
-      <c r="I23" s="258">
+      <c r="I23" s="260">
         <v>5.78</v>
       </c>
-      <c r="J23" s="263">
+      <c r="J23" s="255">
         <v>3.91</v>
       </c>
-      <c r="K23" s="259">
+      <c r="K23" s="258">
         <v>6.83</v>
       </c>
-      <c r="L23" s="255">
+      <c r="L23" s="261">
         <v>4.79</v>
       </c>
-      <c r="M23" s="260">
+      <c r="M23" s="253">
         <v>5.08</v>
       </c>
-      <c r="N23" s="256">
+      <c r="N23" s="254">
         <v>4.5</v>
       </c>
-      <c r="O23" s="264">
+      <c r="O23" s="256">
         <v>1.4</v>
       </c>
       <c r="P23" s="262">
         <v>-0.29</v>
       </c>
-      <c r="Q23" s="253">
+      <c r="Q23" s="263">
         <v>-3.97</v>
       </c>
-      <c r="R23" s="261">
+      <c r="R23" s="264">
         <v>-4.9</v>
       </c>
-      <c r="S23" s="254">
+      <c r="S23" s="257">
         <v>-3.33</v>
       </c>
-      <c r="T23" s="257">
+      <c r="T23" s="259">
         <v>7.18</v>
       </c>
     </row>
@@ -10989,10 +10989,10 @@
       <c r="H24">
         <v>-1.89</v>
       </c>
-      <c r="I24" s="274">
+      <c r="I24" s="269">
         <v>-0.93</v>
       </c>
-      <c r="J24" s="269">
+      <c r="J24" s="272">
         <v>-2.54</v>
       </c>
       <c r="K24" s="276">
@@ -11001,28 +11001,28 @@
       <c r="L24" s="270">
         <v>-12.46</v>
       </c>
-      <c r="M24" s="265">
+      <c r="M24" s="267">
         <v>-11.46</v>
       </c>
-      <c r="N24" s="266">
+      <c r="N24" s="265">
         <v>-11.81</v>
       </c>
-      <c r="O24" s="267">
+      <c r="O24" s="271">
         <v>-7.66</v>
       </c>
-      <c r="P24" s="268">
+      <c r="P24" s="273">
         <v>-9.54</v>
       </c>
-      <c r="Q24" s="275">
+      <c r="Q24" s="274">
         <v>-15.61</v>
       </c>
-      <c r="R24" s="271">
+      <c r="R24" s="268">
         <v>-18.67</v>
       </c>
-      <c r="S24" s="272">
+      <c r="S24" s="266">
         <v>-17.03</v>
       </c>
-      <c r="T24" s="273">
+      <c r="T24" s="275">
         <v>-9.13</v>
       </c>
     </row>
@@ -11054,37 +11054,37 @@
       <c r="I25" s="288">
         <v>-2.24</v>
       </c>
-      <c r="J25" s="283">
+      <c r="J25" s="282">
         <v>-4.3</v>
       </c>
-      <c r="K25" s="279">
+      <c r="K25" s="278">
         <v>-7.68</v>
       </c>
-      <c r="L25" s="284">
+      <c r="L25" s="286">
         <v>-8.54</v>
       </c>
-      <c r="M25" s="280">
+      <c r="M25" s="279">
         <v>-10.25</v>
       </c>
-      <c r="N25" s="285">
+      <c r="N25" s="277">
         <v>-8.15</v>
       </c>
-      <c r="O25" s="277">
+      <c r="O25" s="283">
         <v>-11.42</v>
       </c>
-      <c r="P25" s="287">
+      <c r="P25" s="280">
         <v>-14.55</v>
       </c>
-      <c r="Q25" s="281">
+      <c r="Q25" s="287">
         <v>-17.04</v>
       </c>
-      <c r="R25" s="282">
+      <c r="R25" s="284">
         <v>-15.58</v>
       </c>
-      <c r="S25" s="278">
+      <c r="S25" s="285">
         <v>-12.95</v>
       </c>
-      <c r="T25" s="286">
+      <c r="T25" s="281">
         <v>-15.69</v>
       </c>
     </row>
@@ -11113,40 +11113,40 @@
       <c r="H26">
         <v>-1.56</v>
       </c>
-      <c r="I26" s="293">
+      <c r="I26" s="290">
         <v>-2.6</v>
       </c>
-      <c r="J26" s="297">
+      <c r="J26" s="298">
         <v>0.56</v>
       </c>
       <c r="K26" s="291">
         <v>-2.94</v>
       </c>
-      <c r="L26" s="299">
+      <c r="L26" s="293">
         <v>-7.91</v>
       </c>
-      <c r="M26" s="294">
+      <c r="M26" s="299">
         <v>1.36</v>
       </c>
-      <c r="N26" s="292">
+      <c r="N26" s="300">
         <v>3.39</v>
       </c>
-      <c r="O26" s="295">
+      <c r="O26" s="297">
         <v>-2.26</v>
       </c>
-      <c r="P26" s="300">
+      <c r="P26" s="294">
         <v>2.37</v>
       </c>
-      <c r="Q26" s="296">
+      <c r="Q26" s="295">
         <v>7.01</v>
       </c>
       <c r="R26" s="289">
         <v>12.66</v>
       </c>
-      <c r="S26" s="298">
+      <c r="S26" s="296">
         <v>6.55</v>
       </c>
-      <c r="T26" s="290">
+      <c r="T26" s="292">
         <v>-12.09</v>
       </c>
     </row>
@@ -11175,40 +11175,40 @@
       <c r="H27">
         <v>-0.99</v>
       </c>
-      <c r="I27" s="312">
+      <c r="I27" s="303">
         <v>-1.23</v>
       </c>
-      <c r="J27" s="301">
+      <c r="J27" s="308">
         <v>-4.31</v>
       </c>
-      <c r="K27" s="305">
+      <c r="K27" s="309">
         <v>-6.09</v>
       </c>
-      <c r="L27" s="306">
+      <c r="L27" s="304">
         <v>-10.4</v>
       </c>
-      <c r="M27" s="308">
+      <c r="M27" s="310">
         <v>-13.17</v>
       </c>
-      <c r="N27" s="302">
+      <c r="N27" s="306">
         <v>-12.71</v>
       </c>
-      <c r="O27" s="303">
+      <c r="O27" s="311">
         <v>-11.48</v>
       </c>
-      <c r="P27" s="307">
+      <c r="P27" s="301">
         <v>-14.1</v>
       </c>
-      <c r="Q27" s="309">
+      <c r="Q27" s="312">
         <v>-9.78</v>
       </c>
-      <c r="R27" s="304">
+      <c r="R27" s="307">
         <v>-7.24</v>
       </c>
-      <c r="S27" s="310">
+      <c r="S27" s="302">
         <v>-12.33</v>
       </c>
-      <c r="T27" s="311">
+      <c r="T27" s="305">
         <v>-12.02</v>
       </c>
     </row>
@@ -11237,40 +11237,40 @@
       <c r="H28">
         <v>-2.89</v>
       </c>
-      <c r="I28" s="321">
+      <c r="I28" s="323">
         <v>1.28</v>
       </c>
-      <c r="J28" s="316">
+      <c r="J28" s="322">
         <v>2.92</v>
       </c>
-      <c r="K28" s="317">
+      <c r="K28" s="324">
         <v>4.72</v>
       </c>
-      <c r="L28" s="324">
+      <c r="L28" s="315">
         <v>6.25</v>
       </c>
-      <c r="M28" s="322">
+      <c r="M28" s="318">
         <v>16.86</v>
       </c>
       <c r="N28" s="313">
         <v>13.12</v>
       </c>
-      <c r="O28" s="318">
+      <c r="O28" s="319">
         <v>24.45</v>
       </c>
-      <c r="P28" s="319">
+      <c r="P28" s="320">
         <v>36.9</v>
       </c>
-      <c r="Q28" s="323">
+      <c r="Q28" s="316">
         <v>46.03</v>
       </c>
-      <c r="R28" s="314">
+      <c r="R28" s="321">
         <v>45.46</v>
       </c>
-      <c r="S28" s="320">
+      <c r="S28" s="314">
         <v>42.9</v>
       </c>
-      <c r="T28" s="315">
+      <c r="T28" s="317">
         <v>55.61</v>
       </c>
     </row>
@@ -11299,40 +11299,40 @@
       <c r="H29">
         <v>0.22</v>
       </c>
-      <c r="I29" s="326">
+      <c r="I29" s="334">
         <v>3.14</v>
       </c>
-      <c r="J29" s="331">
+      <c r="J29" s="330">
         <v>-1.16</v>
       </c>
       <c r="K29" s="335">
         <v>-1.1</v>
       </c>
-      <c r="L29" s="332">
+      <c r="L29" s="331">
         <v>-0.61</v>
       </c>
       <c r="M29" s="336">
         <v>6.71</v>
       </c>
-      <c r="N29" s="327">
+      <c r="N29" s="332">
         <v>3.47</v>
       </c>
-      <c r="O29" s="328">
+      <c r="O29" s="325">
         <v>-0.94</v>
       </c>
       <c r="P29" s="333">
         <v>1.65</v>
       </c>
-      <c r="Q29" s="329">
+      <c r="Q29" s="326">
         <v>-0.28</v>
       </c>
-      <c r="R29" s="325">
+      <c r="R29" s="327">
         <v>0.11</v>
       </c>
-      <c r="S29" s="334">
+      <c r="S29" s="328">
         <v>2.42</v>
       </c>
-      <c r="T29" s="330">
+      <c r="T29" s="329">
         <v>11.61</v>
       </c>
     </row>
@@ -11361,40 +11361,40 @@
       <c r="H30">
         <v>-3.98</v>
       </c>
-      <c r="I30" s="347">
+      <c r="I30" s="338">
         <v>1.85</v>
       </c>
-      <c r="J30" s="348">
+      <c r="J30" s="343">
         <v>7.78</v>
       </c>
-      <c r="K30" s="339">
+      <c r="K30" s="344">
         <v>13.84</v>
       </c>
-      <c r="L30" s="341">
+      <c r="L30" s="339">
         <v>11.93</v>
       </c>
-      <c r="M30" s="337">
+      <c r="M30" s="345">
         <v>5.23</v>
       </c>
-      <c r="N30" s="342">
+      <c r="N30" s="347">
         <v>-5.17</v>
       </c>
-      <c r="O30" s="343">
+      <c r="O30" s="348">
         <v>-8.48</v>
       </c>
-      <c r="P30" s="344">
+      <c r="P30" s="340">
         <v>-8.61</v>
       </c>
-      <c r="Q30" s="345">
+      <c r="Q30" s="346">
         <v>-15.82</v>
       </c>
-      <c r="R30" s="346">
+      <c r="R30" s="341">
         <v>-7.4</v>
       </c>
-      <c r="S30" s="338">
+      <c r="S30" s="337">
         <v>-5.36</v>
       </c>
-      <c r="T30" s="340">
+      <c r="T30" s="342">
         <v>-16.45</v>
       </c>
     </row>
@@ -11423,34 +11423,34 @@
       <c r="H31">
         <v>-1</v>
       </c>
-      <c r="I31" s="360">
+      <c r="I31" s="349">
         <v>1.82</v>
       </c>
-      <c r="J31" s="351">
+      <c r="J31" s="356">
         <v>6.88</v>
       </c>
-      <c r="K31" s="349">
+      <c r="K31" s="357">
         <v>4.25</v>
       </c>
-      <c r="L31" s="356">
+      <c r="L31" s="358">
         <v>1.42</v>
       </c>
-      <c r="M31" s="357">
+      <c r="M31" s="352">
         <v>-7.09</v>
       </c>
       <c r="N31" s="350">
         <v>-13.56</v>
       </c>
-      <c r="O31" s="358">
+      <c r="O31" s="353">
         <v>-10.32</v>
       </c>
-      <c r="P31" s="352">
+      <c r="P31" s="359">
         <v>-19.23</v>
       </c>
-      <c r="Q31" s="359">
+      <c r="Q31" s="351">
         <v>-17</v>
       </c>
-      <c r="R31" s="353">
+      <c r="R31" s="360">
         <v>-16.8</v>
       </c>
       <c r="S31" s="354">
@@ -11488,34 +11488,34 @@
       <c r="I32" s="361">
         <v>-1.18</v>
       </c>
-      <c r="J32" s="365">
+      <c r="J32" s="362">
         <v>0.27</v>
       </c>
-      <c r="K32" s="362">
+      <c r="K32" s="368">
         <v>2.99</v>
       </c>
-      <c r="L32" s="366">
+      <c r="L32" s="364">
         <v>2.35</v>
       </c>
-      <c r="M32" s="363">
+      <c r="M32" s="371">
         <v>0.72</v>
       </c>
-      <c r="N32" s="367">
+      <c r="N32" s="369">
         <v>1</v>
       </c>
-      <c r="O32" s="368">
+      <c r="O32" s="365">
         <v>-2.35</v>
       </c>
-      <c r="P32" s="371">
+      <c r="P32" s="366">
         <v>-0.09</v>
       </c>
-      <c r="Q32" s="364">
+      <c r="Q32" s="367">
         <v>3.26</v>
       </c>
-      <c r="R32" s="369">
+      <c r="R32" s="370">
         <v>1</v>
       </c>
-      <c r="S32" s="370">
+      <c r="S32" s="363">
         <v>1.45</v>
       </c>
       <c r="T32" s="372">
@@ -11547,40 +11547,40 @@
       <c r="H33">
         <v>-0.94</v>
       </c>
-      <c r="I33" s="382">
+      <c r="I33" s="384">
         <v>-2.27</v>
       </c>
-      <c r="J33" s="383">
+      <c r="J33" s="378">
         <v>0.57</v>
       </c>
-      <c r="K33" s="374">
+      <c r="K33" s="379">
         <v>-8.88</v>
       </c>
-      <c r="L33" s="384">
+      <c r="L33" s="373">
         <v>-13.42</v>
       </c>
-      <c r="M33" s="373">
+      <c r="M33" s="381">
         <v>-13.04</v>
       </c>
-      <c r="N33" s="375">
+      <c r="N33" s="374">
         <v>-20.6</v>
       </c>
       <c r="O33" s="376">
         <v>-19.47</v>
       </c>
-      <c r="P33" s="378">
+      <c r="P33" s="380">
         <v>-18.9</v>
       </c>
-      <c r="Q33" s="379">
+      <c r="Q33" s="382">
         <v>-20.23</v>
       </c>
-      <c r="R33" s="380">
+      <c r="R33" s="377">
         <v>-20.6</v>
       </c>
-      <c r="S33" s="377">
+      <c r="S33" s="375">
         <v>-18.71</v>
       </c>
-      <c r="T33" s="381">
+      <c r="T33" s="383">
         <v>-21.55</v>
       </c>
     </row>
@@ -11609,37 +11609,37 @@
       <c r="H34">
         <v>-2.25</v>
       </c>
-      <c r="I34" s="386">
+      <c r="I34" s="388">
         <v>-3</v>
       </c>
-      <c r="J34" s="393">
+      <c r="J34" s="389">
         <v>-7.14</v>
       </c>
-      <c r="K34" s="394">
+      <c r="K34" s="390">
         <v>-11.52</v>
       </c>
-      <c r="L34" s="390">
+      <c r="L34" s="395">
         <v>-19.35</v>
       </c>
-      <c r="M34" s="387">
+      <c r="M34" s="396">
         <v>-16.82</v>
       </c>
-      <c r="N34" s="385">
+      <c r="N34" s="391">
         <v>-18.2</v>
       </c>
-      <c r="O34" s="395">
+      <c r="O34" s="385">
         <v>-16.59</v>
       </c>
-      <c r="P34" s="388">
+      <c r="P34" s="393">
         <v>-19.82</v>
       </c>
-      <c r="Q34" s="389">
+      <c r="Q34" s="386">
         <v>-22.12</v>
       </c>
-      <c r="R34" s="396">
+      <c r="R34" s="387">
         <v>-20.05</v>
       </c>
-      <c r="S34" s="391">
+      <c r="S34" s="394">
         <v>-21.43</v>
       </c>
       <c r="T34" s="392">
@@ -11671,40 +11671,40 @@
       <c r="H35">
         <v>0.9</v>
       </c>
-      <c r="I35" s="406">
+      <c r="I35" s="408">
         <v>4.2</v>
       </c>
-      <c r="J35" s="401">
+      <c r="J35" s="397">
         <v>3.72</v>
       </c>
-      <c r="K35" s="407">
+      <c r="K35" s="404">
         <v>-0.66</v>
       </c>
-      <c r="L35" s="398">
+      <c r="L35" s="406">
         <v>-2.43</v>
       </c>
-      <c r="M35" s="402">
+      <c r="M35" s="398">
         <v>-3.1</v>
       </c>
-      <c r="N35" s="408">
+      <c r="N35" s="399">
         <v>6.61</v>
       </c>
-      <c r="O35" s="403">
+      <c r="O35" s="400">
         <v>5.5</v>
       </c>
-      <c r="P35" s="399">
+      <c r="P35" s="401">
         <v>2.74</v>
       </c>
-      <c r="Q35" s="404">
+      <c r="Q35" s="405">
         <v>1.68</v>
       </c>
-      <c r="R35" s="397">
+      <c r="R35" s="407">
         <v>1.37</v>
       </c>
-      <c r="S35" s="400">
+      <c r="S35" s="402">
         <v>0.08</v>
       </c>
-      <c r="T35" s="405">
+      <c r="T35" s="403">
         <v>-0.48</v>
       </c>
     </row>
@@ -11733,40 +11733,40 @@
       <c r="H36">
         <v>-3.03</v>
       </c>
-      <c r="I36" s="410">
+      <c r="I36" s="412">
         <v>5.57</v>
       </c>
-      <c r="J36" s="411">
+      <c r="J36" s="415">
         <v>16.17</v>
       </c>
-      <c r="K36" s="412">
+      <c r="K36" s="416">
         <v>22.01</v>
       </c>
       <c r="L36" s="417">
         <v>16.85</v>
       </c>
-      <c r="M36" s="418">
+      <c r="M36" s="409">
         <v>7.07</v>
       </c>
-      <c r="N36" s="419">
+      <c r="N36" s="418">
         <v>0.27</v>
       </c>
       <c r="O36" s="413">
         <v>2.45</v>
       </c>
-      <c r="P36" s="420">
+      <c r="P36" s="419">
         <v>-2.31</v>
       </c>
-      <c r="Q36" s="414">
+      <c r="Q36" s="410">
         <v>-0.27</v>
       </c>
-      <c r="R36" s="415">
+      <c r="R36" s="420">
         <v>9.65</v>
       </c>
-      <c r="S36" s="409">
+      <c r="S36" s="414">
         <v>7.47</v>
       </c>
-      <c r="T36" s="416">
+      <c r="T36" s="411">
         <v>-6.66</v>
       </c>
     </row>
@@ -11795,28 +11795,28 @@
       <c r="H37">
         <v>-2.15</v>
       </c>
-      <c r="I37" s="425">
+      <c r="I37" s="431">
         <v>-2.93</v>
       </c>
-      <c r="J37" s="423">
+      <c r="J37" s="422">
         <v>-2.9</v>
       </c>
-      <c r="K37" s="426">
+      <c r="K37" s="425">
         <v>-1.16</v>
       </c>
-      <c r="L37" s="421">
+      <c r="L37" s="423">
         <v>7.57</v>
       </c>
-      <c r="M37" s="424">
+      <c r="M37" s="429">
         <v>5.6</v>
       </c>
-      <c r="N37" s="429">
+      <c r="N37" s="432">
         <v>4.48</v>
       </c>
-      <c r="O37" s="430">
+      <c r="O37" s="426">
         <v>3.32</v>
       </c>
-      <c r="P37" s="422">
+      <c r="P37" s="424">
         <v>5.48</v>
       </c>
       <c r="Q37" s="427">
@@ -11825,10 +11825,10 @@
       <c r="R37" s="428">
         <v>8.07</v>
       </c>
-      <c r="S37" s="431">
+      <c r="S37" s="421">
         <v>11.74</v>
       </c>
-      <c r="T37" s="432">
+      <c r="T37" s="430">
         <v>0.39</v>
       </c>
     </row>
@@ -11857,40 +11857,40 @@
       <c r="H38">
         <v>-1.68</v>
       </c>
-      <c r="I38" s="441">
+      <c r="I38" s="438">
         <v>6.62</v>
       </c>
-      <c r="J38" s="436">
+      <c r="J38" s="444">
         <v>10.07</v>
       </c>
-      <c r="K38" s="434">
+      <c r="K38" s="435">
         <v>6.26</v>
       </c>
-      <c r="L38" s="442">
+      <c r="L38" s="439">
         <v>2.13</v>
       </c>
-      <c r="M38" s="437">
+      <c r="M38" s="436">
         <v>1.41</v>
       </c>
-      <c r="N38" s="438">
+      <c r="N38" s="437">
         <v>7.72</v>
       </c>
-      <c r="O38" s="444">
+      <c r="O38" s="433">
         <v>5.74</v>
       </c>
-      <c r="P38" s="435">
+      <c r="P38" s="442">
         <v>10.77</v>
       </c>
-      <c r="Q38" s="443">
+      <c r="Q38" s="440">
         <v>14.45</v>
       </c>
-      <c r="R38" s="433">
+      <c r="R38" s="443">
         <v>18.62</v>
       </c>
-      <c r="S38" s="439">
+      <c r="S38" s="434">
         <v>14.8</v>
       </c>
-      <c r="T38" s="440">
+      <c r="T38" s="441">
         <v>1.05</v>
       </c>
     </row>
@@ -11919,40 +11919,40 @@
       <c r="H39">
         <v>2.63</v>
       </c>
-      <c r="I39" s="449">
+      <c r="I39" s="448">
         <v>7.14</v>
       </c>
-      <c r="J39" s="446">
+      <c r="J39" s="453">
         <v>7.82</v>
       </c>
-      <c r="K39" s="453">
+      <c r="K39" s="454">
         <v>7.68</v>
       </c>
-      <c r="L39" s="447">
+      <c r="L39" s="455">
         <v>8.49</v>
       </c>
-      <c r="M39" s="454">
+      <c r="M39" s="446">
         <v>9.43</v>
       </c>
-      <c r="N39" s="450">
+      <c r="N39" s="449">
         <v>5.39</v>
       </c>
-      <c r="O39" s="452">
+      <c r="O39" s="456">
         <v>8.49</v>
       </c>
-      <c r="P39" s="455">
+      <c r="P39" s="445">
         <v>7.28</v>
       </c>
-      <c r="Q39" s="448">
+      <c r="Q39" s="451">
         <v>11.99</v>
       </c>
-      <c r="R39" s="451">
+      <c r="R39" s="450">
         <v>7.95</v>
       </c>
-      <c r="S39" s="456">
+      <c r="S39" s="452">
         <v>7.55</v>
       </c>
-      <c r="T39" s="445">
+      <c r="T39" s="447">
         <v>-8.36</v>
       </c>
     </row>
@@ -11981,40 +11981,40 @@
       <c r="H40">
         <v>-1.51</v>
       </c>
-      <c r="I40" s="461">
+      <c r="I40" s="465">
         <v>-0.66</v>
       </c>
-      <c r="J40" s="458">
+      <c r="J40" s="457">
         <v>-0.66</v>
       </c>
       <c r="K40" s="462">
         <v>-0.44</v>
       </c>
-      <c r="L40" s="463">
+      <c r="L40" s="460">
         <v>0</v>
       </c>
-      <c r="M40" s="464">
+      <c r="M40" s="458">
         <v>-1.31</v>
       </c>
-      <c r="N40" s="457">
+      <c r="N40" s="466">
         <v>0.33</v>
       </c>
-      <c r="O40" s="468">
+      <c r="O40" s="461">
         <v>0</v>
       </c>
       <c r="P40" s="459">
         <v>1.97</v>
       </c>
-      <c r="Q40" s="465">
+      <c r="Q40" s="467">
         <v>-0.22</v>
       </c>
-      <c r="R40" s="466">
+      <c r="R40" s="468">
         <v>2.51</v>
       </c>
-      <c r="S40" s="467">
+      <c r="S40" s="463">
         <v>-0.55</v>
       </c>
-      <c r="T40" s="460">
+      <c r="T40" s="464">
         <v>-2.51</v>
       </c>
     </row>
@@ -12043,40 +12043,40 @@
       <c r="H41">
         <v>-1.83</v>
       </c>
-      <c r="I41" s="472">
+      <c r="I41" s="474">
         <v>0.59</v>
       </c>
-      <c r="J41" s="473">
+      <c r="J41" s="475">
         <v>-1.18</v>
       </c>
-      <c r="K41" s="470">
+      <c r="K41" s="478">
         <v>-3.73</v>
       </c>
-      <c r="L41" s="474">
+      <c r="L41" s="469">
         <v>-3.24</v>
       </c>
-      <c r="M41" s="477">
+      <c r="M41" s="470">
         <v>-4.61</v>
       </c>
-      <c r="N41" s="471">
+      <c r="N41" s="476">
         <v>-7.55</v>
       </c>
-      <c r="O41" s="479">
+      <c r="O41" s="471">
         <v>-6.76</v>
       </c>
-      <c r="P41" s="475">
+      <c r="P41" s="479">
         <v>-8.43</v>
       </c>
       <c r="Q41" s="480">
         <v>-9.51</v>
       </c>
-      <c r="R41" s="469">
+      <c r="R41" s="472">
         <v>-7.55</v>
       </c>
-      <c r="S41" s="476">
+      <c r="S41" s="477">
         <v>-9.12</v>
       </c>
-      <c r="T41" s="478">
+      <c r="T41" s="473">
         <v>-8.33</v>
       </c>
     </row>
@@ -12105,40 +12105,40 @@
       <c r="H42">
         <v>-0.31</v>
       </c>
-      <c r="I42" s="485">
+      <c r="I42" s="491">
         <v>2.08</v>
       </c>
-      <c r="J42" s="492">
+      <c r="J42" s="483">
         <v>2.7</v>
       </c>
-      <c r="K42" s="486">
+      <c r="K42" s="492">
         <v>0</v>
       </c>
-      <c r="L42" s="487">
+      <c r="L42" s="486">
         <v>1.25</v>
       </c>
-      <c r="M42" s="482">
+      <c r="M42" s="489">
         <v>1.04</v>
       </c>
-      <c r="N42" s="488">
+      <c r="N42" s="484">
         <v>1.56</v>
       </c>
-      <c r="O42" s="489">
+      <c r="O42" s="487">
         <v>-0.52</v>
       </c>
-      <c r="P42" s="483">
+      <c r="P42" s="490">
         <v>-1.56</v>
       </c>
-      <c r="Q42" s="481">
+      <c r="Q42" s="488">
         <v>-6.75</v>
       </c>
-      <c r="R42" s="490">
+      <c r="R42" s="481">
         <v>-5.61</v>
       </c>
-      <c r="S42" s="484">
+      <c r="S42" s="482">
         <v>-8.93</v>
       </c>
-      <c r="T42" s="491">
+      <c r="T42" s="485">
         <v>-8.93</v>
       </c>
     </row>
@@ -12167,7 +12167,7 @@
       <c r="H43">
         <v>-1.2</v>
       </c>
-      <c r="I43" s="495">
+      <c r="I43" s="502">
         <v>-0.65</v>
       </c>
       <c r="J43" s="496">
@@ -12176,29 +12176,29 @@
       <c r="K43" s="497">
         <v>-1.38</v>
       </c>
-      <c r="L43" s="501">
+      <c r="L43" s="503">
         <v>8.46</v>
       </c>
-      <c r="M43" s="500">
+      <c r="M43" s="498">
         <v>10.98</v>
       </c>
       <c r="N43" s="493">
         <v>10.41</v>
       </c>
-      <c r="O43" s="498">
+      <c r="O43" s="494">
         <v>21.46</v>
       </c>
       <c r="P43" s="499">
         <v>26.1</v>
       </c>
-      <c r="Q43" s="494">
+      <c r="Q43" s="500">
         <v>22.85</v>
       </c>
-      <c r="R43" s="502">
+      <c r="R43" s="501">
         <v>19.76</v>
       </c>
       <c r="S43" t="str"/>
-      <c r="T43" s="503">
+      <c r="T43" s="495">
         <v>19.76</v>
       </c>
     </row>
@@ -12227,36 +12227,36 @@
       <c r="H44">
         <v>-0.64</v>
       </c>
-      <c r="I44" s="504">
+      <c r="I44" s="506">
         <v>10.68</v>
       </c>
-      <c r="J44" s="507">
+      <c r="J44" s="512">
         <v>1.78</v>
       </c>
-      <c r="K44" s="505">
+      <c r="K44" s="509">
         <v>-1.94</v>
       </c>
-      <c r="L44" s="508">
+      <c r="L44" s="507">
         <v>3.72</v>
       </c>
-      <c r="M44" s="509">
+      <c r="M44" s="510">
         <v>2.1</v>
       </c>
       <c r="N44" s="513">
         <v>6.15</v>
       </c>
-      <c r="O44" s="506">
+      <c r="O44" s="511">
         <v>9.06</v>
       </c>
-      <c r="P44" s="510">
+      <c r="P44" s="504">
         <v>-0.97</v>
       </c>
-      <c r="Q44" s="511">
+      <c r="Q44" s="505">
         <v>-9.06</v>
       </c>
       <c r="R44" t="str"/>
       <c r="S44" t="str"/>
-      <c r="T44" s="512">
+      <c r="T44" s="508">
         <v>-9.06</v>
       </c>
     </row>
@@ -12285,34 +12285,34 @@
       <c r="H45">
         <v>-1.13</v>
       </c>
-      <c r="I45" s="514">
+      <c r="I45" s="518">
         <v>2.03</v>
       </c>
-      <c r="J45" s="515">
+      <c r="J45" s="522">
         <v>5.03</v>
       </c>
-      <c r="K45" s="517">
+      <c r="K45" s="514">
         <v>5.82</v>
       </c>
-      <c r="L45" s="518">
+      <c r="L45" s="519">
         <v>3.17</v>
       </c>
-      <c r="M45" s="522">
+      <c r="M45" s="515">
         <v>-0.26</v>
       </c>
       <c r="N45" s="516">
         <v>-2.65</v>
       </c>
-      <c r="O45" s="521">
+      <c r="O45" s="517">
         <v>-7.58</v>
       </c>
-      <c r="P45" s="519">
+      <c r="P45" s="520">
         <v>1.68</v>
       </c>
       <c r="Q45" t="str"/>
       <c r="R45" t="str"/>
       <c r="S45" t="str"/>
-      <c r="T45" s="520">
+      <c r="T45" s="521">
         <v>1.68</v>
       </c>
     </row>
@@ -12393,19 +12393,19 @@
       <c r="H47">
         <v>0.36</v>
       </c>
-      <c r="I47" s="530">
+      <c r="I47" s="533">
         <v>-1.87</v>
       </c>
-      <c r="J47" s="531">
+      <c r="J47" s="534">
         <v>-0.72</v>
       </c>
-      <c r="K47" s="532">
+      <c r="K47" s="535">
         <v>2.87</v>
       </c>
-      <c r="L47" s="533">
+      <c r="L47" s="530">
         <v>-1.03</v>
       </c>
-      <c r="M47" s="534">
+      <c r="M47" s="531">
         <v>-3.37</v>
       </c>
       <c r="N47" t="str"/>
@@ -12414,7 +12414,7 @@
       <c r="Q47" t="str"/>
       <c r="R47" t="str"/>
       <c r="S47" t="str"/>
-      <c r="T47" s="535">
+      <c r="T47" s="532">
         <v>-3.37</v>
       </c>
     </row>
@@ -12443,16 +12443,16 @@
       <c r="H48">
         <v>-1.29</v>
       </c>
-      <c r="I48" s="540">
+      <c r="I48" s="537">
         <v>3.67</v>
       </c>
-      <c r="J48" s="536">
+      <c r="J48" s="538">
         <v>6.46</v>
       </c>
-      <c r="K48" s="537">
+      <c r="K48" s="539">
         <v>-0.77</v>
       </c>
-      <c r="L48" s="538">
+      <c r="L48" s="540">
         <v>-2.9</v>
       </c>
       <c r="M48" t="str"/>
@@ -12462,7 +12462,7 @@
       <c r="Q48" t="str"/>
       <c r="R48" t="str"/>
       <c r="S48" t="str"/>
-      <c r="T48" s="539">
+      <c r="T48" s="536">
         <v>-2.9</v>
       </c>
     </row>
@@ -12701,37 +12701,37 @@
       <c r="F54" t="str"/>
       <c r="G54" t="str"/>
       <c r="H54" t="str"/>
-      <c r="I54" s="563">
+      <c r="I54" s="554">
         <v>56.86</v>
       </c>
-      <c r="J54" s="564">
+      <c r="J54" s="560">
         <v>58</v>
       </c>
-      <c r="K54" s="559">
+      <c r="K54" s="561">
         <v>51.02</v>
       </c>
-      <c r="L54" s="553">
+      <c r="L54" s="555">
         <v>57.45</v>
       </c>
-      <c r="M54" s="560">
+      <c r="M54" s="556">
         <v>52.17</v>
       </c>
-      <c r="N54" s="561">
+      <c r="N54" s="559">
         <v>55.56</v>
       </c>
-      <c r="O54" s="555">
+      <c r="O54" s="563">
         <v>40.91</v>
       </c>
-      <c r="P54" s="562">
+      <c r="P54" s="564">
         <v>43.18</v>
       </c>
-      <c r="Q54" s="556">
+      <c r="Q54" s="557">
         <v>39.53</v>
       </c>
-      <c r="R54" s="554">
+      <c r="R54" s="562">
         <v>47.62</v>
       </c>
-      <c r="S54" s="557">
+      <c r="S54" s="553">
         <v>46.34</v>
       </c>
       <c r="T54" s="558">
@@ -12749,40 +12749,40 @@
       <c r="F55" t="str"/>
       <c r="G55" t="str"/>
       <c r="H55" t="str"/>
-      <c r="I55" s="573">
+      <c r="I55" s="567">
         <v>1.83</v>
       </c>
-      <c r="J55" s="566">
+      <c r="J55" s="571">
         <v>2.08</v>
       </c>
-      <c r="K55" s="567">
+      <c r="K55" s="576">
         <v>1.59</v>
       </c>
-      <c r="L55" s="569">
+      <c r="L55" s="568">
         <v>1.1</v>
       </c>
-      <c r="M55" s="576">
+      <c r="M55" s="574">
         <v>1.23</v>
       </c>
-      <c r="N55" s="570">
+      <c r="N55" s="565">
         <v>0.2</v>
       </c>
-      <c r="O55" s="571">
+      <c r="O55" s="566">
         <v>0.14</v>
       </c>
-      <c r="P55" s="574">
+      <c r="P55" s="572">
         <v>0.2</v>
       </c>
-      <c r="Q55" s="565">
+      <c r="Q55" s="569">
         <v>-0.5</v>
       </c>
       <c r="R55" s="575">
         <v>0.88</v>
       </c>
-      <c r="S55" s="572">
+      <c r="S55" s="573">
         <v>0.39</v>
       </c>
-      <c r="T55" s="568">
+      <c r="T55" s="570">
         <v>-4.03</v>
       </c>
     </row>

--- a/youzi/鸭王/index.xlsx
+++ b/youzi/鸭王/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="578">
+  <fills count="590">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,12 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEFF8F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD7EEDC"/>
         <bgColor/>
       </patternFill>
@@ -57,13 +99,1255 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E9D0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1F9F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF29A746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C0C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F9F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8DBDE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46470"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF5F6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8892"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF65C07A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FCF9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF8F9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7AC88C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF93D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2BA847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB9E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5CACE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC8E8CF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77983"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBEE4C6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF6F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF45B35E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,13 +1359,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
+        <fgColor rgb="FFF7D2D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15462"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,55 +1443,1069 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB22230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD7EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9ED7AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77680"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C8CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45B35E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAE9D1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8992"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BCC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9E1E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA0A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87B85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA868F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15562"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF79C88B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB0DEBA"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F9F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9099"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,175 +2517,973 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BD6A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE77883"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF81CB92"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C6CA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73342"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED99A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF51B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FBF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73C586"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38AD53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46874"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DD09C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF75C687"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B6BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF2F3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9848D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDEB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8B94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4DB665"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF57BA6D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF86CD96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ABB1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6747F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE9EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBEAD2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8A93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D6D9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED97A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3BAF55"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,205 +3495,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF29A746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0F9F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C0C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8DBDE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBFE5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
+        <fgColor rgb="FFEC939C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -543,811 +3507,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDF5F6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46470"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8892"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF65C07A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE5F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FCF9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF42B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF8F9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7AC88C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2BA847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB9E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5CACE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC8E8CF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF77C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBEE4C6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE9EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77983"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF6F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3B4A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1357,2144 +3565,92 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D2D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFF8F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB22230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD7EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9ED7AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C8CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77680"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAE9D1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45B35E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8992"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BCC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA0A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBFDFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87B85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA868F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D6D9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9E1E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF79C88B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9099"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15562"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9BD6A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81CB92"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C6CA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73342"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF93D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FBF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED99A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF73C586"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF38AD53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CCD0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8DD09C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF75C687"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B6BC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF2F3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9848D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDEB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8B94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF57BA6D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF86CD96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6747F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46874"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8E97"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBEAD2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3BAF55"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4654"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E9D0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8D7DA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9828C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA6AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="577">
+  <borders count="589">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7538,7 +7694,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="577">
+  <cellXfs count="589">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -9266,6 +9422,42 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="576" fillId="577" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="577" fillId="578" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="578" fillId="579" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="579" fillId="580" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="580" fillId="581" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="581" fillId="582" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="582" fillId="583" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="583" fillId="584" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="584" fillId="585" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="585" fillId="586" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="586" fillId="587" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="587" fillId="588" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="588" fillId="589" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9625,41 +9817,41 @@
       <c r="H2">
         <v>1.02</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="4">
         <v>4.95</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>-0.37</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="5">
         <v>1.74</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="9">
         <v>-0.92</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="10">
         <v>-2.39</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="11">
         <v>-1.83</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="2">
         <v>-4.31</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="12">
         <v>-5.87</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="3">
         <v>-4.86</v>
       </c>
-      <